--- a/clang-x64/Scattered unsuccessful looukp.xlsx
+++ b/clang-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.62977</v>
+        <v>3.30615</v>
       </c>
       <c r="C2" t="n">
-        <v>3.56064</v>
+        <v>2.64507</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5766</v>
+        <v>12.2732</v>
       </c>
       <c r="E2" t="n">
-        <v>2.97275</v>
+        <v>2.89601</v>
       </c>
       <c r="F2" t="n">
-        <v>3.19317</v>
+        <v>2.92274</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.75183</v>
+        <v>3.31435</v>
       </c>
       <c r="C3" t="n">
-        <v>3.92058</v>
+        <v>2.77337</v>
       </c>
       <c r="D3" t="n">
-        <v>13.2372</v>
+        <v>12.8195</v>
       </c>
       <c r="E3" t="n">
-        <v>3.04392</v>
+        <v>2.9679</v>
       </c>
       <c r="F3" t="n">
-        <v>3.30641</v>
+        <v>2.99127</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.9827</v>
+        <v>3.56022</v>
       </c>
       <c r="C4" t="n">
-        <v>4.07486</v>
+        <v>2.97895</v>
       </c>
       <c r="D4" t="n">
-        <v>13.6536</v>
+        <v>13.2414</v>
       </c>
       <c r="E4" t="n">
-        <v>3.14589</v>
+        <v>3.10214</v>
       </c>
       <c r="F4" t="n">
-        <v>3.38582</v>
+        <v>3.10959</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>4.52277</v>
+        <v>4.1105</v>
       </c>
       <c r="C5" t="n">
-        <v>4.735</v>
+        <v>3.31579</v>
       </c>
       <c r="D5" t="n">
-        <v>14.273</v>
+        <v>13.9176</v>
       </c>
       <c r="E5" t="n">
-        <v>3.25252</v>
+        <v>3.23425</v>
       </c>
       <c r="F5" t="n">
-        <v>3.56499</v>
+        <v>3.25374</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>5.68875</v>
+        <v>4.95222</v>
       </c>
       <c r="C6" t="n">
-        <v>5.69114</v>
+        <v>4.32329</v>
       </c>
       <c r="D6" t="n">
-        <v>14.6729</v>
+        <v>14.5433</v>
       </c>
       <c r="E6" t="n">
-        <v>3.54451</v>
+        <v>3.51203</v>
       </c>
       <c r="F6" t="n">
-        <v>3.96954</v>
+        <v>3.4686</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>7.93807</v>
+        <v>7.91463</v>
       </c>
       <c r="C7" t="n">
-        <v>8.27023</v>
+        <v>6.37272</v>
       </c>
       <c r="D7" t="n">
-        <v>10.153</v>
+        <v>10.1986</v>
       </c>
       <c r="E7" t="n">
-        <v>4.23301</v>
+        <v>4.2872</v>
       </c>
       <c r="F7" t="n">
-        <v>4.67502</v>
+        <v>4.06394</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>11.7084</v>
+        <v>11.0177</v>
       </c>
       <c r="C8" t="n">
-        <v>11.3719</v>
+        <v>2.24939</v>
       </c>
       <c r="D8" t="n">
-        <v>10.7569</v>
+        <v>10.8922</v>
       </c>
       <c r="E8" t="n">
-        <v>6.15747</v>
+        <v>5.81186</v>
       </c>
       <c r="F8" t="n">
-        <v>6.37709</v>
+        <v>5.75718</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.934</v>
+        <v>16.0382</v>
       </c>
       <c r="C9" t="n">
-        <v>15.7647</v>
+        <v>2.27494</v>
       </c>
       <c r="D9" t="n">
-        <v>11.4101</v>
+        <v>11.5125</v>
       </c>
       <c r="E9" t="n">
-        <v>2.77004</v>
+        <v>2.68941</v>
       </c>
       <c r="F9" t="n">
-        <v>2.90861</v>
+        <v>2.71274</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.27573</v>
+        <v>3.18048</v>
       </c>
       <c r="C10" t="n">
-        <v>3.37309</v>
+        <v>2.29994</v>
       </c>
       <c r="D10" t="n">
-        <v>11.8204</v>
+        <v>12.1228</v>
       </c>
       <c r="E10" t="n">
-        <v>2.796</v>
+        <v>2.70631</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9367</v>
+        <v>2.73718</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.3404</v>
+        <v>3.19763</v>
       </c>
       <c r="C11" t="n">
-        <v>3.48493</v>
+        <v>2.3207</v>
       </c>
       <c r="D11" t="n">
-        <v>12.4018</v>
+        <v>12.7916</v>
       </c>
       <c r="E11" t="n">
-        <v>2.82308</v>
+        <v>2.73523</v>
       </c>
       <c r="F11" t="n">
-        <v>2.96847</v>
+        <v>2.7768</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.38978</v>
+        <v>3.23186</v>
       </c>
       <c r="C12" t="n">
-        <v>3.53389</v>
+        <v>2.39379</v>
       </c>
       <c r="D12" t="n">
-        <v>12.9027</v>
+        <v>13.0802</v>
       </c>
       <c r="E12" t="n">
-        <v>2.87765</v>
+        <v>2.78371</v>
       </c>
       <c r="F12" t="n">
-        <v>3.04049</v>
+        <v>2.82767</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.4621</v>
+        <v>3.28466</v>
       </c>
       <c r="C13" t="n">
-        <v>3.57228</v>
+        <v>2.43593</v>
       </c>
       <c r="D13" t="n">
-        <v>13.4063</v>
+        <v>13.7324</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9152</v>
+        <v>2.81933</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0954</v>
+        <v>2.87795</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.56616</v>
+        <v>3.38712</v>
       </c>
       <c r="C14" t="n">
-        <v>3.66842</v>
+        <v>2.48286</v>
       </c>
       <c r="D14" t="n">
-        <v>13.8581</v>
+        <v>14.1966</v>
       </c>
       <c r="E14" t="n">
-        <v>2.95835</v>
+        <v>2.85302</v>
       </c>
       <c r="F14" t="n">
-        <v>3.14632</v>
+        <v>2.91703</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.67249</v>
+        <v>3.40336</v>
       </c>
       <c r="C15" t="n">
-        <v>3.7831</v>
+        <v>2.56794</v>
       </c>
       <c r="D15" t="n">
-        <v>14.2732</v>
+        <v>14.5991</v>
       </c>
       <c r="E15" t="n">
-        <v>3.03891</v>
+        <v>2.92451</v>
       </c>
       <c r="F15" t="n">
-        <v>3.22713</v>
+        <v>3.00526</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.83508</v>
+        <v>3.56023</v>
       </c>
       <c r="C16" t="n">
-        <v>3.97347</v>
+        <v>2.68196</v>
       </c>
       <c r="D16" t="n">
-        <v>14.6237</v>
+        <v>14.9931</v>
       </c>
       <c r="E16" t="n">
-        <v>3.11998</v>
+        <v>3.00686</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31929</v>
+        <v>3.09922</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.02842</v>
+        <v>3.79176</v>
       </c>
       <c r="C17" t="n">
-        <v>4.2435</v>
+        <v>2.84875</v>
       </c>
       <c r="D17" t="n">
-        <v>15.0762</v>
+        <v>15.4106</v>
       </c>
       <c r="E17" t="n">
-        <v>3.24324</v>
+        <v>3.10956</v>
       </c>
       <c r="F17" t="n">
-        <v>3.46325</v>
+        <v>3.21237</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.35094</v>
+        <v>4.28325</v>
       </c>
       <c r="C18" t="n">
-        <v>4.75641</v>
+        <v>3.1212</v>
       </c>
       <c r="D18" t="n">
-        <v>15.4482</v>
+        <v>15.7689</v>
       </c>
       <c r="E18" t="n">
-        <v>3.35596</v>
+        <v>3.24151</v>
       </c>
       <c r="F18" t="n">
-        <v>3.57993</v>
+        <v>3.3327</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>5.12417</v>
+        <v>4.96659</v>
       </c>
       <c r="C19" t="n">
-        <v>5.25253</v>
+        <v>3.61424</v>
       </c>
       <c r="D19" t="n">
-        <v>15.8403</v>
+        <v>16.2309</v>
       </c>
       <c r="E19" t="n">
-        <v>3.52879</v>
+        <v>3.41126</v>
       </c>
       <c r="F19" t="n">
-        <v>3.80131</v>
+        <v>3.50489</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>6.21287</v>
+        <v>6.19229</v>
       </c>
       <c r="C20" t="n">
-        <v>6.28939</v>
+        <v>4.57457</v>
       </c>
       <c r="D20" t="n">
-        <v>16.2519</v>
+        <v>16.6262</v>
       </c>
       <c r="E20" t="n">
-        <v>3.92726</v>
+        <v>3.881</v>
       </c>
       <c r="F20" t="n">
-        <v>4.22593</v>
+        <v>3.89526</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>8.141170000000001</v>
+        <v>8.12097</v>
       </c>
       <c r="C21" t="n">
-        <v>8.181850000000001</v>
+        <v>6.39711</v>
       </c>
       <c r="D21" t="n">
-        <v>11.634</v>
+        <v>11.9576</v>
       </c>
       <c r="E21" t="n">
-        <v>4.83593</v>
+        <v>4.64217</v>
       </c>
       <c r="F21" t="n">
-        <v>5.09045</v>
+        <v>4.65054</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>10.5265</v>
+        <v>10.8081</v>
       </c>
       <c r="C22" t="n">
-        <v>10.5983</v>
+        <v>2.29669</v>
       </c>
       <c r="D22" t="n">
-        <v>12.18</v>
+        <v>12.4766</v>
       </c>
       <c r="E22" t="n">
-        <v>7.02133</v>
+        <v>6.37668</v>
       </c>
       <c r="F22" t="n">
-        <v>6.95473</v>
+        <v>6.49405</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>14.6937</v>
+        <v>13.9977</v>
       </c>
       <c r="C23" t="n">
-        <v>14.2027</v>
+        <v>2.33585</v>
       </c>
       <c r="D23" t="n">
-        <v>12.6454</v>
+        <v>12.9285</v>
       </c>
       <c r="E23" t="n">
-        <v>2.83619</v>
+        <v>2.70515</v>
       </c>
       <c r="F23" t="n">
-        <v>3.03373</v>
+        <v>2.82189</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>3.40749</v>
+        <v>3.24483</v>
       </c>
       <c r="C24" t="n">
-        <v>3.63527</v>
+        <v>2.36277</v>
       </c>
       <c r="D24" t="n">
-        <v>13.1911</v>
+        <v>13.4518</v>
       </c>
       <c r="E24" t="n">
-        <v>2.86659</v>
+        <v>2.73631</v>
       </c>
       <c r="F24" t="n">
-        <v>3.0804</v>
+        <v>2.87099</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.44783</v>
+        <v>3.28429</v>
       </c>
       <c r="C25" t="n">
-        <v>3.69837</v>
+        <v>2.41377</v>
       </c>
       <c r="D25" t="n">
-        <v>13.6219</v>
+        <v>13.8765</v>
       </c>
       <c r="E25" t="n">
-        <v>2.88935</v>
+        <v>2.76786</v>
       </c>
       <c r="F25" t="n">
-        <v>3.1045</v>
+        <v>2.90236</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.5383</v>
+        <v>3.4198</v>
       </c>
       <c r="C26" t="n">
-        <v>3.7807</v>
+        <v>2.45295</v>
       </c>
       <c r="D26" t="n">
-        <v>14.0445</v>
+        <v>14.2614</v>
       </c>
       <c r="E26" t="n">
-        <v>2.92465</v>
+        <v>2.79944</v>
       </c>
       <c r="F26" t="n">
-        <v>3.16828</v>
+        <v>2.94626</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.59229</v>
+        <v>3.48083</v>
       </c>
       <c r="C27" t="n">
-        <v>3.88506</v>
+        <v>2.50854</v>
       </c>
       <c r="D27" t="n">
-        <v>14.4965</v>
+        <v>14.7345</v>
       </c>
       <c r="E27" t="n">
-        <v>2.96914</v>
+        <v>2.84384</v>
       </c>
       <c r="F27" t="n">
-        <v>3.23001</v>
+        <v>2.99937</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.73479</v>
+        <v>3.52489</v>
       </c>
       <c r="C28" t="n">
-        <v>4.02517</v>
+        <v>2.58165</v>
       </c>
       <c r="D28" t="n">
-        <v>14.9539</v>
+        <v>15.2056</v>
       </c>
       <c r="E28" t="n">
-        <v>3.01557</v>
+        <v>2.9123</v>
       </c>
       <c r="F28" t="n">
-        <v>3.30547</v>
+        <v>3.07173</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.81271</v>
+        <v>3.72683</v>
       </c>
       <c r="C29" t="n">
-        <v>4.14516</v>
+        <v>2.65344</v>
       </c>
       <c r="D29" t="n">
-        <v>15.341</v>
+        <v>15.6752</v>
       </c>
       <c r="E29" t="n">
-        <v>3.11839</v>
+        <v>2.98585</v>
       </c>
       <c r="F29" t="n">
-        <v>3.39382</v>
+        <v>3.16294</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>4.04979</v>
+        <v>3.93138</v>
       </c>
       <c r="C30" t="n">
-        <v>4.3189</v>
+        <v>2.79273</v>
       </c>
       <c r="D30" t="n">
-        <v>15.7651</v>
+        <v>16.0802</v>
       </c>
       <c r="E30" t="n">
-        <v>3.17989</v>
+        <v>3.06921</v>
       </c>
       <c r="F30" t="n">
-        <v>3.47713</v>
+        <v>3.2483</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.36568</v>
+        <v>4.22953</v>
       </c>
       <c r="C31" t="n">
-        <v>4.60123</v>
+        <v>2.9695</v>
       </c>
       <c r="D31" t="n">
-        <v>16.1598</v>
+        <v>16.5052</v>
       </c>
       <c r="E31" t="n">
-        <v>3.29024</v>
+        <v>3.17164</v>
       </c>
       <c r="F31" t="n">
-        <v>3.61595</v>
+        <v>3.36561</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.86249</v>
+        <v>4.78823</v>
       </c>
       <c r="C32" t="n">
-        <v>5.06398</v>
+        <v>3.25871</v>
       </c>
       <c r="D32" t="n">
-        <v>16.4735</v>
+        <v>16.8192</v>
       </c>
       <c r="E32" t="n">
-        <v>3.41889</v>
+        <v>3.30568</v>
       </c>
       <c r="F32" t="n">
-        <v>3.76492</v>
+        <v>3.50306</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>5.47202</v>
+        <v>5.4148</v>
       </c>
       <c r="C33" t="n">
-        <v>5.67189</v>
+        <v>3.69766</v>
       </c>
       <c r="D33" t="n">
-        <v>16.8666</v>
+        <v>17.2413</v>
       </c>
       <c r="E33" t="n">
-        <v>3.63575</v>
+        <v>3.5138</v>
       </c>
       <c r="F33" t="n">
-        <v>3.97432</v>
+        <v>3.72381</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>6.49394</v>
+        <v>6.52118</v>
       </c>
       <c r="C34" t="n">
-        <v>6.64457</v>
+        <v>4.66385</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2887</v>
+        <v>17.6193</v>
       </c>
       <c r="E34" t="n">
-        <v>4.11413</v>
+        <v>3.93496</v>
       </c>
       <c r="F34" t="n">
-        <v>4.36739</v>
+        <v>4.12829</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>8.134219999999999</v>
+        <v>8.07499</v>
       </c>
       <c r="C35" t="n">
-        <v>8.034369999999999</v>
+        <v>6.07224</v>
       </c>
       <c r="D35" t="n">
-        <v>12.044</v>
+        <v>12.3272</v>
       </c>
       <c r="E35" t="n">
-        <v>4.96655</v>
+        <v>4.6856</v>
       </c>
       <c r="F35" t="n">
-        <v>5.13183</v>
+        <v>4.90672</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>10.2033</v>
+        <v>10.479</v>
       </c>
       <c r="C36" t="n">
-        <v>10.2743</v>
+        <v>8.25206</v>
       </c>
       <c r="D36" t="n">
-        <v>12.5476</v>
+        <v>12.8258</v>
       </c>
       <c r="E36" t="n">
-        <v>6.44424</v>
+        <v>5.94432</v>
       </c>
       <c r="F36" t="n">
-        <v>6.44499</v>
+        <v>6.16469</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.6696</v>
+        <v>14.1386</v>
       </c>
       <c r="C37" t="n">
-        <v>13.7027</v>
+        <v>2.32016</v>
       </c>
       <c r="D37" t="n">
-        <v>13.0016</v>
+        <v>13.286</v>
       </c>
       <c r="E37" t="n">
-        <v>2.87348</v>
+        <v>2.74594</v>
       </c>
       <c r="F37" t="n">
-        <v>3.12536</v>
+        <v>2.93276</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>3.49137</v>
+        <v>3.3379</v>
       </c>
       <c r="C38" t="n">
-        <v>3.87064</v>
+        <v>2.39945</v>
       </c>
       <c r="D38" t="n">
-        <v>13.4858</v>
+        <v>13.773</v>
       </c>
       <c r="E38" t="n">
-        <v>2.93889</v>
+        <v>2.78338</v>
       </c>
       <c r="F38" t="n">
-        <v>3.17949</v>
+        <v>2.98831</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.57896</v>
+        <v>3.40406</v>
       </c>
       <c r="C39" t="n">
-        <v>3.94094</v>
+        <v>2.44458</v>
       </c>
       <c r="D39" t="n">
-        <v>13.9738</v>
+        <v>14.2718</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9697</v>
+        <v>2.82095</v>
       </c>
       <c r="F39" t="n">
-        <v>3.2222</v>
+        <v>3.03895</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.60114</v>
+        <v>3.46748</v>
       </c>
       <c r="C40" t="n">
-        <v>4.04966</v>
+        <v>2.45213</v>
       </c>
       <c r="D40" t="n">
-        <v>14.3912</v>
+        <v>14.6849</v>
       </c>
       <c r="E40" t="n">
-        <v>3.00135</v>
+        <v>2.86892</v>
       </c>
       <c r="F40" t="n">
-        <v>3.28101</v>
+        <v>3.10597</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.6885</v>
+        <v>3.54671</v>
       </c>
       <c r="C41" t="n">
-        <v>4.12872</v>
+        <v>2.50928</v>
       </c>
       <c r="D41" t="n">
-        <v>14.836</v>
+        <v>15.1368</v>
       </c>
       <c r="E41" t="n">
-        <v>3.04952</v>
+        <v>2.91149</v>
       </c>
       <c r="F41" t="n">
-        <v>3.34644</v>
+        <v>3.16187</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.82564</v>
+        <v>3.65192</v>
       </c>
       <c r="C42" t="n">
-        <v>4.25521</v>
+        <v>2.57848</v>
       </c>
       <c r="D42" t="n">
-        <v>15.257</v>
+        <v>15.5466</v>
       </c>
       <c r="E42" t="n">
-        <v>3.08675</v>
+        <v>2.95969</v>
       </c>
       <c r="F42" t="n">
-        <v>3.41689</v>
+        <v>3.23451</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.95681</v>
+        <v>3.77869</v>
       </c>
       <c r="C43" t="n">
-        <v>4.37797</v>
+        <v>2.68625</v>
       </c>
       <c r="D43" t="n">
-        <v>15.7081</v>
+        <v>15.9883</v>
       </c>
       <c r="E43" t="n">
-        <v>3.15095</v>
+        <v>3.03943</v>
       </c>
       <c r="F43" t="n">
-        <v>3.52099</v>
+        <v>3.32225</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.19554</v>
+        <v>4.04565</v>
       </c>
       <c r="C44" t="n">
-        <v>4.58277</v>
+        <v>2.84144</v>
       </c>
       <c r="D44" t="n">
-        <v>16.0513</v>
+        <v>16.3755</v>
       </c>
       <c r="E44" t="n">
-        <v>3.24461</v>
+        <v>3.12779</v>
       </c>
       <c r="F44" t="n">
-        <v>3.64009</v>
+        <v>3.4452</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.47916</v>
+        <v>4.37246</v>
       </c>
       <c r="C45" t="n">
-        <v>4.82009</v>
+        <v>3.0674</v>
       </c>
       <c r="D45" t="n">
-        <v>16.4673</v>
+        <v>16.7925</v>
       </c>
       <c r="E45" t="n">
-        <v>3.36926</v>
+        <v>3.23454</v>
       </c>
       <c r="F45" t="n">
-        <v>3.75725</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.87985</v>
+        <v>4.79569</v>
       </c>
       <c r="C46" t="n">
-        <v>5.17527</v>
+        <v>3.35424</v>
       </c>
       <c r="D46" t="n">
-        <v>16.8065</v>
+        <v>17.187</v>
       </c>
       <c r="E46" t="n">
-        <v>3.55692</v>
+        <v>3.41974</v>
       </c>
       <c r="F46" t="n">
-        <v>3.94618</v>
+        <v>3.75201</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>5.45284</v>
+        <v>5.41824</v>
       </c>
       <c r="C47" t="n">
-        <v>5.71734</v>
+        <v>3.81957</v>
       </c>
       <c r="D47" t="n">
-        <v>17.1968</v>
+        <v>17.6253</v>
       </c>
       <c r="E47" t="n">
-        <v>3.81807</v>
+        <v>3.62785</v>
       </c>
       <c r="F47" t="n">
-        <v>4.16342</v>
+        <v>3.96159</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>6.27785</v>
+        <v>6.26173</v>
       </c>
       <c r="C48" t="n">
-        <v>6.53921</v>
+        <v>4.61172</v>
       </c>
       <c r="D48" t="n">
-        <v>17.6341</v>
+        <v>18.0473</v>
       </c>
       <c r="E48" t="n">
-        <v>4.28533</v>
+        <v>4.05394</v>
       </c>
       <c r="F48" t="n">
-        <v>4.57613</v>
+        <v>4.39541</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>7.55323</v>
+        <v>7.54302</v>
       </c>
       <c r="C49" t="n">
-        <v>7.74511</v>
+        <v>5.66247</v>
       </c>
       <c r="D49" t="n">
-        <v>18.0765</v>
+        <v>18.5002</v>
       </c>
       <c r="E49" t="n">
-        <v>4.96127</v>
+        <v>4.64947</v>
       </c>
       <c r="F49" t="n">
-        <v>5.19841</v>
+        <v>4.97722</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>9.60445</v>
+        <v>9.59332</v>
       </c>
       <c r="C50" t="n">
-        <v>9.645149999999999</v>
+        <v>7.30269</v>
       </c>
       <c r="D50" t="n">
-        <v>12.6693</v>
+        <v>12.9445</v>
       </c>
       <c r="E50" t="n">
-        <v>6.05718</v>
+        <v>5.63443</v>
       </c>
       <c r="F50" t="n">
-        <v>6.13443</v>
+        <v>5.92982</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>12.6274</v>
+        <v>12.5948</v>
       </c>
       <c r="C51" t="n">
-        <v>12.6609</v>
+        <v>2.53082</v>
       </c>
       <c r="D51" t="n">
-        <v>13.1295</v>
+        <v>13.4145</v>
       </c>
       <c r="E51" t="n">
-        <v>3.22939</v>
+        <v>3.00961</v>
       </c>
       <c r="F51" t="n">
-        <v>3.63069</v>
+        <v>3.44125</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>17.2046</v>
+        <v>17.3047</v>
       </c>
       <c r="C52" t="n">
-        <v>17.3007</v>
+        <v>2.54965</v>
       </c>
       <c r="D52" t="n">
-        <v>13.6212</v>
+        <v>13.8933</v>
       </c>
       <c r="E52" t="n">
-        <v>3.26195</v>
+        <v>3.04562</v>
       </c>
       <c r="F52" t="n">
-        <v>3.59241</v>
+        <v>3.49409</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.72118</v>
+        <v>3.65201</v>
       </c>
       <c r="C53" t="n">
-        <v>4.25294</v>
+        <v>2.59233</v>
       </c>
       <c r="D53" t="n">
-        <v>14.081</v>
+        <v>14.3594</v>
       </c>
       <c r="E53" t="n">
-        <v>3.14547</v>
+        <v>3.48376</v>
       </c>
       <c r="F53" t="n">
-        <v>3.64835</v>
+        <v>3.75779</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.76223</v>
+        <v>3.67921</v>
       </c>
       <c r="C54" t="n">
-        <v>4.35353</v>
+        <v>2.97435</v>
       </c>
       <c r="D54" t="n">
-        <v>14.5689</v>
+        <v>14.8387</v>
       </c>
       <c r="E54" t="n">
-        <v>3.29271</v>
+        <v>3.11702</v>
       </c>
       <c r="F54" t="n">
-        <v>3.73373</v>
+        <v>3.60568</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.87928</v>
+        <v>3.80481</v>
       </c>
       <c r="C55" t="n">
-        <v>4.44882</v>
+        <v>2.69521</v>
       </c>
       <c r="D55" t="n">
-        <v>15.0418</v>
+        <v>15.2966</v>
       </c>
       <c r="E55" t="n">
-        <v>3.33217</v>
+        <v>3.17094</v>
       </c>
       <c r="F55" t="n">
-        <v>3.78042</v>
+        <v>3.66081</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.98941</v>
+        <v>3.91605</v>
       </c>
       <c r="C56" t="n">
-        <v>4.55193</v>
+        <v>2.7673</v>
       </c>
       <c r="D56" t="n">
-        <v>15.5132</v>
+        <v>15.7728</v>
       </c>
       <c r="E56" t="n">
-        <v>3.43248</v>
+        <v>3.32201</v>
       </c>
       <c r="F56" t="n">
-        <v>3.86615</v>
+        <v>3.7475</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>4.12156</v>
+        <v>4.07272</v>
       </c>
       <c r="C57" t="n">
-        <v>4.68048</v>
+        <v>2.85611</v>
       </c>
       <c r="D57" t="n">
-        <v>15.9899</v>
+        <v>16.2118</v>
       </c>
       <c r="E57" t="n">
-        <v>3.41394</v>
+        <v>3.2832</v>
       </c>
       <c r="F57" t="n">
-        <v>3.90464</v>
+        <v>3.82069</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>4.33388</v>
+        <v>4.31197</v>
       </c>
       <c r="C58" t="n">
-        <v>4.84865</v>
+        <v>2.9714</v>
       </c>
       <c r="D58" t="n">
-        <v>16.4422</v>
+        <v>16.6172</v>
       </c>
       <c r="E58" t="n">
-        <v>3.4268</v>
+        <v>3.33377</v>
       </c>
       <c r="F58" t="n">
-        <v>3.96915</v>
+        <v>3.78742</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>4.57155</v>
+        <v>4.5085</v>
       </c>
       <c r="C59" t="n">
-        <v>5.07436</v>
+        <v>3.19019</v>
       </c>
       <c r="D59" t="n">
-        <v>16.8993</v>
+        <v>17.0722</v>
       </c>
       <c r="E59" t="n">
-        <v>3.56965</v>
+        <v>3.50956</v>
       </c>
       <c r="F59" t="n">
-        <v>4.16444</v>
+        <v>3.90314</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.06626</v>
+        <v>4.83617</v>
       </c>
       <c r="C60" t="n">
-        <v>5.40058</v>
+        <v>3.5226</v>
       </c>
       <c r="D60" t="n">
-        <v>17.333</v>
+        <v>17.5687</v>
       </c>
       <c r="E60" t="n">
-        <v>3.78415</v>
+        <v>3.67421</v>
       </c>
       <c r="F60" t="n">
-        <v>4.29177</v>
+        <v>4.05789</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.55617</v>
+        <v>5.41642</v>
       </c>
       <c r="C61" t="n">
-        <v>6.04158</v>
+        <v>3.99345</v>
       </c>
       <c r="D61" t="n">
-        <v>17.8268</v>
+        <v>18.0997</v>
       </c>
       <c r="E61" t="n">
-        <v>4.15512</v>
+        <v>3.90095</v>
       </c>
       <c r="F61" t="n">
-        <v>4.52857</v>
+        <v>4.25643</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>6.23081</v>
+        <v>6.31598</v>
       </c>
       <c r="C62" t="n">
-        <v>6.68078</v>
+        <v>4.58039</v>
       </c>
       <c r="D62" t="n">
-        <v>18.2822</v>
+        <v>18.566</v>
       </c>
       <c r="E62" t="n">
-        <v>4.56212</v>
+        <v>4.25455</v>
       </c>
       <c r="F62" t="n">
-        <v>4.88957</v>
+        <v>4.65844</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>7.55306</v>
+        <v>7.50132</v>
       </c>
       <c r="C63" t="n">
-        <v>7.89579</v>
+        <v>5.5544</v>
       </c>
       <c r="D63" t="n">
-        <v>18.9849</v>
+        <v>19.1794</v>
       </c>
       <c r="E63" t="n">
-        <v>5.16185</v>
+        <v>4.80963</v>
       </c>
       <c r="F63" t="n">
-        <v>5.4804</v>
+        <v>5.17608</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>9.36735</v>
+        <v>9.117100000000001</v>
       </c>
       <c r="C64" t="n">
-        <v>9.625080000000001</v>
+        <v>7.10649</v>
       </c>
       <c r="D64" t="n">
-        <v>14.4846</v>
+        <v>14.5699</v>
       </c>
       <c r="E64" t="n">
-        <v>6.02799</v>
+        <v>5.65553</v>
       </c>
       <c r="F64" t="n">
-        <v>6.36322</v>
+        <v>6.01434</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>12.242</v>
+        <v>12.3051</v>
       </c>
       <c r="C65" t="n">
-        <v>12.4444</v>
+        <v>3.01771</v>
       </c>
       <c r="D65" t="n">
-        <v>15.2509</v>
+        <v>15.5066</v>
       </c>
       <c r="E65" t="n">
-        <v>7.76864</v>
+        <v>7.2957</v>
       </c>
       <c r="F65" t="n">
-        <v>7.97692</v>
+        <v>7.53692</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.8836</v>
+        <v>16.567</v>
       </c>
       <c r="C66" t="n">
-        <v>16.8858</v>
+        <v>2.93017</v>
       </c>
       <c r="D66" t="n">
-        <v>16.1358</v>
+        <v>16.4266</v>
       </c>
       <c r="E66" t="n">
-        <v>3.66272</v>
+        <v>3.79968</v>
       </c>
       <c r="F66" t="n">
-        <v>4.23174</v>
+        <v>3.99639</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>4.19521</v>
+        <v>4.12372</v>
       </c>
       <c r="C67" t="n">
-        <v>5.04051</v>
+        <v>2.95618</v>
       </c>
       <c r="D67" t="n">
-        <v>17.1319</v>
+        <v>17.0362</v>
       </c>
       <c r="E67" t="n">
-        <v>3.69283</v>
+        <v>3.52687</v>
       </c>
       <c r="F67" t="n">
-        <v>4.29712</v>
+        <v>4.04855</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>4.29291</v>
+        <v>4.24614</v>
       </c>
       <c r="C68" t="n">
-        <v>5.19584</v>
+        <v>3.00026</v>
       </c>
       <c r="D68" t="n">
-        <v>17.9321</v>
+        <v>18.083</v>
       </c>
       <c r="E68" t="n">
-        <v>3.73728</v>
+        <v>3.75043</v>
       </c>
       <c r="F68" t="n">
-        <v>4.36781</v>
+        <v>4.11398</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>4.37539</v>
+        <v>4.32367</v>
       </c>
       <c r="C69" t="n">
-        <v>5.27048</v>
+        <v>3.05568</v>
       </c>
       <c r="D69" t="n">
-        <v>18.8569</v>
+        <v>18.899</v>
       </c>
       <c r="E69" t="n">
-        <v>3.78789</v>
+        <v>3.81592</v>
       </c>
       <c r="F69" t="n">
-        <v>4.43534</v>
+        <v>4.18633</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>4.46848</v>
+        <v>4.44491</v>
       </c>
       <c r="C70" t="n">
-        <v>5.42179</v>
+        <v>3.14177</v>
       </c>
       <c r="D70" t="n">
-        <v>20.0657</v>
+        <v>19.8181</v>
       </c>
       <c r="E70" t="n">
-        <v>3.78169</v>
+        <v>3.93915</v>
       </c>
       <c r="F70" t="n">
-        <v>4.52139</v>
+        <v>4.26809</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>4.57266</v>
+        <v>4.54453</v>
       </c>
       <c r="C71" t="n">
-        <v>5.6124</v>
+        <v>3.20981</v>
       </c>
       <c r="D71" t="n">
-        <v>21.0428</v>
+        <v>20.7309</v>
       </c>
       <c r="E71" t="n">
-        <v>3.87791</v>
+        <v>3.77217</v>
       </c>
       <c r="F71" t="n">
-        <v>4.54688</v>
+        <v>4.39634</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.75692</v>
+        <v>4.7493</v>
       </c>
       <c r="C72" t="n">
-        <v>5.86594</v>
+        <v>3.35832</v>
       </c>
       <c r="D72" t="n">
-        <v>22.4031</v>
+        <v>21.7495</v>
       </c>
       <c r="E72" t="n">
-        <v>3.96791</v>
+        <v>3.8497</v>
       </c>
       <c r="F72" t="n">
-        <v>4.65871</v>
+        <v>4.53692</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>5.01414</v>
+        <v>4.97029</v>
       </c>
       <c r="C73" t="n">
-        <v>6.20941</v>
+        <v>3.5374</v>
       </c>
       <c r="D73" t="n">
-        <v>23.6359</v>
+        <v>23.1133</v>
       </c>
       <c r="E73" t="n">
-        <v>4.05936</v>
+        <v>3.95155</v>
       </c>
       <c r="F73" t="n">
-        <v>4.85591</v>
+        <v>4.6724</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>5.38436</v>
+        <v>5.23887</v>
       </c>
       <c r="C74" t="n">
-        <v>6.58343</v>
+        <v>3.77785</v>
       </c>
       <c r="D74" t="n">
-        <v>24.9498</v>
+        <v>24.4486</v>
       </c>
       <c r="E74" t="n">
-        <v>4.23903</v>
+        <v>4.07817</v>
       </c>
       <c r="F74" t="n">
-        <v>5.01466</v>
+        <v>4.94435</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.87889</v>
+        <v>5.75384</v>
       </c>
       <c r="C75" t="n">
-        <v>7.23003</v>
+        <v>4.18755</v>
       </c>
       <c r="D75" t="n">
-        <v>26.1883</v>
+        <v>25.6658</v>
       </c>
       <c r="E75" t="n">
-        <v>4.46959</v>
+        <v>4.25482</v>
       </c>
       <c r="F75" t="n">
-        <v>5.21455</v>
+        <v>5.08022</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>6.5995</v>
+        <v>6.45043</v>
       </c>
       <c r="C76" t="n">
-        <v>8.21312</v>
+        <v>4.80953</v>
       </c>
       <c r="D76" t="n">
-        <v>27.6544</v>
+        <v>27.0159</v>
       </c>
       <c r="E76" t="n">
-        <v>4.8016</v>
+        <v>4.59836</v>
       </c>
       <c r="F76" t="n">
-        <v>5.66423</v>
+        <v>5.45906</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>7.77343</v>
+        <v>7.6175</v>
       </c>
       <c r="C77" t="n">
-        <v>9.733169999999999</v>
+        <v>5.81041</v>
       </c>
       <c r="D77" t="n">
-        <v>28.9414</v>
+        <v>28.5304</v>
       </c>
       <c r="E77" t="n">
-        <v>5.34096</v>
+        <v>5.09313</v>
       </c>
       <c r="F77" t="n">
-        <v>6.23491</v>
+        <v>6.00105</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>9.32494</v>
+        <v>9.34727</v>
       </c>
       <c r="C78" t="n">
-        <v>11.6752</v>
+        <v>7.25187</v>
       </c>
       <c r="D78" t="n">
-        <v>24.4801</v>
+        <v>24.692</v>
       </c>
       <c r="E78" t="n">
-        <v>6.21311</v>
+        <v>5.87453</v>
       </c>
       <c r="F78" t="n">
-        <v>7.18299</v>
+        <v>6.83611</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>12.0922</v>
+        <v>12.0056</v>
       </c>
       <c r="C79" t="n">
-        <v>15.075</v>
+        <v>3.239</v>
       </c>
       <c r="D79" t="n">
-        <v>25.6188</v>
+        <v>25.8701</v>
       </c>
       <c r="E79" t="n">
-        <v>7.73309</v>
+        <v>7.29337</v>
       </c>
       <c r="F79" t="n">
-        <v>8.76534</v>
+        <v>8.55064</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.2706</v>
+        <v>16.2278</v>
       </c>
       <c r="C80" t="n">
-        <v>19.9269</v>
+        <v>3.26412</v>
       </c>
       <c r="D80" t="n">
-        <v>26.9074</v>
+        <v>27.1873</v>
       </c>
       <c r="E80" t="n">
-        <v>4.01353</v>
+        <v>3.93348</v>
       </c>
       <c r="F80" t="n">
-        <v>4.72856</v>
+        <v>4.56533</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.9312</v>
+        <v>4.72449</v>
       </c>
       <c r="C81" t="n">
-        <v>6.78614</v>
+        <v>3.31744</v>
       </c>
       <c r="D81" t="n">
-        <v>28.2648</v>
+        <v>28.573</v>
       </c>
       <c r="E81" t="n">
-        <v>4.19792</v>
+        <v>3.97569</v>
       </c>
       <c r="F81" t="n">
-        <v>4.98401</v>
+        <v>4.71329</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>5.05853</v>
+        <v>4.84518</v>
       </c>
       <c r="C82" t="n">
-        <v>7.21024</v>
+        <v>3.37496</v>
       </c>
       <c r="D82" t="n">
-        <v>29.6341</v>
+        <v>29.9883</v>
       </c>
       <c r="E82" t="n">
-        <v>4.25455</v>
+        <v>4.02127</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1465</v>
+        <v>4.85337</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>5.26874</v>
+        <v>5.0471</v>
       </c>
       <c r="C83" t="n">
-        <v>7.72844</v>
+        <v>3.4781</v>
       </c>
       <c r="D83" t="n">
-        <v>31.0485</v>
+        <v>31.4688</v>
       </c>
       <c r="E83" t="n">
-        <v>4.33785</v>
+        <v>4.09577</v>
       </c>
       <c r="F83" t="n">
-        <v>5.35678</v>
+        <v>5.06585</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>5.5362</v>
+        <v>5.18275</v>
       </c>
       <c r="C84" t="n">
-        <v>8.27449</v>
+        <v>3.56375</v>
       </c>
       <c r="D84" t="n">
-        <v>32.5091</v>
+        <v>33.0376</v>
       </c>
       <c r="E84" t="n">
-        <v>4.43623</v>
+        <v>4.15723</v>
       </c>
       <c r="F84" t="n">
-        <v>5.57128</v>
+        <v>5.26039</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>5.87419</v>
+        <v>5.42388</v>
       </c>
       <c r="C85" t="n">
-        <v>8.95147</v>
+        <v>3.69352</v>
       </c>
       <c r="D85" t="n">
-        <v>34.0632</v>
+        <v>34.6611</v>
       </c>
       <c r="E85" t="n">
-        <v>4.60649</v>
+        <v>4.27952</v>
       </c>
       <c r="F85" t="n">
-        <v>5.91585</v>
+        <v>5.33161</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>6.203</v>
+        <v>5.63917</v>
       </c>
       <c r="C86" t="n">
-        <v>9.58498</v>
+        <v>3.85364</v>
       </c>
       <c r="D86" t="n">
-        <v>35.6158</v>
+        <v>36.3143</v>
       </c>
       <c r="E86" t="n">
-        <v>4.80443</v>
+        <v>4.41418</v>
       </c>
       <c r="F86" t="n">
-        <v>6.33213</v>
+        <v>5.60944</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>6.62956</v>
+        <v>6.01708</v>
       </c>
       <c r="C87" t="n">
-        <v>10.4336</v>
+        <v>4.11805</v>
       </c>
       <c r="D87" t="n">
-        <v>37.374</v>
+        <v>38.0231</v>
       </c>
       <c r="E87" t="n">
-        <v>4.97177</v>
+        <v>4.68698</v>
       </c>
       <c r="F87" t="n">
-        <v>6.74292</v>
+        <v>6.03688</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>7.11154</v>
+        <v>6.6066</v>
       </c>
       <c r="C88" t="n">
-        <v>11.3938</v>
+        <v>4.50748</v>
       </c>
       <c r="D88" t="n">
-        <v>39.0978</v>
+        <v>39.8347</v>
       </c>
       <c r="E88" t="n">
-        <v>5.19047</v>
+        <v>5.05374</v>
       </c>
       <c r="F88" t="n">
-        <v>7.242</v>
+        <v>6.92805</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>7.89965</v>
+        <v>7.28053</v>
       </c>
       <c r="C89" t="n">
-        <v>12.4547</v>
+        <v>5.00939</v>
       </c>
       <c r="D89" t="n">
-        <v>40.8592</v>
+        <v>41.6853</v>
       </c>
       <c r="E89" t="n">
-        <v>5.5976</v>
+        <v>5.36054</v>
       </c>
       <c r="F89" t="n">
-        <v>7.85837</v>
+        <v>7.36528</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>8.5753</v>
+        <v>8.224019999999999</v>
       </c>
       <c r="C90" t="n">
-        <v>13.6141</v>
+        <v>5.69402</v>
       </c>
       <c r="D90" t="n">
-        <v>42.8219</v>
+        <v>43.6287</v>
       </c>
       <c r="E90" t="n">
-        <v>6.13568</v>
+        <v>5.79234</v>
       </c>
       <c r="F90" t="n">
-        <v>8.59117</v>
+        <v>8.17163</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>10.1523</v>
+        <v>10.1708</v>
       </c>
       <c r="C91" t="n">
-        <v>15.3639</v>
+        <v>6.96404</v>
       </c>
       <c r="D91" t="n">
-        <v>44.7927</v>
+        <v>45.6281</v>
       </c>
       <c r="E91" t="n">
-        <v>6.77529</v>
+        <v>6.37751</v>
       </c>
       <c r="F91" t="n">
-        <v>9.641389999999999</v>
+        <v>8.873749999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>11.8791</v>
+        <v>11.8648</v>
       </c>
       <c r="C92" t="n">
-        <v>17.7364</v>
+        <v>8.45247</v>
       </c>
       <c r="D92" t="n">
-        <v>36.6577</v>
+        <v>37.6203</v>
       </c>
       <c r="E92" t="n">
-        <v>7.78397</v>
+        <v>7.68966</v>
       </c>
       <c r="F92" t="n">
-        <v>11.0085</v>
+        <v>10.3344</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>14.5513</v>
+        <v>14.4147</v>
       </c>
       <c r="C93" t="n">
-        <v>21.1207</v>
+        <v>10.8438</v>
       </c>
       <c r="D93" t="n">
-        <v>37.891</v>
+        <v>38.8431</v>
       </c>
       <c r="E93" t="n">
-        <v>9.41502</v>
+        <v>8.63434</v>
       </c>
       <c r="F93" t="n">
-        <v>12.6525</v>
+        <v>12.2832</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>18.2205</v>
+        <v>18.0903</v>
       </c>
       <c r="C94" t="n">
-        <v>25.7609</v>
+        <v>4.19385</v>
       </c>
       <c r="D94" t="n">
-        <v>39.0993</v>
+        <v>40.0576</v>
       </c>
       <c r="E94" t="n">
-        <v>5.25537</v>
+        <v>4.91662</v>
       </c>
       <c r="F94" t="n">
-        <v>7.09076</v>
+        <v>6.52398</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>6.968</v>
+        <v>6.63121</v>
       </c>
       <c r="C95" t="n">
-        <v>10.898</v>
+        <v>4.28923</v>
       </c>
       <c r="D95" t="n">
-        <v>40.4284</v>
+        <v>41.3057</v>
       </c>
       <c r="E95" t="n">
-        <v>5.41642</v>
+        <v>5.01263</v>
       </c>
       <c r="F95" t="n">
-        <v>7.36236</v>
+        <v>6.77707</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>7.30584</v>
+        <v>6.87957</v>
       </c>
       <c r="C96" t="n">
-        <v>11.4352</v>
+        <v>4.45789</v>
       </c>
       <c r="D96" t="n">
-        <v>41.7539</v>
+        <v>42.703</v>
       </c>
       <c r="E96" t="n">
-        <v>5.60568</v>
+        <v>5.17636</v>
       </c>
       <c r="F96" t="n">
-        <v>7.71286</v>
+        <v>7.11374</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>7.59591</v>
+        <v>7.20657</v>
       </c>
       <c r="C97" t="n">
-        <v>11.978</v>
+        <v>4.58649</v>
       </c>
       <c r="D97" t="n">
-        <v>43.1502</v>
+        <v>44.0962</v>
       </c>
       <c r="E97" t="n">
-        <v>5.82578</v>
+        <v>5.25702</v>
       </c>
       <c r="F97" t="n">
-        <v>8.06786</v>
+        <v>7.59789</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>7.95264</v>
+        <v>7.68244</v>
       </c>
       <c r="C98" t="n">
-        <v>12.6348</v>
+        <v>4.86154</v>
       </c>
       <c r="D98" t="n">
-        <v>44.5353</v>
+        <v>45.4915</v>
       </c>
       <c r="E98" t="n">
-        <v>6.00412</v>
+        <v>5.55423</v>
       </c>
       <c r="F98" t="n">
-        <v>8.42792</v>
+        <v>8.11763</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>8.338900000000001</v>
+        <v>8.100350000000001</v>
       </c>
       <c r="C99" t="n">
-        <v>13.4257</v>
+        <v>5.13596</v>
       </c>
       <c r="D99" t="n">
-        <v>46.0501</v>
+        <v>46.9802</v>
       </c>
       <c r="E99" t="n">
-        <v>6.22898</v>
+        <v>5.81483</v>
       </c>
       <c r="F99" t="n">
-        <v>8.83141</v>
+        <v>8.82734</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>8.70459</v>
+        <v>8.66713</v>
       </c>
       <c r="C100" t="n">
-        <v>14.2826</v>
+        <v>5.46533</v>
       </c>
       <c r="D100" t="n">
-        <v>47.6578</v>
+        <v>48.5396</v>
       </c>
       <c r="E100" t="n">
-        <v>6.38594</v>
+        <v>6.13525</v>
       </c>
       <c r="F100" t="n">
-        <v>9.178699999999999</v>
+        <v>9.515040000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>9.14359</v>
+        <v>9.394640000000001</v>
       </c>
       <c r="C101" t="n">
-        <v>15.3433</v>
+        <v>5.90992</v>
       </c>
       <c r="D101" t="n">
-        <v>49.2856</v>
+        <v>50.1998</v>
       </c>
       <c r="E101" t="n">
-        <v>6.65436</v>
+        <v>6.56088</v>
       </c>
       <c r="F101" t="n">
-        <v>9.52947</v>
+        <v>10.4105</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>9.64321</v>
+        <v>10.2101</v>
       </c>
       <c r="C102" t="n">
-        <v>16.4625</v>
+        <v>6.40857</v>
       </c>
       <c r="D102" t="n">
-        <v>51.0419</v>
+        <v>51.9505</v>
       </c>
       <c r="E102" t="n">
-        <v>6.95324</v>
+        <v>7.038</v>
       </c>
       <c r="F102" t="n">
-        <v>10.0765</v>
+        <v>11.2767</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>10.3756</v>
+        <v>11.1452</v>
       </c>
       <c r="C103" t="n">
-        <v>17.7696</v>
+        <v>7.04608</v>
       </c>
       <c r="D103" t="n">
-        <v>52.906</v>
+        <v>53.7345</v>
       </c>
       <c r="E103" t="n">
-        <v>7.33294</v>
+        <v>7.59495</v>
       </c>
       <c r="F103" t="n">
-        <v>10.697</v>
+        <v>12.1088</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>11.2759</v>
+        <v>12.1351</v>
       </c>
       <c r="C104" t="n">
-        <v>19.3084</v>
+        <v>7.87788</v>
       </c>
       <c r="D104" t="n">
-        <v>54.7203</v>
+        <v>55.5544</v>
       </c>
       <c r="E104" t="n">
-        <v>7.6099</v>
+        <v>8.27211</v>
       </c>
       <c r="F104" t="n">
-        <v>11.5282</v>
+        <v>12.9989</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>12.5096</v>
+        <v>13.388</v>
       </c>
       <c r="C105" t="n">
-        <v>21.1278</v>
+        <v>8.94145</v>
       </c>
       <c r="D105" t="n">
-        <v>56.6124</v>
+        <v>57.8087</v>
       </c>
       <c r="E105" t="n">
-        <v>8.381629999999999</v>
+        <v>8.994350000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>12.5806</v>
+        <v>13.9969</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>14.2323</v>
+        <v>14.9528</v>
       </c>
       <c r="C106" t="n">
-        <v>23.3886</v>
+        <v>10.3265</v>
       </c>
       <c r="D106" t="n">
-        <v>58.6572</v>
+        <v>59.6674</v>
       </c>
       <c r="E106" t="n">
-        <v>9.293419999999999</v>
+        <v>9.95993</v>
       </c>
       <c r="F106" t="n">
-        <v>14.101</v>
+        <v>15.2824</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>16.678</v>
+        <v>17.1697</v>
       </c>
       <c r="C107" t="n">
-        <v>26.3176</v>
+        <v>12.3306</v>
       </c>
       <c r="D107" t="n">
-        <v>44.6185</v>
+        <v>45.9723</v>
       </c>
       <c r="E107" t="n">
-        <v>10.7608</v>
+        <v>11.2868</v>
       </c>
       <c r="F107" t="n">
-        <v>16.2438</v>
+        <v>16.915</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>20.0694</v>
+        <v>20.3196</v>
       </c>
       <c r="C108" t="n">
-        <v>30.7816</v>
+        <v>5.82494</v>
       </c>
       <c r="D108" t="n">
-        <v>45.7746</v>
+        <v>47.1544</v>
       </c>
       <c r="E108" t="n">
-        <v>5.9795</v>
+        <v>6.70664</v>
       </c>
       <c r="F108" t="n">
-        <v>8.76972</v>
+        <v>10.1074</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>24.9795</v>
+        <v>25.056</v>
       </c>
       <c r="C109" t="n">
-        <v>37.6642</v>
+        <v>6.03411</v>
       </c>
       <c r="D109" t="n">
-        <v>46.9261</v>
+        <v>48.3089</v>
       </c>
       <c r="E109" t="n">
-        <v>6.22805</v>
+        <v>6.8921</v>
       </c>
       <c r="F109" t="n">
-        <v>9.157489999999999</v>
+        <v>10.4604</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>8.525169999999999</v>
+        <v>9.864800000000001</v>
       </c>
       <c r="C110" t="n">
-        <v>15.3253</v>
+        <v>6.19472</v>
       </c>
       <c r="D110" t="n">
-        <v>48.1842</v>
+        <v>49.599</v>
       </c>
       <c r="E110" t="n">
-        <v>6.38062</v>
+        <v>7.15058</v>
       </c>
       <c r="F110" t="n">
-        <v>9.349460000000001</v>
+        <v>10.809</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>8.889139999999999</v>
+        <v>10.017</v>
       </c>
       <c r="C111" t="n">
-        <v>15.9595</v>
+        <v>6.39381</v>
       </c>
       <c r="D111" t="n">
-        <v>49.4376</v>
+        <v>50.8196</v>
       </c>
       <c r="E111" t="n">
-        <v>6.52919</v>
+        <v>7.33792</v>
       </c>
       <c r="F111" t="n">
-        <v>9.990069999999999</v>
+        <v>11.1285</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>9.190110000000001</v>
+        <v>10.4579</v>
       </c>
       <c r="C112" t="n">
-        <v>16.5549</v>
+        <v>6.57875</v>
       </c>
       <c r="D112" t="n">
-        <v>50.8502</v>
+        <v>52.1989</v>
       </c>
       <c r="E112" t="n">
-        <v>6.71736</v>
+        <v>7.5603</v>
       </c>
       <c r="F112" t="n">
-        <v>10.5039</v>
+        <v>11.4858</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>9.61955</v>
+        <v>10.7882</v>
       </c>
       <c r="C113" t="n">
-        <v>17.1823</v>
+        <v>6.80331</v>
       </c>
       <c r="D113" t="n">
-        <v>52.2136</v>
+        <v>53.657</v>
       </c>
       <c r="E113" t="n">
-        <v>6.92466</v>
+        <v>7.7424</v>
       </c>
       <c r="F113" t="n">
-        <v>11.1286</v>
+        <v>11.8582</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>10.2455</v>
+        <v>11.0542</v>
       </c>
       <c r="C114" t="n">
-        <v>17.8761</v>
+        <v>7.0677</v>
       </c>
       <c r="D114" t="n">
-        <v>53.7522</v>
+        <v>55.0889</v>
       </c>
       <c r="E114" t="n">
-        <v>7.28251</v>
+        <v>8.044840000000001</v>
       </c>
       <c r="F114" t="n">
-        <v>11.7441</v>
+        <v>12.3059</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>10.7422</v>
+        <v>11.5427</v>
       </c>
       <c r="C115" t="n">
-        <v>18.6247</v>
+        <v>7.37329</v>
       </c>
       <c r="D115" t="n">
-        <v>54.9627</v>
+        <v>56.6586</v>
       </c>
       <c r="E115" t="n">
-        <v>7.61094</v>
+        <v>8.28562</v>
       </c>
       <c r="F115" t="n">
-        <v>12.3869</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>11.3857</v>
+        <v>12.036</v>
       </c>
       <c r="C116" t="n">
-        <v>19.4345</v>
+        <v>7.7604</v>
       </c>
       <c r="D116" t="n">
-        <v>56.6116</v>
+        <v>58.3947</v>
       </c>
       <c r="E116" t="n">
-        <v>7.98617</v>
+        <v>8.56221</v>
       </c>
       <c r="F116" t="n">
-        <v>13.0114</v>
+        <v>13.1739</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>12.2803</v>
+        <v>12.6799</v>
       </c>
       <c r="C117" t="n">
-        <v>20.4329</v>
+        <v>8.23203</v>
       </c>
       <c r="D117" t="n">
-        <v>58.8678</v>
+        <v>60.1785</v>
       </c>
       <c r="E117" t="n">
-        <v>8.292310000000001</v>
+        <v>8.97752</v>
       </c>
       <c r="F117" t="n">
-        <v>13.7094</v>
+        <v>13.7861</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>13.214</v>
+        <v>13.4735</v>
       </c>
       <c r="C118" t="n">
-        <v>21.6585</v>
+        <v>8.876379999999999</v>
       </c>
       <c r="D118" t="n">
-        <v>60.703</v>
+        <v>62.001</v>
       </c>
       <c r="E118" t="n">
-        <v>8.912459999999999</v>
+        <v>9.413489999999999</v>
       </c>
       <c r="F118" t="n">
-        <v>14.4479</v>
+        <v>14.4838</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>14.4344</v>
+        <v>14.5271</v>
       </c>
       <c r="C119" t="n">
-        <v>23.2613</v>
+        <v>9.752890000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>62.398</v>
+        <v>64.1293</v>
       </c>
       <c r="E119" t="n">
-        <v>9.86666</v>
+        <v>9.977819999999999</v>
       </c>
       <c r="F119" t="n">
-        <v>15.4102</v>
+        <v>15.377</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>15.9424</v>
+        <v>15.9312</v>
       </c>
       <c r="C120" t="n">
-        <v>25.3441</v>
+        <v>10.9404</v>
       </c>
       <c r="D120" t="n">
-        <v>64.7843</v>
+        <v>66.1467</v>
       </c>
       <c r="E120" t="n">
-        <v>10.606</v>
+        <v>10.8365</v>
       </c>
       <c r="F120" t="n">
-        <v>16.5989</v>
+        <v>16.5547</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>18.0246</v>
+        <v>17.9063</v>
       </c>
       <c r="C121" t="n">
-        <v>28.2775</v>
+        <v>12.767</v>
       </c>
       <c r="D121" t="n">
-        <v>48.062</v>
+        <v>49.6681</v>
       </c>
       <c r="E121" t="n">
-        <v>12.0609</v>
+        <v>12.0489</v>
       </c>
       <c r="F121" t="n">
-        <v>18.3561</v>
+        <v>18.281</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>20.9583</v>
+        <v>20.6485</v>
       </c>
       <c r="C122" t="n">
-        <v>32.6108</v>
+        <v>7.17173</v>
       </c>
       <c r="D122" t="n">
-        <v>48.8095</v>
+        <v>50.4615</v>
       </c>
       <c r="E122" t="n">
-        <v>14.2458</v>
+        <v>14.2414</v>
       </c>
       <c r="F122" t="n">
-        <v>21.1652</v>
+        <v>21.0046</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>25.2705</v>
+        <v>24.9776</v>
       </c>
       <c r="C123" t="n">
-        <v>39.3367</v>
+        <v>7.13283</v>
       </c>
       <c r="D123" t="n">
-        <v>50.3854</v>
+        <v>51.8962</v>
       </c>
       <c r="E123" t="n">
-        <v>8.25484</v>
+        <v>8.34422</v>
       </c>
       <c r="F123" t="n">
-        <v>12.0769</v>
+        <v>12.4764</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>11.0282</v>
+        <v>11.164</v>
       </c>
       <c r="C124" t="n">
-        <v>17.733</v>
+        <v>7.88287</v>
       </c>
       <c r="D124" t="n">
-        <v>51.5876</v>
+        <v>53.0536</v>
       </c>
       <c r="E124" t="n">
-        <v>8.468669999999999</v>
+        <v>8.608639999999999</v>
       </c>
       <c r="F124" t="n">
-        <v>12.3702</v>
+        <v>13.0654</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>11.5618</v>
+        <v>11.7499</v>
       </c>
       <c r="C125" t="n">
-        <v>17.8919</v>
+        <v>7.57917</v>
       </c>
       <c r="D125" t="n">
-        <v>52.4815</v>
+        <v>54.2512</v>
       </c>
       <c r="E125" t="n">
-        <v>9.60965</v>
+        <v>8.70722</v>
       </c>
       <c r="F125" t="n">
-        <v>13.5964</v>
+        <v>12.2683</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>11.5676</v>
+        <v>11.6804</v>
       </c>
       <c r="C126" t="n">
-        <v>18.7541</v>
+        <v>7.60032</v>
       </c>
       <c r="D126" t="n">
-        <v>54.2567</v>
+        <v>55.6997</v>
       </c>
       <c r="E126" t="n">
-        <v>9.014699999999999</v>
+        <v>9.00366</v>
       </c>
       <c r="F126" t="n">
-        <v>13.1756</v>
+        <v>13.2712</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>11.9574</v>
+        <v>12.0334</v>
       </c>
       <c r="C127" t="n">
-        <v>18.7168</v>
+        <v>7.7524</v>
       </c>
       <c r="D127" t="n">
-        <v>55.6007</v>
+        <v>57.1198</v>
       </c>
       <c r="E127" t="n">
-        <v>9.40738</v>
+        <v>9.106780000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>14.225</v>
+        <v>13.5473</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>12.1968</v>
+        <v>12.3604</v>
       </c>
       <c r="C128" t="n">
-        <v>20.0921</v>
+        <v>8.369249999999999</v>
       </c>
       <c r="D128" t="n">
-        <v>57.126</v>
+        <v>58.5613</v>
       </c>
       <c r="E128" t="n">
-        <v>9.21575</v>
+        <v>9.487579999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>14.044</v>
+        <v>14.3371</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>12.6937</v>
+        <v>12.8739</v>
       </c>
       <c r="C129" t="n">
-        <v>20.4983</v>
+        <v>8.48645</v>
       </c>
       <c r="D129" t="n">
-        <v>58.7446</v>
+        <v>60.1128</v>
       </c>
       <c r="E129" t="n">
-        <v>9.83962</v>
+        <v>9.969799999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>14.5314</v>
+        <v>14.8159</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>13.1116</v>
+        <v>13.383</v>
       </c>
       <c r="C130" t="n">
-        <v>20.8467</v>
+        <v>9.135160000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>60.4147</v>
+        <v>61.7173</v>
       </c>
       <c r="E130" t="n">
-        <v>9.65272</v>
+        <v>10.008</v>
       </c>
       <c r="F130" t="n">
-        <v>14.7229</v>
+        <v>15.1906</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>13.908</v>
+        <v>13.7025</v>
       </c>
       <c r="C131" t="n">
-        <v>22.3973</v>
+        <v>9.13247</v>
       </c>
       <c r="D131" t="n">
-        <v>62.2152</v>
+        <v>63.5507</v>
       </c>
       <c r="E131" t="n">
-        <v>10.3763</v>
+        <v>10.2906</v>
       </c>
       <c r="F131" t="n">
-        <v>15.469</v>
+        <v>15.6948</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.3501</v>
+        <v>14.7381</v>
       </c>
       <c r="C132" t="n">
-        <v>23.5582</v>
+        <v>9.58569</v>
       </c>
       <c r="D132" t="n">
-        <v>64.13249999999999</v>
+        <v>65.20659999999999</v>
       </c>
       <c r="E132" t="n">
-        <v>10.5674</v>
+        <v>10.7302</v>
       </c>
       <c r="F132" t="n">
-        <v>16.0776</v>
+        <v>16.3386</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>15.5112</v>
+        <v>15.5555</v>
       </c>
       <c r="C133" t="n">
-        <v>25.1326</v>
+        <v>10.4785</v>
       </c>
       <c r="D133" t="n">
-        <v>66.158</v>
+        <v>67.1973</v>
       </c>
       <c r="E133" t="n">
-        <v>11.3315</v>
+        <v>11.4054</v>
       </c>
       <c r="F133" t="n">
-        <v>17.3247</v>
+        <v>17.3236</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>17.029</v>
+        <v>16.7782</v>
       </c>
       <c r="C134" t="n">
-        <v>26.9703</v>
+        <v>11.5075</v>
       </c>
       <c r="D134" t="n">
-        <v>68.3015</v>
+        <v>69.5014</v>
       </c>
       <c r="E134" t="n">
-        <v>12.1883</v>
+        <v>11.8949</v>
       </c>
       <c r="F134" t="n">
-        <v>18.2933</v>
+        <v>18.3773</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>18.6951</v>
+        <v>18.7445</v>
       </c>
       <c r="C135" t="n">
-        <v>29.7929</v>
+        <v>13.2604</v>
       </c>
       <c r="D135" t="n">
-        <v>49.7713</v>
+        <v>51.6635</v>
       </c>
       <c r="E135" t="n">
-        <v>12.8514</v>
+        <v>13.0018</v>
       </c>
       <c r="F135" t="n">
-        <v>19.9201</v>
+        <v>19.8924</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>21.4935</v>
+        <v>21.2534</v>
       </c>
       <c r="C136" t="n">
-        <v>33.9181</v>
+        <v>14.0908</v>
       </c>
       <c r="D136" t="n">
-        <v>50.9183</v>
+        <v>52.719</v>
       </c>
       <c r="E136" t="n">
-        <v>15.0627</v>
+        <v>14.9895</v>
       </c>
       <c r="F136" t="n">
-        <v>22.4463</v>
+        <v>22.2797</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>25.0064</v>
+        <v>25.4056</v>
       </c>
       <c r="C137" t="n">
-        <v>40.2322</v>
+        <v>14.278</v>
       </c>
       <c r="D137" t="n">
-        <v>52.3359</v>
+        <v>53.8827</v>
       </c>
       <c r="E137" t="n">
-        <v>15.9233</v>
+        <v>16.9055</v>
       </c>
       <c r="F137" t="n">
-        <v>19.5411</v>
+        <v>19.6914</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.701</v>
+        <v>19.0853</v>
       </c>
       <c r="C138" t="n">
-        <v>24.4034</v>
+        <v>14.2308</v>
       </c>
       <c r="D138" t="n">
-        <v>53.274</v>
+        <v>55.0913</v>
       </c>
       <c r="E138" t="n">
-        <v>16.5307</v>
+        <v>16.9948</v>
       </c>
       <c r="F138" t="n">
-        <v>20.8653</v>
+        <v>20.4961</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>18.4836</v>
+        <v>19.1293</v>
       </c>
       <c r="C139" t="n">
-        <v>25.68</v>
+        <v>14.4045</v>
       </c>
       <c r="D139" t="n">
-        <v>54.8453</v>
+        <v>56.3389</v>
       </c>
       <c r="E139" t="n">
-        <v>16.8882</v>
+        <v>17.2016</v>
       </c>
       <c r="F139" t="n">
-        <v>20.9772</v>
+        <v>21.9875</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>19.1791</v>
+        <v>19.3309</v>
       </c>
       <c r="C140" t="n">
-        <v>26.0652</v>
+        <v>14.4739</v>
       </c>
       <c r="D140" t="n">
-        <v>56.1461</v>
+        <v>57.6234</v>
       </c>
       <c r="E140" t="n">
-        <v>17.0439</v>
+        <v>17.3061</v>
       </c>
       <c r="F140" t="n">
-        <v>21.4367</v>
+        <v>21.7944</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>18.9638</v>
+        <v>19.5635</v>
       </c>
       <c r="C141" t="n">
-        <v>26.6267</v>
+        <v>14.7102</v>
       </c>
       <c r="D141" t="n">
-        <v>57.5582</v>
+        <v>58.9706</v>
       </c>
       <c r="E141" t="n">
-        <v>16.6915</v>
+        <v>17.7679</v>
       </c>
       <c r="F141" t="n">
-        <v>21.2055</v>
+        <v>22.2773</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>19.5616</v>
+        <v>19.7154</v>
       </c>
       <c r="C142" t="n">
-        <v>27.2934</v>
+        <v>14.854</v>
       </c>
       <c r="D142" t="n">
-        <v>59.0552</v>
+        <v>60.4854</v>
       </c>
       <c r="E142" t="n">
-        <v>17.3691</v>
+        <v>17.6706</v>
       </c>
       <c r="F142" t="n">
-        <v>22.3025</v>
+        <v>22.578</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>19.6806</v>
+        <v>20.2186</v>
       </c>
       <c r="C143" t="n">
-        <v>27.8645</v>
+        <v>15.1084</v>
       </c>
       <c r="D143" t="n">
-        <v>60.365</v>
+        <v>62.0484</v>
       </c>
       <c r="E143" t="n">
-        <v>17.6671</v>
+        <v>17.031</v>
       </c>
       <c r="F143" t="n">
-        <v>21.954</v>
+        <v>23.0285</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered unsuccessful looukp.xlsx
+++ b/clang-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.65831</v>
+        <v>2.72035</v>
       </c>
       <c r="C2" t="n">
-        <v>2.075</v>
+        <v>2.07799</v>
       </c>
       <c r="D2" t="n">
-        <v>12.4762</v>
+        <v>12.58</v>
       </c>
       <c r="E2" t="n">
-        <v>2.63297</v>
+        <v>2.62571</v>
       </c>
       <c r="F2" t="n">
-        <v>2.45577</v>
+        <v>2.43768</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.73137</v>
+        <v>2.78625</v>
       </c>
       <c r="C3" t="n">
-        <v>2.17606</v>
+        <v>2.17014</v>
       </c>
       <c r="D3" t="n">
-        <v>12.8391</v>
+        <v>12.9871</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7113</v>
+        <v>2.71159</v>
       </c>
       <c r="F3" t="n">
-        <v>2.54336</v>
+        <v>2.52631</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.86526</v>
+        <v>2.82768</v>
       </c>
       <c r="C4" t="n">
-        <v>2.34791</v>
+        <v>2.34636</v>
       </c>
       <c r="D4" t="n">
-        <v>13.4424</v>
+        <v>13.4817</v>
       </c>
       <c r="E4" t="n">
-        <v>2.78578</v>
+        <v>2.78141</v>
       </c>
       <c r="F4" t="n">
-        <v>2.67175</v>
+        <v>2.65791</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.23377</v>
+        <v>3.20713</v>
       </c>
       <c r="C5" t="n">
-        <v>2.72026</v>
+        <v>2.69226</v>
       </c>
       <c r="D5" t="n">
-        <v>14.0345</v>
+        <v>13.998</v>
       </c>
       <c r="E5" t="n">
-        <v>2.91502</v>
+        <v>2.9206</v>
       </c>
       <c r="F5" t="n">
-        <v>2.83271</v>
+        <v>2.80208</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.02099</v>
+        <v>4.04414</v>
       </c>
       <c r="C6" t="n">
-        <v>3.58018</v>
+        <v>3.56348</v>
       </c>
       <c r="D6" t="n">
-        <v>14.5575</v>
+        <v>14.5961</v>
       </c>
       <c r="E6" t="n">
-        <v>3.15345</v>
+        <v>3.13637</v>
       </c>
       <c r="F6" t="n">
-        <v>2.99954</v>
+        <v>2.97361</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.56782</v>
+        <v>6.58402</v>
       </c>
       <c r="C7" t="n">
-        <v>5.27936</v>
+        <v>5.26056</v>
       </c>
       <c r="D7" t="n">
-        <v>10.1536</v>
+        <v>10.1943</v>
       </c>
       <c r="E7" t="n">
-        <v>3.53799</v>
+        <v>2.38015</v>
       </c>
       <c r="F7" t="n">
-        <v>3.50214</v>
+        <v>2.12808</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.371029999999999</v>
+        <v>9.543480000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1.74313</v>
+        <v>1.7441</v>
       </c>
       <c r="D8" t="n">
-        <v>10.7988</v>
+        <v>10.869</v>
       </c>
       <c r="E8" t="n">
-        <v>4.75142</v>
+        <v>2.39696</v>
       </c>
       <c r="F8" t="n">
-        <v>4.8517</v>
+        <v>2.14919</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.6607</v>
+        <v>13.8565</v>
       </c>
       <c r="C9" t="n">
-        <v>1.76176</v>
+        <v>1.7647</v>
       </c>
       <c r="D9" t="n">
-        <v>11.437</v>
+        <v>11.5094</v>
       </c>
       <c r="E9" t="n">
-        <v>2.41372</v>
+        <v>2.41603</v>
       </c>
       <c r="F9" t="n">
-        <v>2.19174</v>
+        <v>2.18098</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.6069</v>
+        <v>2.62346</v>
       </c>
       <c r="C10" t="n">
-        <v>1.80145</v>
+        <v>1.80183</v>
       </c>
       <c r="D10" t="n">
-        <v>12.049</v>
+        <v>12.1792</v>
       </c>
       <c r="E10" t="n">
-        <v>2.44464</v>
+        <v>2.44457</v>
       </c>
       <c r="F10" t="n">
-        <v>2.23322</v>
+        <v>2.22212</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.67202</v>
+        <v>2.69121</v>
       </c>
       <c r="C11" t="n">
-        <v>1.84401</v>
+        <v>1.83837</v>
       </c>
       <c r="D11" t="n">
-        <v>12.6233</v>
+        <v>12.7438</v>
       </c>
       <c r="E11" t="n">
-        <v>2.46757</v>
+        <v>2.47504</v>
       </c>
       <c r="F11" t="n">
-        <v>2.28134</v>
+        <v>2.2479</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.73949</v>
+        <v>2.69998</v>
       </c>
       <c r="C12" t="n">
-        <v>1.87848</v>
+        <v>1.87667</v>
       </c>
       <c r="D12" t="n">
-        <v>13.1461</v>
+        <v>13.2827</v>
       </c>
       <c r="E12" t="n">
-        <v>2.49235</v>
+        <v>2.50051</v>
       </c>
       <c r="F12" t="n">
-        <v>2.31948</v>
+        <v>2.29679</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.79513</v>
+        <v>2.68372</v>
       </c>
       <c r="C13" t="n">
-        <v>1.92042</v>
+        <v>1.92185</v>
       </c>
       <c r="D13" t="n">
-        <v>13.609</v>
+        <v>13.7599</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5161</v>
+        <v>2.51813</v>
       </c>
       <c r="F13" t="n">
-        <v>2.36118</v>
+        <v>2.31044</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.84875</v>
+        <v>2.77216</v>
       </c>
       <c r="C14" t="n">
-        <v>2.03165</v>
+        <v>2.03881</v>
       </c>
       <c r="D14" t="n">
-        <v>14.1148</v>
+        <v>14.2335</v>
       </c>
       <c r="E14" t="n">
-        <v>2.54773</v>
+        <v>2.56088</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4197</v>
+        <v>2.39445</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.8945</v>
+        <v>2.89731</v>
       </c>
       <c r="C15" t="n">
-        <v>2.10908</v>
+        <v>2.11549</v>
       </c>
       <c r="D15" t="n">
-        <v>14.5292</v>
+        <v>14.6558</v>
       </c>
       <c r="E15" t="n">
-        <v>2.60132</v>
+        <v>2.61587</v>
       </c>
       <c r="F15" t="n">
-        <v>2.48763</v>
+        <v>2.47602</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.98195</v>
+        <v>2.97056</v>
       </c>
       <c r="C16" t="n">
-        <v>2.2363</v>
+        <v>2.24897</v>
       </c>
       <c r="D16" t="n">
-        <v>14.9437</v>
+        <v>15.0577</v>
       </c>
       <c r="E16" t="n">
-        <v>2.65906</v>
+        <v>2.67076</v>
       </c>
       <c r="F16" t="n">
-        <v>2.55675</v>
+        <v>2.54209</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.17076</v>
+        <v>3.18098</v>
       </c>
       <c r="C17" t="n">
-        <v>2.40178</v>
+        <v>2.40396</v>
       </c>
       <c r="D17" t="n">
-        <v>15.3656</v>
+        <v>15.4588</v>
       </c>
       <c r="E17" t="n">
-        <v>2.7316</v>
+        <v>2.75316</v>
       </c>
       <c r="F17" t="n">
-        <v>2.64825</v>
+        <v>2.63555</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.42048</v>
+        <v>3.55934</v>
       </c>
       <c r="C18" t="n">
-        <v>2.68996</v>
+        <v>2.69843</v>
       </c>
       <c r="D18" t="n">
-        <v>15.7901</v>
+        <v>15.8709</v>
       </c>
       <c r="E18" t="n">
-        <v>2.85027</v>
+        <v>2.86826</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8083</v>
+        <v>2.80797</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>3.99826</v>
+        <v>4.14686</v>
       </c>
       <c r="C19" t="n">
-        <v>3.28671</v>
+        <v>3.30651</v>
       </c>
       <c r="D19" t="n">
-        <v>16.1759</v>
+        <v>16.2648</v>
       </c>
       <c r="E19" t="n">
-        <v>3.03817</v>
+        <v>3.0571</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0386</v>
+        <v>3.01716</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.32088</v>
+        <v>5.23738</v>
       </c>
       <c r="C20" t="n">
-        <v>4.25045</v>
+        <v>4.24999</v>
       </c>
       <c r="D20" t="n">
-        <v>16.58</v>
+        <v>16.6689</v>
       </c>
       <c r="E20" t="n">
-        <v>3.4089</v>
+        <v>3.43205</v>
       </c>
       <c r="F20" t="n">
-        <v>3.43568</v>
+        <v>3.4459</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.98767</v>
+        <v>6.97224</v>
       </c>
       <c r="C21" t="n">
-        <v>5.51956</v>
+        <v>5.51899</v>
       </c>
       <c r="D21" t="n">
-        <v>11.765</v>
+        <v>11.7971</v>
       </c>
       <c r="E21" t="n">
-        <v>4.05455</v>
+        <v>2.42143</v>
       </c>
       <c r="F21" t="n">
-        <v>4.14139</v>
+        <v>2.24268</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.436859999999999</v>
+        <v>9.325419999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>1.80953</v>
+        <v>1.81846</v>
       </c>
       <c r="D22" t="n">
-        <v>12.3071</v>
+        <v>12.3245</v>
       </c>
       <c r="E22" t="n">
-        <v>5.3994</v>
+        <v>2.44584</v>
       </c>
       <c r="F22" t="n">
-        <v>5.52882</v>
+        <v>2.28261</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.65</v>
+        <v>12.5895</v>
       </c>
       <c r="C23" t="n">
-        <v>1.88591</v>
+        <v>1.83812</v>
       </c>
       <c r="D23" t="n">
-        <v>12.8056</v>
+        <v>12.8156</v>
       </c>
       <c r="E23" t="n">
-        <v>2.45166</v>
+        <v>2.46075</v>
       </c>
       <c r="F23" t="n">
-        <v>2.30049</v>
+        <v>2.29669</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.75174</v>
+        <v>2.73903</v>
       </c>
       <c r="C24" t="n">
-        <v>1.86698</v>
+        <v>1.89221</v>
       </c>
       <c r="D24" t="n">
-        <v>13.3271</v>
+        <v>13.3423</v>
       </c>
       <c r="E24" t="n">
-        <v>2.48177</v>
+        <v>2.48835</v>
       </c>
       <c r="F24" t="n">
-        <v>2.32623</v>
+        <v>2.35759</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.79278</v>
+        <v>2.79217</v>
       </c>
       <c r="C25" t="n">
-        <v>1.90387</v>
+        <v>1.92376</v>
       </c>
       <c r="D25" t="n">
-        <v>13.791</v>
+        <v>13.7909</v>
       </c>
       <c r="E25" t="n">
-        <v>2.50534</v>
+        <v>2.51189</v>
       </c>
       <c r="F25" t="n">
-        <v>2.37541</v>
+        <v>2.40298</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.83983</v>
+        <v>2.84291</v>
       </c>
       <c r="C26" t="n">
-        <v>1.94139</v>
+        <v>1.95554</v>
       </c>
       <c r="D26" t="n">
-        <v>14.1718</v>
+        <v>14.1962</v>
       </c>
       <c r="E26" t="n">
-        <v>2.54127</v>
+        <v>2.55071</v>
       </c>
       <c r="F26" t="n">
-        <v>2.43874</v>
+        <v>2.45635</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.90644</v>
+        <v>2.93582</v>
       </c>
       <c r="C27" t="n">
-        <v>1.98174</v>
+        <v>1.9951</v>
       </c>
       <c r="D27" t="n">
-        <v>14.655</v>
+        <v>14.6679</v>
       </c>
       <c r="E27" t="n">
-        <v>2.56859</v>
+        <v>2.57989</v>
       </c>
       <c r="F27" t="n">
-        <v>2.48528</v>
+        <v>2.51042</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.01324</v>
+        <v>3.01206</v>
       </c>
       <c r="C28" t="n">
-        <v>2.06059</v>
+        <v>2.08367</v>
       </c>
       <c r="D28" t="n">
-        <v>15.1157</v>
+        <v>15.121</v>
       </c>
       <c r="E28" t="n">
-        <v>2.60921</v>
+        <v>2.62268</v>
       </c>
       <c r="F28" t="n">
-        <v>2.54824</v>
+        <v>2.58875</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.11581</v>
+        <v>3.15368</v>
       </c>
       <c r="C29" t="n">
-        <v>2.17654</v>
+        <v>2.19089</v>
       </c>
       <c r="D29" t="n">
-        <v>15.5292</v>
+        <v>15.5556</v>
       </c>
       <c r="E29" t="n">
-        <v>2.66677</v>
+        <v>2.68377</v>
       </c>
       <c r="F29" t="n">
-        <v>2.64534</v>
+        <v>2.67331</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.31047</v>
+        <v>3.32952</v>
       </c>
       <c r="C30" t="n">
-        <v>2.31251</v>
+        <v>2.32763</v>
       </c>
       <c r="D30" t="n">
-        <v>15.9777</v>
+        <v>15.9894</v>
       </c>
       <c r="E30" t="n">
-        <v>2.72063</v>
+        <v>2.74206</v>
       </c>
       <c r="F30" t="n">
-        <v>2.73553</v>
+        <v>2.76802</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.57003</v>
+        <v>3.57213</v>
       </c>
       <c r="C31" t="n">
-        <v>2.48516</v>
+        <v>2.50949</v>
       </c>
       <c r="D31" t="n">
-        <v>16.3542</v>
+        <v>16.3792</v>
       </c>
       <c r="E31" t="n">
-        <v>2.79487</v>
+        <v>2.81134</v>
       </c>
       <c r="F31" t="n">
-        <v>2.8304</v>
+        <v>2.855</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.98159</v>
+        <v>4.00238</v>
       </c>
       <c r="C32" t="n">
-        <v>2.76965</v>
+        <v>2.77285</v>
       </c>
       <c r="D32" t="n">
-        <v>16.6816</v>
+        <v>16.6877</v>
       </c>
       <c r="E32" t="n">
-        <v>2.91154</v>
+        <v>2.92459</v>
       </c>
       <c r="F32" t="n">
-        <v>3.0007</v>
+        <v>3.01283</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.83554</v>
+        <v>4.71082</v>
       </c>
       <c r="C33" t="n">
-        <v>3.30881</v>
+        <v>3.32028</v>
       </c>
       <c r="D33" t="n">
-        <v>17.1249</v>
+        <v>17.1523</v>
       </c>
       <c r="E33" t="n">
-        <v>3.11462</v>
+        <v>3.13671</v>
       </c>
       <c r="F33" t="n">
-        <v>3.24517</v>
+        <v>3.26005</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.63488</v>
+        <v>5.72072</v>
       </c>
       <c r="C34" t="n">
-        <v>4.1087</v>
+        <v>4.12695</v>
       </c>
       <c r="D34" t="n">
-        <v>17.5482</v>
+        <v>17.5477</v>
       </c>
       <c r="E34" t="n">
-        <v>3.54308</v>
+        <v>3.55054</v>
       </c>
       <c r="F34" t="n">
-        <v>3.66723</v>
+        <v>3.69061</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.11034</v>
+        <v>7.24307</v>
       </c>
       <c r="C35" t="n">
-        <v>5.22608</v>
+        <v>5.24706</v>
       </c>
       <c r="D35" t="n">
-        <v>12.1881</v>
+        <v>12.2077</v>
       </c>
       <c r="E35" t="n">
-        <v>4.2193</v>
+        <v>2.43909</v>
       </c>
       <c r="F35" t="n">
-        <v>4.35401</v>
+        <v>2.35322</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.60092</v>
+        <v>9.47611</v>
       </c>
       <c r="C36" t="n">
-        <v>6.90284</v>
+        <v>6.90491</v>
       </c>
       <c r="D36" t="n">
-        <v>12.6914</v>
+        <v>12.7143</v>
       </c>
       <c r="E36" t="n">
-        <v>5.32376</v>
+        <v>2.45708</v>
       </c>
       <c r="F36" t="n">
-        <v>5.46774</v>
+        <v>2.39745</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>12.7211</v>
+        <v>13.1075</v>
       </c>
       <c r="C37" t="n">
-        <v>1.84745</v>
+        <v>1.86517</v>
       </c>
       <c r="D37" t="n">
-        <v>13.1458</v>
+        <v>13.1782</v>
       </c>
       <c r="E37" t="n">
-        <v>2.48227</v>
+        <v>2.48568</v>
       </c>
       <c r="F37" t="n">
-        <v>2.41218</v>
+        <v>2.42512</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.81553</v>
+        <v>2.81644</v>
       </c>
       <c r="C38" t="n">
-        <v>1.91315</v>
+        <v>1.89582</v>
       </c>
       <c r="D38" t="n">
-        <v>13.6559</v>
+        <v>13.6861</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5089</v>
+        <v>2.5116</v>
       </c>
       <c r="F38" t="n">
-        <v>2.45554</v>
+        <v>2.48673</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.87198</v>
+        <v>2.85281</v>
       </c>
       <c r="C39" t="n">
-        <v>1.92719</v>
+        <v>1.94924</v>
       </c>
       <c r="D39" t="n">
-        <v>14.1286</v>
+        <v>14.1652</v>
       </c>
       <c r="E39" t="n">
-        <v>2.53893</v>
+        <v>2.54465</v>
       </c>
       <c r="F39" t="n">
-        <v>2.53213</v>
+        <v>2.54162</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.94599</v>
+        <v>2.93425</v>
       </c>
       <c r="C40" t="n">
-        <v>1.97879</v>
+        <v>1.99362</v>
       </c>
       <c r="D40" t="n">
-        <v>14.5527</v>
+        <v>14.5857</v>
       </c>
       <c r="E40" t="n">
-        <v>2.56421</v>
+        <v>2.57309</v>
       </c>
       <c r="F40" t="n">
-        <v>2.57948</v>
+        <v>2.61773</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.01663</v>
+        <v>3.01031</v>
       </c>
       <c r="C41" t="n">
-        <v>2.05121</v>
+        <v>2.04471</v>
       </c>
       <c r="D41" t="n">
-        <v>14.9858</v>
+        <v>15.0273</v>
       </c>
       <c r="E41" t="n">
-        <v>2.59755</v>
+        <v>2.60643</v>
       </c>
       <c r="F41" t="n">
-        <v>2.63855</v>
+        <v>2.66731</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.11515</v>
+        <v>3.08407</v>
       </c>
       <c r="C42" t="n">
-        <v>2.124</v>
+        <v>2.10542</v>
       </c>
       <c r="D42" t="n">
-        <v>15.4032</v>
+        <v>15.4458</v>
       </c>
       <c r="E42" t="n">
-        <v>2.63761</v>
+        <v>2.64934</v>
       </c>
       <c r="F42" t="n">
-        <v>2.70644</v>
+        <v>2.71981</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.25433</v>
+        <v>3.24263</v>
       </c>
       <c r="C43" t="n">
-        <v>2.21769</v>
+        <v>2.20154</v>
       </c>
       <c r="D43" t="n">
-        <v>15.8407</v>
+        <v>15.9032</v>
       </c>
       <c r="E43" t="n">
-        <v>2.68999</v>
+        <v>2.70373</v>
       </c>
       <c r="F43" t="n">
-        <v>2.78222</v>
+        <v>2.80497</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.43145</v>
+        <v>3.43074</v>
       </c>
       <c r="C44" t="n">
-        <v>2.3379</v>
+        <v>2.33667</v>
       </c>
       <c r="D44" t="n">
-        <v>16.2481</v>
+        <v>16.3055</v>
       </c>
       <c r="E44" t="n">
-        <v>2.76384</v>
+        <v>2.77496</v>
       </c>
       <c r="F44" t="n">
-        <v>2.89433</v>
+        <v>2.92496</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.67119</v>
+        <v>3.68513</v>
       </c>
       <c r="C45" t="n">
-        <v>2.60248</v>
+        <v>2.58882</v>
       </c>
       <c r="D45" t="n">
-        <v>16.6401</v>
+        <v>16.6797</v>
       </c>
       <c r="E45" t="n">
-        <v>2.86274</v>
+        <v>2.86258</v>
       </c>
       <c r="F45" t="n">
-        <v>3.01896</v>
+        <v>3.04138</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.06037</v>
+        <v>4.0533</v>
       </c>
       <c r="C46" t="n">
-        <v>2.89556</v>
+        <v>2.9023</v>
       </c>
       <c r="D46" t="n">
-        <v>17.0709</v>
+        <v>17.0875</v>
       </c>
       <c r="E46" t="n">
-        <v>2.99656</v>
+        <v>3.00411</v>
       </c>
       <c r="F46" t="n">
-        <v>3.16395</v>
+        <v>3.19436</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.61676</v>
+        <v>4.6571</v>
       </c>
       <c r="C47" t="n">
-        <v>3.35805</v>
+        <v>3.35803</v>
       </c>
       <c r="D47" t="n">
-        <v>17.4603</v>
+        <v>17.4971</v>
       </c>
       <c r="E47" t="n">
-        <v>3.22413</v>
+        <v>3.23302</v>
       </c>
       <c r="F47" t="n">
-        <v>3.42894</v>
+        <v>3.46132</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.50968</v>
+        <v>5.44295</v>
       </c>
       <c r="C48" t="n">
-        <v>4.03095</v>
+        <v>4.03346</v>
       </c>
       <c r="D48" t="n">
-        <v>17.8983</v>
+        <v>17.9456</v>
       </c>
       <c r="E48" t="n">
-        <v>3.60289</v>
+        <v>3.60964</v>
       </c>
       <c r="F48" t="n">
-        <v>3.81378</v>
+        <v>3.83523</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.53264</v>
+        <v>6.58218</v>
       </c>
       <c r="C49" t="n">
-        <v>4.97205</v>
+        <v>4.97266</v>
       </c>
       <c r="D49" t="n">
-        <v>18.3733</v>
+        <v>18.4079</v>
       </c>
       <c r="E49" t="n">
-        <v>4.15934</v>
+        <v>4.17052</v>
       </c>
       <c r="F49" t="n">
-        <v>4.3638</v>
+        <v>4.39294</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.597020000000001</v>
+        <v>8.52908</v>
       </c>
       <c r="C50" t="n">
-        <v>6.47019</v>
+        <v>6.48311</v>
       </c>
       <c r="D50" t="n">
-        <v>12.8482</v>
+        <v>12.8605</v>
       </c>
       <c r="E50" t="n">
-        <v>5.12536</v>
+        <v>2.49602</v>
       </c>
       <c r="F50" t="n">
-        <v>5.33631</v>
+        <v>2.5981</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>11.5487</v>
+        <v>11.145</v>
       </c>
       <c r="C51" t="n">
-        <v>2.15583</v>
+        <v>1.97497</v>
       </c>
       <c r="D51" t="n">
-        <v>13.3004</v>
+        <v>13.3109</v>
       </c>
       <c r="E51" t="n">
-        <v>2.94645</v>
+        <v>2.50783</v>
       </c>
       <c r="F51" t="n">
-        <v>2.70058</v>
+        <v>2.61629</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.7007</v>
+        <v>15.572</v>
       </c>
       <c r="C52" t="n">
-        <v>2.41322</v>
+        <v>2.08431</v>
       </c>
       <c r="D52" t="n">
-        <v>13.7888</v>
+        <v>13.7804</v>
       </c>
       <c r="E52" t="n">
-        <v>2.97506</v>
+        <v>2.5374</v>
       </c>
       <c r="F52" t="n">
-        <v>2.72776</v>
+        <v>2.7375</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.10568</v>
+        <v>3.02699</v>
       </c>
       <c r="C53" t="n">
-        <v>2.71803</v>
+        <v>2.04951</v>
       </c>
       <c r="D53" t="n">
-        <v>14.2709</v>
+        <v>14.2708</v>
       </c>
       <c r="E53" t="n">
-        <v>3.00318</v>
+        <v>2.56286</v>
       </c>
       <c r="F53" t="n">
-        <v>2.80208</v>
+        <v>2.71797</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.07946</v>
+        <v>3.02529</v>
       </c>
       <c r="C54" t="n">
-        <v>2.42411</v>
+        <v>2.15216</v>
       </c>
       <c r="D54" t="n">
-        <v>14.7475</v>
+        <v>14.7552</v>
       </c>
       <c r="E54" t="n">
-        <v>3.04334</v>
+        <v>2.69773</v>
       </c>
       <c r="F54" t="n">
-        <v>2.83207</v>
+        <v>2.83134</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.28031</v>
+        <v>3.16609</v>
       </c>
       <c r="C55" t="n">
-        <v>2.77949</v>
+        <v>2.27536</v>
       </c>
       <c r="D55" t="n">
-        <v>15.2068</v>
+        <v>15.2312</v>
       </c>
       <c r="E55" t="n">
-        <v>2.66585</v>
+        <v>2.70697</v>
       </c>
       <c r="F55" t="n">
-        <v>2.91905</v>
+        <v>2.96152</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.29956</v>
+        <v>3.25641</v>
       </c>
       <c r="C56" t="n">
-        <v>2.55493</v>
+        <v>2.25132</v>
       </c>
       <c r="D56" t="n">
-        <v>15.6899</v>
+        <v>15.7073</v>
       </c>
       <c r="E56" t="n">
-        <v>2.71151</v>
+        <v>2.74884</v>
       </c>
       <c r="F56" t="n">
-        <v>2.98672</v>
+        <v>3.01891</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.43815</v>
+        <v>3.35645</v>
       </c>
       <c r="C57" t="n">
-        <v>2.94146</v>
+        <v>2.38274</v>
       </c>
       <c r="D57" t="n">
-        <v>16.1087</v>
+        <v>16.1131</v>
       </c>
       <c r="E57" t="n">
-        <v>2.7694</v>
+        <v>2.82612</v>
       </c>
       <c r="F57" t="n">
-        <v>3.09078</v>
+        <v>3.04885</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.62294</v>
+        <v>3.56582</v>
       </c>
       <c r="C58" t="n">
-        <v>2.56081</v>
+        <v>2.38733</v>
       </c>
       <c r="D58" t="n">
-        <v>16.5936</v>
+        <v>16.5626</v>
       </c>
       <c r="E58" t="n">
-        <v>2.88567</v>
+        <v>2.91572</v>
       </c>
       <c r="F58" t="n">
-        <v>3.12643</v>
+        <v>3.1709</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.80343</v>
+        <v>3.73438</v>
       </c>
       <c r="C59" t="n">
-        <v>2.98805</v>
+        <v>2.65791</v>
       </c>
       <c r="D59" t="n">
-        <v>17.0171</v>
+        <v>16.9775</v>
       </c>
       <c r="E59" t="n">
-        <v>2.92108</v>
+        <v>2.96375</v>
       </c>
       <c r="F59" t="n">
-        <v>3.25622</v>
+        <v>3.21448</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.12934</v>
+        <v>4.21475</v>
       </c>
       <c r="C60" t="n">
-        <v>3.35034</v>
+        <v>2.96219</v>
       </c>
       <c r="D60" t="n">
-        <v>17.4566</v>
+        <v>17.4238</v>
       </c>
       <c r="E60" t="n">
-        <v>3.0862</v>
+        <v>3.13282</v>
       </c>
       <c r="F60" t="n">
-        <v>3.43375</v>
+        <v>3.31048</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.62259</v>
+        <v>4.54879</v>
       </c>
       <c r="C61" t="n">
-        <v>3.54372</v>
+        <v>3.2449</v>
       </c>
       <c r="D61" t="n">
-        <v>17.8532</v>
+        <v>17.8348</v>
       </c>
       <c r="E61" t="n">
-        <v>3.38977</v>
+        <v>3.30057</v>
       </c>
       <c r="F61" t="n">
-        <v>3.63402</v>
+        <v>3.57845</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.30736</v>
+        <v>5.26403</v>
       </c>
       <c r="C62" t="n">
-        <v>3.97008</v>
+        <v>3.98581</v>
       </c>
       <c r="D62" t="n">
-        <v>18.3957</v>
+        <v>18.2498</v>
       </c>
       <c r="E62" t="n">
-        <v>3.6986</v>
+        <v>3.61539</v>
       </c>
       <c r="F62" t="n">
-        <v>3.91938</v>
+        <v>4.08289</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.35879</v>
+        <v>6.36879</v>
       </c>
       <c r="C63" t="n">
-        <v>4.85264</v>
+        <v>4.8556</v>
       </c>
       <c r="D63" t="n">
-        <v>18.9142</v>
+        <v>18.7636</v>
       </c>
       <c r="E63" t="n">
-        <v>4.21585</v>
+        <v>4.12589</v>
       </c>
       <c r="F63" t="n">
-        <v>4.42446</v>
+        <v>4.4258</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>8.08597</v>
+        <v>7.92607</v>
       </c>
       <c r="C64" t="n">
-        <v>6.26662</v>
+        <v>6.11565</v>
       </c>
       <c r="D64" t="n">
-        <v>14.9577</v>
+        <v>13.4903</v>
       </c>
       <c r="E64" t="n">
-        <v>5.03837</v>
+        <v>2.88893</v>
       </c>
       <c r="F64" t="n">
-        <v>5.16636</v>
+        <v>3.25361</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.8025</v>
+        <v>10.7357</v>
       </c>
       <c r="C65" t="n">
-        <v>2.58454</v>
+        <v>2.54153</v>
       </c>
       <c r="D65" t="n">
-        <v>15.7691</v>
+        <v>14.5192</v>
       </c>
       <c r="E65" t="n">
-        <v>6.51943</v>
+        <v>2.90737</v>
       </c>
       <c r="F65" t="n">
-        <v>6.62414</v>
+        <v>3.3129</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.7691</v>
+        <v>14.6391</v>
       </c>
       <c r="C66" t="n">
-        <v>2.57179</v>
+        <v>2.59148</v>
       </c>
       <c r="D66" t="n">
-        <v>16.4389</v>
+        <v>15.3318</v>
       </c>
       <c r="E66" t="n">
-        <v>2.92095</v>
+        <v>2.91704</v>
       </c>
       <c r="F66" t="n">
-        <v>3.31493</v>
+        <v>3.36142</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.54392</v>
+        <v>3.53368</v>
       </c>
       <c r="C67" t="n">
-        <v>2.65137</v>
+        <v>2.5499</v>
       </c>
       <c r="D67" t="n">
-        <v>17.357</v>
+        <v>16.1223</v>
       </c>
       <c r="E67" t="n">
-        <v>2.9432</v>
+        <v>2.95345</v>
       </c>
       <c r="F67" t="n">
-        <v>3.3692</v>
+        <v>3.40783</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.60501</v>
+        <v>3.59052</v>
       </c>
       <c r="C68" t="n">
-        <v>2.6891</v>
+        <v>2.61479</v>
       </c>
       <c r="D68" t="n">
-        <v>18.3547</v>
+        <v>16.9417</v>
       </c>
       <c r="E68" t="n">
-        <v>2.97345</v>
+        <v>2.98529</v>
       </c>
       <c r="F68" t="n">
-        <v>3.4287</v>
+        <v>3.4516</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.76517</v>
+        <v>3.69234</v>
       </c>
       <c r="C69" t="n">
-        <v>2.71809</v>
+        <v>2.67647</v>
       </c>
       <c r="D69" t="n">
-        <v>19.1955</v>
+        <v>17.9131</v>
       </c>
       <c r="E69" t="n">
-        <v>3.09089</v>
+        <v>3.02344</v>
       </c>
       <c r="F69" t="n">
-        <v>3.49606</v>
+        <v>3.51802</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.78724</v>
+        <v>3.77956</v>
       </c>
       <c r="C70" t="n">
-        <v>2.69128</v>
+        <v>2.71578</v>
       </c>
       <c r="D70" t="n">
-        <v>20.1026</v>
+        <v>18.7662</v>
       </c>
       <c r="E70" t="n">
-        <v>3.11121</v>
+        <v>3.09752</v>
       </c>
       <c r="F70" t="n">
-        <v>3.56495</v>
+        <v>3.59127</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>4.0278</v>
+        <v>3.78085</v>
       </c>
       <c r="C71" t="n">
-        <v>2.82175</v>
+        <v>2.80745</v>
       </c>
       <c r="D71" t="n">
-        <v>21.1036</v>
+        <v>19.6786</v>
       </c>
       <c r="E71" t="n">
-        <v>3.15669</v>
+        <v>3.18275</v>
       </c>
       <c r="F71" t="n">
-        <v>3.65632</v>
+        <v>3.67486</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.18296</v>
+        <v>4.05996</v>
       </c>
       <c r="C72" t="n">
-        <v>2.93185</v>
+        <v>2.92856</v>
       </c>
       <c r="D72" t="n">
-        <v>22.1887</v>
+        <v>21.0998</v>
       </c>
       <c r="E72" t="n">
-        <v>3.23217</v>
+        <v>3.25915</v>
       </c>
       <c r="F72" t="n">
-        <v>3.76785</v>
+        <v>3.76664</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.26106</v>
+        <v>4.22972</v>
       </c>
       <c r="C73" t="n">
-        <v>3.14662</v>
+        <v>3.07606</v>
       </c>
       <c r="D73" t="n">
-        <v>23.2733</v>
+        <v>22.0846</v>
       </c>
       <c r="E73" t="n">
-        <v>3.32857</v>
+        <v>3.35476</v>
       </c>
       <c r="F73" t="n">
-        <v>3.9041</v>
+        <v>3.89449</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.52229</v>
+        <v>4.40449</v>
       </c>
       <c r="C74" t="n">
-        <v>3.29666</v>
+        <v>3.31523</v>
       </c>
       <c r="D74" t="n">
-        <v>24.5136</v>
+        <v>23.3897</v>
       </c>
       <c r="E74" t="n">
-        <v>3.51731</v>
+        <v>3.48315</v>
       </c>
       <c r="F74" t="n">
-        <v>4.11183</v>
+        <v>4.06365</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>4.96401</v>
+        <v>4.96425</v>
       </c>
       <c r="C75" t="n">
-        <v>3.70702</v>
+        <v>3.71046</v>
       </c>
       <c r="D75" t="n">
-        <v>25.9832</v>
+        <v>24.7107</v>
       </c>
       <c r="E75" t="n">
-        <v>3.69089</v>
+        <v>3.66156</v>
       </c>
       <c r="F75" t="n">
-        <v>4.39818</v>
+        <v>4.27567</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.63163</v>
+        <v>5.54772</v>
       </c>
       <c r="C76" t="n">
-        <v>4.24914</v>
+        <v>4.21337</v>
       </c>
       <c r="D76" t="n">
-        <v>27.1426</v>
+        <v>26.1542</v>
       </c>
       <c r="E76" t="n">
-        <v>3.94908</v>
+        <v>3.96682</v>
       </c>
       <c r="F76" t="n">
-        <v>4.7908</v>
+        <v>4.69681</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.59181</v>
+        <v>6.50704</v>
       </c>
       <c r="C77" t="n">
-        <v>5.04027</v>
+        <v>5.02672</v>
       </c>
       <c r="D77" t="n">
-        <v>28.7571</v>
+        <v>27.7541</v>
       </c>
       <c r="E77" t="n">
-        <v>4.43074</v>
+        <v>4.43755</v>
       </c>
       <c r="F77" t="n">
-        <v>5.24323</v>
+        <v>5.15398</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.165330000000001</v>
+        <v>8.16558</v>
       </c>
       <c r="C78" t="n">
-        <v>6.35715</v>
+        <v>6.33321</v>
       </c>
       <c r="D78" t="n">
-        <v>24.472</v>
+        <v>24.0328</v>
       </c>
       <c r="E78" t="n">
-        <v>5.20947</v>
+        <v>3.24978</v>
       </c>
       <c r="F78" t="n">
-        <v>6.05743</v>
+        <v>3.78256</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.6575</v>
+        <v>10.4779</v>
       </c>
       <c r="C79" t="n">
-        <v>2.86199</v>
+        <v>2.9326</v>
       </c>
       <c r="D79" t="n">
-        <v>25.7458</v>
+        <v>25.3068</v>
       </c>
       <c r="E79" t="n">
-        <v>6.56035</v>
+        <v>3.3133</v>
       </c>
       <c r="F79" t="n">
-        <v>7.50568</v>
+        <v>3.85458</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>14.6719</v>
+        <v>14.4585</v>
       </c>
       <c r="C80" t="n">
-        <v>2.90362</v>
+        <v>2.97178</v>
       </c>
       <c r="D80" t="n">
-        <v>26.8961</v>
+        <v>26.6889</v>
       </c>
       <c r="E80" t="n">
-        <v>3.30029</v>
+        <v>3.33353</v>
       </c>
       <c r="F80" t="n">
-        <v>3.84825</v>
+        <v>3.97567</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.05763</v>
+        <v>4.28587</v>
       </c>
       <c r="C81" t="n">
-        <v>2.93878</v>
+        <v>3.07526</v>
       </c>
       <c r="D81" t="n">
-        <v>28.4972</v>
+        <v>28.1774</v>
       </c>
       <c r="E81" t="n">
-        <v>3.3319</v>
+        <v>3.37197</v>
       </c>
       <c r="F81" t="n">
-        <v>3.94821</v>
+        <v>4.13435</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.17386</v>
+        <v>4.43335</v>
       </c>
       <c r="C82" t="n">
-        <v>3.02184</v>
+        <v>3.15321</v>
       </c>
       <c r="D82" t="n">
-        <v>29.8076</v>
+        <v>29.5737</v>
       </c>
       <c r="E82" t="n">
-        <v>3.38392</v>
+        <v>3.47398</v>
       </c>
       <c r="F82" t="n">
-        <v>4.09385</v>
+        <v>4.23917</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.29349</v>
+        <v>4.60962</v>
       </c>
       <c r="C83" t="n">
-        <v>3.04316</v>
+        <v>3.24338</v>
       </c>
       <c r="D83" t="n">
-        <v>31.3075</v>
+        <v>31.0904</v>
       </c>
       <c r="E83" t="n">
-        <v>3.42672</v>
+        <v>3.5171</v>
       </c>
       <c r="F83" t="n">
-        <v>4.24925</v>
+        <v>4.37951</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.47209</v>
+        <v>4.82671</v>
       </c>
       <c r="C84" t="n">
-        <v>3.15123</v>
+        <v>3.38824</v>
       </c>
       <c r="D84" t="n">
-        <v>32.7823</v>
+        <v>32.5898</v>
       </c>
       <c r="E84" t="n">
-        <v>3.50027</v>
+        <v>3.72471</v>
       </c>
       <c r="F84" t="n">
-        <v>4.47674</v>
+        <v>4.56687</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>4.67317</v>
+        <v>5.17477</v>
       </c>
       <c r="C85" t="n">
-        <v>3.28703</v>
+        <v>3.57789</v>
       </c>
       <c r="D85" t="n">
-        <v>34.3438</v>
+        <v>34.2006</v>
       </c>
       <c r="E85" t="n">
-        <v>3.55618</v>
+        <v>3.78645</v>
       </c>
       <c r="F85" t="n">
-        <v>4.52829</v>
+        <v>5.39578</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>4.96419</v>
+        <v>5.46407</v>
       </c>
       <c r="C86" t="n">
-        <v>3.49848</v>
+        <v>3.77597</v>
       </c>
       <c r="D86" t="n">
-        <v>35.9261</v>
+        <v>35.7776</v>
       </c>
       <c r="E86" t="n">
-        <v>3.70335</v>
+        <v>3.95935</v>
       </c>
       <c r="F86" t="n">
-        <v>4.8131</v>
+        <v>5.73718</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.3311</v>
+        <v>5.89791</v>
       </c>
       <c r="C87" t="n">
-        <v>3.74487</v>
+        <v>4.05833</v>
       </c>
       <c r="D87" t="n">
-        <v>37.651</v>
+        <v>37.5144</v>
       </c>
       <c r="E87" t="n">
-        <v>3.86507</v>
+        <v>4.10024</v>
       </c>
       <c r="F87" t="n">
-        <v>5.1968</v>
+        <v>6.16976</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>5.76384</v>
+        <v>6.3759</v>
       </c>
       <c r="C88" t="n">
-        <v>4.02605</v>
+        <v>4.41978</v>
       </c>
       <c r="D88" t="n">
-        <v>39.4748</v>
+        <v>39.3375</v>
       </c>
       <c r="E88" t="n">
-        <v>4.14829</v>
+        <v>4.41492</v>
       </c>
       <c r="F88" t="n">
-        <v>5.92552</v>
+        <v>5.86791</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>6.49998</v>
+        <v>7.02993</v>
       </c>
       <c r="C89" t="n">
-        <v>4.47256</v>
+        <v>4.89021</v>
       </c>
       <c r="D89" t="n">
-        <v>41.3749</v>
+        <v>41.1175</v>
       </c>
       <c r="E89" t="n">
-        <v>4.44771</v>
+        <v>4.76415</v>
       </c>
       <c r="F89" t="n">
-        <v>6.45405</v>
+        <v>6.49603</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.48227</v>
+        <v>7.87249</v>
       </c>
       <c r="C90" t="n">
-        <v>5.05063</v>
+        <v>5.46599</v>
       </c>
       <c r="D90" t="n">
-        <v>43.3295</v>
+        <v>43.0875</v>
       </c>
       <c r="E90" t="n">
-        <v>4.83543</v>
+        <v>5.20367</v>
       </c>
       <c r="F90" t="n">
-        <v>7.11286</v>
+        <v>7.22655</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.6875</v>
+        <v>9.047499999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>5.91537</v>
+        <v>6.36395</v>
       </c>
       <c r="D91" t="n">
-        <v>45.4409</v>
+        <v>45.0993</v>
       </c>
       <c r="E91" t="n">
-        <v>5.37762</v>
+        <v>5.82424</v>
       </c>
       <c r="F91" t="n">
-        <v>7.92667</v>
+        <v>8.14659</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.2694</v>
+        <v>10.4438</v>
       </c>
       <c r="C92" t="n">
-        <v>7.18629</v>
+        <v>7.62173</v>
       </c>
       <c r="D92" t="n">
-        <v>37.4108</v>
+        <v>37.0223</v>
       </c>
       <c r="E92" t="n">
-        <v>6.3119</v>
+        <v>3.90342</v>
       </c>
       <c r="F92" t="n">
-        <v>9.001189999999999</v>
+        <v>5.2732</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.1264</v>
+        <v>12.6239</v>
       </c>
       <c r="C93" t="n">
-        <v>9.31884</v>
+        <v>9.50764</v>
       </c>
       <c r="D93" t="n">
-        <v>38.568</v>
+        <v>38.2047</v>
       </c>
       <c r="E93" t="n">
-        <v>7.63617</v>
+        <v>4.08249</v>
       </c>
       <c r="F93" t="n">
-        <v>10.6999</v>
+        <v>5.58214</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.7631</v>
+        <v>15.8692</v>
       </c>
       <c r="C94" t="n">
-        <v>4.03718</v>
+        <v>3.99535</v>
       </c>
       <c r="D94" t="n">
-        <v>39.8292</v>
+        <v>39.4635</v>
       </c>
       <c r="E94" t="n">
-        <v>4.30748</v>
+        <v>4.23599</v>
       </c>
       <c r="F94" t="n">
-        <v>5.8221</v>
+        <v>5.90019</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>6.15554</v>
+        <v>6.14825</v>
       </c>
       <c r="C95" t="n">
-        <v>4.14518</v>
+        <v>4.14168</v>
       </c>
       <c r="D95" t="n">
-        <v>41.0767</v>
+        <v>40.7906</v>
       </c>
       <c r="E95" t="n">
-        <v>4.44786</v>
+        <v>4.3952</v>
       </c>
       <c r="F95" t="n">
-        <v>6.1816</v>
+        <v>6.06808</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.50307</v>
+        <v>6.49124</v>
       </c>
       <c r="C96" t="n">
-        <v>4.33307</v>
+        <v>4.32102</v>
       </c>
       <c r="D96" t="n">
-        <v>42.388</v>
+        <v>42.1068</v>
       </c>
       <c r="E96" t="n">
-        <v>4.60727</v>
+        <v>4.58789</v>
       </c>
       <c r="F96" t="n">
-        <v>6.40395</v>
+        <v>6.57835</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.80281</v>
+        <v>6.78754</v>
       </c>
       <c r="C97" t="n">
-        <v>4.46091</v>
+        <v>4.4716</v>
       </c>
       <c r="D97" t="n">
-        <v>43.7668</v>
+        <v>43.4885</v>
       </c>
       <c r="E97" t="n">
-        <v>4.76158</v>
+        <v>4.74391</v>
       </c>
       <c r="F97" t="n">
-        <v>6.73521</v>
+        <v>6.76478</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>7.10432</v>
+        <v>7.08231</v>
       </c>
       <c r="C98" t="n">
-        <v>4.67143</v>
+        <v>4.6403</v>
       </c>
       <c r="D98" t="n">
-        <v>45.2021</v>
+        <v>44.8815</v>
       </c>
       <c r="E98" t="n">
-        <v>4.97303</v>
+        <v>4.93676</v>
       </c>
       <c r="F98" t="n">
-        <v>7.0627</v>
+        <v>7.08579</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.4397</v>
+        <v>7.41674</v>
       </c>
       <c r="C99" t="n">
-        <v>4.84263</v>
+        <v>4.82048</v>
       </c>
       <c r="D99" t="n">
-        <v>46.7244</v>
+        <v>46.3545</v>
       </c>
       <c r="E99" t="n">
-        <v>5.11246</v>
+        <v>5.10813</v>
       </c>
       <c r="F99" t="n">
-        <v>7.72375</v>
+        <v>7.63941</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>8.765169999999999</v>
+        <v>7.76804</v>
       </c>
       <c r="C100" t="n">
-        <v>5.98969</v>
+        <v>5.05159</v>
       </c>
       <c r="D100" t="n">
-        <v>48.1053</v>
+        <v>47.9054</v>
       </c>
       <c r="E100" t="n">
-        <v>5.28801</v>
+        <v>5.33388</v>
       </c>
       <c r="F100" t="n">
-        <v>7.68061</v>
+        <v>7.98304</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>9.22048</v>
+        <v>8.097709999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>6.38356</v>
+        <v>5.24951</v>
       </c>
       <c r="D101" t="n">
-        <v>49.4534</v>
+        <v>49.3857</v>
       </c>
       <c r="E101" t="n">
-        <v>5.49552</v>
+        <v>5.49664</v>
       </c>
       <c r="F101" t="n">
-        <v>7.92688</v>
+        <v>8.319839999999999</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>9.75769</v>
+        <v>8.588800000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>6.86577</v>
+        <v>5.62447</v>
       </c>
       <c r="D102" t="n">
-        <v>51.2292</v>
+        <v>51.3156</v>
       </c>
       <c r="E102" t="n">
-        <v>5.74883</v>
+        <v>5.76781</v>
       </c>
       <c r="F102" t="n">
-        <v>8.36599</v>
+        <v>8.82053</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>10.3939</v>
+        <v>9.19885</v>
       </c>
       <c r="C103" t="n">
-        <v>7.50517</v>
+        <v>6.06517</v>
       </c>
       <c r="D103" t="n">
-        <v>52.9767</v>
+        <v>53.117</v>
       </c>
       <c r="E103" t="n">
-        <v>5.98504</v>
+        <v>6.06286</v>
       </c>
       <c r="F103" t="n">
-        <v>8.88481</v>
+        <v>9.45481</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>11.13</v>
+        <v>9.97222</v>
       </c>
       <c r="C104" t="n">
-        <v>8.21471</v>
+        <v>6.63774</v>
       </c>
       <c r="D104" t="n">
-        <v>54.8404</v>
+        <v>54.9856</v>
       </c>
       <c r="E104" t="n">
-        <v>6.37994</v>
+        <v>6.44554</v>
       </c>
       <c r="F104" t="n">
-        <v>9.73779</v>
+        <v>10.2378</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>12.1451</v>
+        <v>11.0334</v>
       </c>
       <c r="C105" t="n">
-        <v>9.076180000000001</v>
+        <v>7.50149</v>
       </c>
       <c r="D105" t="n">
-        <v>56.7975</v>
+        <v>56.894</v>
       </c>
       <c r="E105" t="n">
-        <v>6.89474</v>
+        <v>7.0046</v>
       </c>
       <c r="F105" t="n">
-        <v>11.0881</v>
+        <v>11.2224</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>13.5281</v>
+        <v>12.5331</v>
       </c>
       <c r="C106" t="n">
-        <v>10.2709</v>
+        <v>8.728579999999999</v>
       </c>
       <c r="D106" t="n">
-        <v>58.7306</v>
+        <v>58.8663</v>
       </c>
       <c r="E106" t="n">
-        <v>7.684</v>
+        <v>7.87794</v>
       </c>
       <c r="F106" t="n">
-        <v>12.614</v>
+        <v>12.6891</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>15.5592</v>
+        <v>14.5528</v>
       </c>
       <c r="C107" t="n">
-        <v>12.0588</v>
+        <v>10.5726</v>
       </c>
       <c r="D107" t="n">
-        <v>44.6807</v>
+        <v>44.7473</v>
       </c>
       <c r="E107" t="n">
-        <v>9.037319999999999</v>
+        <v>4.91215</v>
       </c>
       <c r="F107" t="n">
-        <v>14.5633</v>
+        <v>7.17289</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>18.6261</v>
+        <v>17.18</v>
       </c>
       <c r="C108" t="n">
-        <v>5.22081</v>
+        <v>4.74947</v>
       </c>
       <c r="D108" t="n">
-        <v>45.7839</v>
+        <v>45.8968</v>
       </c>
       <c r="E108" t="n">
-        <v>5.02168</v>
+        <v>5.01657</v>
       </c>
       <c r="F108" t="n">
-        <v>7.21261</v>
+        <v>7.53032</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.2131</v>
+        <v>21.9709</v>
       </c>
       <c r="C109" t="n">
-        <v>5.33154</v>
+        <v>4.85414</v>
       </c>
       <c r="D109" t="n">
-        <v>46.9648</v>
+        <v>47.0794</v>
       </c>
       <c r="E109" t="n">
-        <v>5.02895</v>
+        <v>5.15997</v>
       </c>
       <c r="F109" t="n">
-        <v>7.64342</v>
+        <v>7.74641</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>8.22003</v>
+        <v>7.65233</v>
       </c>
       <c r="C110" t="n">
-        <v>5.46931</v>
+        <v>4.93933</v>
       </c>
       <c r="D110" t="n">
-        <v>48.2127</v>
+        <v>48.3124</v>
       </c>
       <c r="E110" t="n">
-        <v>5.31783</v>
+        <v>5.24403</v>
       </c>
       <c r="F110" t="n">
-        <v>8.301769999999999</v>
+        <v>8.25329</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>8.870340000000001</v>
+        <v>7.97512</v>
       </c>
       <c r="C111" t="n">
-        <v>5.72365</v>
+        <v>5.1497</v>
       </c>
       <c r="D111" t="n">
-        <v>49.4325</v>
+        <v>49.5269</v>
       </c>
       <c r="E111" t="n">
-        <v>5.5507</v>
+        <v>5.38041</v>
       </c>
       <c r="F111" t="n">
-        <v>9.020580000000001</v>
+        <v>8.63862</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>9.232010000000001</v>
+        <v>8.12946</v>
       </c>
       <c r="C112" t="n">
-        <v>6.0686</v>
+        <v>5.33996</v>
       </c>
       <c r="D112" t="n">
-        <v>50.7821</v>
+        <v>50.9342</v>
       </c>
       <c r="E112" t="n">
-        <v>5.86782</v>
+        <v>5.55599</v>
       </c>
       <c r="F112" t="n">
-        <v>9.741669999999999</v>
+        <v>9.16719</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>9.73288</v>
+        <v>8.61464</v>
       </c>
       <c r="C113" t="n">
-        <v>6.39884</v>
+        <v>5.56838</v>
       </c>
       <c r="D113" t="n">
-        <v>52.1754</v>
+        <v>52.2787</v>
       </c>
       <c r="E113" t="n">
-        <v>6.22538</v>
+        <v>5.79371</v>
       </c>
       <c r="F113" t="n">
-        <v>10.2845</v>
+        <v>9.80378</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>10.1872</v>
+        <v>9.106909999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>6.70837</v>
+        <v>5.81022</v>
       </c>
       <c r="D114" t="n">
-        <v>53.6575</v>
+        <v>53.7558</v>
       </c>
       <c r="E114" t="n">
-        <v>6.61622</v>
+        <v>6.0388</v>
       </c>
       <c r="F114" t="n">
-        <v>10.746</v>
+        <v>10.3504</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>10.6667</v>
+        <v>9.627269999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>7.06398</v>
+        <v>6.22103</v>
       </c>
       <c r="D115" t="n">
-        <v>55.1606</v>
+        <v>55.3189</v>
       </c>
       <c r="E115" t="n">
-        <v>6.92451</v>
+        <v>6.39505</v>
       </c>
       <c r="F115" t="n">
-        <v>11.1871</v>
+        <v>11.0373</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>11.1609</v>
+        <v>10.3257</v>
       </c>
       <c r="C116" t="n">
-        <v>7.47305</v>
+        <v>6.697</v>
       </c>
       <c r="D116" t="n">
-        <v>56.8448</v>
+        <v>57.0115</v>
       </c>
       <c r="E116" t="n">
-        <v>7.24905</v>
+        <v>6.84799</v>
       </c>
       <c r="F116" t="n">
-        <v>11.6436</v>
+        <v>11.5982</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>11.7625</v>
+        <v>11.0944</v>
       </c>
       <c r="C117" t="n">
-        <v>8.019489999999999</v>
+        <v>7.27127</v>
       </c>
       <c r="D117" t="n">
-        <v>58.6975</v>
+        <v>58.812</v>
       </c>
       <c r="E117" t="n">
-        <v>7.62082</v>
+        <v>7.32368</v>
       </c>
       <c r="F117" t="n">
-        <v>12.1189</v>
+        <v>12.0806</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>12.4873</v>
+        <v>11.8067</v>
       </c>
       <c r="C118" t="n">
-        <v>8.63923</v>
+        <v>7.85521</v>
       </c>
       <c r="D118" t="n">
-        <v>60.5556</v>
+        <v>60.6743</v>
       </c>
       <c r="E118" t="n">
-        <v>8.07301</v>
+        <v>7.8291</v>
       </c>
       <c r="F118" t="n">
-        <v>12.7916</v>
+        <v>12.7202</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>13.3985</v>
+        <v>12.7681</v>
       </c>
       <c r="C119" t="n">
-        <v>9.393269999999999</v>
+        <v>8.558719999999999</v>
       </c>
       <c r="D119" t="n">
-        <v>62.5336</v>
+        <v>62.6872</v>
       </c>
       <c r="E119" t="n">
-        <v>8.61032</v>
+        <v>8.32837</v>
       </c>
       <c r="F119" t="n">
-        <v>13.5828</v>
+        <v>13.6549</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.6186</v>
+        <v>13.9484</v>
       </c>
       <c r="C120" t="n">
-        <v>10.4719</v>
+        <v>9.650029999999999</v>
       </c>
       <c r="D120" t="n">
-        <v>64.565</v>
+        <v>64.7586</v>
       </c>
       <c r="E120" t="n">
-        <v>9.339370000000001</v>
+        <v>9.22847</v>
       </c>
       <c r="F120" t="n">
-        <v>14.6137</v>
+        <v>14.6752</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>16.2627</v>
+        <v>15.7262</v>
       </c>
       <c r="C121" t="n">
-        <v>12.0278</v>
+        <v>11.2735</v>
       </c>
       <c r="D121" t="n">
-        <v>47.9068</v>
+        <v>48.0103</v>
       </c>
       <c r="E121" t="n">
-        <v>10.4485</v>
+        <v>6.71203</v>
       </c>
       <c r="F121" t="n">
-        <v>16.1601</v>
+        <v>10.7273</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>18.7529</v>
+        <v>18.0047</v>
       </c>
       <c r="C122" t="n">
-        <v>7.50612</v>
+        <v>6.69394</v>
       </c>
       <c r="D122" t="n">
-        <v>49.0532</v>
+        <v>48.8308</v>
       </c>
       <c r="E122" t="n">
-        <v>12.2857</v>
+        <v>6.89083</v>
       </c>
       <c r="F122" t="n">
-        <v>18.6131</v>
+        <v>10.0245</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.7559</v>
+        <v>22.2498</v>
       </c>
       <c r="C123" t="n">
-        <v>6.91675</v>
+        <v>6.80776</v>
       </c>
       <c r="D123" t="n">
-        <v>50.1301</v>
+        <v>50.326</v>
       </c>
       <c r="E123" t="n">
-        <v>7.53731</v>
+        <v>8.17972</v>
       </c>
       <c r="F123" t="n">
-        <v>10.8123</v>
+        <v>11.3078</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>10.2114</v>
+        <v>9.84943</v>
       </c>
       <c r="C124" t="n">
-        <v>6.98982</v>
+        <v>6.71001</v>
       </c>
       <c r="D124" t="n">
-        <v>51.3771</v>
+        <v>51.529</v>
       </c>
       <c r="E124" t="n">
-        <v>7.4035</v>
+        <v>7.0577</v>
       </c>
       <c r="F124" t="n">
-        <v>11.1014</v>
+        <v>11.0964</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.4869</v>
+        <v>10.1707</v>
       </c>
       <c r="C125" t="n">
-        <v>6.98785</v>
+        <v>6.79008</v>
       </c>
       <c r="D125" t="n">
-        <v>52.5962</v>
+        <v>52.7638</v>
       </c>
       <c r="E125" t="n">
-        <v>7.63423</v>
+        <v>7.8565</v>
       </c>
       <c r="F125" t="n">
-        <v>11.275</v>
+        <v>11.8413</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.8506</v>
+        <v>10.5291</v>
       </c>
       <c r="C126" t="n">
-        <v>7.3165</v>
+        <v>7.22026</v>
       </c>
       <c r="D126" t="n">
-        <v>53.9136</v>
+        <v>54.0229</v>
       </c>
       <c r="E126" t="n">
-        <v>8.301880000000001</v>
+        <v>7.7023</v>
       </c>
       <c r="F126" t="n">
-        <v>11.6998</v>
+        <v>11.8765</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>11.0039</v>
+        <v>10.7314</v>
       </c>
       <c r="C127" t="n">
-        <v>7.30056</v>
+        <v>7.2375</v>
       </c>
       <c r="D127" t="n">
-        <v>55.3509</v>
+        <v>55.5312</v>
       </c>
       <c r="E127" t="n">
-        <v>7.70689</v>
+        <v>8.09361</v>
       </c>
       <c r="F127" t="n">
-        <v>12.3571</v>
+        <v>11.9978</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>11.2007</v>
+        <v>11.0233</v>
       </c>
       <c r="C128" t="n">
-        <v>7.65687</v>
+        <v>7.74624</v>
       </c>
       <c r="D128" t="n">
-        <v>56.7407</v>
+        <v>56.9382</v>
       </c>
       <c r="E128" t="n">
-        <v>8.612740000000001</v>
+        <v>8.343120000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>12.8962</v>
+        <v>12.8306</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.4866</v>
+        <v>11.345</v>
       </c>
       <c r="C129" t="n">
-        <v>7.78501</v>
+        <v>7.62392</v>
       </c>
       <c r="D129" t="n">
-        <v>58.3774</v>
+        <v>58.5335</v>
       </c>
       <c r="E129" t="n">
-        <v>8.23837</v>
+        <v>8.37374</v>
       </c>
       <c r="F129" t="n">
-        <v>12.8124</v>
+        <v>13.1034</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.9626</v>
+        <v>11.7186</v>
       </c>
       <c r="C130" t="n">
-        <v>8.35186</v>
+        <v>7.80518</v>
       </c>
       <c r="D130" t="n">
-        <v>59.967</v>
+        <v>60.1687</v>
       </c>
       <c r="E130" t="n">
-        <v>8.67347</v>
+        <v>8.58437</v>
       </c>
       <c r="F130" t="n">
-        <v>13.412</v>
+        <v>13.5512</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>12.5859</v>
+        <v>11.8493</v>
       </c>
       <c r="C131" t="n">
-        <v>8.327959999999999</v>
+        <v>8.209709999999999</v>
       </c>
       <c r="D131" t="n">
-        <v>61.7917</v>
+        <v>62.0324</v>
       </c>
       <c r="E131" t="n">
-        <v>9.372389999999999</v>
+        <v>9.141999999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>14.124</v>
+        <v>14.1408</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>13.3208</v>
+        <v>12.9416</v>
       </c>
       <c r="C132" t="n">
-        <v>9.084</v>
+        <v>8.810890000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>63.6534</v>
+        <v>63.816</v>
       </c>
       <c r="E132" t="n">
-        <v>9.19336</v>
+        <v>9.47452</v>
       </c>
       <c r="F132" t="n">
-        <v>14.5981</v>
+        <v>14.8407</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.7522</v>
+        <v>13.2296</v>
       </c>
       <c r="C133" t="n">
-        <v>9.838789999999999</v>
+        <v>9.434559999999999</v>
       </c>
       <c r="D133" t="n">
-        <v>65.6467</v>
+        <v>65.8425</v>
       </c>
       <c r="E133" t="n">
-        <v>9.63247</v>
+        <v>9.97958</v>
       </c>
       <c r="F133" t="n">
-        <v>15.1921</v>
+        <v>15.4596</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>15.014</v>
+        <v>15.0924</v>
       </c>
       <c r="C134" t="n">
-        <v>10.6415</v>
+        <v>10.2422</v>
       </c>
       <c r="D134" t="n">
-        <v>67.7664</v>
+        <v>67.76909999999999</v>
       </c>
       <c r="E134" t="n">
-        <v>10.4322</v>
+        <v>10.4361</v>
       </c>
       <c r="F134" t="n">
-        <v>16.2676</v>
+        <v>16.3247</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.559</v>
+        <v>16.4242</v>
       </c>
       <c r="C135" t="n">
-        <v>12.4761</v>
+        <v>11.852</v>
       </c>
       <c r="D135" t="n">
-        <v>49.6578</v>
+        <v>49.7855</v>
       </c>
       <c r="E135" t="n">
-        <v>11.4081</v>
+        <v>14.1447</v>
       </c>
       <c r="F135" t="n">
-        <v>18.0448</v>
+        <v>17.2766</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>19.2612</v>
+        <v>18.616</v>
       </c>
       <c r="C136" t="n">
-        <v>13.1204</v>
+        <v>13.3655</v>
       </c>
       <c r="D136" t="n">
-        <v>50.7373</v>
+        <v>50.9503</v>
       </c>
       <c r="E136" t="n">
-        <v>12.3435</v>
+        <v>14.0585</v>
       </c>
       <c r="F136" t="n">
-        <v>19.6939</v>
+        <v>17.5345</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>22.6014</v>
+        <v>22.6389</v>
       </c>
       <c r="C137" t="n">
-        <v>13.5367</v>
+        <v>13.535</v>
       </c>
       <c r="D137" t="n">
-        <v>51.9473</v>
+        <v>51.8754</v>
       </c>
       <c r="E137" t="n">
-        <v>13.8843</v>
+        <v>14.3655</v>
       </c>
       <c r="F137" t="n">
-        <v>17.897</v>
+        <v>17.9603</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.9742</v>
+        <v>16.7457</v>
       </c>
       <c r="C138" t="n">
-        <v>13.7463</v>
+        <v>13.5564</v>
       </c>
       <c r="D138" t="n">
-        <v>53.1039</v>
+        <v>53.2874</v>
       </c>
       <c r="E138" t="n">
-        <v>13.9762</v>
+        <v>14.4569</v>
       </c>
       <c r="F138" t="n">
-        <v>18.1117</v>
+        <v>18.1443</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>16.5461</v>
+        <v>17.1362</v>
       </c>
       <c r="C139" t="n">
-        <v>13.8136</v>
+        <v>13.8541</v>
       </c>
       <c r="D139" t="n">
-        <v>54.3692</v>
+        <v>54.398</v>
       </c>
       <c r="E139" t="n">
-        <v>14.0781</v>
+        <v>14.6347</v>
       </c>
       <c r="F139" t="n">
-        <v>18.4397</v>
+        <v>18.5035</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>17.3</v>
+        <v>17.1093</v>
       </c>
       <c r="C140" t="n">
-        <v>13.8876</v>
+        <v>13.7207</v>
       </c>
       <c r="D140" t="n">
-        <v>55.7125</v>
+        <v>55.7874</v>
       </c>
       <c r="E140" t="n">
-        <v>14.509</v>
+        <v>14.5716</v>
       </c>
       <c r="F140" t="n">
-        <v>18.8724</v>
+        <v>18.1119</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.8259</v>
+        <v>17.4395</v>
       </c>
       <c r="C141" t="n">
-        <v>13.9385</v>
+        <v>13.9211</v>
       </c>
       <c r="D141" t="n">
-        <v>57.0971</v>
+        <v>57.2555</v>
       </c>
       <c r="E141" t="n">
-        <v>15.0045</v>
+        <v>14.7049</v>
       </c>
       <c r="F141" t="n">
-        <v>19.1068</v>
+        <v>19.1348</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>17.4165</v>
+        <v>17.5556</v>
       </c>
       <c r="C142" t="n">
-        <v>14.0388</v>
+        <v>13.9938</v>
       </c>
       <c r="D142" t="n">
-        <v>58.5691</v>
+        <v>58.6281</v>
       </c>
       <c r="E142" t="n">
-        <v>14.8986</v>
+        <v>14.1599</v>
       </c>
       <c r="F142" t="n">
-        <v>18.6081</v>
+        <v>19.4431</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.5183</v>
+        <v>17.8801</v>
       </c>
       <c r="C143" t="n">
-        <v>14.1973</v>
+        <v>14.3029</v>
       </c>
       <c r="D143" t="n">
-        <v>59.9724</v>
+        <v>60.313</v>
       </c>
       <c r="E143" t="n">
-        <v>15.1353</v>
+        <v>15.721</v>
       </c>
       <c r="F143" t="n">
-        <v>19.8767</v>
+        <v>19.5459</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered unsuccessful looukp.xlsx
+++ b/clang-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.72035</v>
+        <v>2.72755</v>
       </c>
       <c r="C2" t="n">
-        <v>2.07799</v>
+        <v>2.08391</v>
       </c>
       <c r="D2" t="n">
-        <v>12.58</v>
+        <v>12.4804</v>
       </c>
       <c r="E2" t="n">
-        <v>2.62571</v>
+        <v>2.60665</v>
       </c>
       <c r="F2" t="n">
-        <v>2.43768</v>
+        <v>2.39732</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.78625</v>
+        <v>2.76152</v>
       </c>
       <c r="C3" t="n">
-        <v>2.17014</v>
+        <v>2.17862</v>
       </c>
       <c r="D3" t="n">
-        <v>12.9871</v>
+        <v>13.0156</v>
       </c>
       <c r="E3" t="n">
-        <v>2.71159</v>
+        <v>2.69982</v>
       </c>
       <c r="F3" t="n">
-        <v>2.52631</v>
+        <v>2.50345</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.82768</v>
+        <v>2.86374</v>
       </c>
       <c r="C4" t="n">
-        <v>2.34636</v>
+        <v>2.36135</v>
       </c>
       <c r="D4" t="n">
-        <v>13.4817</v>
+        <v>13.5246</v>
       </c>
       <c r="E4" t="n">
-        <v>2.78141</v>
+        <v>2.78778</v>
       </c>
       <c r="F4" t="n">
-        <v>2.65791</v>
+        <v>2.64837</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.20713</v>
+        <v>3.22342</v>
       </c>
       <c r="C5" t="n">
-        <v>2.69226</v>
+        <v>2.74195</v>
       </c>
       <c r="D5" t="n">
-        <v>13.998</v>
+        <v>14.0553</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9206</v>
+        <v>2.93558</v>
       </c>
       <c r="F5" t="n">
-        <v>2.80208</v>
+        <v>2.79766</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.04414</v>
+        <v>4.05344</v>
       </c>
       <c r="C6" t="n">
-        <v>3.56348</v>
+        <v>3.52777</v>
       </c>
       <c r="D6" t="n">
-        <v>14.5961</v>
+        <v>14.6348</v>
       </c>
       <c r="E6" t="n">
-        <v>3.13637</v>
+        <v>3.13062</v>
       </c>
       <c r="F6" t="n">
-        <v>2.97361</v>
+        <v>3.02557</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.58402</v>
+        <v>6.59641</v>
       </c>
       <c r="C7" t="n">
-        <v>5.26056</v>
+        <v>5.2575</v>
       </c>
       <c r="D7" t="n">
-        <v>10.1943</v>
+        <v>10.2817</v>
       </c>
       <c r="E7" t="n">
-        <v>2.38015</v>
+        <v>2.36193</v>
       </c>
       <c r="F7" t="n">
-        <v>2.12808</v>
+        <v>2.12676</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.543480000000001</v>
+        <v>9.53346</v>
       </c>
       <c r="C8" t="n">
-        <v>1.7441</v>
+        <v>1.75145</v>
       </c>
       <c r="D8" t="n">
-        <v>10.869</v>
+        <v>10.8902</v>
       </c>
       <c r="E8" t="n">
-        <v>2.39696</v>
+        <v>2.37643</v>
       </c>
       <c r="F8" t="n">
-        <v>2.14919</v>
+        <v>2.17447</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.8565</v>
+        <v>13.8528</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7647</v>
+        <v>1.77111</v>
       </c>
       <c r="D9" t="n">
-        <v>11.5094</v>
+        <v>11.5295</v>
       </c>
       <c r="E9" t="n">
-        <v>2.41603</v>
+        <v>2.40063</v>
       </c>
       <c r="F9" t="n">
-        <v>2.18098</v>
+        <v>2.17908</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.62346</v>
+        <v>2.6411</v>
       </c>
       <c r="C10" t="n">
-        <v>1.80183</v>
+        <v>1.80895</v>
       </c>
       <c r="D10" t="n">
-        <v>12.1792</v>
+        <v>12.146</v>
       </c>
       <c r="E10" t="n">
-        <v>2.44457</v>
+        <v>2.42676</v>
       </c>
       <c r="F10" t="n">
-        <v>2.22212</v>
+        <v>2.22508</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.69121</v>
+        <v>2.71632</v>
       </c>
       <c r="C11" t="n">
-        <v>1.83837</v>
+        <v>1.85263</v>
       </c>
       <c r="D11" t="n">
-        <v>12.7438</v>
+        <v>12.7265</v>
       </c>
       <c r="E11" t="n">
-        <v>2.47504</v>
+        <v>2.44808</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2479</v>
+        <v>2.25793</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.69998</v>
+        <v>2.72589</v>
       </c>
       <c r="C12" t="n">
-        <v>1.87667</v>
+        <v>1.88837</v>
       </c>
       <c r="D12" t="n">
-        <v>13.2827</v>
+        <v>13.2219</v>
       </c>
       <c r="E12" t="n">
-        <v>2.50051</v>
+        <v>2.48119</v>
       </c>
       <c r="F12" t="n">
-        <v>2.29679</v>
+        <v>2.30265</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.68372</v>
+        <v>2.69139</v>
       </c>
       <c r="C13" t="n">
-        <v>1.92185</v>
+        <v>1.93082</v>
       </c>
       <c r="D13" t="n">
-        <v>13.7599</v>
+        <v>13.7065</v>
       </c>
       <c r="E13" t="n">
-        <v>2.51813</v>
+        <v>2.50211</v>
       </c>
       <c r="F13" t="n">
-        <v>2.31044</v>
+        <v>2.3146</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.77216</v>
+        <v>2.77539</v>
       </c>
       <c r="C14" t="n">
-        <v>2.03881</v>
+        <v>2.03885</v>
       </c>
       <c r="D14" t="n">
-        <v>14.2335</v>
+        <v>14.2065</v>
       </c>
       <c r="E14" t="n">
-        <v>2.56088</v>
+        <v>2.53238</v>
       </c>
       <c r="F14" t="n">
-        <v>2.39445</v>
+        <v>2.37188</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.89731</v>
+        <v>2.90316</v>
       </c>
       <c r="C15" t="n">
-        <v>2.11549</v>
+        <v>2.11694</v>
       </c>
       <c r="D15" t="n">
-        <v>14.6558</v>
+        <v>14.5902</v>
       </c>
       <c r="E15" t="n">
-        <v>2.61587</v>
+        <v>2.58659</v>
       </c>
       <c r="F15" t="n">
-        <v>2.47602</v>
+        <v>2.44677</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.97056</v>
+        <v>2.96831</v>
       </c>
       <c r="C16" t="n">
-        <v>2.24897</v>
+        <v>2.24262</v>
       </c>
       <c r="D16" t="n">
-        <v>15.0577</v>
+        <v>14.9823</v>
       </c>
       <c r="E16" t="n">
-        <v>2.67076</v>
+        <v>2.6322</v>
       </c>
       <c r="F16" t="n">
-        <v>2.54209</v>
+        <v>2.49501</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.18098</v>
+        <v>3.16623</v>
       </c>
       <c r="C17" t="n">
-        <v>2.40396</v>
+        <v>2.40356</v>
       </c>
       <c r="D17" t="n">
-        <v>15.4588</v>
+        <v>15.409</v>
       </c>
       <c r="E17" t="n">
-        <v>2.75316</v>
+        <v>2.70823</v>
       </c>
       <c r="F17" t="n">
-        <v>2.63555</v>
+        <v>2.5844</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.55934</v>
+        <v>3.55794</v>
       </c>
       <c r="C18" t="n">
-        <v>2.69843</v>
+        <v>2.69512</v>
       </c>
       <c r="D18" t="n">
-        <v>15.8709</v>
+        <v>15.7956</v>
       </c>
       <c r="E18" t="n">
-        <v>2.86826</v>
+        <v>2.82752</v>
       </c>
       <c r="F18" t="n">
-        <v>2.80797</v>
+        <v>2.76597</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.14686</v>
+        <v>4.14325</v>
       </c>
       <c r="C19" t="n">
-        <v>3.30651</v>
+        <v>3.29564</v>
       </c>
       <c r="D19" t="n">
-        <v>16.2648</v>
+        <v>16.2291</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0571</v>
+        <v>3.01358</v>
       </c>
       <c r="F19" t="n">
-        <v>3.01716</v>
+        <v>2.97945</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.23738</v>
+        <v>5.22292</v>
       </c>
       <c r="C20" t="n">
-        <v>4.24999</v>
+        <v>4.26734</v>
       </c>
       <c r="D20" t="n">
-        <v>16.6689</v>
+        <v>16.6184</v>
       </c>
       <c r="E20" t="n">
-        <v>3.43205</v>
+        <v>3.42697</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4459</v>
+        <v>3.40042</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.97224</v>
+        <v>6.9686</v>
       </c>
       <c r="C21" t="n">
-        <v>5.51899</v>
+        <v>5.51017</v>
       </c>
       <c r="D21" t="n">
-        <v>11.7971</v>
+        <v>11.7886</v>
       </c>
       <c r="E21" t="n">
-        <v>2.42143</v>
+        <v>2.38795</v>
       </c>
       <c r="F21" t="n">
-        <v>2.24268</v>
+        <v>2.20456</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.325419999999999</v>
+        <v>9.333909999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>1.81846</v>
+        <v>1.81384</v>
       </c>
       <c r="D22" t="n">
-        <v>12.3245</v>
+        <v>12.3354</v>
       </c>
       <c r="E22" t="n">
-        <v>2.44584</v>
+        <v>2.41503</v>
       </c>
       <c r="F22" t="n">
-        <v>2.28261</v>
+        <v>2.23781</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.5895</v>
+        <v>12.5956</v>
       </c>
       <c r="C23" t="n">
         <v>1.83812</v>
       </c>
       <c r="D23" t="n">
-        <v>12.8156</v>
+        <v>12.8283</v>
       </c>
       <c r="E23" t="n">
-        <v>2.46075</v>
+        <v>2.43369</v>
       </c>
       <c r="F23" t="n">
-        <v>2.29669</v>
+        <v>2.26902</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.73903</v>
+        <v>2.73072</v>
       </c>
       <c r="C24" t="n">
-        <v>1.89221</v>
+        <v>1.87798</v>
       </c>
       <c r="D24" t="n">
-        <v>13.3423</v>
+        <v>13.3484</v>
       </c>
       <c r="E24" t="n">
-        <v>2.48835</v>
+        <v>2.45704</v>
       </c>
       <c r="F24" t="n">
-        <v>2.35759</v>
+        <v>2.30332</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.79217</v>
+        <v>2.76256</v>
       </c>
       <c r="C25" t="n">
-        <v>1.92376</v>
+        <v>1.90464</v>
       </c>
       <c r="D25" t="n">
-        <v>13.7909</v>
+        <v>13.8121</v>
       </c>
       <c r="E25" t="n">
-        <v>2.51189</v>
+        <v>2.48714</v>
       </c>
       <c r="F25" t="n">
-        <v>2.40298</v>
+        <v>2.34363</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.84291</v>
+        <v>2.84731</v>
       </c>
       <c r="C26" t="n">
-        <v>1.95554</v>
+        <v>1.95539</v>
       </c>
       <c r="D26" t="n">
-        <v>14.1962</v>
+        <v>14.2004</v>
       </c>
       <c r="E26" t="n">
-        <v>2.55071</v>
+        <v>2.51868</v>
       </c>
       <c r="F26" t="n">
-        <v>2.45635</v>
+        <v>2.39043</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.93582</v>
+        <v>2.93299</v>
       </c>
       <c r="C27" t="n">
-        <v>1.9951</v>
+        <v>1.98952</v>
       </c>
       <c r="D27" t="n">
-        <v>14.6679</v>
+        <v>14.6754</v>
       </c>
       <c r="E27" t="n">
-        <v>2.57989</v>
+        <v>2.54901</v>
       </c>
       <c r="F27" t="n">
-        <v>2.51042</v>
+        <v>2.43593</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.01206</v>
+        <v>3.01015</v>
       </c>
       <c r="C28" t="n">
-        <v>2.08367</v>
+        <v>2.05676</v>
       </c>
       <c r="D28" t="n">
-        <v>15.121</v>
+        <v>15.1426</v>
       </c>
       <c r="E28" t="n">
-        <v>2.62268</v>
+        <v>2.59801</v>
       </c>
       <c r="F28" t="n">
-        <v>2.58875</v>
+        <v>2.51368</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.15368</v>
+        <v>3.1516</v>
       </c>
       <c r="C29" t="n">
-        <v>2.19089</v>
+        <v>2.18176</v>
       </c>
       <c r="D29" t="n">
-        <v>15.5556</v>
+        <v>15.558</v>
       </c>
       <c r="E29" t="n">
-        <v>2.68377</v>
+        <v>2.64786</v>
       </c>
       <c r="F29" t="n">
-        <v>2.67331</v>
+        <v>2.60794</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.32952</v>
+        <v>3.31774</v>
       </c>
       <c r="C30" t="n">
-        <v>2.32763</v>
+        <v>2.30927</v>
       </c>
       <c r="D30" t="n">
-        <v>15.9894</v>
+        <v>16.0001</v>
       </c>
       <c r="E30" t="n">
-        <v>2.74206</v>
+        <v>2.71945</v>
       </c>
       <c r="F30" t="n">
-        <v>2.76802</v>
+        <v>2.70699</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.57213</v>
+        <v>3.57116</v>
       </c>
       <c r="C31" t="n">
-        <v>2.50949</v>
+        <v>2.4952</v>
       </c>
       <c r="D31" t="n">
-        <v>16.3792</v>
+        <v>16.389</v>
       </c>
       <c r="E31" t="n">
-        <v>2.81134</v>
+        <v>2.78823</v>
       </c>
       <c r="F31" t="n">
-        <v>2.855</v>
+        <v>2.79637</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.00238</v>
+        <v>4.00247</v>
       </c>
       <c r="C32" t="n">
-        <v>2.77285</v>
+        <v>2.7598</v>
       </c>
       <c r="D32" t="n">
-        <v>16.6877</v>
+        <v>16.7158</v>
       </c>
       <c r="E32" t="n">
-        <v>2.92459</v>
+        <v>2.9071</v>
       </c>
       <c r="F32" t="n">
-        <v>3.01283</v>
+        <v>2.94091</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.71082</v>
+        <v>4.7188</v>
       </c>
       <c r="C33" t="n">
-        <v>3.32028</v>
+        <v>3.31339</v>
       </c>
       <c r="D33" t="n">
-        <v>17.1523</v>
+        <v>17.1536</v>
       </c>
       <c r="E33" t="n">
-        <v>3.13671</v>
+        <v>3.11609</v>
       </c>
       <c r="F33" t="n">
-        <v>3.26005</v>
+        <v>3.1995</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.72072</v>
+        <v>5.7299</v>
       </c>
       <c r="C34" t="n">
-        <v>4.12695</v>
+        <v>4.11598</v>
       </c>
       <c r="D34" t="n">
-        <v>17.5477</v>
+        <v>17.5742</v>
       </c>
       <c r="E34" t="n">
-        <v>3.55054</v>
+        <v>3.52667</v>
       </c>
       <c r="F34" t="n">
-        <v>3.69061</v>
+        <v>3.57958</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.24307</v>
+        <v>7.24897</v>
       </c>
       <c r="C35" t="n">
-        <v>5.24706</v>
+        <v>5.24278</v>
       </c>
       <c r="D35" t="n">
-        <v>12.2077</v>
+        <v>12.2122</v>
       </c>
       <c r="E35" t="n">
-        <v>2.43909</v>
+        <v>2.41466</v>
       </c>
       <c r="F35" t="n">
-        <v>2.35322</v>
+        <v>2.30593</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.47611</v>
+        <v>9.469290000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>6.90491</v>
+        <v>6.89939</v>
       </c>
       <c r="D36" t="n">
-        <v>12.7143</v>
+        <v>12.7127</v>
       </c>
       <c r="E36" t="n">
-        <v>2.45708</v>
+        <v>2.43404</v>
       </c>
       <c r="F36" t="n">
-        <v>2.39745</v>
+        <v>2.3408</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.1075</v>
+        <v>13.1</v>
       </c>
       <c r="C37" t="n">
-        <v>1.86517</v>
+        <v>1.85369</v>
       </c>
       <c r="D37" t="n">
-        <v>13.1782</v>
+        <v>13.1608</v>
       </c>
       <c r="E37" t="n">
-        <v>2.48568</v>
+        <v>2.46231</v>
       </c>
       <c r="F37" t="n">
-        <v>2.42512</v>
+        <v>2.41302</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.81644</v>
+        <v>2.81885</v>
       </c>
       <c r="C38" t="n">
-        <v>1.89582</v>
+        <v>1.87688</v>
       </c>
       <c r="D38" t="n">
-        <v>13.6861</v>
+        <v>13.6728</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5116</v>
+        <v>2.48717</v>
       </c>
       <c r="F38" t="n">
-        <v>2.48673</v>
+        <v>2.43316</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.85281</v>
+        <v>2.84997</v>
       </c>
       <c r="C39" t="n">
-        <v>1.94924</v>
+        <v>1.92491</v>
       </c>
       <c r="D39" t="n">
-        <v>14.1652</v>
+        <v>14.1529</v>
       </c>
       <c r="E39" t="n">
-        <v>2.54465</v>
+        <v>2.5213</v>
       </c>
       <c r="F39" t="n">
-        <v>2.54162</v>
+        <v>2.51929</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.93425</v>
+        <v>2.93966</v>
       </c>
       <c r="C40" t="n">
-        <v>1.99362</v>
+        <v>1.97417</v>
       </c>
       <c r="D40" t="n">
-        <v>14.5857</v>
+        <v>14.5774</v>
       </c>
       <c r="E40" t="n">
-        <v>2.57309</v>
+        <v>2.54635</v>
       </c>
       <c r="F40" t="n">
-        <v>2.61773</v>
+        <v>2.56408</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.01031</v>
+        <v>3.01839</v>
       </c>
       <c r="C41" t="n">
-        <v>2.04471</v>
+        <v>2.03866</v>
       </c>
       <c r="D41" t="n">
-        <v>15.0273</v>
+        <v>15.0096</v>
       </c>
       <c r="E41" t="n">
-        <v>2.60643</v>
+        <v>2.58234</v>
       </c>
       <c r="F41" t="n">
-        <v>2.66731</v>
+        <v>2.60822</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.08407</v>
+        <v>3.07656</v>
       </c>
       <c r="C42" t="n">
-        <v>2.10542</v>
+        <v>2.09566</v>
       </c>
       <c r="D42" t="n">
-        <v>15.4458</v>
+        <v>15.4474</v>
       </c>
       <c r="E42" t="n">
-        <v>2.64934</v>
+        <v>2.61999</v>
       </c>
       <c r="F42" t="n">
-        <v>2.71981</v>
+        <v>2.6825</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.24263</v>
+        <v>3.25173</v>
       </c>
       <c r="C43" t="n">
-        <v>2.20154</v>
+        <v>2.19741</v>
       </c>
       <c r="D43" t="n">
-        <v>15.9032</v>
+        <v>15.8965</v>
       </c>
       <c r="E43" t="n">
-        <v>2.70373</v>
+        <v>2.67422</v>
       </c>
       <c r="F43" t="n">
-        <v>2.80497</v>
+        <v>2.7628</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.43074</v>
+        <v>3.43132</v>
       </c>
       <c r="C44" t="n">
-        <v>2.33667</v>
+        <v>2.32999</v>
       </c>
       <c r="D44" t="n">
-        <v>16.3055</v>
+        <v>16.2863</v>
       </c>
       <c r="E44" t="n">
-        <v>2.77496</v>
+        <v>2.75511</v>
       </c>
       <c r="F44" t="n">
-        <v>2.92496</v>
+        <v>2.86434</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.68513</v>
+        <v>3.683</v>
       </c>
       <c r="C45" t="n">
-        <v>2.58882</v>
+        <v>2.58004</v>
       </c>
       <c r="D45" t="n">
-        <v>16.6797</v>
+        <v>16.6708</v>
       </c>
       <c r="E45" t="n">
-        <v>2.86258</v>
+        <v>2.84701</v>
       </c>
       <c r="F45" t="n">
-        <v>3.04138</v>
+        <v>2.97089</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.0533</v>
+        <v>4.05174</v>
       </c>
       <c r="C46" t="n">
-        <v>2.9023</v>
+        <v>2.89019</v>
       </c>
       <c r="D46" t="n">
-        <v>17.0875</v>
+        <v>17.0685</v>
       </c>
       <c r="E46" t="n">
-        <v>3.00411</v>
+        <v>2.95853</v>
       </c>
       <c r="F46" t="n">
-        <v>3.19436</v>
+        <v>3.1342</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.6571</v>
+        <v>4.66071</v>
       </c>
       <c r="C47" t="n">
-        <v>3.35803</v>
+        <v>3.34913</v>
       </c>
       <c r="D47" t="n">
-        <v>17.4971</v>
+        <v>17.5056</v>
       </c>
       <c r="E47" t="n">
-        <v>3.23302</v>
+        <v>3.17461</v>
       </c>
       <c r="F47" t="n">
-        <v>3.46132</v>
+        <v>3.36331</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.44295</v>
+        <v>5.45153</v>
       </c>
       <c r="C48" t="n">
-        <v>4.03346</v>
+        <v>4.03094</v>
       </c>
       <c r="D48" t="n">
-        <v>17.9456</v>
+        <v>17.9588</v>
       </c>
       <c r="E48" t="n">
-        <v>3.60964</v>
+        <v>3.54427</v>
       </c>
       <c r="F48" t="n">
-        <v>3.83523</v>
+        <v>3.74655</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.58218</v>
+        <v>6.58532</v>
       </c>
       <c r="C49" t="n">
-        <v>4.97266</v>
+        <v>4.96857</v>
       </c>
       <c r="D49" t="n">
-        <v>18.4079</v>
+        <v>18.3951</v>
       </c>
       <c r="E49" t="n">
-        <v>4.17052</v>
+        <v>4.11364</v>
       </c>
       <c r="F49" t="n">
-        <v>4.39294</v>
+        <v>4.29365</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.52908</v>
+        <v>8.5306</v>
       </c>
       <c r="C50" t="n">
-        <v>6.48311</v>
+        <v>6.46868</v>
       </c>
       <c r="D50" t="n">
-        <v>12.8605</v>
+        <v>12.8337</v>
       </c>
       <c r="E50" t="n">
-        <v>2.49602</v>
+        <v>2.5172</v>
       </c>
       <c r="F50" t="n">
-        <v>2.5981</v>
+        <v>2.7736</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>11.145</v>
+        <v>11.1504</v>
       </c>
       <c r="C51" t="n">
-        <v>1.97497</v>
+        <v>2.14441</v>
       </c>
       <c r="D51" t="n">
-        <v>13.3109</v>
+        <v>13.2871</v>
       </c>
       <c r="E51" t="n">
-        <v>2.50783</v>
+        <v>2.52756</v>
       </c>
       <c r="F51" t="n">
-        <v>2.61629</v>
+        <v>2.79858</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.572</v>
+        <v>15.5632</v>
       </c>
       <c r="C52" t="n">
-        <v>2.08431</v>
+        <v>2.05437</v>
       </c>
       <c r="D52" t="n">
-        <v>13.7804</v>
+        <v>13.7827</v>
       </c>
       <c r="E52" t="n">
-        <v>2.5374</v>
+        <v>2.55622</v>
       </c>
       <c r="F52" t="n">
-        <v>2.7375</v>
+        <v>2.6584</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.02699</v>
+        <v>3.02068</v>
       </c>
       <c r="C53" t="n">
-        <v>2.04951</v>
+        <v>2.16054</v>
       </c>
       <c r="D53" t="n">
-        <v>14.2708</v>
+        <v>14.267</v>
       </c>
       <c r="E53" t="n">
-        <v>2.56286</v>
+        <v>2.58707</v>
       </c>
       <c r="F53" t="n">
-        <v>2.71797</v>
+        <v>2.89601</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.02529</v>
+        <v>3.17783</v>
       </c>
       <c r="C54" t="n">
-        <v>2.15216</v>
+        <v>2.16786</v>
       </c>
       <c r="D54" t="n">
-        <v>14.7552</v>
+        <v>14.7393</v>
       </c>
       <c r="E54" t="n">
-        <v>2.69773</v>
+        <v>2.61831</v>
       </c>
       <c r="F54" t="n">
-        <v>2.83134</v>
+        <v>2.75605</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.16609</v>
+        <v>3.21979</v>
       </c>
       <c r="C55" t="n">
-        <v>2.27536</v>
+        <v>2.28984</v>
       </c>
       <c r="D55" t="n">
-        <v>15.2312</v>
+        <v>15.2125</v>
       </c>
       <c r="E55" t="n">
-        <v>2.70697</v>
+        <v>2.65262</v>
       </c>
       <c r="F55" t="n">
-        <v>2.96152</v>
+        <v>2.81497</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.25641</v>
+        <v>3.2812</v>
       </c>
       <c r="C56" t="n">
-        <v>2.25132</v>
+        <v>2.25812</v>
       </c>
       <c r="D56" t="n">
-        <v>15.7073</v>
+        <v>15.6812</v>
       </c>
       <c r="E56" t="n">
-        <v>2.74884</v>
+        <v>2.69755</v>
       </c>
       <c r="F56" t="n">
-        <v>3.01891</v>
+        <v>2.86998</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.35645</v>
+        <v>3.38086</v>
       </c>
       <c r="C57" t="n">
-        <v>2.38274</v>
+        <v>2.36368</v>
       </c>
       <c r="D57" t="n">
-        <v>16.1131</v>
+        <v>16.1255</v>
       </c>
       <c r="E57" t="n">
-        <v>2.82612</v>
+        <v>2.76507</v>
       </c>
       <c r="F57" t="n">
-        <v>3.04885</v>
+        <v>2.93328</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.56582</v>
+        <v>3.57928</v>
       </c>
       <c r="C58" t="n">
-        <v>2.38733</v>
+        <v>2.47199</v>
       </c>
       <c r="D58" t="n">
-        <v>16.5626</v>
+        <v>16.5305</v>
       </c>
       <c r="E58" t="n">
-        <v>2.91572</v>
+        <v>2.85435</v>
       </c>
       <c r="F58" t="n">
-        <v>3.1709</v>
+        <v>3.15904</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.73438</v>
+        <v>3.87555</v>
       </c>
       <c r="C59" t="n">
-        <v>2.65791</v>
+        <v>2.68347</v>
       </c>
       <c r="D59" t="n">
-        <v>16.9775</v>
+        <v>16.9258</v>
       </c>
       <c r="E59" t="n">
-        <v>2.96375</v>
+        <v>2.94697</v>
       </c>
       <c r="F59" t="n">
-        <v>3.21448</v>
+        <v>3.14624</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.21475</v>
+        <v>4.22352</v>
       </c>
       <c r="C60" t="n">
-        <v>2.96219</v>
+        <v>2.98103</v>
       </c>
       <c r="D60" t="n">
-        <v>17.4238</v>
+        <v>17.358</v>
       </c>
       <c r="E60" t="n">
-        <v>3.13282</v>
+        <v>3.04819</v>
       </c>
       <c r="F60" t="n">
-        <v>3.31048</v>
+        <v>3.43221</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.54879</v>
+        <v>4.55002</v>
       </c>
       <c r="C61" t="n">
-        <v>3.2449</v>
+        <v>3.33625</v>
       </c>
       <c r="D61" t="n">
-        <v>17.8348</v>
+        <v>17.8103</v>
       </c>
       <c r="E61" t="n">
-        <v>3.30057</v>
+        <v>3.226</v>
       </c>
       <c r="F61" t="n">
-        <v>3.57845</v>
+        <v>3.47664</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.26403</v>
+        <v>5.28601</v>
       </c>
       <c r="C62" t="n">
-        <v>3.98581</v>
+        <v>3.88927</v>
       </c>
       <c r="D62" t="n">
-        <v>18.2498</v>
+        <v>18.3195</v>
       </c>
       <c r="E62" t="n">
-        <v>3.61539</v>
+        <v>3.53144</v>
       </c>
       <c r="F62" t="n">
-        <v>4.08289</v>
+        <v>3.79992</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.36879</v>
+        <v>6.40453</v>
       </c>
       <c r="C63" t="n">
-        <v>4.8556</v>
+        <v>4.76482</v>
       </c>
       <c r="D63" t="n">
-        <v>18.7636</v>
+        <v>18.7283</v>
       </c>
       <c r="E63" t="n">
-        <v>4.12589</v>
+        <v>4.03861</v>
       </c>
       <c r="F63" t="n">
-        <v>4.4258</v>
+        <v>4.33198</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>7.92607</v>
+        <v>8.03956</v>
       </c>
       <c r="C64" t="n">
-        <v>6.11565</v>
+        <v>6.13463</v>
       </c>
       <c r="D64" t="n">
-        <v>13.4903</v>
+        <v>13.6466</v>
       </c>
       <c r="E64" t="n">
-        <v>2.88893</v>
+        <v>2.79398</v>
       </c>
       <c r="F64" t="n">
-        <v>3.25361</v>
+        <v>3.12131</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.7357</v>
+        <v>10.7195</v>
       </c>
       <c r="C65" t="n">
-        <v>2.54153</v>
+        <v>2.55851</v>
       </c>
       <c r="D65" t="n">
-        <v>14.5192</v>
+        <v>14.406</v>
       </c>
       <c r="E65" t="n">
-        <v>2.90737</v>
+        <v>2.81014</v>
       </c>
       <c r="F65" t="n">
-        <v>3.3129</v>
+        <v>3.16526</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.6391</v>
+        <v>14.6933</v>
       </c>
       <c r="C66" t="n">
-        <v>2.59148</v>
+        <v>2.52773</v>
       </c>
       <c r="D66" t="n">
-        <v>15.3318</v>
+        <v>15.1692</v>
       </c>
       <c r="E66" t="n">
-        <v>2.91704</v>
+        <v>2.79542</v>
       </c>
       <c r="F66" t="n">
-        <v>3.36142</v>
+        <v>3.21071</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.53368</v>
+        <v>3.60728</v>
       </c>
       <c r="C67" t="n">
-        <v>2.5499</v>
+        <v>2.55592</v>
       </c>
       <c r="D67" t="n">
-        <v>16.1223</v>
+        <v>16.0379</v>
       </c>
       <c r="E67" t="n">
-        <v>2.95345</v>
+        <v>2.85166</v>
       </c>
       <c r="F67" t="n">
-        <v>3.40783</v>
+        <v>3.25834</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.59052</v>
+        <v>3.69783</v>
       </c>
       <c r="C68" t="n">
-        <v>2.61479</v>
+        <v>2.5935</v>
       </c>
       <c r="D68" t="n">
-        <v>16.9417</v>
+        <v>16.7324</v>
       </c>
       <c r="E68" t="n">
-        <v>2.98529</v>
+        <v>2.89581</v>
       </c>
       <c r="F68" t="n">
-        <v>3.4516</v>
+        <v>3.31716</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.69234</v>
+        <v>3.70414</v>
       </c>
       <c r="C69" t="n">
-        <v>2.67647</v>
+        <v>2.81465</v>
       </c>
       <c r="D69" t="n">
-        <v>17.9131</v>
+        <v>17.691</v>
       </c>
       <c r="E69" t="n">
-        <v>3.02344</v>
+        <v>2.9115</v>
       </c>
       <c r="F69" t="n">
-        <v>3.51802</v>
+        <v>3.38196</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.77956</v>
+        <v>3.81126</v>
       </c>
       <c r="C70" t="n">
-        <v>2.71578</v>
+        <v>2.85138</v>
       </c>
       <c r="D70" t="n">
-        <v>18.7662</v>
+        <v>18.7414</v>
       </c>
       <c r="E70" t="n">
-        <v>3.09752</v>
+        <v>2.99612</v>
       </c>
       <c r="F70" t="n">
-        <v>3.59127</v>
+        <v>3.44384</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.78085</v>
+        <v>3.91435</v>
       </c>
       <c r="C71" t="n">
-        <v>2.80745</v>
+        <v>2.79516</v>
       </c>
       <c r="D71" t="n">
-        <v>19.6786</v>
+        <v>19.7291</v>
       </c>
       <c r="E71" t="n">
-        <v>3.18275</v>
+        <v>3.1001</v>
       </c>
       <c r="F71" t="n">
-        <v>3.67486</v>
+        <v>3.66529</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.05996</v>
+        <v>4.03702</v>
       </c>
       <c r="C72" t="n">
-        <v>2.92856</v>
+        <v>3.21071</v>
       </c>
       <c r="D72" t="n">
-        <v>21.0998</v>
+        <v>20.8097</v>
       </c>
       <c r="E72" t="n">
-        <v>3.25915</v>
+        <v>3.18157</v>
       </c>
       <c r="F72" t="n">
-        <v>3.76664</v>
+        <v>3.77268</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.22972</v>
+        <v>4.24741</v>
       </c>
       <c r="C73" t="n">
-        <v>3.07606</v>
+        <v>3.13647</v>
       </c>
       <c r="D73" t="n">
-        <v>22.0846</v>
+        <v>22.0418</v>
       </c>
       <c r="E73" t="n">
-        <v>3.35476</v>
+        <v>3.27906</v>
       </c>
       <c r="F73" t="n">
-        <v>3.89449</v>
+        <v>3.89301</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.40449</v>
+        <v>4.54325</v>
       </c>
       <c r="C74" t="n">
-        <v>3.31523</v>
+        <v>3.31364</v>
       </c>
       <c r="D74" t="n">
-        <v>23.3897</v>
+        <v>23.2648</v>
       </c>
       <c r="E74" t="n">
-        <v>3.48315</v>
+        <v>3.63548</v>
       </c>
       <c r="F74" t="n">
-        <v>4.06365</v>
+        <v>3.93503</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>4.96425</v>
+        <v>5.06453</v>
       </c>
       <c r="C75" t="n">
-        <v>3.71046</v>
+        <v>3.69475</v>
       </c>
       <c r="D75" t="n">
-        <v>24.7107</v>
+        <v>24.4407</v>
       </c>
       <c r="E75" t="n">
-        <v>3.66156</v>
+        <v>3.62491</v>
       </c>
       <c r="F75" t="n">
-        <v>4.27567</v>
+        <v>4.15257</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.54772</v>
+        <v>5.66779</v>
       </c>
       <c r="C76" t="n">
-        <v>4.21337</v>
+        <v>4.18956</v>
       </c>
       <c r="D76" t="n">
-        <v>26.1542</v>
+        <v>25.8546</v>
       </c>
       <c r="E76" t="n">
-        <v>3.96682</v>
+        <v>3.95927</v>
       </c>
       <c r="F76" t="n">
-        <v>4.69681</v>
+        <v>4.49889</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.50704</v>
+        <v>6.61576</v>
       </c>
       <c r="C77" t="n">
-        <v>5.02672</v>
+        <v>5.07343</v>
       </c>
       <c r="D77" t="n">
-        <v>27.7541</v>
+        <v>27.5748</v>
       </c>
       <c r="E77" t="n">
-        <v>4.43755</v>
+        <v>4.46799</v>
       </c>
       <c r="F77" t="n">
-        <v>5.15398</v>
+        <v>4.95234</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.16558</v>
+        <v>8.171900000000001</v>
       </c>
       <c r="C78" t="n">
-        <v>6.33321</v>
+        <v>6.65525</v>
       </c>
       <c r="D78" t="n">
-        <v>24.0328</v>
+        <v>24.4652</v>
       </c>
       <c r="E78" t="n">
-        <v>3.24978</v>
+        <v>3.10365</v>
       </c>
       <c r="F78" t="n">
-        <v>3.78256</v>
+        <v>3.67082</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.4779</v>
+        <v>10.9458</v>
       </c>
       <c r="C79" t="n">
-        <v>2.9326</v>
+        <v>2.87942</v>
       </c>
       <c r="D79" t="n">
-        <v>25.3068</v>
+        <v>25.742</v>
       </c>
       <c r="E79" t="n">
-        <v>3.3133</v>
+        <v>3.12157</v>
       </c>
       <c r="F79" t="n">
-        <v>3.85458</v>
+        <v>3.73268</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>14.4585</v>
+        <v>15.0577</v>
       </c>
       <c r="C80" t="n">
-        <v>2.97178</v>
+        <v>2.92047</v>
       </c>
       <c r="D80" t="n">
-        <v>26.6889</v>
+        <v>27.0634</v>
       </c>
       <c r="E80" t="n">
-        <v>3.33353</v>
+        <v>3.23552</v>
       </c>
       <c r="F80" t="n">
-        <v>3.97567</v>
+        <v>3.85963</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.28587</v>
+        <v>4.23092</v>
       </c>
       <c r="C81" t="n">
-        <v>3.07526</v>
+        <v>3.01435</v>
       </c>
       <c r="D81" t="n">
-        <v>28.1774</v>
+        <v>28.3857</v>
       </c>
       <c r="E81" t="n">
-        <v>3.37197</v>
+        <v>3.3021</v>
       </c>
       <c r="F81" t="n">
-        <v>4.13435</v>
+        <v>3.85534</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.43335</v>
+        <v>4.34631</v>
       </c>
       <c r="C82" t="n">
-        <v>3.15321</v>
+        <v>3.08031</v>
       </c>
       <c r="D82" t="n">
-        <v>29.5737</v>
+        <v>29.8063</v>
       </c>
       <c r="E82" t="n">
-        <v>3.47398</v>
+        <v>3.39473</v>
       </c>
       <c r="F82" t="n">
-        <v>4.23917</v>
+        <v>4.11787</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.60962</v>
+        <v>4.55889</v>
       </c>
       <c r="C83" t="n">
-        <v>3.24338</v>
+        <v>3.17947</v>
       </c>
       <c r="D83" t="n">
-        <v>31.0904</v>
+        <v>31.1953</v>
       </c>
       <c r="E83" t="n">
-        <v>3.5171</v>
+        <v>3.50937</v>
       </c>
       <c r="F83" t="n">
-        <v>4.37951</v>
+        <v>4.36555</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.82671</v>
+        <v>4.84032</v>
       </c>
       <c r="C84" t="n">
-        <v>3.38824</v>
+        <v>3.33568</v>
       </c>
       <c r="D84" t="n">
-        <v>32.5898</v>
+        <v>32.7481</v>
       </c>
       <c r="E84" t="n">
-        <v>3.72471</v>
+        <v>3.64814</v>
       </c>
       <c r="F84" t="n">
-        <v>4.56687</v>
+        <v>4.6204</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>5.17477</v>
+        <v>5.05321</v>
       </c>
       <c r="C85" t="n">
-        <v>3.57789</v>
+        <v>3.53835</v>
       </c>
       <c r="D85" t="n">
-        <v>34.2006</v>
+        <v>34.2779</v>
       </c>
       <c r="E85" t="n">
-        <v>3.78645</v>
+        <v>3.81425</v>
       </c>
       <c r="F85" t="n">
-        <v>5.39578</v>
+        <v>4.58637</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.46407</v>
+        <v>5.42507</v>
       </c>
       <c r="C86" t="n">
-        <v>3.77597</v>
+        <v>3.69048</v>
       </c>
       <c r="D86" t="n">
-        <v>35.7776</v>
+        <v>35.8866</v>
       </c>
       <c r="E86" t="n">
-        <v>3.95935</v>
+        <v>4.0198</v>
       </c>
       <c r="F86" t="n">
-        <v>5.73718</v>
+        <v>4.88445</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.89791</v>
+        <v>5.88002</v>
       </c>
       <c r="C87" t="n">
-        <v>4.05833</v>
+        <v>3.98083</v>
       </c>
       <c r="D87" t="n">
-        <v>37.5144</v>
+        <v>37.5704</v>
       </c>
       <c r="E87" t="n">
-        <v>4.10024</v>
+        <v>4.1989</v>
       </c>
       <c r="F87" t="n">
-        <v>6.16976</v>
+        <v>5.34355</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.3759</v>
+        <v>6.2156</v>
       </c>
       <c r="C88" t="n">
-        <v>4.41978</v>
+        <v>4.30592</v>
       </c>
       <c r="D88" t="n">
-        <v>39.3375</v>
+        <v>38.8639</v>
       </c>
       <c r="E88" t="n">
-        <v>4.41492</v>
+        <v>4.47218</v>
       </c>
       <c r="F88" t="n">
-        <v>5.86791</v>
+        <v>5.78746</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>7.02993</v>
+        <v>6.81583</v>
       </c>
       <c r="C89" t="n">
-        <v>4.89021</v>
+        <v>4.75361</v>
       </c>
       <c r="D89" t="n">
-        <v>41.1175</v>
+        <v>40.6066</v>
       </c>
       <c r="E89" t="n">
-        <v>4.76415</v>
+        <v>4.78149</v>
       </c>
       <c r="F89" t="n">
-        <v>6.49603</v>
+        <v>6.16588</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.87249</v>
+        <v>7.68498</v>
       </c>
       <c r="C90" t="n">
-        <v>5.46599</v>
+        <v>5.38491</v>
       </c>
       <c r="D90" t="n">
-        <v>43.0875</v>
+        <v>42.967</v>
       </c>
       <c r="E90" t="n">
-        <v>5.20367</v>
+        <v>5.16834</v>
       </c>
       <c r="F90" t="n">
-        <v>7.22655</v>
+        <v>7.20633</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>9.047499999999999</v>
+        <v>8.90616</v>
       </c>
       <c r="C91" t="n">
-        <v>6.36395</v>
+        <v>6.2263</v>
       </c>
       <c r="D91" t="n">
-        <v>45.0993</v>
+        <v>44.8937</v>
       </c>
       <c r="E91" t="n">
-        <v>5.82424</v>
+        <v>5.73752</v>
       </c>
       <c r="F91" t="n">
-        <v>8.14659</v>
+        <v>7.79158</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.4438</v>
+        <v>10.2441</v>
       </c>
       <c r="C92" t="n">
-        <v>7.62173</v>
+        <v>7.49263</v>
       </c>
       <c r="D92" t="n">
-        <v>37.0223</v>
+        <v>36.7649</v>
       </c>
       <c r="E92" t="n">
-        <v>3.90342</v>
+        <v>3.87917</v>
       </c>
       <c r="F92" t="n">
-        <v>5.2732</v>
+        <v>5.04404</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>12.6239</v>
+        <v>12.4212</v>
       </c>
       <c r="C93" t="n">
-        <v>9.50764</v>
+        <v>9.36238</v>
       </c>
       <c r="D93" t="n">
-        <v>38.2047</v>
+        <v>37.873</v>
       </c>
       <c r="E93" t="n">
-        <v>4.08249</v>
+        <v>4.05181</v>
       </c>
       <c r="F93" t="n">
-        <v>5.58214</v>
+        <v>5.37908</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>15.8692</v>
+        <v>15.7345</v>
       </c>
       <c r="C94" t="n">
-        <v>3.99535</v>
+        <v>3.93313</v>
       </c>
       <c r="D94" t="n">
-        <v>39.4635</v>
+        <v>39.0334</v>
       </c>
       <c r="E94" t="n">
-        <v>4.23599</v>
+        <v>4.20005</v>
       </c>
       <c r="F94" t="n">
-        <v>5.90019</v>
+        <v>5.65231</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>6.14825</v>
+        <v>6.04967</v>
       </c>
       <c r="C95" t="n">
-        <v>4.14168</v>
+        <v>4.10805</v>
       </c>
       <c r="D95" t="n">
-        <v>40.7906</v>
+        <v>40.3969</v>
       </c>
       <c r="E95" t="n">
-        <v>4.3952</v>
+        <v>4.36616</v>
       </c>
       <c r="F95" t="n">
-        <v>6.06808</v>
+        <v>5.96293</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.49124</v>
+        <v>6.46735</v>
       </c>
       <c r="C96" t="n">
-        <v>4.32102</v>
+        <v>4.29754</v>
       </c>
       <c r="D96" t="n">
-        <v>42.1068</v>
+        <v>41.6961</v>
       </c>
       <c r="E96" t="n">
-        <v>4.58789</v>
+        <v>4.53269</v>
       </c>
       <c r="F96" t="n">
-        <v>6.57835</v>
+        <v>6.31586</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.78754</v>
+        <v>6.72095</v>
       </c>
       <c r="C97" t="n">
-        <v>4.4716</v>
+        <v>4.45176</v>
       </c>
       <c r="D97" t="n">
-        <v>43.4885</v>
+        <v>43.0734</v>
       </c>
       <c r="E97" t="n">
-        <v>4.74391</v>
+        <v>4.66988</v>
       </c>
       <c r="F97" t="n">
-        <v>6.76478</v>
+        <v>6.60679</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>7.08231</v>
+        <v>7.04053</v>
       </c>
       <c r="C98" t="n">
-        <v>4.6403</v>
+        <v>4.62572</v>
       </c>
       <c r="D98" t="n">
-        <v>44.8815</v>
+        <v>44.4055</v>
       </c>
       <c r="E98" t="n">
-        <v>4.93676</v>
+        <v>4.82503</v>
       </c>
       <c r="F98" t="n">
-        <v>7.08579</v>
+        <v>6.87067</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.41674</v>
+        <v>7.31399</v>
       </c>
       <c r="C99" t="n">
-        <v>4.82048</v>
+        <v>4.79716</v>
       </c>
       <c r="D99" t="n">
-        <v>46.3545</v>
+        <v>45.9277</v>
       </c>
       <c r="E99" t="n">
-        <v>5.10813</v>
+        <v>4.98132</v>
       </c>
       <c r="F99" t="n">
-        <v>7.63941</v>
+        <v>7.14764</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.76804</v>
+        <v>7.61439</v>
       </c>
       <c r="C100" t="n">
-        <v>5.05159</v>
+        <v>4.98711</v>
       </c>
       <c r="D100" t="n">
-        <v>47.9054</v>
+        <v>47.4678</v>
       </c>
       <c r="E100" t="n">
-        <v>5.33388</v>
+        <v>5.18391</v>
       </c>
       <c r="F100" t="n">
-        <v>7.98304</v>
+        <v>7.46174</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>8.097709999999999</v>
+        <v>7.92422</v>
       </c>
       <c r="C101" t="n">
-        <v>5.24951</v>
+        <v>5.236</v>
       </c>
       <c r="D101" t="n">
-        <v>49.3857</v>
+        <v>48.813</v>
       </c>
       <c r="E101" t="n">
-        <v>5.49664</v>
+        <v>5.44325</v>
       </c>
       <c r="F101" t="n">
-        <v>8.319839999999999</v>
+        <v>7.88836</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.588800000000001</v>
+        <v>8.38669</v>
       </c>
       <c r="C102" t="n">
-        <v>5.62447</v>
+        <v>5.47374</v>
       </c>
       <c r="D102" t="n">
-        <v>51.3156</v>
+        <v>50.8089</v>
       </c>
       <c r="E102" t="n">
-        <v>5.76781</v>
+        <v>5.71901</v>
       </c>
       <c r="F102" t="n">
-        <v>8.82053</v>
+        <v>8.40582</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>9.19885</v>
+        <v>8.896409999999999</v>
       </c>
       <c r="C103" t="n">
-        <v>6.06517</v>
+        <v>5.90059</v>
       </c>
       <c r="D103" t="n">
-        <v>53.117</v>
+        <v>52.7222</v>
       </c>
       <c r="E103" t="n">
-        <v>6.06286</v>
+        <v>6.06081</v>
       </c>
       <c r="F103" t="n">
-        <v>9.45481</v>
+        <v>8.92309</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.97222</v>
+        <v>9.6584</v>
       </c>
       <c r="C104" t="n">
-        <v>6.63774</v>
+        <v>6.43956</v>
       </c>
       <c r="D104" t="n">
-        <v>54.9856</v>
+        <v>54.4158</v>
       </c>
       <c r="E104" t="n">
-        <v>6.44554</v>
+        <v>6.53082</v>
       </c>
       <c r="F104" t="n">
-        <v>10.2378</v>
+        <v>9.832689999999999</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>11.0334</v>
+        <v>10.7753</v>
       </c>
       <c r="C105" t="n">
-        <v>7.50149</v>
+        <v>7.29428</v>
       </c>
       <c r="D105" t="n">
-        <v>56.894</v>
+        <v>56.3098</v>
       </c>
       <c r="E105" t="n">
-        <v>7.0046</v>
+        <v>7.15471</v>
       </c>
       <c r="F105" t="n">
-        <v>11.2224</v>
+        <v>10.4962</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>12.5331</v>
+        <v>12.2217</v>
       </c>
       <c r="C106" t="n">
-        <v>8.728579999999999</v>
+        <v>8.575379999999999</v>
       </c>
       <c r="D106" t="n">
-        <v>58.8663</v>
+        <v>58.0879</v>
       </c>
       <c r="E106" t="n">
-        <v>7.87794</v>
+        <v>7.9653</v>
       </c>
       <c r="F106" t="n">
-        <v>12.6891</v>
+        <v>12.0366</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>14.5528</v>
+        <v>14.2146</v>
       </c>
       <c r="C107" t="n">
-        <v>10.5726</v>
+        <v>10.3993</v>
       </c>
       <c r="D107" t="n">
-        <v>44.7473</v>
+        <v>44.1732</v>
       </c>
       <c r="E107" t="n">
-        <v>4.91215</v>
+        <v>4.77732</v>
       </c>
       <c r="F107" t="n">
-        <v>7.17289</v>
+        <v>6.82536</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.18</v>
+        <v>17.0466</v>
       </c>
       <c r="C108" t="n">
-        <v>4.74947</v>
+        <v>4.67754</v>
       </c>
       <c r="D108" t="n">
-        <v>45.8968</v>
+        <v>45.271</v>
       </c>
       <c r="E108" t="n">
-        <v>5.01657</v>
+        <v>5.05434</v>
       </c>
       <c r="F108" t="n">
-        <v>7.53032</v>
+        <v>7.12855</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.9709</v>
+        <v>21.8759</v>
       </c>
       <c r="C109" t="n">
-        <v>4.85414</v>
+        <v>4.86925</v>
       </c>
       <c r="D109" t="n">
-        <v>47.0794</v>
+        <v>46.4531</v>
       </c>
       <c r="E109" t="n">
-        <v>5.15997</v>
+        <v>5.24809</v>
       </c>
       <c r="F109" t="n">
-        <v>7.74641</v>
+        <v>7.49705</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.65233</v>
+        <v>7.58114</v>
       </c>
       <c r="C110" t="n">
-        <v>4.93933</v>
+        <v>4.95275</v>
       </c>
       <c r="D110" t="n">
-        <v>48.3124</v>
+        <v>47.675</v>
       </c>
       <c r="E110" t="n">
-        <v>5.24403</v>
+        <v>5.47971</v>
       </c>
       <c r="F110" t="n">
-        <v>8.25329</v>
+        <v>7.86272</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.97512</v>
+        <v>7.87851</v>
       </c>
       <c r="C111" t="n">
-        <v>5.1497</v>
+        <v>5.07447</v>
       </c>
       <c r="D111" t="n">
-        <v>49.5269</v>
+        <v>48.9523</v>
       </c>
       <c r="E111" t="n">
-        <v>5.38041</v>
+        <v>5.72361</v>
       </c>
       <c r="F111" t="n">
-        <v>8.63862</v>
+        <v>8.303089999999999</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>8.12946</v>
+        <v>8.096690000000001</v>
       </c>
       <c r="C112" t="n">
-        <v>5.33996</v>
+        <v>5.29121</v>
       </c>
       <c r="D112" t="n">
-        <v>50.9342</v>
+        <v>50.2974</v>
       </c>
       <c r="E112" t="n">
-        <v>5.55599</v>
+        <v>5.9685</v>
       </c>
       <c r="F112" t="n">
-        <v>9.16719</v>
+        <v>8.78654</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.61464</v>
+        <v>8.607939999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>5.56838</v>
+        <v>5.52658</v>
       </c>
       <c r="D113" t="n">
-        <v>52.2787</v>
+        <v>51.6851</v>
       </c>
       <c r="E113" t="n">
-        <v>5.79371</v>
+        <v>6.17868</v>
       </c>
       <c r="F113" t="n">
-        <v>9.80378</v>
+        <v>9.34037</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>9.106909999999999</v>
+        <v>9.04537</v>
       </c>
       <c r="C114" t="n">
-        <v>5.81022</v>
+        <v>5.81586</v>
       </c>
       <c r="D114" t="n">
-        <v>53.7558</v>
+        <v>53.1645</v>
       </c>
       <c r="E114" t="n">
-        <v>6.0388</v>
+        <v>6.4823</v>
       </c>
       <c r="F114" t="n">
-        <v>10.3504</v>
+        <v>9.912800000000001</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.627269999999999</v>
+        <v>9.71407</v>
       </c>
       <c r="C115" t="n">
-        <v>6.22103</v>
+        <v>6.2221</v>
       </c>
       <c r="D115" t="n">
-        <v>55.3189</v>
+        <v>54.7306</v>
       </c>
       <c r="E115" t="n">
-        <v>6.39505</v>
+        <v>6.72365</v>
       </c>
       <c r="F115" t="n">
-        <v>11.0373</v>
+        <v>10.4486</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>10.3257</v>
+        <v>10.329</v>
       </c>
       <c r="C116" t="n">
-        <v>6.697</v>
+        <v>6.68656</v>
       </c>
       <c r="D116" t="n">
-        <v>57.0115</v>
+        <v>56.4126</v>
       </c>
       <c r="E116" t="n">
-        <v>6.84799</v>
+        <v>6.99311</v>
       </c>
       <c r="F116" t="n">
-        <v>11.5982</v>
+        <v>11.0311</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>11.0944</v>
+        <v>11.0096</v>
       </c>
       <c r="C117" t="n">
-        <v>7.27127</v>
+        <v>7.19491</v>
       </c>
       <c r="D117" t="n">
-        <v>58.812</v>
+        <v>58.2405</v>
       </c>
       <c r="E117" t="n">
-        <v>7.32368</v>
+        <v>7.34284</v>
       </c>
       <c r="F117" t="n">
-        <v>12.0806</v>
+        <v>11.5973</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.8067</v>
+        <v>11.7183</v>
       </c>
       <c r="C118" t="n">
-        <v>7.85521</v>
+        <v>7.76927</v>
       </c>
       <c r="D118" t="n">
-        <v>60.6743</v>
+        <v>60.0613</v>
       </c>
       <c r="E118" t="n">
-        <v>7.8291</v>
+        <v>7.71214</v>
       </c>
       <c r="F118" t="n">
-        <v>12.7202</v>
+        <v>12.215</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.7681</v>
+        <v>12.6516</v>
       </c>
       <c r="C119" t="n">
-        <v>8.558719999999999</v>
+        <v>8.51333</v>
       </c>
       <c r="D119" t="n">
-        <v>62.6872</v>
+        <v>62.0467</v>
       </c>
       <c r="E119" t="n">
-        <v>8.32837</v>
+        <v>8.11023</v>
       </c>
       <c r="F119" t="n">
-        <v>13.6549</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.9484</v>
+        <v>13.9</v>
       </c>
       <c r="C120" t="n">
-        <v>9.650029999999999</v>
+        <v>9.58441</v>
       </c>
       <c r="D120" t="n">
-        <v>64.7586</v>
+        <v>64.1373</v>
       </c>
       <c r="E120" t="n">
-        <v>9.22847</v>
+        <v>8.92224</v>
       </c>
       <c r="F120" t="n">
-        <v>14.6752</v>
+        <v>13.9851</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.7262</v>
+        <v>15.6255</v>
       </c>
       <c r="C121" t="n">
-        <v>11.2735</v>
+        <v>11.19</v>
       </c>
       <c r="D121" t="n">
-        <v>48.0103</v>
+        <v>47.5118</v>
       </c>
       <c r="E121" t="n">
-        <v>6.71203</v>
+        <v>6.53399</v>
       </c>
       <c r="F121" t="n">
-        <v>10.7273</v>
+        <v>10.0537</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>18.0047</v>
+        <v>18.1246</v>
       </c>
       <c r="C122" t="n">
-        <v>6.69394</v>
+        <v>6.5546</v>
       </c>
       <c r="D122" t="n">
-        <v>48.8308</v>
+        <v>48.6475</v>
       </c>
       <c r="E122" t="n">
-        <v>6.89083</v>
+        <v>6.74594</v>
       </c>
       <c r="F122" t="n">
-        <v>10.0245</v>
+        <v>9.985950000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.2498</v>
+        <v>22.0486</v>
       </c>
       <c r="C123" t="n">
-        <v>6.80776</v>
+        <v>6.76088</v>
       </c>
       <c r="D123" t="n">
-        <v>50.326</v>
+        <v>49.5624</v>
       </c>
       <c r="E123" t="n">
-        <v>8.17972</v>
+        <v>7.45382</v>
       </c>
       <c r="F123" t="n">
-        <v>11.3078</v>
+        <v>10.117</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>9.84943</v>
+        <v>10.2449</v>
       </c>
       <c r="C124" t="n">
-        <v>6.71001</v>
+        <v>6.80938</v>
       </c>
       <c r="D124" t="n">
-        <v>51.529</v>
+        <v>50.9414</v>
       </c>
       <c r="E124" t="n">
-        <v>7.0577</v>
+        <v>7.5039</v>
       </c>
       <c r="F124" t="n">
-        <v>11.0964</v>
+        <v>10.7359</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.1707</v>
+        <v>10.2561</v>
       </c>
       <c r="C125" t="n">
-        <v>6.79008</v>
+        <v>6.81989</v>
       </c>
       <c r="D125" t="n">
-        <v>52.7638</v>
+        <v>52.0919</v>
       </c>
       <c r="E125" t="n">
-        <v>7.8565</v>
+        <v>7.74717</v>
       </c>
       <c r="F125" t="n">
-        <v>11.8413</v>
+        <v>10.7967</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.5291</v>
+        <v>10.4119</v>
       </c>
       <c r="C126" t="n">
-        <v>7.22026</v>
+        <v>7.05221</v>
       </c>
       <c r="D126" t="n">
-        <v>54.0229</v>
+        <v>53.5523</v>
       </c>
       <c r="E126" t="n">
-        <v>7.7023</v>
+        <v>8.190329999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>11.8765</v>
+        <v>11.5047</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.7314</v>
+        <v>10.8066</v>
       </c>
       <c r="C127" t="n">
-        <v>7.2375</v>
+        <v>7.47919</v>
       </c>
       <c r="D127" t="n">
-        <v>55.5312</v>
+        <v>54.9353</v>
       </c>
       <c r="E127" t="n">
-        <v>8.09361</v>
+        <v>8.353120000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>11.9978</v>
+        <v>11.3487</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>11.0233</v>
+        <v>11.0258</v>
       </c>
       <c r="C128" t="n">
-        <v>7.74624</v>
+        <v>7.44856</v>
       </c>
       <c r="D128" t="n">
-        <v>56.9382</v>
+        <v>56.4173</v>
       </c>
       <c r="E128" t="n">
-        <v>8.343120000000001</v>
+        <v>8.59887</v>
       </c>
       <c r="F128" t="n">
-        <v>12.8306</v>
+        <v>12.2052</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.345</v>
+        <v>10.976</v>
       </c>
       <c r="C129" t="n">
-        <v>7.62392</v>
+        <v>7.5991</v>
       </c>
       <c r="D129" t="n">
-        <v>58.5335</v>
+        <v>57.9989</v>
       </c>
       <c r="E129" t="n">
-        <v>8.37374</v>
+        <v>8.576499999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>13.1034</v>
+        <v>12.3918</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.7186</v>
+        <v>11.796</v>
       </c>
       <c r="C130" t="n">
-        <v>7.80518</v>
+        <v>7.82711</v>
       </c>
       <c r="D130" t="n">
-        <v>60.1687</v>
+        <v>59.6088</v>
       </c>
       <c r="E130" t="n">
-        <v>8.58437</v>
+        <v>9.03711</v>
       </c>
       <c r="F130" t="n">
-        <v>13.5512</v>
+        <v>12.8463</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>11.8493</v>
+        <v>11.8636</v>
       </c>
       <c r="C131" t="n">
-        <v>8.209709999999999</v>
+        <v>8.167590000000001</v>
       </c>
       <c r="D131" t="n">
-        <v>62.0324</v>
+        <v>61.4308</v>
       </c>
       <c r="E131" t="n">
-        <v>9.141999999999999</v>
+        <v>9.316319999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>14.1408</v>
+        <v>13.5743</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>12.9416</v>
+        <v>12.7518</v>
       </c>
       <c r="C132" t="n">
-        <v>8.810890000000001</v>
+        <v>8.591699999999999</v>
       </c>
       <c r="D132" t="n">
-        <v>63.816</v>
+        <v>63.3483</v>
       </c>
       <c r="E132" t="n">
-        <v>9.47452</v>
+        <v>9.65564</v>
       </c>
       <c r="F132" t="n">
-        <v>14.8407</v>
+        <v>13.8873</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.2296</v>
+        <v>13.8079</v>
       </c>
       <c r="C133" t="n">
-        <v>9.434559999999999</v>
+        <v>9.39813</v>
       </c>
       <c r="D133" t="n">
-        <v>65.8425</v>
+        <v>65.0427</v>
       </c>
       <c r="E133" t="n">
-        <v>9.97958</v>
+        <v>10.2857</v>
       </c>
       <c r="F133" t="n">
-        <v>15.4596</v>
+        <v>14.7497</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>15.0924</v>
+        <v>14.8088</v>
       </c>
       <c r="C134" t="n">
-        <v>10.2422</v>
+        <v>10.244</v>
       </c>
       <c r="D134" t="n">
-        <v>67.76909999999999</v>
+        <v>67.3541</v>
       </c>
       <c r="E134" t="n">
-        <v>10.4361</v>
+        <v>10.66</v>
       </c>
       <c r="F134" t="n">
-        <v>16.3247</v>
+        <v>15.4855</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.4242</v>
+        <v>16.5408</v>
       </c>
       <c r="C135" t="n">
-        <v>11.852</v>
+        <v>11.7619</v>
       </c>
       <c r="D135" t="n">
-        <v>49.7855</v>
+        <v>49.473</v>
       </c>
       <c r="E135" t="n">
-        <v>14.1447</v>
+        <v>13.6545</v>
       </c>
       <c r="F135" t="n">
-        <v>17.2766</v>
+        <v>16.4154</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.616</v>
+        <v>18.6679</v>
       </c>
       <c r="C136" t="n">
-        <v>13.3655</v>
+        <v>13.3718</v>
       </c>
       <c r="D136" t="n">
-        <v>50.9503</v>
+        <v>50.5283</v>
       </c>
       <c r="E136" t="n">
-        <v>14.0585</v>
+        <v>13.8267</v>
       </c>
       <c r="F136" t="n">
-        <v>17.5345</v>
+        <v>16.719</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>22.6389</v>
+        <v>22.3563</v>
       </c>
       <c r="C137" t="n">
-        <v>13.535</v>
+        <v>13.4367</v>
       </c>
       <c r="D137" t="n">
-        <v>51.8754</v>
+        <v>51.5051</v>
       </c>
       <c r="E137" t="n">
-        <v>14.3655</v>
+        <v>13.9375</v>
       </c>
       <c r="F137" t="n">
-        <v>17.9603</v>
+        <v>16.8258</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.7457</v>
+        <v>16.816</v>
       </c>
       <c r="C138" t="n">
-        <v>13.5564</v>
+        <v>13.5367</v>
       </c>
       <c r="D138" t="n">
-        <v>53.2874</v>
+        <v>52.906</v>
       </c>
       <c r="E138" t="n">
-        <v>14.4569</v>
+        <v>14.0914</v>
       </c>
       <c r="F138" t="n">
-        <v>18.1443</v>
+        <v>17.1137</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.1362</v>
+        <v>16.9881</v>
       </c>
       <c r="C139" t="n">
-        <v>13.8541</v>
+        <v>13.5897</v>
       </c>
       <c r="D139" t="n">
-        <v>54.398</v>
+        <v>54.105</v>
       </c>
       <c r="E139" t="n">
-        <v>14.6347</v>
+        <v>14.2147</v>
       </c>
       <c r="F139" t="n">
-        <v>18.5035</v>
+        <v>17.3634</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>17.1093</v>
+        <v>17.2503</v>
       </c>
       <c r="C140" t="n">
-        <v>13.7207</v>
+        <v>13.7187</v>
       </c>
       <c r="D140" t="n">
-        <v>55.7874</v>
+        <v>55.319</v>
       </c>
       <c r="E140" t="n">
-        <v>14.5716</v>
+        <v>14.4057</v>
       </c>
       <c r="F140" t="n">
-        <v>18.1119</v>
+        <v>17.7995</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>17.4395</v>
+        <v>17.3371</v>
       </c>
       <c r="C141" t="n">
-        <v>13.9211</v>
+        <v>13.9544</v>
       </c>
       <c r="D141" t="n">
-        <v>57.2555</v>
+        <v>56.8031</v>
       </c>
       <c r="E141" t="n">
-        <v>14.7049</v>
+        <v>14.0666</v>
       </c>
       <c r="F141" t="n">
-        <v>19.1348</v>
+        <v>18.1555</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>17.5556</v>
+        <v>17.5551</v>
       </c>
       <c r="C142" t="n">
-        <v>13.9938</v>
+        <v>13.8651</v>
       </c>
       <c r="D142" t="n">
-        <v>58.6281</v>
+        <v>58.274</v>
       </c>
       <c r="E142" t="n">
-        <v>14.1599</v>
+        <v>14.7526</v>
       </c>
       <c r="F142" t="n">
-        <v>19.4431</v>
+        <v>18.3762</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.8801</v>
+        <v>17.5665</v>
       </c>
       <c r="C143" t="n">
-        <v>14.3029</v>
+        <v>14.3555</v>
       </c>
       <c r="D143" t="n">
-        <v>60.313</v>
+        <v>59.8433</v>
       </c>
       <c r="E143" t="n">
-        <v>15.721</v>
+        <v>14.2385</v>
       </c>
       <c r="F143" t="n">
-        <v>19.5459</v>
+        <v>18.7263</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered unsuccessful looukp.xlsx
+++ b/clang-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.72755</v>
+        <v>2.72544</v>
       </c>
       <c r="C2" t="n">
-        <v>2.08391</v>
+        <v>2.07382</v>
       </c>
       <c r="D2" t="n">
-        <v>12.4804</v>
+        <v>12.2879</v>
       </c>
       <c r="E2" t="n">
-        <v>2.60665</v>
+        <v>2.61428</v>
       </c>
       <c r="F2" t="n">
-        <v>2.39732</v>
+        <v>2.41503</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.76152</v>
+        <v>2.7543</v>
       </c>
       <c r="C3" t="n">
-        <v>2.17862</v>
+        <v>2.16839</v>
       </c>
       <c r="D3" t="n">
-        <v>13.0156</v>
+        <v>12.7707</v>
       </c>
       <c r="E3" t="n">
-        <v>2.69982</v>
+        <v>2.69341</v>
       </c>
       <c r="F3" t="n">
-        <v>2.50345</v>
+        <v>2.4987</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.86374</v>
+        <v>2.84937</v>
       </c>
       <c r="C4" t="n">
-        <v>2.36135</v>
+        <v>2.3583</v>
       </c>
       <c r="D4" t="n">
-        <v>13.5246</v>
+        <v>13.2669</v>
       </c>
       <c r="E4" t="n">
-        <v>2.78778</v>
+        <v>2.77472</v>
       </c>
       <c r="F4" t="n">
-        <v>2.64837</v>
+        <v>2.62131</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.22342</v>
+        <v>3.21722</v>
       </c>
       <c r="C5" t="n">
-        <v>2.74195</v>
+        <v>2.73354</v>
       </c>
       <c r="D5" t="n">
-        <v>14.0553</v>
+        <v>13.8992</v>
       </c>
       <c r="E5" t="n">
-        <v>2.93558</v>
+        <v>2.90809</v>
       </c>
       <c r="F5" t="n">
-        <v>2.79766</v>
+        <v>2.77943</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.05344</v>
+        <v>4.07725</v>
       </c>
       <c r="C6" t="n">
-        <v>3.52777</v>
+        <v>3.52042</v>
       </c>
       <c r="D6" t="n">
-        <v>14.6348</v>
+        <v>14.5626</v>
       </c>
       <c r="E6" t="n">
-        <v>3.13062</v>
+        <v>3.10702</v>
       </c>
       <c r="F6" t="n">
-        <v>3.02557</v>
+        <v>2.97679</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.59641</v>
+        <v>6.57206</v>
       </c>
       <c r="C7" t="n">
-        <v>5.2575</v>
+        <v>5.2672</v>
       </c>
       <c r="D7" t="n">
-        <v>10.2817</v>
+        <v>10.1346</v>
       </c>
       <c r="E7" t="n">
-        <v>2.36193</v>
+        <v>2.3559</v>
       </c>
       <c r="F7" t="n">
-        <v>2.12676</v>
+        <v>2.11174</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.53346</v>
+        <v>9.53595</v>
       </c>
       <c r="C8" t="n">
-        <v>1.75145</v>
+        <v>1.74689</v>
       </c>
       <c r="D8" t="n">
-        <v>10.8902</v>
+        <v>10.8011</v>
       </c>
       <c r="E8" t="n">
-        <v>2.37643</v>
+        <v>2.37018</v>
       </c>
       <c r="F8" t="n">
-        <v>2.17447</v>
+        <v>2.13525</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.8528</v>
+        <v>13.8536</v>
       </c>
       <c r="C9" t="n">
-        <v>1.77111</v>
+        <v>1.76777</v>
       </c>
       <c r="D9" t="n">
-        <v>11.5295</v>
+        <v>11.4007</v>
       </c>
       <c r="E9" t="n">
-        <v>2.40063</v>
+        <v>2.3948</v>
       </c>
       <c r="F9" t="n">
-        <v>2.17908</v>
+        <v>2.16222</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.6411</v>
+        <v>2.62243</v>
       </c>
       <c r="C10" t="n">
-        <v>1.80895</v>
+        <v>1.80493</v>
       </c>
       <c r="D10" t="n">
-        <v>12.146</v>
+        <v>12.0953</v>
       </c>
       <c r="E10" t="n">
-        <v>2.42676</v>
+        <v>2.42141</v>
       </c>
       <c r="F10" t="n">
-        <v>2.22508</v>
+        <v>2.20115</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.71632</v>
+        <v>2.69804</v>
       </c>
       <c r="C11" t="n">
-        <v>1.85263</v>
+        <v>1.8438</v>
       </c>
       <c r="D11" t="n">
-        <v>12.7265</v>
+        <v>12.6927</v>
       </c>
       <c r="E11" t="n">
-        <v>2.44808</v>
+        <v>2.44409</v>
       </c>
       <c r="F11" t="n">
-        <v>2.25793</v>
+        <v>2.2442</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.72589</v>
+        <v>2.70613</v>
       </c>
       <c r="C12" t="n">
-        <v>1.88837</v>
+        <v>1.87731</v>
       </c>
       <c r="D12" t="n">
-        <v>13.2219</v>
+        <v>13.1926</v>
       </c>
       <c r="E12" t="n">
-        <v>2.48119</v>
+        <v>2.46999</v>
       </c>
       <c r="F12" t="n">
-        <v>2.30265</v>
+        <v>2.29315</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.69139</v>
+        <v>2.68567</v>
       </c>
       <c r="C13" t="n">
-        <v>1.93082</v>
+        <v>1.91942</v>
       </c>
       <c r="D13" t="n">
-        <v>13.7065</v>
+        <v>13.6032</v>
       </c>
       <c r="E13" t="n">
-        <v>2.50211</v>
+        <v>2.49505</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3146</v>
+        <v>2.30423</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.77539</v>
+        <v>2.77232</v>
       </c>
       <c r="C14" t="n">
-        <v>2.03885</v>
+        <v>2.02874</v>
       </c>
       <c r="D14" t="n">
-        <v>14.2065</v>
+        <v>14.1267</v>
       </c>
       <c r="E14" t="n">
-        <v>2.53238</v>
+        <v>2.52132</v>
       </c>
       <c r="F14" t="n">
-        <v>2.37188</v>
+        <v>2.3576</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.90316</v>
+        <v>2.88474</v>
       </c>
       <c r="C15" t="n">
-        <v>2.11694</v>
+        <v>2.10813</v>
       </c>
       <c r="D15" t="n">
-        <v>14.5902</v>
+        <v>14.5548</v>
       </c>
       <c r="E15" t="n">
-        <v>2.58659</v>
+        <v>2.57371</v>
       </c>
       <c r="F15" t="n">
-        <v>2.44677</v>
+        <v>2.43108</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.96831</v>
+        <v>2.97073</v>
       </c>
       <c r="C16" t="n">
-        <v>2.24262</v>
+        <v>2.23642</v>
       </c>
       <c r="D16" t="n">
-        <v>14.9823</v>
+        <v>14.9759</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6322</v>
+        <v>2.62246</v>
       </c>
       <c r="F16" t="n">
-        <v>2.49501</v>
+        <v>2.49567</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.16623</v>
+        <v>3.16559</v>
       </c>
       <c r="C17" t="n">
-        <v>2.40356</v>
+        <v>2.40087</v>
       </c>
       <c r="D17" t="n">
-        <v>15.409</v>
+        <v>15.3971</v>
       </c>
       <c r="E17" t="n">
-        <v>2.70823</v>
+        <v>2.688</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5844</v>
+        <v>2.58836</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.55794</v>
+        <v>3.54382</v>
       </c>
       <c r="C18" t="n">
-        <v>2.69512</v>
+        <v>2.69241</v>
       </c>
       <c r="D18" t="n">
-        <v>15.7956</v>
+        <v>15.7785</v>
       </c>
       <c r="E18" t="n">
-        <v>2.82752</v>
+        <v>2.81007</v>
       </c>
       <c r="F18" t="n">
-        <v>2.76597</v>
+        <v>2.77917</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.14325</v>
+        <v>4.13751</v>
       </c>
       <c r="C19" t="n">
-        <v>3.29564</v>
+        <v>3.29031</v>
       </c>
       <c r="D19" t="n">
-        <v>16.2291</v>
+        <v>16.2403</v>
       </c>
       <c r="E19" t="n">
-        <v>3.01358</v>
+        <v>2.99883</v>
       </c>
       <c r="F19" t="n">
-        <v>2.97945</v>
+        <v>2.97525</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.22292</v>
+        <v>5.21248</v>
       </c>
       <c r="C20" t="n">
-        <v>4.26734</v>
+        <v>4.25768</v>
       </c>
       <c r="D20" t="n">
-        <v>16.6184</v>
+        <v>16.6032</v>
       </c>
       <c r="E20" t="n">
-        <v>3.42697</v>
+        <v>3.39793</v>
       </c>
       <c r="F20" t="n">
-        <v>3.40042</v>
+        <v>3.3652</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.9686</v>
+        <v>6.97315</v>
       </c>
       <c r="C21" t="n">
-        <v>5.51017</v>
+        <v>5.53108</v>
       </c>
       <c r="D21" t="n">
-        <v>11.7886</v>
+        <v>11.7893</v>
       </c>
       <c r="E21" t="n">
-        <v>2.38795</v>
+        <v>2.38421</v>
       </c>
       <c r="F21" t="n">
-        <v>2.20456</v>
+        <v>2.18164</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.333909999999999</v>
+        <v>9.28983</v>
       </c>
       <c r="C22" t="n">
-        <v>1.81384</v>
+        <v>1.86066</v>
       </c>
       <c r="D22" t="n">
-        <v>12.3354</v>
+        <v>12.3239</v>
       </c>
       <c r="E22" t="n">
-        <v>2.41503</v>
+        <v>2.40578</v>
       </c>
       <c r="F22" t="n">
-        <v>2.23781</v>
+        <v>2.22494</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.5956</v>
+        <v>12.5804</v>
       </c>
       <c r="C23" t="n">
-        <v>1.83812</v>
+        <v>1.8759</v>
       </c>
       <c r="D23" t="n">
-        <v>12.8283</v>
+        <v>12.8769</v>
       </c>
       <c r="E23" t="n">
-        <v>2.43369</v>
+        <v>2.42693</v>
       </c>
       <c r="F23" t="n">
-        <v>2.26902</v>
+        <v>2.24488</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.73072</v>
+        <v>2.76607</v>
       </c>
       <c r="C24" t="n">
-        <v>1.87798</v>
+        <v>1.91746</v>
       </c>
       <c r="D24" t="n">
-        <v>13.3484</v>
+        <v>13.3427</v>
       </c>
       <c r="E24" t="n">
-        <v>2.45704</v>
+        <v>2.45171</v>
       </c>
       <c r="F24" t="n">
-        <v>2.30332</v>
+        <v>2.28543</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.76256</v>
+        <v>2.7749</v>
       </c>
       <c r="C25" t="n">
-        <v>1.90464</v>
+        <v>1.94901</v>
       </c>
       <c r="D25" t="n">
-        <v>13.8121</v>
+        <v>13.8073</v>
       </c>
       <c r="E25" t="n">
-        <v>2.48714</v>
+        <v>2.47913</v>
       </c>
       <c r="F25" t="n">
-        <v>2.34363</v>
+        <v>2.35582</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.84731</v>
+        <v>2.87168</v>
       </c>
       <c r="C26" t="n">
-        <v>1.95539</v>
+        <v>1.99105</v>
       </c>
       <c r="D26" t="n">
-        <v>14.2004</v>
+        <v>14.1918</v>
       </c>
       <c r="E26" t="n">
-        <v>2.51868</v>
+        <v>2.51076</v>
       </c>
       <c r="F26" t="n">
-        <v>2.39043</v>
+        <v>2.40149</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.93299</v>
+        <v>2.96329</v>
       </c>
       <c r="C27" t="n">
-        <v>1.98952</v>
+        <v>1.99153</v>
       </c>
       <c r="D27" t="n">
-        <v>14.6754</v>
+        <v>14.673</v>
       </c>
       <c r="E27" t="n">
-        <v>2.54901</v>
+        <v>2.5375</v>
       </c>
       <c r="F27" t="n">
-        <v>2.43593</v>
+        <v>2.43926</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.01015</v>
+        <v>3.03432</v>
       </c>
       <c r="C28" t="n">
-        <v>2.05676</v>
+        <v>2.10009</v>
       </c>
       <c r="D28" t="n">
-        <v>15.1426</v>
+        <v>15.1295</v>
       </c>
       <c r="E28" t="n">
-        <v>2.59801</v>
+        <v>2.58366</v>
       </c>
       <c r="F28" t="n">
-        <v>2.51368</v>
+        <v>2.5245</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.1516</v>
+        <v>3.17058</v>
       </c>
       <c r="C29" t="n">
-        <v>2.18176</v>
+        <v>2.21151</v>
       </c>
       <c r="D29" t="n">
-        <v>15.558</v>
+        <v>15.5514</v>
       </c>
       <c r="E29" t="n">
-        <v>2.64786</v>
+        <v>2.63637</v>
       </c>
       <c r="F29" t="n">
-        <v>2.60794</v>
+        <v>2.60239</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.31774</v>
+        <v>3.32597</v>
       </c>
       <c r="C30" t="n">
-        <v>2.30927</v>
+        <v>2.3506</v>
       </c>
       <c r="D30" t="n">
-        <v>16.0001</v>
+        <v>16.0024</v>
       </c>
       <c r="E30" t="n">
-        <v>2.71945</v>
+        <v>2.69726</v>
       </c>
       <c r="F30" t="n">
-        <v>2.70699</v>
+        <v>2.68891</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.57116</v>
+        <v>3.58023</v>
       </c>
       <c r="C31" t="n">
-        <v>2.4952</v>
+        <v>2.49148</v>
       </c>
       <c r="D31" t="n">
-        <v>16.389</v>
+        <v>16.3862</v>
       </c>
       <c r="E31" t="n">
-        <v>2.78823</v>
+        <v>2.76491</v>
       </c>
       <c r="F31" t="n">
-        <v>2.79637</v>
+        <v>2.78456</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.00247</v>
+        <v>4.00361</v>
       </c>
       <c r="C32" t="n">
-        <v>2.7598</v>
+        <v>2.7896</v>
       </c>
       <c r="D32" t="n">
-        <v>16.7158</v>
+        <v>16.703</v>
       </c>
       <c r="E32" t="n">
-        <v>2.9071</v>
+        <v>2.87177</v>
       </c>
       <c r="F32" t="n">
-        <v>2.94091</v>
+        <v>2.94829</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.7188</v>
+        <v>4.7215</v>
       </c>
       <c r="C33" t="n">
-        <v>3.31339</v>
+        <v>3.32974</v>
       </c>
       <c r="D33" t="n">
-        <v>17.1536</v>
+        <v>17.1578</v>
       </c>
       <c r="E33" t="n">
-        <v>3.11609</v>
+        <v>3.09295</v>
       </c>
       <c r="F33" t="n">
-        <v>3.1995</v>
+        <v>3.18937</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.7299</v>
+        <v>5.72622</v>
       </c>
       <c r="C34" t="n">
-        <v>4.11598</v>
+        <v>4.11936</v>
       </c>
       <c r="D34" t="n">
-        <v>17.5742</v>
+        <v>17.5566</v>
       </c>
       <c r="E34" t="n">
-        <v>3.52667</v>
+        <v>3.49143</v>
       </c>
       <c r="F34" t="n">
-        <v>3.57958</v>
+        <v>3.60833</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.24897</v>
+        <v>7.25176</v>
       </c>
       <c r="C35" t="n">
-        <v>5.24278</v>
+        <v>5.24826</v>
       </c>
       <c r="D35" t="n">
-        <v>12.2122</v>
+        <v>12.2475</v>
       </c>
       <c r="E35" t="n">
-        <v>2.41466</v>
+        <v>2.402</v>
       </c>
       <c r="F35" t="n">
-        <v>2.30593</v>
+        <v>2.31989</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.469290000000001</v>
+        <v>9.474080000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>6.89939</v>
+        <v>6.85672</v>
       </c>
       <c r="D36" t="n">
-        <v>12.7127</v>
+        <v>12.7279</v>
       </c>
       <c r="E36" t="n">
-        <v>2.43404</v>
+        <v>2.42084</v>
       </c>
       <c r="F36" t="n">
-        <v>2.3408</v>
+        <v>2.35165</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.1</v>
+        <v>13.0868</v>
       </c>
       <c r="C37" t="n">
-        <v>1.85369</v>
+        <v>1.88573</v>
       </c>
       <c r="D37" t="n">
-        <v>13.1608</v>
+        <v>13.1724</v>
       </c>
       <c r="E37" t="n">
-        <v>2.46231</v>
+        <v>2.44759</v>
       </c>
       <c r="F37" t="n">
-        <v>2.41302</v>
+        <v>2.39044</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.81885</v>
+        <v>2.8235</v>
       </c>
       <c r="C38" t="n">
-        <v>1.87688</v>
+        <v>1.88765</v>
       </c>
       <c r="D38" t="n">
-        <v>13.6728</v>
+        <v>13.6831</v>
       </c>
       <c r="E38" t="n">
-        <v>2.48717</v>
+        <v>2.47356</v>
       </c>
       <c r="F38" t="n">
-        <v>2.43316</v>
+        <v>2.44169</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.84997</v>
+        <v>2.8736</v>
       </c>
       <c r="C39" t="n">
-        <v>1.92491</v>
+        <v>1.98678</v>
       </c>
       <c r="D39" t="n">
-        <v>14.1529</v>
+        <v>14.1509</v>
       </c>
       <c r="E39" t="n">
-        <v>2.5213</v>
+        <v>2.5101</v>
       </c>
       <c r="F39" t="n">
-        <v>2.51929</v>
+        <v>2.49247</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.93966</v>
+        <v>2.93817</v>
       </c>
       <c r="C40" t="n">
-        <v>1.97417</v>
+        <v>2.02123</v>
       </c>
       <c r="D40" t="n">
-        <v>14.5774</v>
+        <v>14.5958</v>
       </c>
       <c r="E40" t="n">
-        <v>2.54635</v>
+        <v>2.53609</v>
       </c>
       <c r="F40" t="n">
-        <v>2.56408</v>
+        <v>2.54814</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.01839</v>
+        <v>3.02445</v>
       </c>
       <c r="C41" t="n">
-        <v>2.03866</v>
+        <v>2.11756</v>
       </c>
       <c r="D41" t="n">
-        <v>15.0096</v>
+        <v>15.0192</v>
       </c>
       <c r="E41" t="n">
-        <v>2.58234</v>
+        <v>2.56997</v>
       </c>
       <c r="F41" t="n">
-        <v>2.60822</v>
+        <v>2.61146</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.07656</v>
+        <v>3.08376</v>
       </c>
       <c r="C42" t="n">
-        <v>2.09566</v>
+        <v>2.14214</v>
       </c>
       <c r="D42" t="n">
-        <v>15.4474</v>
+        <v>15.4636</v>
       </c>
       <c r="E42" t="n">
-        <v>2.61999</v>
+        <v>2.61036</v>
       </c>
       <c r="F42" t="n">
-        <v>2.6825</v>
+        <v>2.65704</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.25173</v>
+        <v>3.24805</v>
       </c>
       <c r="C43" t="n">
-        <v>2.19741</v>
+        <v>2.19091</v>
       </c>
       <c r="D43" t="n">
-        <v>15.8965</v>
+        <v>15.8999</v>
       </c>
       <c r="E43" t="n">
-        <v>2.67422</v>
+        <v>2.65595</v>
       </c>
       <c r="F43" t="n">
-        <v>2.7628</v>
+        <v>2.73539</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.43132</v>
+        <v>3.43374</v>
       </c>
       <c r="C44" t="n">
-        <v>2.32999</v>
+        <v>2.3309</v>
       </c>
       <c r="D44" t="n">
-        <v>16.2863</v>
+        <v>16.3037</v>
       </c>
       <c r="E44" t="n">
-        <v>2.75511</v>
+        <v>2.73122</v>
       </c>
       <c r="F44" t="n">
-        <v>2.86434</v>
+        <v>2.85145</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.683</v>
+        <v>3.6862</v>
       </c>
       <c r="C45" t="n">
-        <v>2.58004</v>
+        <v>2.59304</v>
       </c>
       <c r="D45" t="n">
-        <v>16.6708</v>
+        <v>16.6909</v>
       </c>
       <c r="E45" t="n">
-        <v>2.84701</v>
+        <v>2.81511</v>
       </c>
       <c r="F45" t="n">
-        <v>2.97089</v>
+        <v>2.96648</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.05174</v>
+        <v>4.055</v>
       </c>
       <c r="C46" t="n">
-        <v>2.89019</v>
+        <v>2.8952</v>
       </c>
       <c r="D46" t="n">
-        <v>17.0685</v>
+        <v>17.0891</v>
       </c>
       <c r="E46" t="n">
-        <v>2.95853</v>
+        <v>2.94228</v>
       </c>
       <c r="F46" t="n">
-        <v>3.1342</v>
+        <v>3.14569</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.66071</v>
+        <v>4.66306</v>
       </c>
       <c r="C47" t="n">
-        <v>3.34913</v>
+        <v>3.35147</v>
       </c>
       <c r="D47" t="n">
-        <v>17.5056</v>
+        <v>17.5216</v>
       </c>
       <c r="E47" t="n">
-        <v>3.17461</v>
+        <v>3.16693</v>
       </c>
       <c r="F47" t="n">
-        <v>3.36331</v>
+        <v>3.36605</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.45153</v>
+        <v>5.45538</v>
       </c>
       <c r="C48" t="n">
-        <v>4.03094</v>
+        <v>4.05537</v>
       </c>
       <c r="D48" t="n">
-        <v>17.9588</v>
+        <v>17.9552</v>
       </c>
       <c r="E48" t="n">
-        <v>3.54427</v>
+        <v>3.5448</v>
       </c>
       <c r="F48" t="n">
-        <v>3.74655</v>
+        <v>3.73873</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.58532</v>
+        <v>6.58931</v>
       </c>
       <c r="C49" t="n">
-        <v>4.96857</v>
+        <v>4.99195</v>
       </c>
       <c r="D49" t="n">
-        <v>18.3951</v>
+        <v>18.4132</v>
       </c>
       <c r="E49" t="n">
-        <v>4.11364</v>
+        <v>4.08799</v>
       </c>
       <c r="F49" t="n">
-        <v>4.29365</v>
+        <v>4.26668</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.5306</v>
+        <v>8.530900000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>6.46868</v>
+        <v>6.48248</v>
       </c>
       <c r="D50" t="n">
-        <v>12.8337</v>
+        <v>12.8458</v>
       </c>
       <c r="E50" t="n">
-        <v>2.5172</v>
+        <v>2.45926</v>
       </c>
       <c r="F50" t="n">
-        <v>2.7736</v>
+        <v>2.57648</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>11.1504</v>
+        <v>11.1653</v>
       </c>
       <c r="C51" t="n">
-        <v>2.14441</v>
+        <v>1.97623</v>
       </c>
       <c r="D51" t="n">
-        <v>13.2871</v>
+        <v>13.3034</v>
       </c>
       <c r="E51" t="n">
-        <v>2.52756</v>
+        <v>2.47182</v>
       </c>
       <c r="F51" t="n">
-        <v>2.79858</v>
+        <v>2.60476</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.5632</v>
+        <v>15.5802</v>
       </c>
       <c r="C52" t="n">
-        <v>2.05437</v>
+        <v>2.0479</v>
       </c>
       <c r="D52" t="n">
-        <v>13.7827</v>
+        <v>13.7811</v>
       </c>
       <c r="E52" t="n">
-        <v>2.55622</v>
+        <v>2.49641</v>
       </c>
       <c r="F52" t="n">
-        <v>2.6584</v>
+        <v>2.6877</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.02068</v>
+        <v>3.0449</v>
       </c>
       <c r="C53" t="n">
-        <v>2.16054</v>
+        <v>2.08024</v>
       </c>
       <c r="D53" t="n">
-        <v>14.267</v>
+        <v>14.274</v>
       </c>
       <c r="E53" t="n">
-        <v>2.58707</v>
+        <v>2.52255</v>
       </c>
       <c r="F53" t="n">
-        <v>2.89601</v>
+        <v>2.69939</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.17783</v>
+        <v>3.12671</v>
       </c>
       <c r="C54" t="n">
-        <v>2.16786</v>
+        <v>2.22895</v>
       </c>
       <c r="D54" t="n">
-        <v>14.7393</v>
+        <v>14.7655</v>
       </c>
       <c r="E54" t="n">
-        <v>2.61831</v>
+        <v>2.58948</v>
       </c>
       <c r="F54" t="n">
-        <v>2.75605</v>
+        <v>2.77631</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.21979</v>
+        <v>3.13506</v>
       </c>
       <c r="C55" t="n">
-        <v>2.28984</v>
+        <v>2.36133</v>
       </c>
       <c r="D55" t="n">
-        <v>15.2125</v>
+        <v>15.231</v>
       </c>
       <c r="E55" t="n">
-        <v>2.65262</v>
+        <v>2.61363</v>
       </c>
       <c r="F55" t="n">
-        <v>2.81497</v>
+        <v>2.88865</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.2812</v>
+        <v>3.31406</v>
       </c>
       <c r="C56" t="n">
-        <v>2.25812</v>
+        <v>2.23236</v>
       </c>
       <c r="D56" t="n">
-        <v>15.6812</v>
+        <v>15.7047</v>
       </c>
       <c r="E56" t="n">
-        <v>2.69755</v>
+        <v>2.65766</v>
       </c>
       <c r="F56" t="n">
-        <v>2.86998</v>
+        <v>2.94272</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.38086</v>
+        <v>3.41809</v>
       </c>
       <c r="C57" t="n">
-        <v>2.36368</v>
+        <v>2.37192</v>
       </c>
       <c r="D57" t="n">
-        <v>16.1255</v>
+        <v>16.1056</v>
       </c>
       <c r="E57" t="n">
-        <v>2.76507</v>
+        <v>2.7206</v>
       </c>
       <c r="F57" t="n">
-        <v>2.93328</v>
+        <v>2.98461</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.57928</v>
+        <v>3.63623</v>
       </c>
       <c r="C58" t="n">
-        <v>2.47199</v>
+        <v>2.43971</v>
       </c>
       <c r="D58" t="n">
-        <v>16.5305</v>
+        <v>16.5521</v>
       </c>
       <c r="E58" t="n">
-        <v>2.85435</v>
+        <v>2.79326</v>
       </c>
       <c r="F58" t="n">
-        <v>3.15904</v>
+        <v>3.02275</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.87555</v>
+        <v>3.83914</v>
       </c>
       <c r="C59" t="n">
-        <v>2.68347</v>
+        <v>2.68019</v>
       </c>
       <c r="D59" t="n">
-        <v>16.9258</v>
+        <v>16.9322</v>
       </c>
       <c r="E59" t="n">
-        <v>2.94697</v>
+        <v>3.12983</v>
       </c>
       <c r="F59" t="n">
-        <v>3.14624</v>
+        <v>3.17308</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.22352</v>
+        <v>4.17696</v>
       </c>
       <c r="C60" t="n">
-        <v>2.98103</v>
+        <v>3.36803</v>
       </c>
       <c r="D60" t="n">
-        <v>17.358</v>
+        <v>17.3742</v>
       </c>
       <c r="E60" t="n">
-        <v>3.04819</v>
+        <v>3.21375</v>
       </c>
       <c r="F60" t="n">
-        <v>3.43221</v>
+        <v>3.29419</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.55002</v>
+        <v>4.56405</v>
       </c>
       <c r="C61" t="n">
-        <v>3.33625</v>
+        <v>3.29767</v>
       </c>
       <c r="D61" t="n">
-        <v>17.8103</v>
+        <v>17.8261</v>
       </c>
       <c r="E61" t="n">
-        <v>3.226</v>
+        <v>3.23821</v>
       </c>
       <c r="F61" t="n">
-        <v>3.47664</v>
+        <v>3.48038</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.28601</v>
+        <v>5.27237</v>
       </c>
       <c r="C62" t="n">
-        <v>3.88927</v>
+        <v>3.93073</v>
       </c>
       <c r="D62" t="n">
-        <v>18.3195</v>
+        <v>18.2523</v>
       </c>
       <c r="E62" t="n">
-        <v>3.53144</v>
+        <v>3.55025</v>
       </c>
       <c r="F62" t="n">
-        <v>3.79992</v>
+        <v>3.84595</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.40453</v>
+        <v>6.3783</v>
       </c>
       <c r="C63" t="n">
-        <v>4.76482</v>
+        <v>4.80007</v>
       </c>
       <c r="D63" t="n">
-        <v>18.7283</v>
+        <v>18.8205</v>
       </c>
       <c r="E63" t="n">
-        <v>4.03861</v>
+        <v>4.05566</v>
       </c>
       <c r="F63" t="n">
-        <v>4.33198</v>
+        <v>4.32457</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>8.03956</v>
+        <v>8.04485</v>
       </c>
       <c r="C64" t="n">
-        <v>6.13463</v>
+        <v>6.14772</v>
       </c>
       <c r="D64" t="n">
-        <v>13.6466</v>
+        <v>14.2143</v>
       </c>
       <c r="E64" t="n">
-        <v>2.79398</v>
+        <v>2.72508</v>
       </c>
       <c r="F64" t="n">
-        <v>3.12131</v>
+        <v>3.12233</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.7195</v>
+        <v>10.7337</v>
       </c>
       <c r="C65" t="n">
-        <v>2.55851</v>
+        <v>2.57216</v>
       </c>
       <c r="D65" t="n">
-        <v>14.406</v>
+        <v>14.7224</v>
       </c>
       <c r="E65" t="n">
-        <v>2.81014</v>
+        <v>2.83339</v>
       </c>
       <c r="F65" t="n">
-        <v>3.16526</v>
+        <v>3.18592</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.6933</v>
+        <v>14.6422</v>
       </c>
       <c r="C66" t="n">
-        <v>2.52773</v>
+        <v>2.61666</v>
       </c>
       <c r="D66" t="n">
-        <v>15.1692</v>
+        <v>15.6231</v>
       </c>
       <c r="E66" t="n">
-        <v>2.79542</v>
+        <v>2.85143</v>
       </c>
       <c r="F66" t="n">
-        <v>3.21071</v>
+        <v>3.23324</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.60728</v>
+        <v>3.69212</v>
       </c>
       <c r="C67" t="n">
-        <v>2.55592</v>
+        <v>2.6417</v>
       </c>
       <c r="D67" t="n">
-        <v>16.0379</v>
+        <v>16.3855</v>
       </c>
       <c r="E67" t="n">
-        <v>2.85166</v>
+        <v>2.88247</v>
       </c>
       <c r="F67" t="n">
-        <v>3.25834</v>
+        <v>3.28404</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.69783</v>
+        <v>3.74404</v>
       </c>
       <c r="C68" t="n">
-        <v>2.5935</v>
+        <v>2.66649</v>
       </c>
       <c r="D68" t="n">
-        <v>16.7324</v>
+        <v>17.2861</v>
       </c>
       <c r="E68" t="n">
-        <v>2.89581</v>
+        <v>2.92978</v>
       </c>
       <c r="F68" t="n">
-        <v>3.31716</v>
+        <v>3.33453</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.70414</v>
+        <v>3.72026</v>
       </c>
       <c r="C69" t="n">
-        <v>2.81465</v>
+        <v>2.66781</v>
       </c>
       <c r="D69" t="n">
-        <v>17.691</v>
+        <v>18.174</v>
       </c>
       <c r="E69" t="n">
-        <v>2.9115</v>
+        <v>2.90352</v>
       </c>
       <c r="F69" t="n">
-        <v>3.38196</v>
+        <v>3.39815</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.81126</v>
+        <v>3.78387</v>
       </c>
       <c r="C70" t="n">
-        <v>2.85138</v>
+        <v>2.78268</v>
       </c>
       <c r="D70" t="n">
-        <v>18.7414</v>
+        <v>19.0638</v>
       </c>
       <c r="E70" t="n">
-        <v>2.99612</v>
+        <v>2.96295</v>
       </c>
       <c r="F70" t="n">
-        <v>3.44384</v>
+        <v>3.47645</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.91435</v>
+        <v>3.85728</v>
       </c>
       <c r="C71" t="n">
-        <v>2.79516</v>
+        <v>2.81274</v>
       </c>
       <c r="D71" t="n">
-        <v>19.7291</v>
+        <v>20.0366</v>
       </c>
       <c r="E71" t="n">
-        <v>3.1001</v>
+        <v>3.03945</v>
       </c>
       <c r="F71" t="n">
-        <v>3.66529</v>
+        <v>3.51754</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.03702</v>
+        <v>4.01267</v>
       </c>
       <c r="C72" t="n">
-        <v>3.21071</v>
+        <v>2.94022</v>
       </c>
       <c r="D72" t="n">
-        <v>20.8097</v>
+        <v>21.1288</v>
       </c>
       <c r="E72" t="n">
-        <v>3.18157</v>
+        <v>3.11806</v>
       </c>
       <c r="F72" t="n">
-        <v>3.77268</v>
+        <v>3.62193</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.24741</v>
+        <v>4.23877</v>
       </c>
       <c r="C73" t="n">
-        <v>3.13647</v>
+        <v>3.13485</v>
       </c>
       <c r="D73" t="n">
-        <v>22.0418</v>
+        <v>22.1732</v>
       </c>
       <c r="E73" t="n">
-        <v>3.27906</v>
+        <v>3.21049</v>
       </c>
       <c r="F73" t="n">
-        <v>3.89301</v>
+        <v>3.74584</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.54325</v>
+        <v>4.48596</v>
       </c>
       <c r="C74" t="n">
-        <v>3.31364</v>
+        <v>3.31762</v>
       </c>
       <c r="D74" t="n">
-        <v>23.2648</v>
+        <v>23.545</v>
       </c>
       <c r="E74" t="n">
-        <v>3.63548</v>
+        <v>3.31017</v>
       </c>
       <c r="F74" t="n">
-        <v>3.93503</v>
+        <v>3.9594</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.06453</v>
+        <v>4.99406</v>
       </c>
       <c r="C75" t="n">
-        <v>3.69475</v>
+        <v>3.63187</v>
       </c>
       <c r="D75" t="n">
-        <v>24.4407</v>
+        <v>24.8739</v>
       </c>
       <c r="E75" t="n">
-        <v>3.62491</v>
+        <v>3.49887</v>
       </c>
       <c r="F75" t="n">
-        <v>4.15257</v>
+        <v>4.15165</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.66779</v>
+        <v>5.53655</v>
       </c>
       <c r="C76" t="n">
-        <v>4.18956</v>
+        <v>4.16763</v>
       </c>
       <c r="D76" t="n">
-        <v>25.8546</v>
+        <v>26.2464</v>
       </c>
       <c r="E76" t="n">
-        <v>3.95927</v>
+        <v>3.84076</v>
       </c>
       <c r="F76" t="n">
-        <v>4.49889</v>
+        <v>4.54659</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.61576</v>
+        <v>6.51638</v>
       </c>
       <c r="C77" t="n">
-        <v>5.07343</v>
+        <v>5.00964</v>
       </c>
       <c r="D77" t="n">
-        <v>27.5748</v>
+        <v>27.8325</v>
       </c>
       <c r="E77" t="n">
-        <v>4.46799</v>
+        <v>4.31254</v>
       </c>
       <c r="F77" t="n">
-        <v>4.95234</v>
+        <v>4.92281</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.171900000000001</v>
+        <v>8.11439</v>
       </c>
       <c r="C78" t="n">
-        <v>6.65525</v>
+        <v>6.3128</v>
       </c>
       <c r="D78" t="n">
-        <v>24.4652</v>
+        <v>24.038</v>
       </c>
       <c r="E78" t="n">
-        <v>3.10365</v>
+        <v>3.0508</v>
       </c>
       <c r="F78" t="n">
-        <v>3.67082</v>
+        <v>3.56008</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.9458</v>
+        <v>10.4531</v>
       </c>
       <c r="C79" t="n">
-        <v>2.87942</v>
+        <v>2.8916</v>
       </c>
       <c r="D79" t="n">
-        <v>25.742</v>
+        <v>25.4406</v>
       </c>
       <c r="E79" t="n">
-        <v>3.12157</v>
+        <v>3.18945</v>
       </c>
       <c r="F79" t="n">
-        <v>3.73268</v>
+        <v>3.6253</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>15.0577</v>
+        <v>14.2876</v>
       </c>
       <c r="C80" t="n">
-        <v>2.92047</v>
+        <v>2.91229</v>
       </c>
       <c r="D80" t="n">
-        <v>27.0634</v>
+        <v>26.7122</v>
       </c>
       <c r="E80" t="n">
-        <v>3.23552</v>
+        <v>3.12476</v>
       </c>
       <c r="F80" t="n">
-        <v>3.85963</v>
+        <v>3.74049</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.23092</v>
+        <v>4.17345</v>
       </c>
       <c r="C81" t="n">
-        <v>3.01435</v>
+        <v>3.01865</v>
       </c>
       <c r="D81" t="n">
-        <v>28.3857</v>
+        <v>28.0498</v>
       </c>
       <c r="E81" t="n">
-        <v>3.3021</v>
+        <v>3.16893</v>
       </c>
       <c r="F81" t="n">
-        <v>3.85534</v>
+        <v>3.81223</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.34631</v>
+        <v>4.31817</v>
       </c>
       <c r="C82" t="n">
-        <v>3.08031</v>
+        <v>3.12251</v>
       </c>
       <c r="D82" t="n">
-        <v>29.8063</v>
+        <v>29.4175</v>
       </c>
       <c r="E82" t="n">
-        <v>3.39473</v>
+        <v>3.22682</v>
       </c>
       <c r="F82" t="n">
-        <v>4.11787</v>
+        <v>3.98438</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.55889</v>
+        <v>4.50499</v>
       </c>
       <c r="C83" t="n">
-        <v>3.17947</v>
+        <v>3.23018</v>
       </c>
       <c r="D83" t="n">
-        <v>31.1953</v>
+        <v>30.8291</v>
       </c>
       <c r="E83" t="n">
-        <v>3.50937</v>
+        <v>3.27821</v>
       </c>
       <c r="F83" t="n">
-        <v>4.36555</v>
+        <v>4.13612</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.84032</v>
+        <v>4.78378</v>
       </c>
       <c r="C84" t="n">
-        <v>3.33568</v>
+        <v>3.39354</v>
       </c>
       <c r="D84" t="n">
-        <v>32.7481</v>
+        <v>32.3512</v>
       </c>
       <c r="E84" t="n">
-        <v>3.64814</v>
+        <v>3.43947</v>
       </c>
       <c r="F84" t="n">
-        <v>4.6204</v>
+        <v>4.34709</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>5.05321</v>
+        <v>5.14802</v>
       </c>
       <c r="C85" t="n">
-        <v>3.53835</v>
+        <v>3.55567</v>
       </c>
       <c r="D85" t="n">
-        <v>34.2779</v>
+        <v>33.8652</v>
       </c>
       <c r="E85" t="n">
-        <v>3.81425</v>
+        <v>3.53741</v>
       </c>
       <c r="F85" t="n">
-        <v>4.58637</v>
+        <v>4.66091</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.42507</v>
+        <v>5.50502</v>
       </c>
       <c r="C86" t="n">
-        <v>3.69048</v>
+        <v>3.82653</v>
       </c>
       <c r="D86" t="n">
-        <v>35.8866</v>
+        <v>35.4296</v>
       </c>
       <c r="E86" t="n">
-        <v>4.0198</v>
+        <v>3.72251</v>
       </c>
       <c r="F86" t="n">
-        <v>4.88445</v>
+        <v>5.00407</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.88002</v>
+        <v>5.96158</v>
       </c>
       <c r="C87" t="n">
-        <v>3.98083</v>
+        <v>4.13513</v>
       </c>
       <c r="D87" t="n">
-        <v>37.5704</v>
+        <v>37.1264</v>
       </c>
       <c r="E87" t="n">
-        <v>4.1989</v>
+        <v>3.9565</v>
       </c>
       <c r="F87" t="n">
-        <v>5.34355</v>
+        <v>5.42135</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.2156</v>
+        <v>6.49687</v>
       </c>
       <c r="C88" t="n">
-        <v>4.30592</v>
+        <v>4.48845</v>
       </c>
       <c r="D88" t="n">
-        <v>38.8639</v>
+        <v>38.7937</v>
       </c>
       <c r="E88" t="n">
-        <v>4.47218</v>
+        <v>4.23381</v>
       </c>
       <c r="F88" t="n">
-        <v>5.78746</v>
+        <v>5.7729</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>6.81583</v>
+        <v>7.16673</v>
       </c>
       <c r="C89" t="n">
-        <v>4.75361</v>
+        <v>4.94267</v>
       </c>
       <c r="D89" t="n">
-        <v>40.6066</v>
+        <v>40.7074</v>
       </c>
       <c r="E89" t="n">
-        <v>4.78149</v>
+        <v>4.57515</v>
       </c>
       <c r="F89" t="n">
-        <v>6.16588</v>
+        <v>6.37491</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.68498</v>
+        <v>8.048080000000001</v>
       </c>
       <c r="C90" t="n">
-        <v>5.38491</v>
+        <v>5.55457</v>
       </c>
       <c r="D90" t="n">
-        <v>42.967</v>
+        <v>42.5487</v>
       </c>
       <c r="E90" t="n">
-        <v>5.16834</v>
+        <v>5.04751</v>
       </c>
       <c r="F90" t="n">
-        <v>7.20633</v>
+        <v>7.06507</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.90616</v>
+        <v>9.17521</v>
       </c>
       <c r="C91" t="n">
-        <v>6.2263</v>
+        <v>6.42998</v>
       </c>
       <c r="D91" t="n">
-        <v>44.8937</v>
+        <v>44.6164</v>
       </c>
       <c r="E91" t="n">
-        <v>5.73752</v>
+        <v>5.67172</v>
       </c>
       <c r="F91" t="n">
-        <v>7.79158</v>
+        <v>7.9468</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.2441</v>
+        <v>10.5811</v>
       </c>
       <c r="C92" t="n">
-        <v>7.49263</v>
+        <v>7.65267</v>
       </c>
       <c r="D92" t="n">
-        <v>36.7649</v>
+        <v>36.5582</v>
       </c>
       <c r="E92" t="n">
-        <v>3.87917</v>
+        <v>3.74172</v>
       </c>
       <c r="F92" t="n">
-        <v>5.04404</v>
+        <v>5.2241</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>12.4212</v>
+        <v>12.7043</v>
       </c>
       <c r="C93" t="n">
-        <v>9.36238</v>
+        <v>9.509</v>
       </c>
       <c r="D93" t="n">
-        <v>37.873</v>
+        <v>37.7502</v>
       </c>
       <c r="E93" t="n">
-        <v>4.05181</v>
+        <v>3.8859</v>
       </c>
       <c r="F93" t="n">
-        <v>5.37908</v>
+        <v>5.5287</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>15.7345</v>
+        <v>15.8863</v>
       </c>
       <c r="C94" t="n">
-        <v>3.93313</v>
+        <v>3.98793</v>
       </c>
       <c r="D94" t="n">
-        <v>39.0334</v>
+        <v>39.0239</v>
       </c>
       <c r="E94" t="n">
-        <v>4.20005</v>
+        <v>4.00187</v>
       </c>
       <c r="F94" t="n">
-        <v>5.65231</v>
+        <v>5.85842</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>6.04967</v>
+        <v>6.11981</v>
       </c>
       <c r="C95" t="n">
-        <v>4.10805</v>
+        <v>4.12095</v>
       </c>
       <c r="D95" t="n">
-        <v>40.3969</v>
+        <v>40.2764</v>
       </c>
       <c r="E95" t="n">
-        <v>4.36616</v>
+        <v>4.1912</v>
       </c>
       <c r="F95" t="n">
-        <v>5.96293</v>
+        <v>5.97192</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.46735</v>
+        <v>6.4316</v>
       </c>
       <c r="C96" t="n">
-        <v>4.29754</v>
+        <v>4.26757</v>
       </c>
       <c r="D96" t="n">
-        <v>41.6961</v>
+        <v>41.6062</v>
       </c>
       <c r="E96" t="n">
-        <v>4.53269</v>
+        <v>4.33224</v>
       </c>
       <c r="F96" t="n">
-        <v>6.31586</v>
+        <v>6.47705</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.72095</v>
+        <v>6.75278</v>
       </c>
       <c r="C97" t="n">
-        <v>4.45176</v>
+        <v>4.47047</v>
       </c>
       <c r="D97" t="n">
-        <v>43.0734</v>
+        <v>42.9589</v>
       </c>
       <c r="E97" t="n">
-        <v>4.66988</v>
+        <v>4.56208</v>
       </c>
       <c r="F97" t="n">
-        <v>6.60679</v>
+        <v>6.64052</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>7.04053</v>
+        <v>7.03754</v>
       </c>
       <c r="C98" t="n">
-        <v>4.62572</v>
+        <v>4.61025</v>
       </c>
       <c r="D98" t="n">
-        <v>44.4055</v>
+        <v>44.3419</v>
       </c>
       <c r="E98" t="n">
-        <v>4.82503</v>
+        <v>4.70559</v>
       </c>
       <c r="F98" t="n">
-        <v>6.87067</v>
+        <v>6.91128</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.31399</v>
+        <v>7.27909</v>
       </c>
       <c r="C99" t="n">
-        <v>4.79716</v>
+        <v>4.78777</v>
       </c>
       <c r="D99" t="n">
-        <v>45.9277</v>
+        <v>45.8202</v>
       </c>
       <c r="E99" t="n">
-        <v>4.98132</v>
+        <v>4.8458</v>
       </c>
       <c r="F99" t="n">
-        <v>7.14764</v>
+        <v>7.21275</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.61439</v>
+        <v>7.63153</v>
       </c>
       <c r="C100" t="n">
-        <v>4.98711</v>
+        <v>4.96179</v>
       </c>
       <c r="D100" t="n">
-        <v>47.4678</v>
+        <v>47.3907</v>
       </c>
       <c r="E100" t="n">
-        <v>5.18391</v>
+        <v>5.02278</v>
       </c>
       <c r="F100" t="n">
-        <v>7.46174</v>
+        <v>7.58957</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.92422</v>
+        <v>7.92308</v>
       </c>
       <c r="C101" t="n">
-        <v>5.236</v>
+        <v>5.21722</v>
       </c>
       <c r="D101" t="n">
-        <v>48.813</v>
+        <v>48.8107</v>
       </c>
       <c r="E101" t="n">
-        <v>5.44325</v>
+        <v>5.24791</v>
       </c>
       <c r="F101" t="n">
-        <v>7.88836</v>
+        <v>8.02543</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.38669</v>
+        <v>8.46489</v>
       </c>
       <c r="C102" t="n">
-        <v>5.47374</v>
+        <v>5.5626</v>
       </c>
       <c r="D102" t="n">
-        <v>50.8089</v>
+        <v>50.7298</v>
       </c>
       <c r="E102" t="n">
-        <v>5.71901</v>
+        <v>5.51461</v>
       </c>
       <c r="F102" t="n">
-        <v>8.40582</v>
+        <v>8.38611</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.896409999999999</v>
+        <v>8.99682</v>
       </c>
       <c r="C103" t="n">
-        <v>5.90059</v>
+        <v>5.94384</v>
       </c>
       <c r="D103" t="n">
-        <v>52.7222</v>
+        <v>52.5567</v>
       </c>
       <c r="E103" t="n">
-        <v>6.06081</v>
+        <v>5.75285</v>
       </c>
       <c r="F103" t="n">
-        <v>8.92309</v>
+        <v>8.92431</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.6584</v>
+        <v>9.752739999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>6.43956</v>
+        <v>6.51299</v>
       </c>
       <c r="D104" t="n">
-        <v>54.4158</v>
+        <v>54.3999</v>
       </c>
       <c r="E104" t="n">
-        <v>6.53082</v>
+        <v>6.12383</v>
       </c>
       <c r="F104" t="n">
-        <v>9.832689999999999</v>
+        <v>9.62872</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.7753</v>
+        <v>10.8568</v>
       </c>
       <c r="C105" t="n">
-        <v>7.29428</v>
+        <v>7.3603</v>
       </c>
       <c r="D105" t="n">
-        <v>56.3098</v>
+        <v>56.3034</v>
       </c>
       <c r="E105" t="n">
-        <v>7.15471</v>
+        <v>6.671</v>
       </c>
       <c r="F105" t="n">
-        <v>10.4962</v>
+        <v>10.5974</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>12.2217</v>
+        <v>12.2724</v>
       </c>
       <c r="C106" t="n">
-        <v>8.575379999999999</v>
+        <v>8.5421</v>
       </c>
       <c r="D106" t="n">
-        <v>58.0879</v>
+        <v>58.1193</v>
       </c>
       <c r="E106" t="n">
-        <v>7.9653</v>
+        <v>7.43875</v>
       </c>
       <c r="F106" t="n">
-        <v>12.0366</v>
+        <v>11.8423</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>14.2146</v>
+        <v>14.2981</v>
       </c>
       <c r="C107" t="n">
-        <v>10.3993</v>
+        <v>10.3767</v>
       </c>
       <c r="D107" t="n">
-        <v>44.1732</v>
+        <v>44.1354</v>
       </c>
       <c r="E107" t="n">
-        <v>4.77732</v>
+        <v>4.59445</v>
       </c>
       <c r="F107" t="n">
-        <v>6.82536</v>
+        <v>6.84215</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.0466</v>
+        <v>17.1008</v>
       </c>
       <c r="C108" t="n">
-        <v>4.67754</v>
+        <v>4.72004</v>
       </c>
       <c r="D108" t="n">
-        <v>45.271</v>
+        <v>45.3416</v>
       </c>
       <c r="E108" t="n">
-        <v>5.05434</v>
+        <v>4.76312</v>
       </c>
       <c r="F108" t="n">
-        <v>7.12855</v>
+        <v>7.14956</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.8759</v>
+        <v>21.9587</v>
       </c>
       <c r="C109" t="n">
-        <v>4.86925</v>
+        <v>4.83235</v>
       </c>
       <c r="D109" t="n">
-        <v>46.4531</v>
+        <v>46.4529</v>
       </c>
       <c r="E109" t="n">
-        <v>5.24809</v>
+        <v>4.91794</v>
       </c>
       <c r="F109" t="n">
-        <v>7.49705</v>
+        <v>7.34653</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.58114</v>
+        <v>7.56427</v>
       </c>
       <c r="C110" t="n">
-        <v>4.95275</v>
+        <v>4.90721</v>
       </c>
       <c r="D110" t="n">
-        <v>47.675</v>
+        <v>47.677</v>
       </c>
       <c r="E110" t="n">
-        <v>5.47971</v>
+        <v>4.98769</v>
       </c>
       <c r="F110" t="n">
-        <v>7.86272</v>
+        <v>7.85743</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.87851</v>
+        <v>7.83047</v>
       </c>
       <c r="C111" t="n">
-        <v>5.07447</v>
+        <v>5.11628</v>
       </c>
       <c r="D111" t="n">
-        <v>48.9523</v>
+        <v>48.9239</v>
       </c>
       <c r="E111" t="n">
-        <v>5.72361</v>
+        <v>5.16981</v>
       </c>
       <c r="F111" t="n">
-        <v>8.303089999999999</v>
+        <v>8.29387</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>8.096690000000001</v>
+        <v>8.23237</v>
       </c>
       <c r="C112" t="n">
-        <v>5.29121</v>
+        <v>5.3068</v>
       </c>
       <c r="D112" t="n">
-        <v>50.2974</v>
+        <v>50.2367</v>
       </c>
       <c r="E112" t="n">
-        <v>5.9685</v>
+        <v>5.31306</v>
       </c>
       <c r="F112" t="n">
-        <v>8.78654</v>
+        <v>8.80035</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.607939999999999</v>
+        <v>8.62237</v>
       </c>
       <c r="C113" t="n">
-        <v>5.52658</v>
+        <v>5.50758</v>
       </c>
       <c r="D113" t="n">
-        <v>51.6851</v>
+        <v>51.67</v>
       </c>
       <c r="E113" t="n">
-        <v>6.17868</v>
+        <v>5.48016</v>
       </c>
       <c r="F113" t="n">
-        <v>9.34037</v>
+        <v>9.27849</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>9.04537</v>
+        <v>9.05578</v>
       </c>
       <c r="C114" t="n">
-        <v>5.81586</v>
+        <v>5.81729</v>
       </c>
       <c r="D114" t="n">
-        <v>53.1645</v>
+        <v>53.1604</v>
       </c>
       <c r="E114" t="n">
-        <v>6.4823</v>
+        <v>5.75542</v>
       </c>
       <c r="F114" t="n">
-        <v>9.912800000000001</v>
+        <v>9.840339999999999</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.71407</v>
+        <v>9.694000000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>6.2221</v>
+        <v>6.2165</v>
       </c>
       <c r="D115" t="n">
-        <v>54.7306</v>
+        <v>54.7386</v>
       </c>
       <c r="E115" t="n">
-        <v>6.72365</v>
+        <v>6.11923</v>
       </c>
       <c r="F115" t="n">
-        <v>10.4486</v>
+        <v>10.4441</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>10.329</v>
+        <v>10.3255</v>
       </c>
       <c r="C116" t="n">
-        <v>6.68656</v>
+        <v>6.70414</v>
       </c>
       <c r="D116" t="n">
-        <v>56.4126</v>
+        <v>56.4095</v>
       </c>
       <c r="E116" t="n">
-        <v>6.99311</v>
+        <v>6.57693</v>
       </c>
       <c r="F116" t="n">
-        <v>11.0311</v>
+        <v>11.0322</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>11.0096</v>
+        <v>10.9518</v>
       </c>
       <c r="C117" t="n">
-        <v>7.19491</v>
+        <v>7.16427</v>
       </c>
       <c r="D117" t="n">
-        <v>58.2405</v>
+        <v>58.2264</v>
       </c>
       <c r="E117" t="n">
-        <v>7.34284</v>
+        <v>7.02592</v>
       </c>
       <c r="F117" t="n">
-        <v>11.5973</v>
+        <v>11.6211</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.7183</v>
+        <v>11.7358</v>
       </c>
       <c r="C118" t="n">
-        <v>7.76927</v>
+        <v>7.77014</v>
       </c>
       <c r="D118" t="n">
-        <v>60.0613</v>
+        <v>60.0982</v>
       </c>
       <c r="E118" t="n">
-        <v>7.71214</v>
+        <v>7.5243</v>
       </c>
       <c r="F118" t="n">
-        <v>12.215</v>
+        <v>12.2633</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.6516</v>
+        <v>12.6654</v>
       </c>
       <c r="C119" t="n">
-        <v>8.51333</v>
+        <v>8.521509999999999</v>
       </c>
       <c r="D119" t="n">
-        <v>62.0467</v>
+        <v>62.0477</v>
       </c>
       <c r="E119" t="n">
-        <v>8.11023</v>
+        <v>7.99169</v>
       </c>
       <c r="F119" t="n">
-        <v>12.99</v>
+        <v>13.0196</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.9</v>
+        <v>13.9313</v>
       </c>
       <c r="C120" t="n">
-        <v>9.58441</v>
+        <v>9.625439999999999</v>
       </c>
       <c r="D120" t="n">
-        <v>64.1373</v>
+        <v>64.1427</v>
       </c>
       <c r="E120" t="n">
-        <v>8.92224</v>
+        <v>8.86675</v>
       </c>
       <c r="F120" t="n">
-        <v>13.9851</v>
+        <v>14.0342</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.6255</v>
+        <v>15.6534</v>
       </c>
       <c r="C121" t="n">
-        <v>11.19</v>
+        <v>11.1921</v>
       </c>
       <c r="D121" t="n">
-        <v>47.5118</v>
+        <v>47.5102</v>
       </c>
       <c r="E121" t="n">
-        <v>6.53399</v>
+        <v>6.70299</v>
       </c>
       <c r="F121" t="n">
-        <v>10.0537</v>
+        <v>10.0472</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>18.1246</v>
+        <v>17.9656</v>
       </c>
       <c r="C122" t="n">
-        <v>6.5546</v>
+        <v>6.66438</v>
       </c>
       <c r="D122" t="n">
-        <v>48.6475</v>
+        <v>48.6172</v>
       </c>
       <c r="E122" t="n">
-        <v>6.74594</v>
+        <v>7.41098</v>
       </c>
       <c r="F122" t="n">
-        <v>9.985950000000001</v>
+        <v>10.9243</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.0486</v>
+        <v>22.2439</v>
       </c>
       <c r="C123" t="n">
-        <v>6.76088</v>
+        <v>6.8768</v>
       </c>
       <c r="D123" t="n">
-        <v>49.5624</v>
+        <v>49.8622</v>
       </c>
       <c r="E123" t="n">
-        <v>7.45382</v>
+        <v>6.76865</v>
       </c>
       <c r="F123" t="n">
-        <v>10.117</v>
+        <v>10.5406</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>10.2449</v>
+        <v>10.0512</v>
       </c>
       <c r="C124" t="n">
-        <v>6.80938</v>
+        <v>6.86668</v>
       </c>
       <c r="D124" t="n">
-        <v>50.9414</v>
+        <v>50.8027</v>
       </c>
       <c r="E124" t="n">
-        <v>7.5039</v>
+        <v>7.1585</v>
       </c>
       <c r="F124" t="n">
-        <v>10.7359</v>
+        <v>10.8543</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.2561</v>
+        <v>10.2124</v>
       </c>
       <c r="C125" t="n">
-        <v>6.81989</v>
+        <v>7.24393</v>
       </c>
       <c r="D125" t="n">
-        <v>52.0919</v>
+        <v>52.2881</v>
       </c>
       <c r="E125" t="n">
-        <v>7.74717</v>
+        <v>7.53736</v>
       </c>
       <c r="F125" t="n">
-        <v>10.7967</v>
+        <v>11.5461</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.4119</v>
+        <v>10.8578</v>
       </c>
       <c r="C126" t="n">
-        <v>7.05221</v>
+        <v>7.10089</v>
       </c>
       <c r="D126" t="n">
-        <v>53.5523</v>
+        <v>53.4451</v>
       </c>
       <c r="E126" t="n">
-        <v>8.190329999999999</v>
+        <v>7.80468</v>
       </c>
       <c r="F126" t="n">
-        <v>11.5047</v>
+        <v>11.6775</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.8066</v>
+        <v>10.8979</v>
       </c>
       <c r="C127" t="n">
-        <v>7.47919</v>
+        <v>7.35589</v>
       </c>
       <c r="D127" t="n">
-        <v>54.9353</v>
+        <v>54.9691</v>
       </c>
       <c r="E127" t="n">
-        <v>8.353120000000001</v>
+        <v>7.84602</v>
       </c>
       <c r="F127" t="n">
-        <v>11.3487</v>
+        <v>11.7826</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>11.0258</v>
+        <v>11.247</v>
       </c>
       <c r="C128" t="n">
-        <v>7.44856</v>
+        <v>7.32797</v>
       </c>
       <c r="D128" t="n">
-        <v>56.4173</v>
+        <v>56.4372</v>
       </c>
       <c r="E128" t="n">
-        <v>8.59887</v>
+        <v>8.06019</v>
       </c>
       <c r="F128" t="n">
-        <v>12.2052</v>
+        <v>12.3494</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>10.976</v>
+        <v>11.4365</v>
       </c>
       <c r="C129" t="n">
-        <v>7.5991</v>
+        <v>7.53398</v>
       </c>
       <c r="D129" t="n">
-        <v>57.9989</v>
+        <v>57.9929</v>
       </c>
       <c r="E129" t="n">
-        <v>8.576499999999999</v>
+        <v>8.16878</v>
       </c>
       <c r="F129" t="n">
-        <v>12.3918</v>
+        <v>12.4295</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.796</v>
+        <v>11.8147</v>
       </c>
       <c r="C130" t="n">
-        <v>7.82711</v>
+        <v>7.8677</v>
       </c>
       <c r="D130" t="n">
-        <v>59.6088</v>
+        <v>59.6557</v>
       </c>
       <c r="E130" t="n">
-        <v>9.03711</v>
+        <v>8.213839999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>12.8463</v>
+        <v>12.8633</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>11.8636</v>
+        <v>11.9637</v>
       </c>
       <c r="C131" t="n">
-        <v>8.167590000000001</v>
+        <v>8.276260000000001</v>
       </c>
       <c r="D131" t="n">
-        <v>61.4308</v>
+        <v>61.4599</v>
       </c>
       <c r="E131" t="n">
-        <v>9.316319999999999</v>
+        <v>8.718640000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>13.5743</v>
+        <v>13.6451</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>12.7518</v>
+        <v>13.0737</v>
       </c>
       <c r="C132" t="n">
-        <v>8.591699999999999</v>
+        <v>8.688219999999999</v>
       </c>
       <c r="D132" t="n">
-        <v>63.3483</v>
+        <v>63.3202</v>
       </c>
       <c r="E132" t="n">
-        <v>9.65564</v>
+        <v>8.968500000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>13.8873</v>
+        <v>14.0018</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.8079</v>
+        <v>13.2393</v>
       </c>
       <c r="C133" t="n">
-        <v>9.39813</v>
+        <v>9.372640000000001</v>
       </c>
       <c r="D133" t="n">
-        <v>65.0427</v>
+        <v>65.1215</v>
       </c>
       <c r="E133" t="n">
-        <v>10.2857</v>
+        <v>9.527229999999999</v>
       </c>
       <c r="F133" t="n">
-        <v>14.7497</v>
+        <v>14.8754</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.8088</v>
+        <v>14.9062</v>
       </c>
       <c r="C134" t="n">
-        <v>10.244</v>
+        <v>10.2283</v>
       </c>
       <c r="D134" t="n">
-        <v>67.3541</v>
+        <v>67.3844</v>
       </c>
       <c r="E134" t="n">
-        <v>10.66</v>
+        <v>10.0767</v>
       </c>
       <c r="F134" t="n">
-        <v>15.4855</v>
+        <v>15.6625</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.5408</v>
+        <v>16.4731</v>
       </c>
       <c r="C135" t="n">
-        <v>11.7619</v>
+        <v>11.7832</v>
       </c>
       <c r="D135" t="n">
-        <v>49.473</v>
+        <v>49.4703</v>
       </c>
       <c r="E135" t="n">
-        <v>13.6545</v>
+        <v>13.0639</v>
       </c>
       <c r="F135" t="n">
-        <v>16.4154</v>
+        <v>16.2319</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.6679</v>
+        <v>18.5871</v>
       </c>
       <c r="C136" t="n">
-        <v>13.3718</v>
+        <v>13.3913</v>
       </c>
       <c r="D136" t="n">
-        <v>50.5283</v>
+        <v>50.3306</v>
       </c>
       <c r="E136" t="n">
-        <v>13.8267</v>
+        <v>13.289</v>
       </c>
       <c r="F136" t="n">
-        <v>16.719</v>
+        <v>16.5844</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>22.3563</v>
+        <v>22.4102</v>
       </c>
       <c r="C137" t="n">
-        <v>13.4367</v>
+        <v>13.4725</v>
       </c>
       <c r="D137" t="n">
-        <v>51.5051</v>
+        <v>51.6757</v>
       </c>
       <c r="E137" t="n">
-        <v>13.9375</v>
+        <v>13.4992</v>
       </c>
       <c r="F137" t="n">
-        <v>16.8258</v>
+        <v>16.7389</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.816</v>
+        <v>16.8094</v>
       </c>
       <c r="C138" t="n">
-        <v>13.5367</v>
+        <v>13.4295</v>
       </c>
       <c r="D138" t="n">
-        <v>52.906</v>
+        <v>52.873</v>
       </c>
       <c r="E138" t="n">
-        <v>14.0914</v>
+        <v>13.4975</v>
       </c>
       <c r="F138" t="n">
-        <v>17.1137</v>
+        <v>17.1593</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>16.9881</v>
+        <v>17.0648</v>
       </c>
       <c r="C139" t="n">
-        <v>13.5897</v>
+        <v>13.7517</v>
       </c>
       <c r="D139" t="n">
-        <v>54.105</v>
+        <v>53.9194</v>
       </c>
       <c r="E139" t="n">
-        <v>14.2147</v>
+        <v>12.9234</v>
       </c>
       <c r="F139" t="n">
-        <v>17.3634</v>
+        <v>17.4312</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>17.2503</v>
+        <v>17.0972</v>
       </c>
       <c r="C140" t="n">
-        <v>13.7187</v>
+        <v>13.6223</v>
       </c>
       <c r="D140" t="n">
-        <v>55.319</v>
+        <v>55.3281</v>
       </c>
       <c r="E140" t="n">
-        <v>14.4057</v>
+        <v>13.8655</v>
       </c>
       <c r="F140" t="n">
-        <v>17.7995</v>
+        <v>16.9394</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>17.3371</v>
+        <v>17.4134</v>
       </c>
       <c r="C141" t="n">
-        <v>13.9544</v>
+        <v>13.9246</v>
       </c>
       <c r="D141" t="n">
-        <v>56.8031</v>
+        <v>56.8242</v>
       </c>
       <c r="E141" t="n">
-        <v>14.0666</v>
+        <v>13.5031</v>
       </c>
       <c r="F141" t="n">
-        <v>18.1555</v>
+        <v>17.9719</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>17.5551</v>
+        <v>17.4517</v>
       </c>
       <c r="C142" t="n">
-        <v>13.8651</v>
+        <v>13.9849</v>
       </c>
       <c r="D142" t="n">
-        <v>58.274</v>
+        <v>58.2971</v>
       </c>
       <c r="E142" t="n">
-        <v>14.7526</v>
+        <v>13.4188</v>
       </c>
       <c r="F142" t="n">
-        <v>18.3762</v>
+        <v>18.4375</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.5665</v>
+        <v>17.1906</v>
       </c>
       <c r="C143" t="n">
-        <v>14.3555</v>
+        <v>14.2482</v>
       </c>
       <c r="D143" t="n">
-        <v>59.8433</v>
+        <v>59.8939</v>
       </c>
       <c r="E143" t="n">
-        <v>14.2385</v>
+        <v>14.2442</v>
       </c>
       <c r="F143" t="n">
-        <v>18.7263</v>
+        <v>18.7114</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered unsuccessful looukp.xlsx
+++ b/clang-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.72544</v>
+        <v>2.72521</v>
       </c>
       <c r="C2" t="n">
-        <v>2.07382</v>
+        <v>2.07048</v>
       </c>
       <c r="D2" t="n">
-        <v>12.2879</v>
+        <v>12.526</v>
       </c>
       <c r="E2" t="n">
-        <v>2.61428</v>
+        <v>2.6195</v>
       </c>
       <c r="F2" t="n">
-        <v>2.41503</v>
+        <v>2.46762</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.7543</v>
+        <v>2.78648</v>
       </c>
       <c r="C3" t="n">
-        <v>2.16839</v>
+        <v>2.17882</v>
       </c>
       <c r="D3" t="n">
-        <v>12.7707</v>
+        <v>13.068</v>
       </c>
       <c r="E3" t="n">
-        <v>2.69341</v>
+        <v>2.6984</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4987</v>
+        <v>2.5438</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.84937</v>
+        <v>2.87503</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3583</v>
+        <v>2.37783</v>
       </c>
       <c r="D4" t="n">
-        <v>13.2669</v>
+        <v>13.6543</v>
       </c>
       <c r="E4" t="n">
-        <v>2.77472</v>
+        <v>2.78574</v>
       </c>
       <c r="F4" t="n">
-        <v>2.62131</v>
+        <v>2.68356</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.21722</v>
+        <v>3.24888</v>
       </c>
       <c r="C5" t="n">
-        <v>2.73354</v>
+        <v>2.72416</v>
       </c>
       <c r="D5" t="n">
-        <v>13.8992</v>
+        <v>14.1533</v>
       </c>
       <c r="E5" t="n">
-        <v>2.90809</v>
+        <v>2.91871</v>
       </c>
       <c r="F5" t="n">
-        <v>2.77943</v>
+        <v>2.78839</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.07725</v>
+        <v>4.10196</v>
       </c>
       <c r="C6" t="n">
-        <v>3.52042</v>
+        <v>3.54205</v>
       </c>
       <c r="D6" t="n">
-        <v>14.5626</v>
+        <v>14.8808</v>
       </c>
       <c r="E6" t="n">
-        <v>3.10702</v>
+        <v>3.13546</v>
       </c>
       <c r="F6" t="n">
-        <v>2.97679</v>
+        <v>3.00458</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.57206</v>
+        <v>6.59284</v>
       </c>
       <c r="C7" t="n">
-        <v>5.2672</v>
+        <v>5.26127</v>
       </c>
       <c r="D7" t="n">
-        <v>10.1346</v>
+        <v>10.4434</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3559</v>
+        <v>2.36287</v>
       </c>
       <c r="F7" t="n">
-        <v>2.11174</v>
+        <v>2.111</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.53595</v>
+        <v>9.53125</v>
       </c>
       <c r="C8" t="n">
-        <v>1.74689</v>
+        <v>1.74216</v>
       </c>
       <c r="D8" t="n">
-        <v>10.8011</v>
+        <v>11.0693</v>
       </c>
       <c r="E8" t="n">
-        <v>2.37018</v>
+        <v>2.37802</v>
       </c>
       <c r="F8" t="n">
-        <v>2.13525</v>
+        <v>2.1418</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.8536</v>
+        <v>13.9063</v>
       </c>
       <c r="C9" t="n">
-        <v>1.76777</v>
+        <v>1.76224</v>
       </c>
       <c r="D9" t="n">
-        <v>11.4007</v>
+        <v>11.6</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3948</v>
+        <v>2.39855</v>
       </c>
       <c r="F9" t="n">
-        <v>2.16222</v>
+        <v>2.16632</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.62243</v>
+        <v>2.62111</v>
       </c>
       <c r="C10" t="n">
-        <v>1.80493</v>
+        <v>1.79891</v>
       </c>
       <c r="D10" t="n">
-        <v>12.0953</v>
+        <v>12.2836</v>
       </c>
       <c r="E10" t="n">
-        <v>2.42141</v>
+        <v>2.42701</v>
       </c>
       <c r="F10" t="n">
-        <v>2.20115</v>
+        <v>2.20805</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.69804</v>
+        <v>2.6899</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8438</v>
+        <v>1.84233</v>
       </c>
       <c r="D11" t="n">
-        <v>12.6927</v>
+        <v>12.8727</v>
       </c>
       <c r="E11" t="n">
-        <v>2.44409</v>
+        <v>2.4514</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2442</v>
+        <v>2.24335</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.70613</v>
+        <v>2.70817</v>
       </c>
       <c r="C12" t="n">
-        <v>1.87731</v>
+        <v>1.87973</v>
       </c>
       <c r="D12" t="n">
-        <v>13.1926</v>
+        <v>13.3018</v>
       </c>
       <c r="E12" t="n">
-        <v>2.46999</v>
+        <v>2.47578</v>
       </c>
       <c r="F12" t="n">
-        <v>2.29315</v>
+        <v>2.28802</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.68567</v>
+        <v>2.69146</v>
       </c>
       <c r="C13" t="n">
-        <v>1.91942</v>
+        <v>1.91617</v>
       </c>
       <c r="D13" t="n">
-        <v>13.6032</v>
+        <v>13.7245</v>
       </c>
       <c r="E13" t="n">
-        <v>2.49505</v>
+        <v>2.50163</v>
       </c>
       <c r="F13" t="n">
-        <v>2.30423</v>
+        <v>2.32904</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.77232</v>
+        <v>2.76887</v>
       </c>
       <c r="C14" t="n">
-        <v>2.02874</v>
+        <v>2.03651</v>
       </c>
       <c r="D14" t="n">
-        <v>14.1267</v>
+        <v>14.1439</v>
       </c>
       <c r="E14" t="n">
-        <v>2.52132</v>
+        <v>2.52997</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3576</v>
+        <v>2.385</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.88474</v>
+        <v>2.8875</v>
       </c>
       <c r="C15" t="n">
-        <v>2.10813</v>
+        <v>2.11172</v>
       </c>
       <c r="D15" t="n">
-        <v>14.5548</v>
+        <v>14.5707</v>
       </c>
       <c r="E15" t="n">
-        <v>2.57371</v>
+        <v>2.58233</v>
       </c>
       <c r="F15" t="n">
-        <v>2.43108</v>
+        <v>2.46343</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.97073</v>
+        <v>2.96893</v>
       </c>
       <c r="C16" t="n">
-        <v>2.23642</v>
+        <v>2.23201</v>
       </c>
       <c r="D16" t="n">
-        <v>14.9759</v>
+        <v>14.9826</v>
       </c>
       <c r="E16" t="n">
-        <v>2.62246</v>
+        <v>2.63222</v>
       </c>
       <c r="F16" t="n">
-        <v>2.49567</v>
+        <v>2.54793</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.16559</v>
+        <v>3.16512</v>
       </c>
       <c r="C17" t="n">
-        <v>2.40087</v>
+        <v>2.40345</v>
       </c>
       <c r="D17" t="n">
-        <v>15.3971</v>
+        <v>15.435</v>
       </c>
       <c r="E17" t="n">
-        <v>2.688</v>
+        <v>2.70092</v>
       </c>
       <c r="F17" t="n">
-        <v>2.58836</v>
+        <v>2.62172</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.54382</v>
+        <v>3.53894</v>
       </c>
       <c r="C18" t="n">
-        <v>2.69241</v>
+        <v>2.68296</v>
       </c>
       <c r="D18" t="n">
-        <v>15.7785</v>
+        <v>15.8104</v>
       </c>
       <c r="E18" t="n">
-        <v>2.81007</v>
+        <v>2.82331</v>
       </c>
       <c r="F18" t="n">
-        <v>2.77917</v>
+        <v>2.80797</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.13751</v>
+        <v>4.1475</v>
       </c>
       <c r="C19" t="n">
-        <v>3.29031</v>
+        <v>3.28546</v>
       </c>
       <c r="D19" t="n">
-        <v>16.2403</v>
+        <v>16.2341</v>
       </c>
       <c r="E19" t="n">
-        <v>2.99883</v>
+        <v>3.01171</v>
       </c>
       <c r="F19" t="n">
-        <v>2.97525</v>
+        <v>3.02111</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.21248</v>
+        <v>5.22334</v>
       </c>
       <c r="C20" t="n">
-        <v>4.25768</v>
+        <v>4.25828</v>
       </c>
       <c r="D20" t="n">
-        <v>16.6032</v>
+        <v>16.6516</v>
       </c>
       <c r="E20" t="n">
-        <v>3.39793</v>
+        <v>3.40954</v>
       </c>
       <c r="F20" t="n">
-        <v>3.3652</v>
+        <v>3.41992</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.97315</v>
+        <v>6.97091</v>
       </c>
       <c r="C21" t="n">
-        <v>5.53108</v>
+        <v>5.52671</v>
       </c>
       <c r="D21" t="n">
-        <v>11.7893</v>
+        <v>11.7491</v>
       </c>
       <c r="E21" t="n">
-        <v>2.38421</v>
+        <v>2.39075</v>
       </c>
       <c r="F21" t="n">
-        <v>2.18164</v>
+        <v>2.21576</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.28983</v>
+        <v>9.322760000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>1.86066</v>
+        <v>1.83359</v>
       </c>
       <c r="D22" t="n">
-        <v>12.3239</v>
+        <v>12.2981</v>
       </c>
       <c r="E22" t="n">
-        <v>2.40578</v>
+        <v>2.41422</v>
       </c>
       <c r="F22" t="n">
-        <v>2.22494</v>
+        <v>2.24283</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.5804</v>
+        <v>12.5993</v>
       </c>
       <c r="C23" t="n">
-        <v>1.8759</v>
+        <v>1.8774</v>
       </c>
       <c r="D23" t="n">
-        <v>12.8769</v>
+        <v>12.7525</v>
       </c>
       <c r="E23" t="n">
-        <v>2.42693</v>
+        <v>2.43593</v>
       </c>
       <c r="F23" t="n">
-        <v>2.24488</v>
+        <v>2.27322</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.76607</v>
+        <v>2.73814</v>
       </c>
       <c r="C24" t="n">
-        <v>1.91746</v>
+        <v>1.86857</v>
       </c>
       <c r="D24" t="n">
-        <v>13.3427</v>
+        <v>13.2995</v>
       </c>
       <c r="E24" t="n">
-        <v>2.45171</v>
+        <v>2.45944</v>
       </c>
       <c r="F24" t="n">
-        <v>2.28543</v>
+        <v>2.32143</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.7749</v>
+        <v>2.76538</v>
       </c>
       <c r="C25" t="n">
-        <v>1.94901</v>
+        <v>1.90357</v>
       </c>
       <c r="D25" t="n">
-        <v>13.8073</v>
+        <v>13.7644</v>
       </c>
       <c r="E25" t="n">
-        <v>2.47913</v>
+        <v>2.49023</v>
       </c>
       <c r="F25" t="n">
-        <v>2.35582</v>
+        <v>2.35734</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.87168</v>
+        <v>2.8419</v>
       </c>
       <c r="C26" t="n">
-        <v>1.99105</v>
+        <v>1.9398</v>
       </c>
       <c r="D26" t="n">
-        <v>14.1918</v>
+        <v>14.1683</v>
       </c>
       <c r="E26" t="n">
-        <v>2.51076</v>
+        <v>2.52131</v>
       </c>
       <c r="F26" t="n">
-        <v>2.40149</v>
+        <v>2.41064</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.96329</v>
+        <v>2.93183</v>
       </c>
       <c r="C27" t="n">
-        <v>1.99153</v>
+        <v>1.98028</v>
       </c>
       <c r="D27" t="n">
-        <v>14.673</v>
+        <v>14.6578</v>
       </c>
       <c r="E27" t="n">
-        <v>2.5375</v>
+        <v>2.54838</v>
       </c>
       <c r="F27" t="n">
-        <v>2.43926</v>
+        <v>2.44945</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.03432</v>
+        <v>3.00808</v>
       </c>
       <c r="C28" t="n">
-        <v>2.10009</v>
+        <v>2.08914</v>
       </c>
       <c r="D28" t="n">
-        <v>15.1295</v>
+        <v>15.1049</v>
       </c>
       <c r="E28" t="n">
-        <v>2.58366</v>
+        <v>2.59376</v>
       </c>
       <c r="F28" t="n">
-        <v>2.5245</v>
+        <v>2.5206</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.17058</v>
+        <v>3.1434</v>
       </c>
       <c r="C29" t="n">
-        <v>2.21151</v>
+        <v>2.17204</v>
       </c>
       <c r="D29" t="n">
-        <v>15.5514</v>
+        <v>15.5259</v>
       </c>
       <c r="E29" t="n">
-        <v>2.63637</v>
+        <v>2.6439</v>
       </c>
       <c r="F29" t="n">
-        <v>2.60239</v>
+        <v>2.60544</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.32597</v>
+        <v>3.31583</v>
       </c>
       <c r="C30" t="n">
-        <v>2.3506</v>
+        <v>2.30636</v>
       </c>
       <c r="D30" t="n">
-        <v>16.0024</v>
+        <v>15.9736</v>
       </c>
       <c r="E30" t="n">
-        <v>2.69726</v>
+        <v>2.70796</v>
       </c>
       <c r="F30" t="n">
-        <v>2.68891</v>
+        <v>2.69175</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.58023</v>
+        <v>3.56809</v>
       </c>
       <c r="C31" t="n">
-        <v>2.49148</v>
+        <v>2.49285</v>
       </c>
       <c r="D31" t="n">
-        <v>16.3862</v>
+        <v>16.3676</v>
       </c>
       <c r="E31" t="n">
-        <v>2.76491</v>
+        <v>2.77622</v>
       </c>
       <c r="F31" t="n">
-        <v>2.78456</v>
+        <v>2.77807</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.00361</v>
+        <v>3.99222</v>
       </c>
       <c r="C32" t="n">
-        <v>2.7896</v>
+        <v>2.7664</v>
       </c>
       <c r="D32" t="n">
-        <v>16.703</v>
+        <v>16.691</v>
       </c>
       <c r="E32" t="n">
-        <v>2.87177</v>
+        <v>2.88777</v>
       </c>
       <c r="F32" t="n">
-        <v>2.94829</v>
+        <v>2.93838</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.7215</v>
+        <v>4.71778</v>
       </c>
       <c r="C33" t="n">
-        <v>3.32974</v>
+        <v>3.31132</v>
       </c>
       <c r="D33" t="n">
-        <v>17.1578</v>
+        <v>17.1261</v>
       </c>
       <c r="E33" t="n">
-        <v>3.09295</v>
+        <v>3.10418</v>
       </c>
       <c r="F33" t="n">
-        <v>3.18937</v>
+        <v>3.18662</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.72622</v>
+        <v>5.7397</v>
       </c>
       <c r="C34" t="n">
-        <v>4.11936</v>
+        <v>4.11096</v>
       </c>
       <c r="D34" t="n">
-        <v>17.5566</v>
+        <v>17.5303</v>
       </c>
       <c r="E34" t="n">
-        <v>3.49143</v>
+        <v>3.5154</v>
       </c>
       <c r="F34" t="n">
-        <v>3.60833</v>
+        <v>3.59787</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.25176</v>
+        <v>7.24746</v>
       </c>
       <c r="C35" t="n">
-        <v>5.24826</v>
+        <v>5.24674</v>
       </c>
       <c r="D35" t="n">
-        <v>12.2475</v>
+        <v>12.1984</v>
       </c>
       <c r="E35" t="n">
-        <v>2.402</v>
+        <v>2.41279</v>
       </c>
       <c r="F35" t="n">
-        <v>2.31989</v>
+        <v>2.31896</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.474080000000001</v>
+        <v>9.478120000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>6.85672</v>
+        <v>6.87131</v>
       </c>
       <c r="D36" t="n">
-        <v>12.7279</v>
+        <v>12.7062</v>
       </c>
       <c r="E36" t="n">
-        <v>2.42084</v>
+        <v>2.43131</v>
       </c>
       <c r="F36" t="n">
-        <v>2.35165</v>
+        <v>2.34924</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.0868</v>
+        <v>13.0819</v>
       </c>
       <c r="C37" t="n">
-        <v>1.88573</v>
+        <v>1.87807</v>
       </c>
       <c r="D37" t="n">
-        <v>13.1724</v>
+        <v>13.1749</v>
       </c>
       <c r="E37" t="n">
-        <v>2.44759</v>
+        <v>2.45895</v>
       </c>
       <c r="F37" t="n">
-        <v>2.39044</v>
+        <v>2.38566</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.8235</v>
+        <v>2.84244</v>
       </c>
       <c r="C38" t="n">
-        <v>1.88765</v>
+        <v>1.8879</v>
       </c>
       <c r="D38" t="n">
-        <v>13.6831</v>
+        <v>13.6613</v>
       </c>
       <c r="E38" t="n">
-        <v>2.47356</v>
+        <v>2.48366</v>
       </c>
       <c r="F38" t="n">
-        <v>2.44169</v>
+        <v>2.43781</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.8736</v>
+        <v>2.90155</v>
       </c>
       <c r="C39" t="n">
-        <v>1.98678</v>
+        <v>1.93385</v>
       </c>
       <c r="D39" t="n">
-        <v>14.1509</v>
+        <v>14.137</v>
       </c>
       <c r="E39" t="n">
-        <v>2.5101</v>
+        <v>2.51911</v>
       </c>
       <c r="F39" t="n">
-        <v>2.49247</v>
+        <v>2.49812</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.93817</v>
+        <v>2.93661</v>
       </c>
       <c r="C40" t="n">
-        <v>2.02123</v>
+        <v>2.01555</v>
       </c>
       <c r="D40" t="n">
-        <v>14.5958</v>
+        <v>14.5754</v>
       </c>
       <c r="E40" t="n">
-        <v>2.53609</v>
+        <v>2.54384</v>
       </c>
       <c r="F40" t="n">
-        <v>2.54814</v>
+        <v>2.5497</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.02445</v>
+        <v>3.01317</v>
       </c>
       <c r="C41" t="n">
-        <v>2.11756</v>
+        <v>2.06989</v>
       </c>
       <c r="D41" t="n">
-        <v>15.0192</v>
+        <v>15.0256</v>
       </c>
       <c r="E41" t="n">
-        <v>2.56997</v>
+        <v>2.57812</v>
       </c>
       <c r="F41" t="n">
-        <v>2.61146</v>
+        <v>2.59278</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.08376</v>
+        <v>3.08279</v>
       </c>
       <c r="C42" t="n">
-        <v>2.14214</v>
+        <v>2.09623</v>
       </c>
       <c r="D42" t="n">
-        <v>15.4636</v>
+        <v>15.4479</v>
       </c>
       <c r="E42" t="n">
-        <v>2.61036</v>
+        <v>2.6162</v>
       </c>
       <c r="F42" t="n">
-        <v>2.65704</v>
+        <v>2.66706</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.24805</v>
+        <v>3.24674</v>
       </c>
       <c r="C43" t="n">
-        <v>2.19091</v>
+        <v>2.20048</v>
       </c>
       <c r="D43" t="n">
-        <v>15.8999</v>
+        <v>15.8768</v>
       </c>
       <c r="E43" t="n">
-        <v>2.65595</v>
+        <v>2.66413</v>
       </c>
       <c r="F43" t="n">
-        <v>2.73539</v>
+        <v>2.73446</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.43374</v>
+        <v>3.42915</v>
       </c>
       <c r="C44" t="n">
-        <v>2.3309</v>
+        <v>2.33222</v>
       </c>
       <c r="D44" t="n">
-        <v>16.3037</v>
+        <v>16.2869</v>
       </c>
       <c r="E44" t="n">
-        <v>2.73122</v>
+        <v>2.74398</v>
       </c>
       <c r="F44" t="n">
-        <v>2.85145</v>
+        <v>2.84214</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.6862</v>
+        <v>3.68863</v>
       </c>
       <c r="C45" t="n">
-        <v>2.59304</v>
+        <v>2.60171</v>
       </c>
       <c r="D45" t="n">
-        <v>16.6909</v>
+        <v>16.6784</v>
       </c>
       <c r="E45" t="n">
-        <v>2.81511</v>
+        <v>2.83199</v>
       </c>
       <c r="F45" t="n">
-        <v>2.96648</v>
+        <v>2.95781</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.055</v>
+        <v>4.05287</v>
       </c>
       <c r="C46" t="n">
-        <v>2.8952</v>
+        <v>2.8981</v>
       </c>
       <c r="D46" t="n">
-        <v>17.0891</v>
+        <v>17.0874</v>
       </c>
       <c r="E46" t="n">
-        <v>2.94228</v>
+        <v>2.9604</v>
       </c>
       <c r="F46" t="n">
-        <v>3.14569</v>
+        <v>3.11361</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.66306</v>
+        <v>4.66261</v>
       </c>
       <c r="C47" t="n">
-        <v>3.35147</v>
+        <v>3.35005</v>
       </c>
       <c r="D47" t="n">
-        <v>17.5216</v>
+        <v>17.4979</v>
       </c>
       <c r="E47" t="n">
-        <v>3.16693</v>
+        <v>3.17975</v>
       </c>
       <c r="F47" t="n">
-        <v>3.36605</v>
+        <v>3.35197</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.45538</v>
+        <v>5.45381</v>
       </c>
       <c r="C48" t="n">
-        <v>4.05537</v>
+        <v>4.03229</v>
       </c>
       <c r="D48" t="n">
-        <v>17.9552</v>
+        <v>17.9495</v>
       </c>
       <c r="E48" t="n">
-        <v>3.5448</v>
+        <v>3.55137</v>
       </c>
       <c r="F48" t="n">
-        <v>3.73873</v>
+        <v>3.73008</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.58931</v>
+        <v>6.58546</v>
       </c>
       <c r="C49" t="n">
-        <v>4.99195</v>
+        <v>4.97205</v>
       </c>
       <c r="D49" t="n">
-        <v>18.4132</v>
+        <v>18.3918</v>
       </c>
       <c r="E49" t="n">
-        <v>4.08799</v>
+        <v>4.10141</v>
       </c>
       <c r="F49" t="n">
-        <v>4.26668</v>
+        <v>4.2705</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.530900000000001</v>
+        <v>8.536490000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>6.48248</v>
+        <v>6.47452</v>
       </c>
       <c r="D50" t="n">
-        <v>12.8458</v>
+        <v>12.8341</v>
       </c>
       <c r="E50" t="n">
-        <v>2.45926</v>
+        <v>2.46597</v>
       </c>
       <c r="F50" t="n">
-        <v>2.57648</v>
+        <v>2.59198</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>11.1653</v>
+        <v>11.1673</v>
       </c>
       <c r="C51" t="n">
-        <v>1.97623</v>
+        <v>1.96052</v>
       </c>
       <c r="D51" t="n">
-        <v>13.3034</v>
+        <v>13.3019</v>
       </c>
       <c r="E51" t="n">
-        <v>2.47182</v>
+        <v>2.47935</v>
       </c>
       <c r="F51" t="n">
-        <v>2.60476</v>
+        <v>2.61548</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.5802</v>
+        <v>15.5757</v>
       </c>
       <c r="C52" t="n">
-        <v>2.0479</v>
+        <v>2.02471</v>
       </c>
       <c r="D52" t="n">
-        <v>13.7811</v>
+        <v>13.7771</v>
       </c>
       <c r="E52" t="n">
-        <v>2.49641</v>
+        <v>2.50621</v>
       </c>
       <c r="F52" t="n">
-        <v>2.6877</v>
+        <v>2.68829</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.0449</v>
+        <v>2.99784</v>
       </c>
       <c r="C53" t="n">
-        <v>2.08024</v>
+        <v>2.07776</v>
       </c>
       <c r="D53" t="n">
-        <v>14.274</v>
+        <v>14.2576</v>
       </c>
       <c r="E53" t="n">
-        <v>2.52255</v>
+        <v>2.5332</v>
       </c>
       <c r="F53" t="n">
-        <v>2.69939</v>
+        <v>2.71459</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.12671</v>
+        <v>3.09956</v>
       </c>
       <c r="C54" t="n">
-        <v>2.22895</v>
+        <v>2.61019</v>
       </c>
       <c r="D54" t="n">
-        <v>14.7655</v>
+        <v>14.7509</v>
       </c>
       <c r="E54" t="n">
-        <v>2.58948</v>
+        <v>2.72548</v>
       </c>
       <c r="F54" t="n">
-        <v>2.77631</v>
+        <v>2.77939</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.13506</v>
+        <v>3.15371</v>
       </c>
       <c r="C55" t="n">
-        <v>2.36133</v>
+        <v>2.50923</v>
       </c>
       <c r="D55" t="n">
-        <v>15.231</v>
+        <v>15.2066</v>
       </c>
       <c r="E55" t="n">
-        <v>2.61363</v>
+        <v>2.93658</v>
       </c>
       <c r="F55" t="n">
-        <v>2.88865</v>
+        <v>2.84002</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.31406</v>
+        <v>3.2601</v>
       </c>
       <c r="C56" t="n">
-        <v>2.23236</v>
+        <v>2.20878</v>
       </c>
       <c r="D56" t="n">
-        <v>15.7047</v>
+        <v>15.6718</v>
       </c>
       <c r="E56" t="n">
-        <v>2.65766</v>
+        <v>2.9847</v>
       </c>
       <c r="F56" t="n">
-        <v>2.94272</v>
+        <v>2.89802</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.41809</v>
+        <v>3.41733</v>
       </c>
       <c r="C57" t="n">
-        <v>2.37192</v>
+        <v>2.67067</v>
       </c>
       <c r="D57" t="n">
-        <v>16.1056</v>
+        <v>16.1119</v>
       </c>
       <c r="E57" t="n">
-        <v>2.7206</v>
+        <v>2.88595</v>
       </c>
       <c r="F57" t="n">
-        <v>2.98461</v>
+        <v>2.93953</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.63623</v>
+        <v>3.55974</v>
       </c>
       <c r="C58" t="n">
-        <v>2.43971</v>
+        <v>2.43487</v>
       </c>
       <c r="D58" t="n">
-        <v>16.5521</v>
+        <v>16.549</v>
       </c>
       <c r="E58" t="n">
-        <v>2.79326</v>
+        <v>2.86017</v>
       </c>
       <c r="F58" t="n">
-        <v>3.02275</v>
+        <v>3.07833</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.83914</v>
+        <v>3.82743</v>
       </c>
       <c r="C59" t="n">
-        <v>2.68019</v>
+        <v>2.97869</v>
       </c>
       <c r="D59" t="n">
-        <v>16.9322</v>
+        <v>16.9545</v>
       </c>
       <c r="E59" t="n">
-        <v>3.12983</v>
+        <v>3.26195</v>
       </c>
       <c r="F59" t="n">
-        <v>3.17308</v>
+        <v>3.12737</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.17696</v>
+        <v>4.1674</v>
       </c>
       <c r="C60" t="n">
-        <v>3.36803</v>
+        <v>3.35198</v>
       </c>
       <c r="D60" t="n">
-        <v>17.3742</v>
+        <v>17.4508</v>
       </c>
       <c r="E60" t="n">
-        <v>3.21375</v>
+        <v>3.30126</v>
       </c>
       <c r="F60" t="n">
-        <v>3.29419</v>
+        <v>3.29285</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.56405</v>
+        <v>4.49362</v>
       </c>
       <c r="C61" t="n">
-        <v>3.29767</v>
+        <v>3.28324</v>
       </c>
       <c r="D61" t="n">
-        <v>17.8261</v>
+        <v>17.9266</v>
       </c>
       <c r="E61" t="n">
-        <v>3.23821</v>
+        <v>3.43525</v>
       </c>
       <c r="F61" t="n">
-        <v>3.48038</v>
+        <v>3.50632</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.27237</v>
+        <v>5.27258</v>
       </c>
       <c r="C62" t="n">
-        <v>3.93073</v>
+        <v>4.28572</v>
       </c>
       <c r="D62" t="n">
-        <v>18.2523</v>
+        <v>18.4458</v>
       </c>
       <c r="E62" t="n">
-        <v>3.55025</v>
+        <v>3.75015</v>
       </c>
       <c r="F62" t="n">
-        <v>3.84595</v>
+        <v>3.80098</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.3783</v>
+        <v>6.38281</v>
       </c>
       <c r="C63" t="n">
-        <v>4.80007</v>
+        <v>5.14031</v>
       </c>
       <c r="D63" t="n">
-        <v>18.8205</v>
+        <v>18.9819</v>
       </c>
       <c r="E63" t="n">
-        <v>4.05566</v>
+        <v>4.27165</v>
       </c>
       <c r="F63" t="n">
-        <v>4.32457</v>
+        <v>4.34514</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>8.04485</v>
+        <v>7.98287</v>
       </c>
       <c r="C64" t="n">
-        <v>6.14772</v>
+        <v>6.20746</v>
       </c>
       <c r="D64" t="n">
-        <v>14.2143</v>
+        <v>14.1441</v>
       </c>
       <c r="E64" t="n">
-        <v>2.72508</v>
+        <v>2.75835</v>
       </c>
       <c r="F64" t="n">
-        <v>3.12233</v>
+        <v>3.11314</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.7337</v>
+        <v>10.7365</v>
       </c>
       <c r="C65" t="n">
-        <v>2.57216</v>
+        <v>2.52516</v>
       </c>
       <c r="D65" t="n">
-        <v>14.7224</v>
+        <v>14.807</v>
       </c>
       <c r="E65" t="n">
-        <v>2.83339</v>
+        <v>2.76422</v>
       </c>
       <c r="F65" t="n">
-        <v>3.18592</v>
+        <v>3.17536</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.6422</v>
+        <v>14.5067</v>
       </c>
       <c r="C66" t="n">
-        <v>2.61666</v>
+        <v>2.58855</v>
       </c>
       <c r="D66" t="n">
-        <v>15.6231</v>
+        <v>15.4991</v>
       </c>
       <c r="E66" t="n">
-        <v>2.85143</v>
+        <v>2.81</v>
       </c>
       <c r="F66" t="n">
-        <v>3.23324</v>
+        <v>3.22415</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.69212</v>
+        <v>3.75943</v>
       </c>
       <c r="C67" t="n">
-        <v>2.6417</v>
+        <v>2.59639</v>
       </c>
       <c r="D67" t="n">
-        <v>16.3855</v>
+        <v>16.4232</v>
       </c>
       <c r="E67" t="n">
-        <v>2.88247</v>
+        <v>2.83128</v>
       </c>
       <c r="F67" t="n">
-        <v>3.28404</v>
+        <v>3.27455</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.74404</v>
+        <v>3.87251</v>
       </c>
       <c r="C68" t="n">
-        <v>2.66649</v>
+        <v>2.62388</v>
       </c>
       <c r="D68" t="n">
-        <v>17.2861</v>
+        <v>17.297</v>
       </c>
       <c r="E68" t="n">
-        <v>2.92978</v>
+        <v>2.8601</v>
       </c>
       <c r="F68" t="n">
-        <v>3.33453</v>
+        <v>3.33112</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.72026</v>
+        <v>3.91488</v>
       </c>
       <c r="C69" t="n">
-        <v>2.66781</v>
+        <v>2.63835</v>
       </c>
       <c r="D69" t="n">
-        <v>18.174</v>
+        <v>18.3921</v>
       </c>
       <c r="E69" t="n">
-        <v>2.90352</v>
+        <v>2.89928</v>
       </c>
       <c r="F69" t="n">
-        <v>3.39815</v>
+        <v>3.39434</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.78387</v>
+        <v>3.84438</v>
       </c>
       <c r="C70" t="n">
-        <v>2.78268</v>
+        <v>2.70735</v>
       </c>
       <c r="D70" t="n">
-        <v>19.0638</v>
+        <v>19.7621</v>
       </c>
       <c r="E70" t="n">
-        <v>2.96295</v>
+        <v>2.94004</v>
       </c>
       <c r="F70" t="n">
-        <v>3.47645</v>
+        <v>3.46525</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.85728</v>
+        <v>3.95698</v>
       </c>
       <c r="C71" t="n">
-        <v>2.81274</v>
+        <v>2.79713</v>
       </c>
       <c r="D71" t="n">
-        <v>20.0366</v>
+        <v>20.9795</v>
       </c>
       <c r="E71" t="n">
-        <v>3.03945</v>
+        <v>3.05759</v>
       </c>
       <c r="F71" t="n">
-        <v>3.51754</v>
+        <v>3.62289</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.01267</v>
+        <v>4.27368</v>
       </c>
       <c r="C72" t="n">
-        <v>2.94022</v>
+        <v>2.88838</v>
       </c>
       <c r="D72" t="n">
-        <v>21.1288</v>
+        <v>22.1592</v>
       </c>
       <c r="E72" t="n">
-        <v>3.11806</v>
+        <v>3.14267</v>
       </c>
       <c r="F72" t="n">
-        <v>3.62193</v>
+        <v>3.7391</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.23877</v>
+        <v>4.34144</v>
       </c>
       <c r="C73" t="n">
-        <v>3.13485</v>
+        <v>3.13268</v>
       </c>
       <c r="D73" t="n">
-        <v>22.1732</v>
+        <v>23.7979</v>
       </c>
       <c r="E73" t="n">
-        <v>3.21049</v>
+        <v>3.24651</v>
       </c>
       <c r="F73" t="n">
-        <v>3.74584</v>
+        <v>3.89018</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.48596</v>
+        <v>4.63214</v>
       </c>
       <c r="C74" t="n">
-        <v>3.31762</v>
+        <v>3.34326</v>
       </c>
       <c r="D74" t="n">
-        <v>23.545</v>
+        <v>25.3992</v>
       </c>
       <c r="E74" t="n">
-        <v>3.31017</v>
+        <v>3.37683</v>
       </c>
       <c r="F74" t="n">
-        <v>3.9594</v>
+        <v>4.12313</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>4.99406</v>
+        <v>5.16938</v>
       </c>
       <c r="C75" t="n">
-        <v>3.63187</v>
+        <v>3.71508</v>
       </c>
       <c r="D75" t="n">
-        <v>24.8739</v>
+        <v>26.4579</v>
       </c>
       <c r="E75" t="n">
-        <v>3.49887</v>
+        <v>3.55928</v>
       </c>
       <c r="F75" t="n">
-        <v>4.15165</v>
+        <v>4.35647</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.53655</v>
+        <v>5.70159</v>
       </c>
       <c r="C76" t="n">
-        <v>4.16763</v>
+        <v>4.2353</v>
       </c>
       <c r="D76" t="n">
-        <v>26.2464</v>
+        <v>27.9213</v>
       </c>
       <c r="E76" t="n">
-        <v>3.84076</v>
+        <v>3.87989</v>
       </c>
       <c r="F76" t="n">
-        <v>4.54659</v>
+        <v>4.47212</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.51638</v>
+        <v>6.72204</v>
       </c>
       <c r="C77" t="n">
-        <v>5.00964</v>
+        <v>5.06774</v>
       </c>
       <c r="D77" t="n">
-        <v>27.8325</v>
+        <v>29.2717</v>
       </c>
       <c r="E77" t="n">
-        <v>4.31254</v>
+        <v>4.36351</v>
       </c>
       <c r="F77" t="n">
-        <v>4.92281</v>
+        <v>4.97407</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.11439</v>
+        <v>8.42112</v>
       </c>
       <c r="C78" t="n">
-        <v>6.3128</v>
+        <v>6.3243</v>
       </c>
       <c r="D78" t="n">
-        <v>24.038</v>
+        <v>24.7827</v>
       </c>
       <c r="E78" t="n">
-        <v>3.0508</v>
+        <v>3.0875</v>
       </c>
       <c r="F78" t="n">
-        <v>3.56008</v>
+        <v>3.65127</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.4531</v>
+        <v>10.6907</v>
       </c>
       <c r="C79" t="n">
-        <v>2.8916</v>
+        <v>2.90606</v>
       </c>
       <c r="D79" t="n">
-        <v>25.4406</v>
+        <v>26.0958</v>
       </c>
       <c r="E79" t="n">
-        <v>3.18945</v>
+        <v>3.16837</v>
       </c>
       <c r="F79" t="n">
-        <v>3.6253</v>
+        <v>3.72386</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>14.2876</v>
+        <v>14.6972</v>
       </c>
       <c r="C80" t="n">
-        <v>2.91229</v>
+        <v>2.95277</v>
       </c>
       <c r="D80" t="n">
-        <v>26.7122</v>
+        <v>27.3774</v>
       </c>
       <c r="E80" t="n">
-        <v>3.12476</v>
+        <v>3.17053</v>
       </c>
       <c r="F80" t="n">
-        <v>3.74049</v>
+        <v>3.81188</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.17345</v>
+        <v>4.25029</v>
       </c>
       <c r="C81" t="n">
-        <v>3.01865</v>
+        <v>3.00219</v>
       </c>
       <c r="D81" t="n">
-        <v>28.0498</v>
+        <v>28.7328</v>
       </c>
       <c r="E81" t="n">
-        <v>3.16893</v>
+        <v>3.22758</v>
       </c>
       <c r="F81" t="n">
-        <v>3.81223</v>
+        <v>3.95919</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.31817</v>
+        <v>4.41837</v>
       </c>
       <c r="C82" t="n">
-        <v>3.12251</v>
+        <v>3.08632</v>
       </c>
       <c r="D82" t="n">
-        <v>29.4175</v>
+        <v>30.117</v>
       </c>
       <c r="E82" t="n">
-        <v>3.22682</v>
+        <v>3.29119</v>
       </c>
       <c r="F82" t="n">
-        <v>3.98438</v>
+        <v>4.09189</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.50499</v>
+        <v>4.59502</v>
       </c>
       <c r="C83" t="n">
-        <v>3.23018</v>
+        <v>3.19937</v>
       </c>
       <c r="D83" t="n">
-        <v>30.8291</v>
+        <v>31.5247</v>
       </c>
       <c r="E83" t="n">
-        <v>3.27821</v>
+        <v>3.37035</v>
       </c>
       <c r="F83" t="n">
-        <v>4.13612</v>
+        <v>4.24076</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.78378</v>
+        <v>4.75032</v>
       </c>
       <c r="C84" t="n">
-        <v>3.39354</v>
+        <v>3.31453</v>
       </c>
       <c r="D84" t="n">
-        <v>32.3512</v>
+        <v>33.0216</v>
       </c>
       <c r="E84" t="n">
-        <v>3.43947</v>
+        <v>3.49603</v>
       </c>
       <c r="F84" t="n">
-        <v>4.34709</v>
+        <v>4.44003</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>5.14802</v>
+        <v>4.96189</v>
       </c>
       <c r="C85" t="n">
-        <v>3.55567</v>
+        <v>3.46815</v>
       </c>
       <c r="D85" t="n">
-        <v>33.8652</v>
+        <v>34.6077</v>
       </c>
       <c r="E85" t="n">
-        <v>3.53741</v>
+        <v>3.54992</v>
       </c>
       <c r="F85" t="n">
-        <v>4.66091</v>
+        <v>4.702</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.50502</v>
+        <v>5.28404</v>
       </c>
       <c r="C86" t="n">
-        <v>3.82653</v>
+        <v>3.62572</v>
       </c>
       <c r="D86" t="n">
-        <v>35.4296</v>
+        <v>36.2299</v>
       </c>
       <c r="E86" t="n">
-        <v>3.72251</v>
+        <v>3.69273</v>
       </c>
       <c r="F86" t="n">
-        <v>5.00407</v>
+        <v>4.98687</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.96158</v>
+        <v>5.63328</v>
       </c>
       <c r="C87" t="n">
-        <v>4.13513</v>
+        <v>3.85994</v>
       </c>
       <c r="D87" t="n">
-        <v>37.1264</v>
+        <v>37.9405</v>
       </c>
       <c r="E87" t="n">
-        <v>3.9565</v>
+        <v>3.86068</v>
       </c>
       <c r="F87" t="n">
-        <v>5.42135</v>
+        <v>5.2563</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.49687</v>
+        <v>6.02481</v>
       </c>
       <c r="C88" t="n">
-        <v>4.48845</v>
+        <v>4.14849</v>
       </c>
       <c r="D88" t="n">
-        <v>38.7937</v>
+        <v>39.5967</v>
       </c>
       <c r="E88" t="n">
-        <v>4.23381</v>
+        <v>4.03584</v>
       </c>
       <c r="F88" t="n">
-        <v>5.7729</v>
+        <v>5.68081</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>7.16673</v>
+        <v>6.43391</v>
       </c>
       <c r="C89" t="n">
-        <v>4.94267</v>
+        <v>4.5</v>
       </c>
       <c r="D89" t="n">
-        <v>40.7074</v>
+        <v>41.8527</v>
       </c>
       <c r="E89" t="n">
-        <v>4.57515</v>
+        <v>4.29927</v>
       </c>
       <c r="F89" t="n">
-        <v>6.37491</v>
+        <v>6.02704</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>8.048080000000001</v>
+        <v>7.33797</v>
       </c>
       <c r="C90" t="n">
-        <v>5.55457</v>
+        <v>5.06583</v>
       </c>
       <c r="D90" t="n">
-        <v>42.5487</v>
+        <v>43.4037</v>
       </c>
       <c r="E90" t="n">
-        <v>5.04751</v>
+        <v>4.66431</v>
       </c>
       <c r="F90" t="n">
-        <v>7.06507</v>
+        <v>6.93087</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>9.17521</v>
+        <v>8.794320000000001</v>
       </c>
       <c r="C91" t="n">
-        <v>6.42998</v>
+        <v>6.03585</v>
       </c>
       <c r="D91" t="n">
-        <v>44.6164</v>
+        <v>45.4729</v>
       </c>
       <c r="E91" t="n">
-        <v>5.67172</v>
+        <v>5.22239</v>
       </c>
       <c r="F91" t="n">
-        <v>7.9468</v>
+        <v>7.85867</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.5811</v>
+        <v>10.5071</v>
       </c>
       <c r="C92" t="n">
-        <v>7.65267</v>
+        <v>7.40394</v>
       </c>
       <c r="D92" t="n">
-        <v>36.5582</v>
+        <v>37.5566</v>
       </c>
       <c r="E92" t="n">
-        <v>3.74172</v>
+        <v>3.74062</v>
       </c>
       <c r="F92" t="n">
-        <v>5.2241</v>
+        <v>4.84039</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>12.7043</v>
+        <v>12.98</v>
       </c>
       <c r="C93" t="n">
-        <v>9.509</v>
+        <v>9.321490000000001</v>
       </c>
       <c r="D93" t="n">
-        <v>37.7502</v>
+        <v>38.7239</v>
       </c>
       <c r="E93" t="n">
-        <v>3.8859</v>
+        <v>3.87339</v>
       </c>
       <c r="F93" t="n">
-        <v>5.5287</v>
+        <v>5.23868</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>15.8863</v>
+        <v>16.3321</v>
       </c>
       <c r="C94" t="n">
-        <v>3.98793</v>
+        <v>3.96508</v>
       </c>
       <c r="D94" t="n">
-        <v>39.0239</v>
+        <v>39.8815</v>
       </c>
       <c r="E94" t="n">
-        <v>4.00187</v>
+        <v>4.01955</v>
       </c>
       <c r="F94" t="n">
-        <v>5.85842</v>
+        <v>5.51589</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>6.11981</v>
+        <v>6.14624</v>
       </c>
       <c r="C95" t="n">
-        <v>4.12095</v>
+        <v>4.16071</v>
       </c>
       <c r="D95" t="n">
-        <v>40.2764</v>
+        <v>41.2186</v>
       </c>
       <c r="E95" t="n">
-        <v>4.1912</v>
+        <v>4.17917</v>
       </c>
       <c r="F95" t="n">
-        <v>5.97192</v>
+        <v>5.84486</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.4316</v>
+        <v>6.44208</v>
       </c>
       <c r="C96" t="n">
-        <v>4.26757</v>
+        <v>4.31835</v>
       </c>
       <c r="D96" t="n">
-        <v>41.6062</v>
+        <v>42.5902</v>
       </c>
       <c r="E96" t="n">
-        <v>4.33224</v>
+        <v>4.38653</v>
       </c>
       <c r="F96" t="n">
-        <v>6.47705</v>
+        <v>6.03493</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.75278</v>
+        <v>6.79969</v>
       </c>
       <c r="C97" t="n">
-        <v>4.47047</v>
+        <v>4.45837</v>
       </c>
       <c r="D97" t="n">
-        <v>42.9589</v>
+        <v>43.9808</v>
       </c>
       <c r="E97" t="n">
-        <v>4.56208</v>
+        <v>4.54339</v>
       </c>
       <c r="F97" t="n">
-        <v>6.64052</v>
+        <v>6.49238</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>7.03754</v>
+        <v>7.09605</v>
       </c>
       <c r="C98" t="n">
-        <v>4.61025</v>
+        <v>4.68079</v>
       </c>
       <c r="D98" t="n">
-        <v>44.3419</v>
+        <v>45.3602</v>
       </c>
       <c r="E98" t="n">
-        <v>4.70559</v>
+        <v>4.72218</v>
       </c>
       <c r="F98" t="n">
-        <v>6.91128</v>
+        <v>6.83453</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.27909</v>
+        <v>7.37673</v>
       </c>
       <c r="C99" t="n">
-        <v>4.78777</v>
+        <v>4.86266</v>
       </c>
       <c r="D99" t="n">
-        <v>45.8202</v>
+        <v>46.8562</v>
       </c>
       <c r="E99" t="n">
-        <v>4.8458</v>
+        <v>4.918</v>
       </c>
       <c r="F99" t="n">
-        <v>7.21275</v>
+        <v>7.22455</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.63153</v>
+        <v>7.74238</v>
       </c>
       <c r="C100" t="n">
-        <v>4.96179</v>
+        <v>5.08194</v>
       </c>
       <c r="D100" t="n">
-        <v>47.3907</v>
+        <v>48.4299</v>
       </c>
       <c r="E100" t="n">
-        <v>5.02278</v>
+        <v>5.12614</v>
       </c>
       <c r="F100" t="n">
-        <v>7.58957</v>
+        <v>7.53477</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.92308</v>
+        <v>8.10563</v>
       </c>
       <c r="C101" t="n">
-        <v>5.21722</v>
+        <v>5.31253</v>
       </c>
       <c r="D101" t="n">
-        <v>48.8107</v>
+        <v>50.099</v>
       </c>
       <c r="E101" t="n">
-        <v>5.24791</v>
+        <v>5.33883</v>
       </c>
       <c r="F101" t="n">
-        <v>8.02543</v>
+        <v>7.83891</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.46489</v>
+        <v>8.65071</v>
       </c>
       <c r="C102" t="n">
-        <v>5.5626</v>
+        <v>5.65272</v>
       </c>
       <c r="D102" t="n">
-        <v>50.7298</v>
+        <v>51.8907</v>
       </c>
       <c r="E102" t="n">
-        <v>5.51461</v>
+        <v>5.52524</v>
       </c>
       <c r="F102" t="n">
-        <v>8.38611</v>
+        <v>8.344670000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.99682</v>
+        <v>9.270110000000001</v>
       </c>
       <c r="C103" t="n">
-        <v>5.94384</v>
+        <v>6.11175</v>
       </c>
       <c r="D103" t="n">
-        <v>52.5567</v>
+        <v>53.6246</v>
       </c>
       <c r="E103" t="n">
-        <v>5.75285</v>
+        <v>5.8659</v>
       </c>
       <c r="F103" t="n">
-        <v>8.92431</v>
+        <v>8.977830000000001</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.752739999999999</v>
+        <v>10.072</v>
       </c>
       <c r="C104" t="n">
-        <v>6.51299</v>
+        <v>6.68027</v>
       </c>
       <c r="D104" t="n">
-        <v>54.3999</v>
+        <v>55.6001</v>
       </c>
       <c r="E104" t="n">
-        <v>6.12383</v>
+        <v>6.20006</v>
       </c>
       <c r="F104" t="n">
-        <v>9.62872</v>
+        <v>9.931150000000001</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.8568</v>
+        <v>11.2569</v>
       </c>
       <c r="C105" t="n">
-        <v>7.3603</v>
+        <v>7.51715</v>
       </c>
       <c r="D105" t="n">
-        <v>56.3034</v>
+        <v>57.5713</v>
       </c>
       <c r="E105" t="n">
-        <v>6.671</v>
+        <v>6.72371</v>
       </c>
       <c r="F105" t="n">
-        <v>10.5974</v>
+        <v>10.8865</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>12.2724</v>
+        <v>12.881</v>
       </c>
       <c r="C106" t="n">
-        <v>8.5421</v>
+        <v>8.751200000000001</v>
       </c>
       <c r="D106" t="n">
-        <v>58.1193</v>
+        <v>59.5229</v>
       </c>
       <c r="E106" t="n">
-        <v>7.43875</v>
+        <v>7.49379</v>
       </c>
       <c r="F106" t="n">
-        <v>11.8423</v>
+        <v>12.2967</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>14.2981</v>
+        <v>15.0314</v>
       </c>
       <c r="C107" t="n">
-        <v>10.3767</v>
+        <v>10.6489</v>
       </c>
       <c r="D107" t="n">
-        <v>44.1354</v>
+        <v>45.3779</v>
       </c>
       <c r="E107" t="n">
-        <v>4.59445</v>
+        <v>4.7455</v>
       </c>
       <c r="F107" t="n">
-        <v>6.84215</v>
+        <v>7.04867</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.1008</v>
+        <v>18.167</v>
       </c>
       <c r="C108" t="n">
-        <v>4.72004</v>
+        <v>4.79346</v>
       </c>
       <c r="D108" t="n">
-        <v>45.3416</v>
+        <v>46.5599</v>
       </c>
       <c r="E108" t="n">
-        <v>4.76312</v>
+        <v>4.86082</v>
       </c>
       <c r="F108" t="n">
-        <v>7.14956</v>
+        <v>7.46364</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.9587</v>
+        <v>23.0134</v>
       </c>
       <c r="C109" t="n">
-        <v>4.83235</v>
+        <v>4.9243</v>
       </c>
       <c r="D109" t="n">
-        <v>46.4529</v>
+        <v>47.7745</v>
       </c>
       <c r="E109" t="n">
-        <v>4.91794</v>
+        <v>4.99026</v>
       </c>
       <c r="F109" t="n">
-        <v>7.34653</v>
+        <v>7.84082</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.56427</v>
+        <v>7.99644</v>
       </c>
       <c r="C110" t="n">
-        <v>4.90721</v>
+        <v>5.14107</v>
       </c>
       <c r="D110" t="n">
-        <v>47.677</v>
+        <v>48.9935</v>
       </c>
       <c r="E110" t="n">
-        <v>4.98769</v>
+        <v>5.17962</v>
       </c>
       <c r="F110" t="n">
-        <v>7.85743</v>
+        <v>8.39429</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.83047</v>
+        <v>8.69833</v>
       </c>
       <c r="C111" t="n">
-        <v>5.11628</v>
+        <v>5.45581</v>
       </c>
       <c r="D111" t="n">
-        <v>48.9239</v>
+        <v>50.2703</v>
       </c>
       <c r="E111" t="n">
-        <v>5.16981</v>
+        <v>5.50397</v>
       </c>
       <c r="F111" t="n">
-        <v>8.29387</v>
+        <v>9.157030000000001</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>8.23237</v>
+        <v>9.081110000000001</v>
       </c>
       <c r="C112" t="n">
-        <v>5.3068</v>
+        <v>5.81526</v>
       </c>
       <c r="D112" t="n">
-        <v>50.2367</v>
+        <v>51.6363</v>
       </c>
       <c r="E112" t="n">
-        <v>5.31306</v>
+        <v>5.83056</v>
       </c>
       <c r="F112" t="n">
-        <v>8.80035</v>
+        <v>9.653359999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.62237</v>
+        <v>9.600899999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>5.50758</v>
+        <v>6.20388</v>
       </c>
       <c r="D113" t="n">
-        <v>51.67</v>
+        <v>53.064</v>
       </c>
       <c r="E113" t="n">
-        <v>5.48016</v>
+        <v>6.18226</v>
       </c>
       <c r="F113" t="n">
-        <v>9.27849</v>
+        <v>10.1682</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>9.05578</v>
+        <v>10.0446</v>
       </c>
       <c r="C114" t="n">
-        <v>5.81729</v>
+        <v>6.544</v>
       </c>
       <c r="D114" t="n">
-        <v>53.1604</v>
+        <v>54.5732</v>
       </c>
       <c r="E114" t="n">
-        <v>5.75542</v>
+        <v>6.50188</v>
       </c>
       <c r="F114" t="n">
-        <v>9.840339999999999</v>
+        <v>10.5787</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.694000000000001</v>
+        <v>10.4592</v>
       </c>
       <c r="C115" t="n">
-        <v>6.2165</v>
+        <v>6.83801</v>
       </c>
       <c r="D115" t="n">
-        <v>54.7386</v>
+        <v>56.1534</v>
       </c>
       <c r="E115" t="n">
-        <v>6.11923</v>
+        <v>6.77306</v>
       </c>
       <c r="F115" t="n">
-        <v>10.4441</v>
+        <v>10.9899</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>10.3255</v>
+        <v>10.9463</v>
       </c>
       <c r="C116" t="n">
-        <v>6.70414</v>
+        <v>7.19533</v>
       </c>
       <c r="D116" t="n">
-        <v>56.4095</v>
+        <v>57.9139</v>
       </c>
       <c r="E116" t="n">
-        <v>6.57693</v>
+        <v>7.09479</v>
       </c>
       <c r="F116" t="n">
-        <v>11.0322</v>
+        <v>11.4445</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>10.9518</v>
+        <v>11.5736</v>
       </c>
       <c r="C117" t="n">
-        <v>7.16427</v>
+        <v>7.65163</v>
       </c>
       <c r="D117" t="n">
-        <v>58.2264</v>
+        <v>59.7561</v>
       </c>
       <c r="E117" t="n">
-        <v>7.02592</v>
+        <v>7.46247</v>
       </c>
       <c r="F117" t="n">
-        <v>11.6211</v>
+        <v>11.9954</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.7358</v>
+        <v>12.2762</v>
       </c>
       <c r="C118" t="n">
-        <v>7.77014</v>
+        <v>8.219939999999999</v>
       </c>
       <c r="D118" t="n">
-        <v>60.0982</v>
+        <v>61.6376</v>
       </c>
       <c r="E118" t="n">
-        <v>7.5243</v>
+        <v>7.88263</v>
       </c>
       <c r="F118" t="n">
-        <v>12.2633</v>
+        <v>12.5916</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.6654</v>
+        <v>13.21</v>
       </c>
       <c r="C119" t="n">
-        <v>8.521509999999999</v>
+        <v>8.95594</v>
       </c>
       <c r="D119" t="n">
-        <v>62.0477</v>
+        <v>63.6332</v>
       </c>
       <c r="E119" t="n">
-        <v>7.99169</v>
+        <v>8.408770000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>13.0196</v>
+        <v>13.3607</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.9313</v>
+        <v>14.5174</v>
       </c>
       <c r="C120" t="n">
-        <v>9.625439999999999</v>
+        <v>10.0724</v>
       </c>
       <c r="D120" t="n">
-        <v>64.1427</v>
+        <v>65.7991</v>
       </c>
       <c r="E120" t="n">
-        <v>8.86675</v>
+        <v>9.13538</v>
       </c>
       <c r="F120" t="n">
-        <v>14.0342</v>
+        <v>14.3893</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.6534</v>
+        <v>16.2997</v>
       </c>
       <c r="C121" t="n">
-        <v>11.1921</v>
+        <v>11.664</v>
       </c>
       <c r="D121" t="n">
-        <v>47.5102</v>
+        <v>48.9338</v>
       </c>
       <c r="E121" t="n">
-        <v>6.70299</v>
+        <v>6.287</v>
       </c>
       <c r="F121" t="n">
-        <v>10.0472</v>
+        <v>10.252</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.9656</v>
+        <v>18.9407</v>
       </c>
       <c r="C122" t="n">
-        <v>6.66438</v>
+        <v>6.39721</v>
       </c>
       <c r="D122" t="n">
-        <v>48.6172</v>
+        <v>50.324</v>
       </c>
       <c r="E122" t="n">
-        <v>7.41098</v>
+        <v>6.67488</v>
       </c>
       <c r="F122" t="n">
-        <v>10.9243</v>
+        <v>10.3464</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.2439</v>
+        <v>23.0487</v>
       </c>
       <c r="C123" t="n">
-        <v>6.8768</v>
+        <v>6.82396</v>
       </c>
       <c r="D123" t="n">
-        <v>49.8622</v>
+        <v>51.4842</v>
       </c>
       <c r="E123" t="n">
-        <v>6.76865</v>
+        <v>6.73145</v>
       </c>
       <c r="F123" t="n">
-        <v>10.5406</v>
+        <v>10.5887</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>10.0512</v>
+        <v>9.80979</v>
       </c>
       <c r="C124" t="n">
-        <v>6.86668</v>
+        <v>6.91581</v>
       </c>
       <c r="D124" t="n">
-        <v>50.8027</v>
+        <v>52.6977</v>
       </c>
       <c r="E124" t="n">
-        <v>7.1585</v>
+        <v>7.4716</v>
       </c>
       <c r="F124" t="n">
-        <v>10.8543</v>
+        <v>11.1681</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.2124</v>
+        <v>10.788</v>
       </c>
       <c r="C125" t="n">
-        <v>7.24393</v>
+        <v>7.05887</v>
       </c>
       <c r="D125" t="n">
-        <v>52.2881</v>
+        <v>53.935</v>
       </c>
       <c r="E125" t="n">
-        <v>7.53736</v>
+        <v>7.67422</v>
       </c>
       <c r="F125" t="n">
-        <v>11.5461</v>
+        <v>11.1072</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.8578</v>
+        <v>10.6663</v>
       </c>
       <c r="C126" t="n">
-        <v>7.10089</v>
+        <v>7.23441</v>
       </c>
       <c r="D126" t="n">
-        <v>53.4451</v>
+        <v>55.1722</v>
       </c>
       <c r="E126" t="n">
-        <v>7.80468</v>
+        <v>7.9397</v>
       </c>
       <c r="F126" t="n">
-        <v>11.6775</v>
+        <v>11.9663</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.8979</v>
+        <v>11.0348</v>
       </c>
       <c r="C127" t="n">
-        <v>7.35589</v>
+        <v>7.46115</v>
       </c>
       <c r="D127" t="n">
-        <v>54.9691</v>
+        <v>56.5878</v>
       </c>
       <c r="E127" t="n">
-        <v>7.84602</v>
+        <v>7.91134</v>
       </c>
       <c r="F127" t="n">
-        <v>11.7826</v>
+        <v>12.3368</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>11.247</v>
+        <v>11.2178</v>
       </c>
       <c r="C128" t="n">
-        <v>7.32797</v>
+        <v>7.81918</v>
       </c>
       <c r="D128" t="n">
-        <v>56.4372</v>
+        <v>58.6164</v>
       </c>
       <c r="E128" t="n">
-        <v>8.06019</v>
+        <v>7.91721</v>
       </c>
       <c r="F128" t="n">
-        <v>12.3494</v>
+        <v>12.247</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.4365</v>
+        <v>11.5135</v>
       </c>
       <c r="C129" t="n">
-        <v>7.53398</v>
+        <v>8.11786</v>
       </c>
       <c r="D129" t="n">
-        <v>57.9929</v>
+        <v>60.3559</v>
       </c>
       <c r="E129" t="n">
-        <v>8.16878</v>
+        <v>8.34226</v>
       </c>
       <c r="F129" t="n">
-        <v>12.4295</v>
+        <v>12.6192</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.8147</v>
+        <v>12.0583</v>
       </c>
       <c r="C130" t="n">
-        <v>7.8677</v>
+        <v>8.490869999999999</v>
       </c>
       <c r="D130" t="n">
-        <v>59.6557</v>
+        <v>61.8782</v>
       </c>
       <c r="E130" t="n">
-        <v>8.213839999999999</v>
+        <v>8.725059999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>12.8633</v>
+        <v>13.5137</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>11.9637</v>
+        <v>12.3903</v>
       </c>
       <c r="C131" t="n">
-        <v>8.276260000000001</v>
+        <v>8.722300000000001</v>
       </c>
       <c r="D131" t="n">
-        <v>61.4599</v>
+        <v>62.9597</v>
       </c>
       <c r="E131" t="n">
-        <v>8.718640000000001</v>
+        <v>8.835990000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>13.6451</v>
+        <v>13.8225</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>13.0737</v>
+        <v>13.3704</v>
       </c>
       <c r="C132" t="n">
-        <v>8.688219999999999</v>
+        <v>9.19988</v>
       </c>
       <c r="D132" t="n">
-        <v>63.3202</v>
+        <v>65.2367</v>
       </c>
       <c r="E132" t="n">
-        <v>8.968500000000001</v>
+        <v>9.198370000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>14.0018</v>
+        <v>14.4091</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.2393</v>
+        <v>14.2119</v>
       </c>
       <c r="C133" t="n">
-        <v>9.372640000000001</v>
+        <v>9.731479999999999</v>
       </c>
       <c r="D133" t="n">
-        <v>65.1215</v>
+        <v>67.39830000000001</v>
       </c>
       <c r="E133" t="n">
-        <v>9.527229999999999</v>
+        <v>9.546860000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>14.8754</v>
+        <v>15.0249</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.9062</v>
+        <v>15.3574</v>
       </c>
       <c r="C134" t="n">
-        <v>10.2283</v>
+        <v>10.8924</v>
       </c>
       <c r="D134" t="n">
-        <v>67.3844</v>
+        <v>69.2214</v>
       </c>
       <c r="E134" t="n">
-        <v>10.0767</v>
+        <v>10.109</v>
       </c>
       <c r="F134" t="n">
-        <v>15.6625</v>
+        <v>15.9206</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.4731</v>
+        <v>17.1789</v>
       </c>
       <c r="C135" t="n">
-        <v>11.7832</v>
+        <v>12.3069</v>
       </c>
       <c r="D135" t="n">
-        <v>49.4703</v>
+        <v>51.0768</v>
       </c>
       <c r="E135" t="n">
-        <v>13.0639</v>
+        <v>13.4921</v>
       </c>
       <c r="F135" t="n">
-        <v>16.2319</v>
+        <v>15.9152</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.5871</v>
+        <v>19.3166</v>
       </c>
       <c r="C136" t="n">
-        <v>13.3913</v>
+        <v>13.6965</v>
       </c>
       <c r="D136" t="n">
-        <v>50.3306</v>
+        <v>52.2793</v>
       </c>
       <c r="E136" t="n">
-        <v>13.289</v>
+        <v>13.6901</v>
       </c>
       <c r="F136" t="n">
-        <v>16.5844</v>
+        <v>16.4931</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>22.4102</v>
+        <v>23.1265</v>
       </c>
       <c r="C137" t="n">
-        <v>13.4725</v>
+        <v>13.6884</v>
       </c>
       <c r="D137" t="n">
-        <v>51.6757</v>
+        <v>53.4414</v>
       </c>
       <c r="E137" t="n">
-        <v>13.4992</v>
+        <v>13.7999</v>
       </c>
       <c r="F137" t="n">
-        <v>16.7389</v>
+        <v>16.4224</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.8094</v>
+        <v>17.3706</v>
       </c>
       <c r="C138" t="n">
-        <v>13.4295</v>
+        <v>13.8336</v>
       </c>
       <c r="D138" t="n">
-        <v>52.873</v>
+        <v>54.6154</v>
       </c>
       <c r="E138" t="n">
-        <v>13.4975</v>
+        <v>13.6998</v>
       </c>
       <c r="F138" t="n">
-        <v>17.1593</v>
+        <v>17.4248</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.0648</v>
+        <v>17.6204</v>
       </c>
       <c r="C139" t="n">
-        <v>13.7517</v>
+        <v>13.8326</v>
       </c>
       <c r="D139" t="n">
-        <v>53.9194</v>
+        <v>55.6677</v>
       </c>
       <c r="E139" t="n">
-        <v>12.9234</v>
+        <v>13.91</v>
       </c>
       <c r="F139" t="n">
-        <v>17.4312</v>
+        <v>17.1258</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>17.0972</v>
+        <v>17.749</v>
       </c>
       <c r="C140" t="n">
-        <v>13.6223</v>
+        <v>13.9515</v>
       </c>
       <c r="D140" t="n">
-        <v>55.3281</v>
+        <v>57.3747</v>
       </c>
       <c r="E140" t="n">
-        <v>13.8655</v>
+        <v>14.0887</v>
       </c>
       <c r="F140" t="n">
-        <v>16.9394</v>
+        <v>18.1202</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>17.4134</v>
+        <v>18.0144</v>
       </c>
       <c r="C141" t="n">
-        <v>13.9246</v>
+        <v>14.2313</v>
       </c>
       <c r="D141" t="n">
-        <v>56.8242</v>
+        <v>58.8196</v>
       </c>
       <c r="E141" t="n">
-        <v>13.5031</v>
+        <v>14.1931</v>
       </c>
       <c r="F141" t="n">
-        <v>17.9719</v>
+        <v>17.7603</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>17.4517</v>
+        <v>18.2149</v>
       </c>
       <c r="C142" t="n">
-        <v>13.9849</v>
+        <v>14.0893</v>
       </c>
       <c r="D142" t="n">
-        <v>58.2971</v>
+        <v>60.2828</v>
       </c>
       <c r="E142" t="n">
-        <v>13.4188</v>
+        <v>14.4749</v>
       </c>
       <c r="F142" t="n">
-        <v>18.4375</v>
+        <v>18.8637</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.1906</v>
+        <v>18.5687</v>
       </c>
       <c r="C143" t="n">
-        <v>14.2482</v>
+        <v>14.4501</v>
       </c>
       <c r="D143" t="n">
-        <v>59.8939</v>
+        <v>61.4392</v>
       </c>
       <c r="E143" t="n">
-        <v>14.2442</v>
+        <v>14.4188</v>
       </c>
       <c r="F143" t="n">
-        <v>18.7114</v>
+        <v>18.4121</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered unsuccessful looukp.xlsx
+++ b/clang-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.72521</v>
+        <v>2.69709</v>
       </c>
       <c r="C2" t="n">
-        <v>2.07048</v>
+        <v>2.58762</v>
       </c>
       <c r="D2" t="n">
-        <v>12.526</v>
+        <v>13.0057</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6195</v>
+        <v>2.7796</v>
       </c>
       <c r="F2" t="n">
-        <v>2.46762</v>
+        <v>2.89093</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.78648</v>
+        <v>2.7816</v>
       </c>
       <c r="C3" t="n">
-        <v>2.17882</v>
+        <v>2.67481</v>
       </c>
       <c r="D3" t="n">
-        <v>13.068</v>
+        <v>13.3258</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6984</v>
+        <v>2.8289</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5438</v>
+        <v>2.93517</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.87503</v>
+        <v>2.85969</v>
       </c>
       <c r="C4" t="n">
-        <v>2.37783</v>
+        <v>2.85582</v>
       </c>
       <c r="D4" t="n">
-        <v>13.6543</v>
+        <v>14.0469</v>
       </c>
       <c r="E4" t="n">
-        <v>2.78574</v>
+        <v>2.95155</v>
       </c>
       <c r="F4" t="n">
-        <v>2.68356</v>
+        <v>3.04653</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.24888</v>
+        <v>3.2719</v>
       </c>
       <c r="C5" t="n">
-        <v>2.72416</v>
+        <v>3.13155</v>
       </c>
       <c r="D5" t="n">
-        <v>14.1533</v>
+        <v>14.611</v>
       </c>
       <c r="E5" t="n">
-        <v>2.91871</v>
+        <v>3.02626</v>
       </c>
       <c r="F5" t="n">
-        <v>2.78839</v>
+        <v>3.21955</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.10196</v>
+        <v>4.6994</v>
       </c>
       <c r="C6" t="n">
-        <v>3.54205</v>
+        <v>4.2937</v>
       </c>
       <c r="D6" t="n">
-        <v>14.8808</v>
+        <v>15.3345</v>
       </c>
       <c r="E6" t="n">
-        <v>3.13546</v>
+        <v>3.22266</v>
       </c>
       <c r="F6" t="n">
-        <v>3.00458</v>
+        <v>3.5319</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.59284</v>
+        <v>6.66202</v>
       </c>
       <c r="C7" t="n">
-        <v>5.26127</v>
+        <v>6.20566</v>
       </c>
       <c r="D7" t="n">
-        <v>10.4434</v>
+        <v>10.716</v>
       </c>
       <c r="E7" t="n">
-        <v>2.36287</v>
+        <v>2.5393</v>
       </c>
       <c r="F7" t="n">
-        <v>2.111</v>
+        <v>2.54401</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.53125</v>
+        <v>9.671810000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1.74216</v>
+        <v>2.23786</v>
       </c>
       <c r="D8" t="n">
-        <v>11.0693</v>
+        <v>11.4599</v>
       </c>
       <c r="E8" t="n">
-        <v>2.37802</v>
+        <v>2.56485</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1418</v>
+        <v>2.57042</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.9063</v>
+        <v>13.968</v>
       </c>
       <c r="C9" t="n">
-        <v>1.76224</v>
+        <v>2.24258</v>
       </c>
       <c r="D9" t="n">
-        <v>11.6</v>
+        <v>12.0024</v>
       </c>
       <c r="E9" t="n">
-        <v>2.39855</v>
+        <v>2.58002</v>
       </c>
       <c r="F9" t="n">
-        <v>2.16632</v>
+        <v>2.58772</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.62111</v>
+        <v>2.71701</v>
       </c>
       <c r="C10" t="n">
-        <v>1.79891</v>
+        <v>2.31777</v>
       </c>
       <c r="D10" t="n">
-        <v>12.2836</v>
+        <v>12.5743</v>
       </c>
       <c r="E10" t="n">
-        <v>2.42701</v>
+        <v>2.59976</v>
       </c>
       <c r="F10" t="n">
-        <v>2.20805</v>
+        <v>2.60272</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.6899</v>
+        <v>2.85353</v>
       </c>
       <c r="C11" t="n">
-        <v>1.84233</v>
+        <v>2.32714</v>
       </c>
       <c r="D11" t="n">
-        <v>12.8727</v>
+        <v>13.0355</v>
       </c>
       <c r="E11" t="n">
-        <v>2.4514</v>
+        <v>2.64805</v>
       </c>
       <c r="F11" t="n">
-        <v>2.24335</v>
+        <v>2.66213</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.70817</v>
+        <v>2.77558</v>
       </c>
       <c r="C12" t="n">
-        <v>1.87973</v>
+        <v>2.39303</v>
       </c>
       <c r="D12" t="n">
-        <v>13.3018</v>
+        <v>13.5771</v>
       </c>
       <c r="E12" t="n">
-        <v>2.47578</v>
+        <v>2.71077</v>
       </c>
       <c r="F12" t="n">
-        <v>2.28802</v>
+        <v>2.71022</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.69146</v>
+        <v>2.90238</v>
       </c>
       <c r="C13" t="n">
-        <v>1.91617</v>
+        <v>2.47092</v>
       </c>
       <c r="D13" t="n">
-        <v>13.7245</v>
+        <v>14.0918</v>
       </c>
       <c r="E13" t="n">
-        <v>2.50163</v>
+        <v>2.71789</v>
       </c>
       <c r="F13" t="n">
-        <v>2.32904</v>
+        <v>2.73962</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.76887</v>
+        <v>2.86658</v>
       </c>
       <c r="C14" t="n">
-        <v>2.03651</v>
+        <v>2.49466</v>
       </c>
       <c r="D14" t="n">
-        <v>14.1439</v>
+        <v>14.5694</v>
       </c>
       <c r="E14" t="n">
-        <v>2.52997</v>
+        <v>2.73746</v>
       </c>
       <c r="F14" t="n">
-        <v>2.385</v>
+        <v>2.82308</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.8875</v>
+        <v>2.95748</v>
       </c>
       <c r="C15" t="n">
-        <v>2.11172</v>
+        <v>2.57878</v>
       </c>
       <c r="D15" t="n">
-        <v>14.5707</v>
+        <v>15.0329</v>
       </c>
       <c r="E15" t="n">
-        <v>2.58233</v>
+        <v>2.81173</v>
       </c>
       <c r="F15" t="n">
-        <v>2.46343</v>
+        <v>2.92064</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>2.96893</v>
+        <v>3.14514</v>
       </c>
       <c r="C16" t="n">
-        <v>2.23201</v>
+        <v>2.68137</v>
       </c>
       <c r="D16" t="n">
-        <v>14.9826</v>
+        <v>15.4346</v>
       </c>
       <c r="E16" t="n">
-        <v>2.63222</v>
+        <v>2.90742</v>
       </c>
       <c r="F16" t="n">
-        <v>2.54793</v>
+        <v>2.95452</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.16512</v>
+        <v>3.23886</v>
       </c>
       <c r="C17" t="n">
-        <v>2.40345</v>
+        <v>2.85496</v>
       </c>
       <c r="D17" t="n">
-        <v>15.435</v>
+        <v>15.8295</v>
       </c>
       <c r="E17" t="n">
-        <v>2.70092</v>
+        <v>2.98253</v>
       </c>
       <c r="F17" t="n">
-        <v>2.62172</v>
+        <v>3.11074</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.53894</v>
+        <v>3.62547</v>
       </c>
       <c r="C18" t="n">
-        <v>2.68296</v>
+        <v>3.12603</v>
       </c>
       <c r="D18" t="n">
-        <v>15.8104</v>
+        <v>16.2849</v>
       </c>
       <c r="E18" t="n">
-        <v>2.82331</v>
+        <v>3.10338</v>
       </c>
       <c r="F18" t="n">
-        <v>2.80797</v>
+        <v>3.24082</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.1475</v>
+        <v>4.30498</v>
       </c>
       <c r="C19" t="n">
-        <v>3.28546</v>
+        <v>3.61154</v>
       </c>
       <c r="D19" t="n">
-        <v>16.2341</v>
+        <v>16.7853</v>
       </c>
       <c r="E19" t="n">
-        <v>3.01171</v>
+        <v>3.26978</v>
       </c>
       <c r="F19" t="n">
-        <v>3.02111</v>
+        <v>3.4163</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.22334</v>
+        <v>5.26068</v>
       </c>
       <c r="C20" t="n">
-        <v>4.25828</v>
+        <v>4.54314</v>
       </c>
       <c r="D20" t="n">
-        <v>16.6516</v>
+        <v>17.1569</v>
       </c>
       <c r="E20" t="n">
-        <v>3.40954</v>
+        <v>3.63453</v>
       </c>
       <c r="F20" t="n">
-        <v>3.41992</v>
+        <v>3.88737</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.97091</v>
+        <v>6.80506</v>
       </c>
       <c r="C21" t="n">
-        <v>5.52671</v>
+        <v>6.30508</v>
       </c>
       <c r="D21" t="n">
-        <v>11.7491</v>
+        <v>12.1869</v>
       </c>
       <c r="E21" t="n">
-        <v>2.39075</v>
+        <v>2.50982</v>
       </c>
       <c r="F21" t="n">
-        <v>2.21576</v>
+        <v>2.67758</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.322760000000001</v>
+        <v>9.14231</v>
       </c>
       <c r="C22" t="n">
-        <v>1.83359</v>
+        <v>2.30664</v>
       </c>
       <c r="D22" t="n">
-        <v>12.2981</v>
+        <v>12.629</v>
       </c>
       <c r="E22" t="n">
-        <v>2.41422</v>
+        <v>2.54522</v>
       </c>
       <c r="F22" t="n">
-        <v>2.24283</v>
+        <v>2.98713</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.5993</v>
+        <v>13.1109</v>
       </c>
       <c r="C23" t="n">
-        <v>1.8774</v>
+        <v>2.4311</v>
       </c>
       <c r="D23" t="n">
-        <v>12.7525</v>
+        <v>13.1981</v>
       </c>
       <c r="E23" t="n">
-        <v>2.43593</v>
+        <v>2.5725</v>
       </c>
       <c r="F23" t="n">
-        <v>2.27322</v>
+        <v>2.79293</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.73814</v>
+        <v>2.83893</v>
       </c>
       <c r="C24" t="n">
-        <v>1.86857</v>
+        <v>2.371</v>
       </c>
       <c r="D24" t="n">
-        <v>13.2995</v>
+        <v>13.6843</v>
       </c>
       <c r="E24" t="n">
-        <v>2.45944</v>
+        <v>2.6483</v>
       </c>
       <c r="F24" t="n">
-        <v>2.32143</v>
+        <v>3.0454</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.76538</v>
+        <v>3.03879</v>
       </c>
       <c r="C25" t="n">
-        <v>1.90357</v>
+        <v>2.49364</v>
       </c>
       <c r="D25" t="n">
-        <v>13.7644</v>
+        <v>14.1442</v>
       </c>
       <c r="E25" t="n">
-        <v>2.49023</v>
+        <v>2.67568</v>
       </c>
       <c r="F25" t="n">
-        <v>2.35734</v>
+        <v>3.09001</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.8419</v>
+        <v>3.09967</v>
       </c>
       <c r="C26" t="n">
-        <v>1.9398</v>
+        <v>2.53362</v>
       </c>
       <c r="D26" t="n">
-        <v>14.1683</v>
+        <v>14.5437</v>
       </c>
       <c r="E26" t="n">
-        <v>2.52131</v>
+        <v>2.67039</v>
       </c>
       <c r="F26" t="n">
-        <v>2.41064</v>
+        <v>2.89956</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.93183</v>
+        <v>3.0655</v>
       </c>
       <c r="C27" t="n">
-        <v>1.98028</v>
+        <v>2.52852</v>
       </c>
       <c r="D27" t="n">
-        <v>14.6578</v>
+        <v>15.07</v>
       </c>
       <c r="E27" t="n">
-        <v>2.54838</v>
+        <v>2.72413</v>
       </c>
       <c r="F27" t="n">
-        <v>2.44945</v>
+        <v>2.96622</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.00808</v>
+        <v>3.22749</v>
       </c>
       <c r="C28" t="n">
-        <v>2.08914</v>
+        <v>2.66803</v>
       </c>
       <c r="D28" t="n">
-        <v>15.1049</v>
+        <v>15.5241</v>
       </c>
       <c r="E28" t="n">
-        <v>2.59376</v>
+        <v>2.77945</v>
       </c>
       <c r="F28" t="n">
-        <v>2.5206</v>
+        <v>3.04098</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.1434</v>
+        <v>3.57558</v>
       </c>
       <c r="C29" t="n">
-        <v>2.17204</v>
+        <v>2.68682</v>
       </c>
       <c r="D29" t="n">
-        <v>15.5259</v>
+        <v>16.0214</v>
       </c>
       <c r="E29" t="n">
-        <v>2.6439</v>
+        <v>2.8579</v>
       </c>
       <c r="F29" t="n">
-        <v>2.60544</v>
+        <v>3.1307</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.31583</v>
+        <v>3.37909</v>
       </c>
       <c r="C30" t="n">
-        <v>2.30636</v>
+        <v>2.80191</v>
       </c>
       <c r="D30" t="n">
-        <v>15.9736</v>
+        <v>16.4195</v>
       </c>
       <c r="E30" t="n">
-        <v>2.70796</v>
+        <v>2.92369</v>
       </c>
       <c r="F30" t="n">
-        <v>2.69175</v>
+        <v>3.47039</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.56809</v>
+        <v>3.60904</v>
       </c>
       <c r="C31" t="n">
-        <v>2.49285</v>
+        <v>2.97951</v>
       </c>
       <c r="D31" t="n">
-        <v>16.3676</v>
+        <v>16.9208</v>
       </c>
       <c r="E31" t="n">
-        <v>2.77622</v>
+        <v>3.03565</v>
       </c>
       <c r="F31" t="n">
-        <v>2.77807</v>
+        <v>3.35982</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.99222</v>
+        <v>3.99365</v>
       </c>
       <c r="C32" t="n">
-        <v>2.7664</v>
+        <v>3.26997</v>
       </c>
       <c r="D32" t="n">
-        <v>16.691</v>
+        <v>17.2423</v>
       </c>
       <c r="E32" t="n">
-        <v>2.88777</v>
+        <v>3.16024</v>
       </c>
       <c r="F32" t="n">
-        <v>2.93838</v>
+        <v>3.61137</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.71778</v>
+        <v>4.69151</v>
       </c>
       <c r="C33" t="n">
-        <v>3.31132</v>
+        <v>3.72668</v>
       </c>
       <c r="D33" t="n">
-        <v>17.1261</v>
+        <v>17.6741</v>
       </c>
       <c r="E33" t="n">
-        <v>3.10418</v>
+        <v>3.43135</v>
       </c>
       <c r="F33" t="n">
-        <v>3.18662</v>
+        <v>3.71197</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.7397</v>
+        <v>5.72803</v>
       </c>
       <c r="C34" t="n">
-        <v>4.11096</v>
+        <v>4.66198</v>
       </c>
       <c r="D34" t="n">
-        <v>17.5303</v>
+        <v>18.1148</v>
       </c>
       <c r="E34" t="n">
-        <v>3.5154</v>
+        <v>3.7735</v>
       </c>
       <c r="F34" t="n">
-        <v>3.59787</v>
+        <v>4.31999</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.24746</v>
+        <v>7.04193</v>
       </c>
       <c r="C35" t="n">
-        <v>5.24674</v>
+        <v>6.06439</v>
       </c>
       <c r="D35" t="n">
-        <v>12.1984</v>
+        <v>12.4109</v>
       </c>
       <c r="E35" t="n">
-        <v>2.41279</v>
+        <v>2.92911</v>
       </c>
       <c r="F35" t="n">
-        <v>2.31896</v>
+        <v>3.15637</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.478120000000001</v>
+        <v>9.37865</v>
       </c>
       <c r="C36" t="n">
-        <v>6.87131</v>
+        <v>8.17319</v>
       </c>
       <c r="D36" t="n">
-        <v>12.7062</v>
+        <v>12.9038</v>
       </c>
       <c r="E36" t="n">
-        <v>2.43131</v>
+        <v>2.9461</v>
       </c>
       <c r="F36" t="n">
-        <v>2.34924</v>
+        <v>3.19311</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.0819</v>
+        <v>12.8312</v>
       </c>
       <c r="C37" t="n">
-        <v>1.87807</v>
+        <v>2.56237</v>
       </c>
       <c r="D37" t="n">
-        <v>13.1749</v>
+        <v>13.4143</v>
       </c>
       <c r="E37" t="n">
-        <v>2.45895</v>
+        <v>2.97003</v>
       </c>
       <c r="F37" t="n">
-        <v>2.38566</v>
+        <v>2.8436</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.84244</v>
+        <v>3.1465</v>
       </c>
       <c r="C38" t="n">
-        <v>1.8879</v>
+        <v>2.66369</v>
       </c>
       <c r="D38" t="n">
-        <v>13.6613</v>
+        <v>14.3228</v>
       </c>
       <c r="E38" t="n">
-        <v>2.48366</v>
+        <v>3.15156</v>
       </c>
       <c r="F38" t="n">
-        <v>2.43781</v>
+        <v>2.91672</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.90155</v>
+        <v>3.20091</v>
       </c>
       <c r="C39" t="n">
-        <v>1.93385</v>
+        <v>2.67375</v>
       </c>
       <c r="D39" t="n">
-        <v>14.137</v>
+        <v>14.8023</v>
       </c>
       <c r="E39" t="n">
-        <v>2.51911</v>
+        <v>2.92035</v>
       </c>
       <c r="F39" t="n">
-        <v>2.49812</v>
+        <v>3.35928</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.93661</v>
+        <v>2.99211</v>
       </c>
       <c r="C40" t="n">
-        <v>2.01555</v>
+        <v>2.67243</v>
       </c>
       <c r="D40" t="n">
-        <v>14.5754</v>
+        <v>15.2964</v>
       </c>
       <c r="E40" t="n">
-        <v>2.54384</v>
+        <v>3.23053</v>
       </c>
       <c r="F40" t="n">
-        <v>2.5497</v>
+        <v>3.00219</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.01317</v>
+        <v>3.31321</v>
       </c>
       <c r="C41" t="n">
-        <v>2.06989</v>
+        <v>2.77093</v>
       </c>
       <c r="D41" t="n">
-        <v>15.0256</v>
+        <v>15.9574</v>
       </c>
       <c r="E41" t="n">
-        <v>2.57812</v>
+        <v>3.24913</v>
       </c>
       <c r="F41" t="n">
-        <v>2.59278</v>
+        <v>3.05507</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.08279</v>
+        <v>3.47247</v>
       </c>
       <c r="C42" t="n">
-        <v>2.09623</v>
+        <v>2.84046</v>
       </c>
       <c r="D42" t="n">
-        <v>15.4479</v>
+        <v>16.5805</v>
       </c>
       <c r="E42" t="n">
-        <v>2.6162</v>
+        <v>3.29331</v>
       </c>
       <c r="F42" t="n">
-        <v>2.66706</v>
+        <v>3.12194</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.24674</v>
+        <v>3.56028</v>
       </c>
       <c r="C43" t="n">
-        <v>2.20048</v>
+        <v>2.98013</v>
       </c>
       <c r="D43" t="n">
-        <v>15.8768</v>
+        <v>16.9631</v>
       </c>
       <c r="E43" t="n">
-        <v>2.66413</v>
+        <v>3.12416</v>
       </c>
       <c r="F43" t="n">
-        <v>2.73446</v>
+        <v>3.58625</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.42915</v>
+        <v>3.70866</v>
       </c>
       <c r="C44" t="n">
-        <v>2.33222</v>
+        <v>3.08236</v>
       </c>
       <c r="D44" t="n">
-        <v>16.2869</v>
+        <v>17.437</v>
       </c>
       <c r="E44" t="n">
-        <v>2.74398</v>
+        <v>3.29207</v>
       </c>
       <c r="F44" t="n">
-        <v>2.84214</v>
+        <v>3.62681</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.68863</v>
+        <v>3.72307</v>
       </c>
       <c r="C45" t="n">
-        <v>2.60171</v>
+        <v>3.08177</v>
       </c>
       <c r="D45" t="n">
-        <v>16.6784</v>
+        <v>17.8817</v>
       </c>
       <c r="E45" t="n">
-        <v>2.83199</v>
+        <v>3.07294</v>
       </c>
       <c r="F45" t="n">
-        <v>2.95781</v>
+        <v>3.6884</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.05287</v>
+        <v>4.26894</v>
       </c>
       <c r="C46" t="n">
-        <v>2.8981</v>
+        <v>3.58065</v>
       </c>
       <c r="D46" t="n">
-        <v>17.0874</v>
+        <v>18.386</v>
       </c>
       <c r="E46" t="n">
-        <v>2.9604</v>
+        <v>3.49861</v>
       </c>
       <c r="F46" t="n">
-        <v>3.11361</v>
+        <v>3.84397</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.66261</v>
+        <v>4.87458</v>
       </c>
       <c r="C47" t="n">
-        <v>3.35005</v>
+        <v>4.0389</v>
       </c>
       <c r="D47" t="n">
-        <v>17.4979</v>
+        <v>18.944</v>
       </c>
       <c r="E47" t="n">
-        <v>3.17975</v>
+        <v>3.77101</v>
       </c>
       <c r="F47" t="n">
-        <v>3.35197</v>
+        <v>4.08393</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.45381</v>
+        <v>5.42158</v>
       </c>
       <c r="C48" t="n">
-        <v>4.03229</v>
+        <v>4.8806</v>
       </c>
       <c r="D48" t="n">
-        <v>17.9495</v>
+        <v>19.314</v>
       </c>
       <c r="E48" t="n">
-        <v>3.55137</v>
+        <v>4.15744</v>
       </c>
       <c r="F48" t="n">
-        <v>3.73008</v>
+        <v>4.53495</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.58546</v>
+        <v>6.61657</v>
       </c>
       <c r="C49" t="n">
-        <v>4.97205</v>
+        <v>5.83389</v>
       </c>
       <c r="D49" t="n">
-        <v>18.3918</v>
+        <v>20.3054</v>
       </c>
       <c r="E49" t="n">
-        <v>4.10141</v>
+        <v>4.73812</v>
       </c>
       <c r="F49" t="n">
-        <v>4.2705</v>
+        <v>4.85083</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.536490000000001</v>
+        <v>8.65996</v>
       </c>
       <c r="C50" t="n">
-        <v>6.47452</v>
+        <v>7.71263</v>
       </c>
       <c r="D50" t="n">
-        <v>12.8341</v>
+        <v>15.0471</v>
       </c>
       <c r="E50" t="n">
-        <v>2.46597</v>
+        <v>2.99059</v>
       </c>
       <c r="F50" t="n">
-        <v>2.59198</v>
+        <v>3.30993</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>11.1673</v>
+        <v>12.0832</v>
       </c>
       <c r="C51" t="n">
-        <v>1.96052</v>
+        <v>2.51138</v>
       </c>
       <c r="D51" t="n">
-        <v>13.3019</v>
+        <v>16.1744</v>
       </c>
       <c r="E51" t="n">
-        <v>2.47935</v>
+        <v>3.0261</v>
       </c>
       <c r="F51" t="n">
-        <v>2.61548</v>
+        <v>3.34852</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.5757</v>
+        <v>16.3777</v>
       </c>
       <c r="C52" t="n">
-        <v>2.02471</v>
+        <v>2.54199</v>
       </c>
       <c r="D52" t="n">
-        <v>13.7771</v>
+        <v>17.4208</v>
       </c>
       <c r="E52" t="n">
-        <v>2.50621</v>
+        <v>3.05834</v>
       </c>
       <c r="F52" t="n">
-        <v>2.68829</v>
+        <v>3.38872</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>2.99784</v>
+        <v>3.05406</v>
       </c>
       <c r="C53" t="n">
-        <v>2.07776</v>
+        <v>2.5841</v>
       </c>
       <c r="D53" t="n">
-        <v>14.2576</v>
+        <v>18.6187</v>
       </c>
       <c r="E53" t="n">
-        <v>2.5332</v>
+        <v>2.89525</v>
       </c>
       <c r="F53" t="n">
-        <v>2.71459</v>
+        <v>3.20215</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.09956</v>
+        <v>3.61672</v>
       </c>
       <c r="C54" t="n">
-        <v>2.61019</v>
+        <v>2.56386</v>
       </c>
       <c r="D54" t="n">
-        <v>14.7509</v>
+        <v>19.7684</v>
       </c>
       <c r="E54" t="n">
-        <v>2.72548</v>
+        <v>2.94021</v>
       </c>
       <c r="F54" t="n">
-        <v>2.77939</v>
+        <v>3.24746</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.15371</v>
+        <v>3.66646</v>
       </c>
       <c r="C55" t="n">
-        <v>2.50923</v>
+        <v>2.69766</v>
       </c>
       <c r="D55" t="n">
-        <v>15.2066</v>
+        <v>21.2855</v>
       </c>
       <c r="E55" t="n">
-        <v>2.93658</v>
+        <v>2.94806</v>
       </c>
       <c r="F55" t="n">
-        <v>2.84002</v>
+        <v>3.36665</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.2601</v>
+        <v>3.29697</v>
       </c>
       <c r="C56" t="n">
-        <v>2.20878</v>
+        <v>2.75128</v>
       </c>
       <c r="D56" t="n">
-        <v>15.6718</v>
+        <v>22.4598</v>
       </c>
       <c r="E56" t="n">
-        <v>2.9847</v>
+        <v>3.05173</v>
       </c>
       <c r="F56" t="n">
-        <v>2.89802</v>
+        <v>3.34419</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.41733</v>
+        <v>3.41307</v>
       </c>
       <c r="C57" t="n">
-        <v>2.67067</v>
+        <v>2.85806</v>
       </c>
       <c r="D57" t="n">
-        <v>16.1119</v>
+        <v>23.9479</v>
       </c>
       <c r="E57" t="n">
-        <v>2.88595</v>
+        <v>3.10602</v>
       </c>
       <c r="F57" t="n">
-        <v>2.93953</v>
+        <v>3.51676</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.55974</v>
+        <v>3.59767</v>
       </c>
       <c r="C58" t="n">
-        <v>2.43487</v>
+        <v>3.00476</v>
       </c>
       <c r="D58" t="n">
-        <v>16.549</v>
+        <v>25.0023</v>
       </c>
       <c r="E58" t="n">
-        <v>2.86017</v>
+        <v>3.14587</v>
       </c>
       <c r="F58" t="n">
-        <v>3.07833</v>
+        <v>3.64191</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.82743</v>
+        <v>3.77591</v>
       </c>
       <c r="C59" t="n">
-        <v>2.97869</v>
+        <v>3.19089</v>
       </c>
       <c r="D59" t="n">
-        <v>16.9545</v>
+        <v>26.0942</v>
       </c>
       <c r="E59" t="n">
-        <v>3.26195</v>
+        <v>3.43381</v>
       </c>
       <c r="F59" t="n">
-        <v>3.12737</v>
+        <v>3.71573</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.1674</v>
+        <v>4.13905</v>
       </c>
       <c r="C60" t="n">
-        <v>3.35198</v>
+        <v>3.49161</v>
       </c>
       <c r="D60" t="n">
-        <v>17.4508</v>
+        <v>26.6106</v>
       </c>
       <c r="E60" t="n">
-        <v>3.30126</v>
+        <v>3.47701</v>
       </c>
       <c r="F60" t="n">
-        <v>3.29285</v>
+        <v>3.86831</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.49362</v>
+        <v>4.61048</v>
       </c>
       <c r="C61" t="n">
-        <v>3.28324</v>
+        <v>3.98343</v>
       </c>
       <c r="D61" t="n">
-        <v>17.9266</v>
+        <v>27.427</v>
       </c>
       <c r="E61" t="n">
-        <v>3.43525</v>
+        <v>3.69871</v>
       </c>
       <c r="F61" t="n">
-        <v>3.50632</v>
+        <v>4.53346</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.27258</v>
+        <v>5.32396</v>
       </c>
       <c r="C62" t="n">
-        <v>4.28572</v>
+        <v>4.61159</v>
       </c>
       <c r="D62" t="n">
-        <v>18.4458</v>
+        <v>28.617</v>
       </c>
       <c r="E62" t="n">
-        <v>3.75015</v>
+        <v>4.05941</v>
       </c>
       <c r="F62" t="n">
-        <v>3.80098</v>
+        <v>4.89047</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.38281</v>
+        <v>6.35936</v>
       </c>
       <c r="C63" t="n">
-        <v>5.14031</v>
+        <v>5.56861</v>
       </c>
       <c r="D63" t="n">
-        <v>18.9819</v>
+        <v>28.5425</v>
       </c>
       <c r="E63" t="n">
-        <v>4.27165</v>
+        <v>4.60812</v>
       </c>
       <c r="F63" t="n">
-        <v>4.34514</v>
+        <v>5.36435</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>7.98287</v>
+        <v>8.082660000000001</v>
       </c>
       <c r="C64" t="n">
-        <v>6.20746</v>
+        <v>7.03826</v>
       </c>
       <c r="D64" t="n">
-        <v>14.1441</v>
+        <v>19.0204</v>
       </c>
       <c r="E64" t="n">
-        <v>2.75835</v>
+        <v>3.56385</v>
       </c>
       <c r="F64" t="n">
-        <v>3.11314</v>
+        <v>3.75083</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.7365</v>
+        <v>10.6074</v>
       </c>
       <c r="C65" t="n">
-        <v>2.52516</v>
+        <v>2.97024</v>
       </c>
       <c r="D65" t="n">
-        <v>14.807</v>
+        <v>18.4692</v>
       </c>
       <c r="E65" t="n">
-        <v>2.76422</v>
+        <v>3.28842</v>
       </c>
       <c r="F65" t="n">
-        <v>3.17536</v>
+        <v>3.80988</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.5067</v>
+        <v>14.5171</v>
       </c>
       <c r="C66" t="n">
-        <v>2.58855</v>
+        <v>2.99946</v>
       </c>
       <c r="D66" t="n">
-        <v>15.4991</v>
+        <v>20.07</v>
       </c>
       <c r="E66" t="n">
-        <v>2.81</v>
+        <v>3.611</v>
       </c>
       <c r="F66" t="n">
-        <v>3.22415</v>
+        <v>3.85329</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.75943</v>
+        <v>3.55715</v>
       </c>
       <c r="C67" t="n">
-        <v>2.59639</v>
+        <v>3.04297</v>
       </c>
       <c r="D67" t="n">
-        <v>16.4232</v>
+        <v>21.686</v>
       </c>
       <c r="E67" t="n">
-        <v>2.83128</v>
+        <v>3.63224</v>
       </c>
       <c r="F67" t="n">
-        <v>3.27455</v>
+        <v>3.91503</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.87251</v>
+        <v>3.93584</v>
       </c>
       <c r="C68" t="n">
-        <v>2.62388</v>
+        <v>3.2075</v>
       </c>
       <c r="D68" t="n">
-        <v>17.297</v>
+        <v>23.3096</v>
       </c>
       <c r="E68" t="n">
-        <v>2.8601</v>
+        <v>3.40154</v>
       </c>
       <c r="F68" t="n">
-        <v>3.33112</v>
+        <v>3.99156</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.91488</v>
+        <v>3.76803</v>
       </c>
       <c r="C69" t="n">
-        <v>2.63835</v>
+        <v>3.25096</v>
       </c>
       <c r="D69" t="n">
-        <v>18.3921</v>
+        <v>24.2352</v>
       </c>
       <c r="E69" t="n">
-        <v>2.89928</v>
+        <v>3.45368</v>
       </c>
       <c r="F69" t="n">
-        <v>3.39434</v>
+        <v>4.04988</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.84438</v>
+        <v>3.78202</v>
       </c>
       <c r="C70" t="n">
-        <v>2.70735</v>
+        <v>3.35122</v>
       </c>
       <c r="D70" t="n">
-        <v>19.7621</v>
+        <v>25.0079</v>
       </c>
       <c r="E70" t="n">
-        <v>2.94004</v>
+        <v>3.62787</v>
       </c>
       <c r="F70" t="n">
-        <v>3.46525</v>
+        <v>4.14135</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.95698</v>
+        <v>3.98681</v>
       </c>
       <c r="C71" t="n">
-        <v>2.79713</v>
+        <v>3.42625</v>
       </c>
       <c r="D71" t="n">
-        <v>20.9795</v>
+        <v>25.8959</v>
       </c>
       <c r="E71" t="n">
-        <v>3.05759</v>
+        <v>3.72657</v>
       </c>
       <c r="F71" t="n">
-        <v>3.62289</v>
+        <v>4.21954</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.27368</v>
+        <v>4.13928</v>
       </c>
       <c r="C72" t="n">
-        <v>2.88838</v>
+        <v>3.56149</v>
       </c>
       <c r="D72" t="n">
-        <v>22.1592</v>
+        <v>26.7248</v>
       </c>
       <c r="E72" t="n">
-        <v>3.14267</v>
+        <v>3.80878</v>
       </c>
       <c r="F72" t="n">
-        <v>3.7391</v>
+        <v>4.33221</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.34144</v>
+        <v>4.25874</v>
       </c>
       <c r="C73" t="n">
-        <v>3.13268</v>
+        <v>3.61008</v>
       </c>
       <c r="D73" t="n">
-        <v>23.7979</v>
+        <v>27.3018</v>
       </c>
       <c r="E73" t="n">
-        <v>3.24651</v>
+        <v>3.90906</v>
       </c>
       <c r="F73" t="n">
-        <v>3.89018</v>
+        <v>4.45666</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.63214</v>
+        <v>4.5914</v>
       </c>
       <c r="C74" t="n">
-        <v>3.34326</v>
+        <v>3.82443</v>
       </c>
       <c r="D74" t="n">
-        <v>25.3992</v>
+        <v>27.9772</v>
       </c>
       <c r="E74" t="n">
-        <v>3.37683</v>
+        <v>4.55405</v>
       </c>
       <c r="F74" t="n">
-        <v>4.12313</v>
+        <v>4.82084</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.16938</v>
+        <v>5.01429</v>
       </c>
       <c r="C75" t="n">
-        <v>3.71508</v>
+        <v>4.24008</v>
       </c>
       <c r="D75" t="n">
-        <v>26.4579</v>
+        <v>28.5911</v>
       </c>
       <c r="E75" t="n">
-        <v>3.55928</v>
+        <v>4.38801</v>
       </c>
       <c r="F75" t="n">
-        <v>4.35647</v>
+        <v>4.89157</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.70159</v>
+        <v>5.6482</v>
       </c>
       <c r="C76" t="n">
-        <v>4.2353</v>
+        <v>4.84044</v>
       </c>
       <c r="D76" t="n">
-        <v>27.9213</v>
+        <v>31.2973</v>
       </c>
       <c r="E76" t="n">
-        <v>3.87989</v>
+        <v>4.49081</v>
       </c>
       <c r="F76" t="n">
-        <v>4.47212</v>
+        <v>5.4323</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.72204</v>
+        <v>6.57255</v>
       </c>
       <c r="C77" t="n">
-        <v>5.06774</v>
+        <v>5.87043</v>
       </c>
       <c r="D77" t="n">
-        <v>29.2717</v>
+        <v>33.3427</v>
       </c>
       <c r="E77" t="n">
-        <v>4.36351</v>
+        <v>5.68829</v>
       </c>
       <c r="F77" t="n">
-        <v>4.97407</v>
+        <v>5.66416</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.42112</v>
+        <v>8.229290000000001</v>
       </c>
       <c r="C78" t="n">
-        <v>6.3243</v>
+        <v>7.4436</v>
       </c>
       <c r="D78" t="n">
-        <v>24.7827</v>
+        <v>24.0913</v>
       </c>
       <c r="E78" t="n">
-        <v>3.0875</v>
+        <v>3.74118</v>
       </c>
       <c r="F78" t="n">
-        <v>3.65127</v>
+        <v>4.4709</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.6907</v>
+        <v>10.6846</v>
       </c>
       <c r="C79" t="n">
-        <v>2.90606</v>
+        <v>3.29967</v>
       </c>
       <c r="D79" t="n">
-        <v>26.0958</v>
+        <v>26.0491</v>
       </c>
       <c r="E79" t="n">
-        <v>3.16837</v>
+        <v>3.78448</v>
       </c>
       <c r="F79" t="n">
-        <v>3.72386</v>
+        <v>4.56346</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>14.6972</v>
+        <v>14.6457</v>
       </c>
       <c r="C80" t="n">
-        <v>2.95277</v>
+        <v>3.38281</v>
       </c>
       <c r="D80" t="n">
-        <v>27.3774</v>
+        <v>27.4107</v>
       </c>
       <c r="E80" t="n">
-        <v>3.17053</v>
+        <v>3.85897</v>
       </c>
       <c r="F80" t="n">
-        <v>3.81188</v>
+        <v>4.77828</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.25029</v>
+        <v>4.5628</v>
       </c>
       <c r="C81" t="n">
-        <v>3.00219</v>
+        <v>3.41777</v>
       </c>
       <c r="D81" t="n">
-        <v>28.7328</v>
+        <v>29.0166</v>
       </c>
       <c r="E81" t="n">
-        <v>3.22758</v>
+        <v>3.94553</v>
       </c>
       <c r="F81" t="n">
-        <v>3.95919</v>
+        <v>4.88143</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.41837</v>
+        <v>4.77104</v>
       </c>
       <c r="C82" t="n">
-        <v>3.08632</v>
+        <v>3.56945</v>
       </c>
       <c r="D82" t="n">
-        <v>30.117</v>
+        <v>30.0728</v>
       </c>
       <c r="E82" t="n">
-        <v>3.29119</v>
+        <v>3.99822</v>
       </c>
       <c r="F82" t="n">
-        <v>4.09189</v>
+        <v>5.20021</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.59502</v>
+        <v>4.84208</v>
       </c>
       <c r="C83" t="n">
-        <v>3.19937</v>
+        <v>3.59572</v>
       </c>
       <c r="D83" t="n">
-        <v>31.5247</v>
+        <v>31.4239</v>
       </c>
       <c r="E83" t="n">
-        <v>3.37035</v>
+        <v>4.15565</v>
       </c>
       <c r="F83" t="n">
-        <v>4.24076</v>
+        <v>5.4498</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.75032</v>
+        <v>5.0556</v>
       </c>
       <c r="C84" t="n">
-        <v>3.31453</v>
+        <v>3.91669</v>
       </c>
       <c r="D84" t="n">
-        <v>33.0216</v>
+        <v>32.8731</v>
       </c>
       <c r="E84" t="n">
-        <v>3.49603</v>
+        <v>4.29468</v>
       </c>
       <c r="F84" t="n">
-        <v>4.44003</v>
+        <v>5.58596</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>4.96189</v>
+        <v>5.34679</v>
       </c>
       <c r="C85" t="n">
-        <v>3.46815</v>
+        <v>3.93213</v>
       </c>
       <c r="D85" t="n">
-        <v>34.6077</v>
+        <v>34.3681</v>
       </c>
       <c r="E85" t="n">
-        <v>3.54992</v>
+        <v>4.39257</v>
       </c>
       <c r="F85" t="n">
-        <v>4.702</v>
+        <v>5.32871</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.28404</v>
+        <v>5.85164</v>
       </c>
       <c r="C86" t="n">
-        <v>3.62572</v>
+        <v>4.42613</v>
       </c>
       <c r="D86" t="n">
-        <v>36.2299</v>
+        <v>36.066</v>
       </c>
       <c r="E86" t="n">
-        <v>3.69273</v>
+        <v>4.61587</v>
       </c>
       <c r="F86" t="n">
-        <v>4.98687</v>
+        <v>5.69257</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.63328</v>
+        <v>6.33241</v>
       </c>
       <c r="C87" t="n">
-        <v>3.85994</v>
+        <v>4.76249</v>
       </c>
       <c r="D87" t="n">
-        <v>37.9405</v>
+        <v>37.6966</v>
       </c>
       <c r="E87" t="n">
-        <v>3.86068</v>
+        <v>4.82694</v>
       </c>
       <c r="F87" t="n">
-        <v>5.2563</v>
+        <v>6.01387</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.02481</v>
+        <v>6.90399</v>
       </c>
       <c r="C88" t="n">
-        <v>4.14849</v>
+        <v>4.97231</v>
       </c>
       <c r="D88" t="n">
-        <v>39.5967</v>
+        <v>39.4389</v>
       </c>
       <c r="E88" t="n">
-        <v>4.03584</v>
+        <v>5.04997</v>
       </c>
       <c r="F88" t="n">
-        <v>5.68081</v>
+        <v>6.80684</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>6.43391</v>
+        <v>7.6896</v>
       </c>
       <c r="C89" t="n">
-        <v>4.5</v>
+        <v>5.68956</v>
       </c>
       <c r="D89" t="n">
-        <v>41.8527</v>
+        <v>41.2337</v>
       </c>
       <c r="E89" t="n">
-        <v>4.29927</v>
+        <v>5.42265</v>
       </c>
       <c r="F89" t="n">
-        <v>6.02704</v>
+        <v>7.42183</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.33797</v>
+        <v>8.468120000000001</v>
       </c>
       <c r="C90" t="n">
-        <v>5.06583</v>
+        <v>6.22577</v>
       </c>
       <c r="D90" t="n">
-        <v>43.4037</v>
+        <v>43.0858</v>
       </c>
       <c r="E90" t="n">
-        <v>4.66431</v>
+        <v>5.97087</v>
       </c>
       <c r="F90" t="n">
-        <v>6.93087</v>
+        <v>8.1517</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.794320000000001</v>
+        <v>8.89795</v>
       </c>
       <c r="C91" t="n">
-        <v>6.03585</v>
+        <v>7.00964</v>
       </c>
       <c r="D91" t="n">
-        <v>45.4729</v>
+        <v>44.913</v>
       </c>
       <c r="E91" t="n">
-        <v>5.22239</v>
+        <v>6.69206</v>
       </c>
       <c r="F91" t="n">
-        <v>7.85867</v>
+        <v>9.12294</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.5071</v>
+        <v>10.3241</v>
       </c>
       <c r="C92" t="n">
-        <v>7.40394</v>
+        <v>8.45473</v>
       </c>
       <c r="D92" t="n">
-        <v>37.5566</v>
+        <v>36.6804</v>
       </c>
       <c r="E92" t="n">
-        <v>3.74062</v>
+        <v>4.5491</v>
       </c>
       <c r="F92" t="n">
-        <v>4.84039</v>
+        <v>6.10879</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>12.98</v>
+        <v>12.4257</v>
       </c>
       <c r="C93" t="n">
-        <v>9.321490000000001</v>
+        <v>10.617</v>
       </c>
       <c r="D93" t="n">
-        <v>38.7239</v>
+        <v>37.858</v>
       </c>
       <c r="E93" t="n">
-        <v>3.87339</v>
+        <v>4.70617</v>
       </c>
       <c r="F93" t="n">
-        <v>5.23868</v>
+        <v>6.50339</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.3321</v>
+        <v>15.738</v>
       </c>
       <c r="C94" t="n">
-        <v>3.96508</v>
+        <v>4.31329</v>
       </c>
       <c r="D94" t="n">
-        <v>39.8815</v>
+        <v>39.1357</v>
       </c>
       <c r="E94" t="n">
-        <v>4.01955</v>
+        <v>4.86878</v>
       </c>
       <c r="F94" t="n">
-        <v>5.51589</v>
+        <v>6.54986</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>6.14624</v>
+        <v>6.12007</v>
       </c>
       <c r="C95" t="n">
-        <v>4.16071</v>
+        <v>4.4581</v>
       </c>
       <c r="D95" t="n">
-        <v>41.2186</v>
+        <v>40.3395</v>
       </c>
       <c r="E95" t="n">
-        <v>4.17917</v>
+        <v>5.07509</v>
       </c>
       <c r="F95" t="n">
-        <v>5.84486</v>
+        <v>7.08815</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.44208</v>
+        <v>6.42238</v>
       </c>
       <c r="C96" t="n">
-        <v>4.31835</v>
+        <v>4.63963</v>
       </c>
       <c r="D96" t="n">
-        <v>42.5902</v>
+        <v>41.7093</v>
       </c>
       <c r="E96" t="n">
-        <v>4.38653</v>
+        <v>5.23938</v>
       </c>
       <c r="F96" t="n">
-        <v>6.03493</v>
+        <v>7.35127</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.79969</v>
+        <v>6.70697</v>
       </c>
       <c r="C97" t="n">
-        <v>4.45837</v>
+        <v>4.80388</v>
       </c>
       <c r="D97" t="n">
-        <v>43.9808</v>
+        <v>43.0649</v>
       </c>
       <c r="E97" t="n">
-        <v>4.54339</v>
+        <v>5.44112</v>
       </c>
       <c r="F97" t="n">
-        <v>6.49238</v>
+        <v>7.62765</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>7.09605</v>
+        <v>6.97749</v>
       </c>
       <c r="C98" t="n">
-        <v>4.68079</v>
+        <v>4.98094</v>
       </c>
       <c r="D98" t="n">
-        <v>45.3602</v>
+        <v>44.4658</v>
       </c>
       <c r="E98" t="n">
-        <v>4.72218</v>
+        <v>5.64514</v>
       </c>
       <c r="F98" t="n">
-        <v>6.83453</v>
+        <v>7.97852</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.37673</v>
+        <v>7.27993</v>
       </c>
       <c r="C99" t="n">
-        <v>4.86266</v>
+        <v>5.18664</v>
       </c>
       <c r="D99" t="n">
-        <v>46.8562</v>
+        <v>45.9369</v>
       </c>
       <c r="E99" t="n">
-        <v>4.918</v>
+        <v>5.81138</v>
       </c>
       <c r="F99" t="n">
-        <v>7.22455</v>
+        <v>8.222060000000001</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.74238</v>
+        <v>7.61842</v>
       </c>
       <c r="C100" t="n">
-        <v>5.08194</v>
+        <v>5.4103</v>
       </c>
       <c r="D100" t="n">
-        <v>48.4299</v>
+        <v>47.4629</v>
       </c>
       <c r="E100" t="n">
-        <v>5.12614</v>
+        <v>6.01934</v>
       </c>
       <c r="F100" t="n">
-        <v>7.53477</v>
+        <v>8.6303</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>8.10563</v>
+        <v>7.97701</v>
       </c>
       <c r="C101" t="n">
-        <v>5.31253</v>
+        <v>5.66373</v>
       </c>
       <c r="D101" t="n">
-        <v>50.099</v>
+        <v>49.0633</v>
       </c>
       <c r="E101" t="n">
-        <v>5.33883</v>
+        <v>6.29842</v>
       </c>
       <c r="F101" t="n">
-        <v>7.83891</v>
+        <v>9.04454</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.65071</v>
+        <v>8.417730000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>5.65272</v>
+        <v>6.01845</v>
       </c>
       <c r="D102" t="n">
-        <v>51.8907</v>
+        <v>50.7794</v>
       </c>
       <c r="E102" t="n">
-        <v>5.52524</v>
+        <v>6.53736</v>
       </c>
       <c r="F102" t="n">
-        <v>8.344670000000001</v>
+        <v>9.54461</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>9.270110000000001</v>
+        <v>9.02131</v>
       </c>
       <c r="C103" t="n">
-        <v>6.11175</v>
+        <v>6.48291</v>
       </c>
       <c r="D103" t="n">
-        <v>53.6246</v>
+        <v>52.5632</v>
       </c>
       <c r="E103" t="n">
-        <v>5.8659</v>
+        <v>6.8838</v>
       </c>
       <c r="F103" t="n">
-        <v>8.977830000000001</v>
+        <v>10.1795</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>10.072</v>
+        <v>9.76768</v>
       </c>
       <c r="C104" t="n">
-        <v>6.68027</v>
+        <v>7.12634</v>
       </c>
       <c r="D104" t="n">
-        <v>55.6001</v>
+        <v>54.3955</v>
       </c>
       <c r="E104" t="n">
-        <v>6.20006</v>
+        <v>7.35315</v>
       </c>
       <c r="F104" t="n">
-        <v>9.931150000000001</v>
+        <v>11.2829</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>11.2569</v>
+        <v>10.7863</v>
       </c>
       <c r="C105" t="n">
-        <v>7.51715</v>
+        <v>8.0931</v>
       </c>
       <c r="D105" t="n">
-        <v>57.5713</v>
+        <v>56.5077</v>
       </c>
       <c r="E105" t="n">
-        <v>6.72371</v>
+        <v>7.90217</v>
       </c>
       <c r="F105" t="n">
-        <v>10.8865</v>
+        <v>12.362</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>12.881</v>
+        <v>12.2944</v>
       </c>
       <c r="C106" t="n">
-        <v>8.751200000000001</v>
+        <v>9.48099</v>
       </c>
       <c r="D106" t="n">
-        <v>59.5229</v>
+        <v>58.4622</v>
       </c>
       <c r="E106" t="n">
-        <v>7.49379</v>
+        <v>8.88203</v>
       </c>
       <c r="F106" t="n">
-        <v>12.2967</v>
+        <v>13.572</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>15.0314</v>
+        <v>14.2791</v>
       </c>
       <c r="C107" t="n">
-        <v>10.6489</v>
+        <v>11.48</v>
       </c>
       <c r="D107" t="n">
-        <v>45.3779</v>
+        <v>44.5381</v>
       </c>
       <c r="E107" t="n">
-        <v>4.7455</v>
+        <v>5.63038</v>
       </c>
       <c r="F107" t="n">
-        <v>7.04867</v>
+        <v>7.86123</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>18.167</v>
+        <v>17.2446</v>
       </c>
       <c r="C108" t="n">
-        <v>4.79346</v>
+        <v>4.99962</v>
       </c>
       <c r="D108" t="n">
-        <v>46.5599</v>
+        <v>45.6588</v>
       </c>
       <c r="E108" t="n">
-        <v>4.86082</v>
+        <v>5.76438</v>
       </c>
       <c r="F108" t="n">
-        <v>7.46364</v>
+        <v>8.15723</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.0134</v>
+        <v>22.0291</v>
       </c>
       <c r="C109" t="n">
-        <v>4.9243</v>
+        <v>5.17743</v>
       </c>
       <c r="D109" t="n">
-        <v>47.7745</v>
+        <v>46.8231</v>
       </c>
       <c r="E109" t="n">
-        <v>4.99026</v>
+        <v>6.05643</v>
       </c>
       <c r="F109" t="n">
-        <v>7.84082</v>
+        <v>8.67939</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.99644</v>
+        <v>7.52704</v>
       </c>
       <c r="C110" t="n">
-        <v>5.14107</v>
+        <v>5.29986</v>
       </c>
       <c r="D110" t="n">
-        <v>48.9935</v>
+        <v>48.0286</v>
       </c>
       <c r="E110" t="n">
-        <v>5.17962</v>
+        <v>6.00805</v>
       </c>
       <c r="F110" t="n">
-        <v>8.39429</v>
+        <v>8.985530000000001</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>8.69833</v>
+        <v>7.94023</v>
       </c>
       <c r="C111" t="n">
-        <v>5.45581</v>
+        <v>5.4771</v>
       </c>
       <c r="D111" t="n">
-        <v>50.2703</v>
+        <v>49.2632</v>
       </c>
       <c r="E111" t="n">
-        <v>5.50397</v>
+        <v>6.2263</v>
       </c>
       <c r="F111" t="n">
-        <v>9.157030000000001</v>
+        <v>9.53627</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>9.081110000000001</v>
+        <v>8.291259999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>5.81526</v>
+        <v>5.72</v>
       </c>
       <c r="D112" t="n">
-        <v>51.6363</v>
+        <v>50.5811</v>
       </c>
       <c r="E112" t="n">
-        <v>5.83056</v>
+        <v>6.38672</v>
       </c>
       <c r="F112" t="n">
-        <v>9.653359999999999</v>
+        <v>9.98847</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>9.600899999999999</v>
+        <v>8.66024</v>
       </c>
       <c r="C113" t="n">
-        <v>6.20388</v>
+        <v>5.94888</v>
       </c>
       <c r="D113" t="n">
-        <v>53.064</v>
+        <v>51.9841</v>
       </c>
       <c r="E113" t="n">
-        <v>6.18226</v>
+        <v>6.56797</v>
       </c>
       <c r="F113" t="n">
-        <v>10.1682</v>
+        <v>10.5582</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>10.0446</v>
+        <v>9.07413</v>
       </c>
       <c r="C114" t="n">
-        <v>6.544</v>
+        <v>6.29201</v>
       </c>
       <c r="D114" t="n">
-        <v>54.5732</v>
+        <v>53.3902</v>
       </c>
       <c r="E114" t="n">
-        <v>6.50188</v>
+        <v>6.88826</v>
       </c>
       <c r="F114" t="n">
-        <v>10.5787</v>
+        <v>11.1883</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>10.4592</v>
+        <v>9.721730000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>6.83801</v>
+        <v>6.68522</v>
       </c>
       <c r="D115" t="n">
-        <v>56.1534</v>
+        <v>55.0016</v>
       </c>
       <c r="E115" t="n">
-        <v>6.77306</v>
+        <v>7.24537</v>
       </c>
       <c r="F115" t="n">
-        <v>10.9899</v>
+        <v>11.8482</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>10.9463</v>
+        <v>10.3137</v>
       </c>
       <c r="C116" t="n">
-        <v>7.19533</v>
+        <v>7.21452</v>
       </c>
       <c r="D116" t="n">
-        <v>57.9139</v>
+        <v>56.5852</v>
       </c>
       <c r="E116" t="n">
-        <v>7.09479</v>
+        <v>7.71995</v>
       </c>
       <c r="F116" t="n">
-        <v>11.4445</v>
+        <v>12.4436</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>11.5736</v>
+        <v>11.0189</v>
       </c>
       <c r="C117" t="n">
-        <v>7.65163</v>
+        <v>7.75415</v>
       </c>
       <c r="D117" t="n">
-        <v>59.7561</v>
+        <v>58.3279</v>
       </c>
       <c r="E117" t="n">
-        <v>7.46247</v>
+        <v>8.194470000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>11.9954</v>
+        <v>13.0245</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>12.2762</v>
+        <v>11.7614</v>
       </c>
       <c r="C118" t="n">
-        <v>8.219939999999999</v>
+        <v>8.38724</v>
       </c>
       <c r="D118" t="n">
-        <v>61.6376</v>
+        <v>60.1453</v>
       </c>
       <c r="E118" t="n">
-        <v>7.88263</v>
+        <v>8.69819</v>
       </c>
       <c r="F118" t="n">
-        <v>12.5916</v>
+        <v>13.7498</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>13.21</v>
+        <v>12.7552</v>
       </c>
       <c r="C119" t="n">
-        <v>8.95594</v>
+        <v>9.29144</v>
       </c>
       <c r="D119" t="n">
-        <v>63.6332</v>
+        <v>62.0604</v>
       </c>
       <c r="E119" t="n">
-        <v>8.408770000000001</v>
+        <v>9.374700000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>13.3607</v>
+        <v>14.6168</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.5174</v>
+        <v>13.9761</v>
       </c>
       <c r="C120" t="n">
-        <v>10.0724</v>
+        <v>10.4731</v>
       </c>
       <c r="D120" t="n">
-        <v>65.7991</v>
+        <v>64.1063</v>
       </c>
       <c r="E120" t="n">
-        <v>9.13538</v>
+        <v>10.2039</v>
       </c>
       <c r="F120" t="n">
-        <v>14.3893</v>
+        <v>15.7777</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>16.2997</v>
+        <v>15.7262</v>
       </c>
       <c r="C121" t="n">
-        <v>11.664</v>
+        <v>12.2584</v>
       </c>
       <c r="D121" t="n">
-        <v>48.9338</v>
+        <v>47.8918</v>
       </c>
       <c r="E121" t="n">
-        <v>6.287</v>
+        <v>7.34565</v>
       </c>
       <c r="F121" t="n">
-        <v>10.252</v>
+        <v>10.7155</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>18.9407</v>
+        <v>18.2183</v>
       </c>
       <c r="C122" t="n">
-        <v>6.39721</v>
+        <v>6.96261</v>
       </c>
       <c r="D122" t="n">
-        <v>50.324</v>
+        <v>48.7644</v>
       </c>
       <c r="E122" t="n">
-        <v>6.67488</v>
+        <v>7.4562</v>
       </c>
       <c r="F122" t="n">
-        <v>10.3464</v>
+        <v>10.636</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>23.0487</v>
+        <v>22.3445</v>
       </c>
       <c r="C123" t="n">
-        <v>6.82396</v>
+        <v>6.9547</v>
       </c>
       <c r="D123" t="n">
-        <v>51.4842</v>
+        <v>50.1489</v>
       </c>
       <c r="E123" t="n">
-        <v>6.73145</v>
+        <v>7.73333</v>
       </c>
       <c r="F123" t="n">
-        <v>10.5887</v>
+        <v>11.3409</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>9.80979</v>
+        <v>9.935919999999999</v>
       </c>
       <c r="C124" t="n">
-        <v>6.91581</v>
+        <v>7.30718</v>
       </c>
       <c r="D124" t="n">
-        <v>52.6977</v>
+        <v>51.3414</v>
       </c>
       <c r="E124" t="n">
-        <v>7.4716</v>
+        <v>8.001620000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>11.1681</v>
+        <v>12.7878</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.788</v>
+        <v>10.2103</v>
       </c>
       <c r="C125" t="n">
-        <v>7.05887</v>
+        <v>7.45562</v>
       </c>
       <c r="D125" t="n">
-        <v>53.935</v>
+        <v>52.5417</v>
       </c>
       <c r="E125" t="n">
-        <v>7.67422</v>
+        <v>8.38862</v>
       </c>
       <c r="F125" t="n">
-        <v>11.1072</v>
+        <v>12.3839</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.6663</v>
+        <v>10.7448</v>
       </c>
       <c r="C126" t="n">
-        <v>7.23441</v>
+        <v>7.75434</v>
       </c>
       <c r="D126" t="n">
-        <v>55.1722</v>
+        <v>53.5582</v>
       </c>
       <c r="E126" t="n">
-        <v>7.9397</v>
+        <v>8.45166</v>
       </c>
       <c r="F126" t="n">
-        <v>11.9663</v>
+        <v>12.5676</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>11.0348</v>
+        <v>10.9656</v>
       </c>
       <c r="C127" t="n">
-        <v>7.46115</v>
+        <v>7.96358</v>
       </c>
       <c r="D127" t="n">
-        <v>56.5878</v>
+        <v>55.1978</v>
       </c>
       <c r="E127" t="n">
-        <v>7.91134</v>
+        <v>8.735620000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>12.3368</v>
+        <v>13.0551</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>11.2178</v>
+        <v>11.0904</v>
       </c>
       <c r="C128" t="n">
-        <v>7.81918</v>
+        <v>7.73984</v>
       </c>
       <c r="D128" t="n">
-        <v>58.6164</v>
+        <v>56.6175</v>
       </c>
       <c r="E128" t="n">
-        <v>7.91721</v>
+        <v>9.08994</v>
       </c>
       <c r="F128" t="n">
-        <v>12.247</v>
+        <v>13.6589</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.5135</v>
+        <v>11.6849</v>
       </c>
       <c r="C129" t="n">
-        <v>8.11786</v>
+        <v>8.29519</v>
       </c>
       <c r="D129" t="n">
-        <v>60.3559</v>
+        <v>58.1471</v>
       </c>
       <c r="E129" t="n">
-        <v>8.34226</v>
+        <v>9.310219999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>12.6192</v>
+        <v>14.0297</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>12.0583</v>
+        <v>12.0384</v>
       </c>
       <c r="C130" t="n">
-        <v>8.490869999999999</v>
+        <v>8.92323</v>
       </c>
       <c r="D130" t="n">
-        <v>61.8782</v>
+        <v>59.7406</v>
       </c>
       <c r="E130" t="n">
-        <v>8.725059999999999</v>
+        <v>9.429209999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>13.5137</v>
+        <v>14.436</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>12.3903</v>
+        <v>12.3629</v>
       </c>
       <c r="C131" t="n">
-        <v>8.722300000000001</v>
+        <v>9.135450000000001</v>
       </c>
       <c r="D131" t="n">
-        <v>62.9597</v>
+        <v>61.5081</v>
       </c>
       <c r="E131" t="n">
-        <v>8.835990000000001</v>
+        <v>9.905670000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>13.8225</v>
+        <v>15.215</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>13.3704</v>
+        <v>13.0166</v>
       </c>
       <c r="C132" t="n">
-        <v>9.19988</v>
+        <v>9.378220000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>65.2367</v>
+        <v>63.3799</v>
       </c>
       <c r="E132" t="n">
-        <v>9.198370000000001</v>
+        <v>10.4899</v>
       </c>
       <c r="F132" t="n">
-        <v>14.4091</v>
+        <v>15.8669</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>14.2119</v>
+        <v>13.8126</v>
       </c>
       <c r="C133" t="n">
-        <v>9.731479999999999</v>
+        <v>10.0324</v>
       </c>
       <c r="D133" t="n">
-        <v>67.39830000000001</v>
+        <v>65.0147</v>
       </c>
       <c r="E133" t="n">
-        <v>9.546860000000001</v>
+        <v>10.9085</v>
       </c>
       <c r="F133" t="n">
-        <v>15.0249</v>
+        <v>16.4789</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>15.3574</v>
+        <v>14.9112</v>
       </c>
       <c r="C134" t="n">
-        <v>10.8924</v>
+        <v>11.4287</v>
       </c>
       <c r="D134" t="n">
-        <v>69.2214</v>
+        <v>67.074</v>
       </c>
       <c r="E134" t="n">
-        <v>10.109</v>
+        <v>11.5827</v>
       </c>
       <c r="F134" t="n">
-        <v>15.9206</v>
+        <v>17.8547</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.1789</v>
+        <v>16.6948</v>
       </c>
       <c r="C135" t="n">
-        <v>12.3069</v>
+        <v>13.0171</v>
       </c>
       <c r="D135" t="n">
-        <v>51.0768</v>
+        <v>49.8188</v>
       </c>
       <c r="E135" t="n">
-        <v>13.4921</v>
+        <v>15.4177</v>
       </c>
       <c r="F135" t="n">
-        <v>15.9152</v>
+        <v>17.9952</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>19.3166</v>
+        <v>18.8078</v>
       </c>
       <c r="C136" t="n">
-        <v>13.6965</v>
+        <v>13.8647</v>
       </c>
       <c r="D136" t="n">
-        <v>52.2793</v>
+        <v>50.9224</v>
       </c>
       <c r="E136" t="n">
-        <v>13.6901</v>
+        <v>15.4971</v>
       </c>
       <c r="F136" t="n">
-        <v>16.4931</v>
+        <v>19.1739</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>23.1265</v>
+        <v>22.3359</v>
       </c>
       <c r="C137" t="n">
-        <v>13.6884</v>
+        <v>14.0344</v>
       </c>
       <c r="D137" t="n">
-        <v>53.4414</v>
+        <v>51.8013</v>
       </c>
       <c r="E137" t="n">
-        <v>13.7999</v>
+        <v>15.4838</v>
       </c>
       <c r="F137" t="n">
-        <v>16.4224</v>
+        <v>19.1218</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.3706</v>
+        <v>16.9917</v>
       </c>
       <c r="C138" t="n">
-        <v>13.8336</v>
+        <v>14.0714</v>
       </c>
       <c r="D138" t="n">
-        <v>54.6154</v>
+        <v>53.1075</v>
       </c>
       <c r="E138" t="n">
-        <v>13.6998</v>
+        <v>15.7429</v>
       </c>
       <c r="F138" t="n">
-        <v>17.4248</v>
+        <v>19.5205</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.6204</v>
+        <v>17.1515</v>
       </c>
       <c r="C139" t="n">
-        <v>13.8326</v>
+        <v>14.2752</v>
       </c>
       <c r="D139" t="n">
-        <v>55.6677</v>
+        <v>54.4383</v>
       </c>
       <c r="E139" t="n">
-        <v>13.91</v>
+        <v>15.867</v>
       </c>
       <c r="F139" t="n">
-        <v>17.1258</v>
+        <v>19.9202</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>17.749</v>
+        <v>17.325</v>
       </c>
       <c r="C140" t="n">
-        <v>13.9515</v>
+        <v>14.4177</v>
       </c>
       <c r="D140" t="n">
-        <v>57.3747</v>
+        <v>55.942</v>
       </c>
       <c r="E140" t="n">
-        <v>14.0887</v>
+        <v>15.9784</v>
       </c>
       <c r="F140" t="n">
-        <v>18.1202</v>
+        <v>19.5343</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>18.0144</v>
+        <v>17.4272</v>
       </c>
       <c r="C141" t="n">
-        <v>14.2313</v>
+        <v>14.4619</v>
       </c>
       <c r="D141" t="n">
-        <v>58.8196</v>
+        <v>56.8912</v>
       </c>
       <c r="E141" t="n">
-        <v>14.1931</v>
+        <v>15.6747</v>
       </c>
       <c r="F141" t="n">
-        <v>17.7603</v>
+        <v>20.7594</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>18.2149</v>
+        <v>16.8697</v>
       </c>
       <c r="C142" t="n">
-        <v>14.0893</v>
+        <v>14.6021</v>
       </c>
       <c r="D142" t="n">
-        <v>60.2828</v>
+        <v>58.1593</v>
       </c>
       <c r="E142" t="n">
-        <v>14.4749</v>
+        <v>16.4612</v>
       </c>
       <c r="F142" t="n">
-        <v>18.8637</v>
+        <v>20.7568</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>18.5687</v>
+        <v>17.9712</v>
       </c>
       <c r="C143" t="n">
-        <v>14.4501</v>
+        <v>14.8471</v>
       </c>
       <c r="D143" t="n">
-        <v>61.4392</v>
+        <v>59.7515</v>
       </c>
       <c r="E143" t="n">
-        <v>14.4188</v>
+        <v>16.7692</v>
       </c>
       <c r="F143" t="n">
-        <v>18.4121</v>
+        <v>20.7455</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered unsuccessful looukp.xlsx
+++ b/clang-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.69709</v>
+        <v>2.70451</v>
       </c>
       <c r="C2" t="n">
-        <v>2.58762</v>
+        <v>2.0584</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0057</v>
+        <v>13.0263</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7796</v>
+        <v>2.31906</v>
       </c>
       <c r="F2" t="n">
-        <v>2.89093</v>
+        <v>2.33274</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.7816</v>
+        <v>2.74691</v>
       </c>
       <c r="C3" t="n">
-        <v>2.67481</v>
+        <v>2.16401</v>
       </c>
       <c r="D3" t="n">
-        <v>13.3258</v>
+        <v>13.3459</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8289</v>
+        <v>2.41218</v>
       </c>
       <c r="F3" t="n">
-        <v>2.93517</v>
+        <v>2.42682</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.85969</v>
+        <v>2.90022</v>
       </c>
       <c r="C4" t="n">
-        <v>2.85582</v>
+        <v>2.317</v>
       </c>
       <c r="D4" t="n">
-        <v>14.0469</v>
+        <v>13.7887</v>
       </c>
       <c r="E4" t="n">
-        <v>2.95155</v>
+        <v>2.51324</v>
       </c>
       <c r="F4" t="n">
-        <v>3.04653</v>
+        <v>2.53649</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.2719</v>
+        <v>3.26191</v>
       </c>
       <c r="C5" t="n">
-        <v>3.13155</v>
+        <v>2.71359</v>
       </c>
       <c r="D5" t="n">
-        <v>14.611</v>
+        <v>14.3586</v>
       </c>
       <c r="E5" t="n">
-        <v>3.02626</v>
+        <v>2.03256</v>
       </c>
       <c r="F5" t="n">
-        <v>3.21955</v>
+        <v>2.03857</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.6994</v>
+        <v>4.6892</v>
       </c>
       <c r="C6" t="n">
-        <v>4.2937</v>
+        <v>3.47324</v>
       </c>
       <c r="D6" t="n">
-        <v>15.3345</v>
+        <v>15.1155</v>
       </c>
       <c r="E6" t="n">
-        <v>3.22266</v>
+        <v>2.04877</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5319</v>
+        <v>2.04457</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.66202</v>
+        <v>6.29383</v>
       </c>
       <c r="C7" t="n">
-        <v>6.20566</v>
+        <v>5.18855</v>
       </c>
       <c r="D7" t="n">
-        <v>10.716</v>
+        <v>10.1297</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5393</v>
+        <v>2.06417</v>
       </c>
       <c r="F7" t="n">
-        <v>2.54401</v>
+        <v>2.06893</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.671810000000001</v>
+        <v>9.656370000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>2.23786</v>
+        <v>1.74485</v>
       </c>
       <c r="D8" t="n">
-        <v>11.4599</v>
+        <v>10.8011</v>
       </c>
       <c r="E8" t="n">
-        <v>2.56485</v>
+        <v>2.08738</v>
       </c>
       <c r="F8" t="n">
-        <v>2.57042</v>
+        <v>2.08764</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.968</v>
+        <v>13.9772</v>
       </c>
       <c r="C9" t="n">
-        <v>2.24258</v>
+        <v>1.7647</v>
       </c>
       <c r="D9" t="n">
-        <v>12.0024</v>
+        <v>11.5114</v>
       </c>
       <c r="E9" t="n">
-        <v>2.58002</v>
+        <v>2.10586</v>
       </c>
       <c r="F9" t="n">
-        <v>2.58772</v>
+        <v>2.10347</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.71701</v>
+        <v>2.64467</v>
       </c>
       <c r="C10" t="n">
-        <v>2.31777</v>
+        <v>1.80309</v>
       </c>
       <c r="D10" t="n">
-        <v>12.5743</v>
+        <v>12.1686</v>
       </c>
       <c r="E10" t="n">
-        <v>2.59976</v>
+        <v>2.13453</v>
       </c>
       <c r="F10" t="n">
-        <v>2.60272</v>
+        <v>2.1343</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.85353</v>
+        <v>2.70493</v>
       </c>
       <c r="C11" t="n">
-        <v>2.32714</v>
+        <v>1.83788</v>
       </c>
       <c r="D11" t="n">
-        <v>13.0355</v>
+        <v>12.6765</v>
       </c>
       <c r="E11" t="n">
-        <v>2.64805</v>
+        <v>2.16163</v>
       </c>
       <c r="F11" t="n">
-        <v>2.66213</v>
+        <v>2.18016</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.77558</v>
+        <v>2.72166</v>
       </c>
       <c r="C12" t="n">
-        <v>2.39303</v>
+        <v>1.86961</v>
       </c>
       <c r="D12" t="n">
-        <v>13.5771</v>
+        <v>13.2543</v>
       </c>
       <c r="E12" t="n">
-        <v>2.71077</v>
+        <v>2.18881</v>
       </c>
       <c r="F12" t="n">
-        <v>2.71022</v>
+        <v>2.19106</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.90238</v>
+        <v>2.72508</v>
       </c>
       <c r="C13" t="n">
-        <v>2.47092</v>
+        <v>1.90458</v>
       </c>
       <c r="D13" t="n">
-        <v>14.0918</v>
+        <v>13.8231</v>
       </c>
       <c r="E13" t="n">
-        <v>2.71789</v>
+        <v>2.21768</v>
       </c>
       <c r="F13" t="n">
-        <v>2.73962</v>
+        <v>2.21396</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.86658</v>
+        <v>2.78338</v>
       </c>
       <c r="C14" t="n">
-        <v>2.49466</v>
+        <v>2.00325</v>
       </c>
       <c r="D14" t="n">
-        <v>14.5694</v>
+        <v>14.4068</v>
       </c>
       <c r="E14" t="n">
-        <v>2.73746</v>
+        <v>2.2535</v>
       </c>
       <c r="F14" t="n">
-        <v>2.82308</v>
+        <v>2.2682</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.95748</v>
+        <v>2.89912</v>
       </c>
       <c r="C15" t="n">
-        <v>2.57878</v>
+        <v>2.08185</v>
       </c>
       <c r="D15" t="n">
-        <v>15.0329</v>
+        <v>14.8348</v>
       </c>
       <c r="E15" t="n">
-        <v>2.81173</v>
+        <v>2.3063</v>
       </c>
       <c r="F15" t="n">
-        <v>2.92064</v>
+        <v>2.34677</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.14514</v>
+        <v>3.05365</v>
       </c>
       <c r="C16" t="n">
-        <v>2.68137</v>
+        <v>2.21809</v>
       </c>
       <c r="D16" t="n">
-        <v>15.4346</v>
+        <v>15.3409</v>
       </c>
       <c r="E16" t="n">
-        <v>2.90742</v>
+        <v>2.3763</v>
       </c>
       <c r="F16" t="n">
-        <v>2.95452</v>
+        <v>2.40488</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.23886</v>
+        <v>3.15498</v>
       </c>
       <c r="C17" t="n">
-        <v>2.85496</v>
+        <v>2.40812</v>
       </c>
       <c r="D17" t="n">
-        <v>15.8295</v>
+        <v>15.8373</v>
       </c>
       <c r="E17" t="n">
-        <v>2.98253</v>
+        <v>2.44192</v>
       </c>
       <c r="F17" t="n">
-        <v>3.11074</v>
+        <v>2.49169</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.62547</v>
+        <v>3.52452</v>
       </c>
       <c r="C18" t="n">
-        <v>3.12603</v>
+        <v>2.66938</v>
       </c>
       <c r="D18" t="n">
-        <v>16.2849</v>
+        <v>16.2441</v>
       </c>
       <c r="E18" t="n">
-        <v>3.10338</v>
+        <v>2.58098</v>
       </c>
       <c r="F18" t="n">
-        <v>3.24082</v>
+        <v>2.65872</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.30498</v>
+        <v>4.03357</v>
       </c>
       <c r="C19" t="n">
-        <v>3.61154</v>
+        <v>3.24519</v>
       </c>
       <c r="D19" t="n">
-        <v>16.7853</v>
+        <v>16.7446</v>
       </c>
       <c r="E19" t="n">
-        <v>3.26978</v>
+        <v>2.78922</v>
       </c>
       <c r="F19" t="n">
-        <v>3.4163</v>
+        <v>2.86568</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.26068</v>
+        <v>5.2695</v>
       </c>
       <c r="C20" t="n">
-        <v>4.54314</v>
+        <v>4.21283</v>
       </c>
       <c r="D20" t="n">
-        <v>17.1569</v>
+        <v>17.197</v>
       </c>
       <c r="E20" t="n">
-        <v>3.63453</v>
+        <v>2.07848</v>
       </c>
       <c r="F20" t="n">
-        <v>3.88737</v>
+        <v>2.13428</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.80506</v>
+        <v>6.76459</v>
       </c>
       <c r="C21" t="n">
-        <v>6.30508</v>
+        <v>5.47049</v>
       </c>
       <c r="D21" t="n">
-        <v>12.1869</v>
+        <v>11.8433</v>
       </c>
       <c r="E21" t="n">
-        <v>2.50982</v>
+        <v>2.09547</v>
       </c>
       <c r="F21" t="n">
-        <v>2.67758</v>
+        <v>2.14263</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.14231</v>
+        <v>9.44924</v>
       </c>
       <c r="C22" t="n">
-        <v>2.30664</v>
+        <v>1.81735</v>
       </c>
       <c r="D22" t="n">
-        <v>12.629</v>
+        <v>12.4041</v>
       </c>
       <c r="E22" t="n">
-        <v>2.54522</v>
+        <v>2.12492</v>
       </c>
       <c r="F22" t="n">
-        <v>2.98713</v>
+        <v>2.19424</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>13.1109</v>
+        <v>12.7487</v>
       </c>
       <c r="C23" t="n">
-        <v>2.4311</v>
+        <v>1.83221</v>
       </c>
       <c r="D23" t="n">
-        <v>13.1981</v>
+        <v>12.9685</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5725</v>
+        <v>2.14011</v>
       </c>
       <c r="F23" t="n">
-        <v>2.79293</v>
+        <v>2.20488</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.83893</v>
+        <v>2.73298</v>
       </c>
       <c r="C24" t="n">
-        <v>2.371</v>
+        <v>1.88414</v>
       </c>
       <c r="D24" t="n">
-        <v>13.6843</v>
+        <v>13.5167</v>
       </c>
       <c r="E24" t="n">
-        <v>2.6483</v>
+        <v>2.16826</v>
       </c>
       <c r="F24" t="n">
-        <v>3.0454</v>
+        <v>2.23995</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.03879</v>
+        <v>2.78516</v>
       </c>
       <c r="C25" t="n">
-        <v>2.49364</v>
+        <v>1.90203</v>
       </c>
       <c r="D25" t="n">
-        <v>14.1442</v>
+        <v>14.0045</v>
       </c>
       <c r="E25" t="n">
-        <v>2.67568</v>
+        <v>2.19621</v>
       </c>
       <c r="F25" t="n">
-        <v>3.09001</v>
+        <v>2.29652</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.09967</v>
+        <v>2.86163</v>
       </c>
       <c r="C26" t="n">
-        <v>2.53362</v>
+        <v>1.94556</v>
       </c>
       <c r="D26" t="n">
-        <v>14.5437</v>
+        <v>14.4595</v>
       </c>
       <c r="E26" t="n">
-        <v>2.67039</v>
+        <v>2.24401</v>
       </c>
       <c r="F26" t="n">
-        <v>2.89956</v>
+        <v>2.36177</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.0655</v>
+        <v>2.91385</v>
       </c>
       <c r="C27" t="n">
-        <v>2.52852</v>
+        <v>1.98802</v>
       </c>
       <c r="D27" t="n">
-        <v>15.07</v>
+        <v>14.9805</v>
       </c>
       <c r="E27" t="n">
-        <v>2.72413</v>
+        <v>2.27068</v>
       </c>
       <c r="F27" t="n">
-        <v>2.96622</v>
+        <v>2.40178</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.22749</v>
+        <v>3.00315</v>
       </c>
       <c r="C28" t="n">
-        <v>2.66803</v>
+        <v>2.05748</v>
       </c>
       <c r="D28" t="n">
-        <v>15.5241</v>
+        <v>15.4662</v>
       </c>
       <c r="E28" t="n">
-        <v>2.77945</v>
+        <v>2.32893</v>
       </c>
       <c r="F28" t="n">
-        <v>3.04098</v>
+        <v>2.46117</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.57558</v>
+        <v>3.22385</v>
       </c>
       <c r="C29" t="n">
-        <v>2.68682</v>
+        <v>2.17508</v>
       </c>
       <c r="D29" t="n">
-        <v>16.0214</v>
+        <v>15.9333</v>
       </c>
       <c r="E29" t="n">
-        <v>2.8579</v>
+        <v>2.39463</v>
       </c>
       <c r="F29" t="n">
-        <v>3.1307</v>
+        <v>2.53726</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.37909</v>
+        <v>3.34772</v>
       </c>
       <c r="C30" t="n">
-        <v>2.80191</v>
+        <v>2.32095</v>
       </c>
       <c r="D30" t="n">
-        <v>16.4195</v>
+        <v>16.4364</v>
       </c>
       <c r="E30" t="n">
-        <v>2.92369</v>
+        <v>2.46384</v>
       </c>
       <c r="F30" t="n">
-        <v>3.47039</v>
+        <v>2.60841</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.60904</v>
+        <v>3.56802</v>
       </c>
       <c r="C31" t="n">
-        <v>2.97951</v>
+        <v>2.48738</v>
       </c>
       <c r="D31" t="n">
-        <v>16.9208</v>
+        <v>16.906</v>
       </c>
       <c r="E31" t="n">
-        <v>3.03565</v>
+        <v>2.5446</v>
       </c>
       <c r="F31" t="n">
-        <v>3.35982</v>
+        <v>2.72069</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>3.99365</v>
+        <v>4.04831</v>
       </c>
       <c r="C32" t="n">
-        <v>3.26997</v>
+        <v>2.75228</v>
       </c>
       <c r="D32" t="n">
-        <v>17.2423</v>
+        <v>17.2853</v>
       </c>
       <c r="E32" t="n">
-        <v>3.16024</v>
+        <v>2.67334</v>
       </c>
       <c r="F32" t="n">
-        <v>3.61137</v>
+        <v>2.86641</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.69151</v>
+        <v>4.81289</v>
       </c>
       <c r="C33" t="n">
-        <v>3.72668</v>
+        <v>3.28117</v>
       </c>
       <c r="D33" t="n">
-        <v>17.6741</v>
+        <v>17.739</v>
       </c>
       <c r="E33" t="n">
-        <v>3.43135</v>
+        <v>2.90247</v>
       </c>
       <c r="F33" t="n">
-        <v>3.71197</v>
+        <v>3.09478</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.72803</v>
+        <v>5.78199</v>
       </c>
       <c r="C34" t="n">
-        <v>4.66198</v>
+        <v>4.1035</v>
       </c>
       <c r="D34" t="n">
-        <v>18.1148</v>
+        <v>18.1793</v>
       </c>
       <c r="E34" t="n">
-        <v>3.7735</v>
+        <v>2.10912</v>
       </c>
       <c r="F34" t="n">
-        <v>4.31999</v>
+        <v>2.25109</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.04193</v>
+        <v>7.28887</v>
       </c>
       <c r="C35" t="n">
-        <v>6.06439</v>
+        <v>5.1935</v>
       </c>
       <c r="D35" t="n">
-        <v>12.4109</v>
+        <v>12.3532</v>
       </c>
       <c r="E35" t="n">
-        <v>2.92911</v>
+        <v>2.1383</v>
       </c>
       <c r="F35" t="n">
-        <v>3.15637</v>
+        <v>2.26851</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.37865</v>
+        <v>9.776680000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>8.17319</v>
+        <v>6.81791</v>
       </c>
       <c r="D36" t="n">
-        <v>12.9038</v>
+        <v>12.8768</v>
       </c>
       <c r="E36" t="n">
-        <v>2.9461</v>
+        <v>2.16279</v>
       </c>
       <c r="F36" t="n">
-        <v>3.19311</v>
+        <v>2.29722</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>12.8312</v>
+        <v>13.0352</v>
       </c>
       <c r="C37" t="n">
-        <v>2.56237</v>
+        <v>1.92646</v>
       </c>
       <c r="D37" t="n">
-        <v>13.4143</v>
+        <v>13.3178</v>
       </c>
       <c r="E37" t="n">
-        <v>2.97003</v>
+        <v>2.19324</v>
       </c>
       <c r="F37" t="n">
-        <v>2.8436</v>
+        <v>2.37563</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>3.1465</v>
+        <v>2.82283</v>
       </c>
       <c r="C38" t="n">
-        <v>2.66369</v>
+        <v>1.92804</v>
       </c>
       <c r="D38" t="n">
-        <v>14.3228</v>
+        <v>13.8305</v>
       </c>
       <c r="E38" t="n">
-        <v>3.15156</v>
+        <v>2.21884</v>
       </c>
       <c r="F38" t="n">
-        <v>2.91672</v>
+        <v>2.38329</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.20091</v>
+        <v>2.87877</v>
       </c>
       <c r="C39" t="n">
-        <v>2.67375</v>
+        <v>2.02828</v>
       </c>
       <c r="D39" t="n">
-        <v>14.8023</v>
+        <v>14.3638</v>
       </c>
       <c r="E39" t="n">
-        <v>2.92035</v>
+        <v>2.25648</v>
       </c>
       <c r="F39" t="n">
-        <v>3.35928</v>
+        <v>2.4381</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.99211</v>
+        <v>2.93914</v>
       </c>
       <c r="C40" t="n">
-        <v>2.67243</v>
+        <v>1.98512</v>
       </c>
       <c r="D40" t="n">
-        <v>15.2964</v>
+        <v>14.824</v>
       </c>
       <c r="E40" t="n">
-        <v>3.23053</v>
+        <v>2.28635</v>
       </c>
       <c r="F40" t="n">
-        <v>3.00219</v>
+        <v>2.51916</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.31321</v>
+        <v>3.02803</v>
       </c>
       <c r="C41" t="n">
-        <v>2.77093</v>
+        <v>2.12221</v>
       </c>
       <c r="D41" t="n">
-        <v>15.9574</v>
+        <v>15.2982</v>
       </c>
       <c r="E41" t="n">
-        <v>3.24913</v>
+        <v>2.3225</v>
       </c>
       <c r="F41" t="n">
-        <v>3.05507</v>
+        <v>2.57096</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.47247</v>
+        <v>3.0964</v>
       </c>
       <c r="C42" t="n">
-        <v>2.84046</v>
+        <v>2.17137</v>
       </c>
       <c r="D42" t="n">
-        <v>16.5805</v>
+        <v>15.7593</v>
       </c>
       <c r="E42" t="n">
-        <v>3.29331</v>
+        <v>2.37689</v>
       </c>
       <c r="F42" t="n">
-        <v>3.12194</v>
+        <v>2.60313</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.56028</v>
+        <v>3.23313</v>
       </c>
       <c r="C43" t="n">
-        <v>2.98013</v>
+        <v>2.208</v>
       </c>
       <c r="D43" t="n">
-        <v>16.9631</v>
+        <v>16.2501</v>
       </c>
       <c r="E43" t="n">
-        <v>3.12416</v>
+        <v>2.43141</v>
       </c>
       <c r="F43" t="n">
-        <v>3.58625</v>
+        <v>2.67469</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.70866</v>
+        <v>3.43912</v>
       </c>
       <c r="C44" t="n">
-        <v>3.08236</v>
+        <v>2.38865</v>
       </c>
       <c r="D44" t="n">
-        <v>17.437</v>
+        <v>16.7032</v>
       </c>
       <c r="E44" t="n">
-        <v>3.29207</v>
+        <v>2.51631</v>
       </c>
       <c r="F44" t="n">
-        <v>3.62681</v>
+        <v>2.79754</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.72307</v>
+        <v>3.69668</v>
       </c>
       <c r="C45" t="n">
-        <v>3.08177</v>
+        <v>2.57169</v>
       </c>
       <c r="D45" t="n">
-        <v>17.8817</v>
+        <v>17.1464</v>
       </c>
       <c r="E45" t="n">
-        <v>3.07294</v>
+        <v>2.61816</v>
       </c>
       <c r="F45" t="n">
-        <v>3.6884</v>
+        <v>2.91419</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.26894</v>
+        <v>4.06904</v>
       </c>
       <c r="C46" t="n">
-        <v>3.58065</v>
+        <v>2.90911</v>
       </c>
       <c r="D46" t="n">
-        <v>18.386</v>
+        <v>17.5941</v>
       </c>
       <c r="E46" t="n">
-        <v>3.49861</v>
+        <v>2.76529</v>
       </c>
       <c r="F46" t="n">
-        <v>3.84397</v>
+        <v>3.04769</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.87458</v>
+        <v>4.60714</v>
       </c>
       <c r="C47" t="n">
-        <v>4.0389</v>
+        <v>3.3664</v>
       </c>
       <c r="D47" t="n">
-        <v>18.944</v>
+        <v>18.0256</v>
       </c>
       <c r="E47" t="n">
-        <v>3.77101</v>
+        <v>3.00228</v>
       </c>
       <c r="F47" t="n">
-        <v>4.08393</v>
+        <v>3.29477</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.42158</v>
+        <v>5.50902</v>
       </c>
       <c r="C48" t="n">
-        <v>4.8806</v>
+        <v>4.00872</v>
       </c>
       <c r="D48" t="n">
-        <v>19.314</v>
+        <v>18.6072</v>
       </c>
       <c r="E48" t="n">
-        <v>4.15744</v>
+        <v>2.25728</v>
       </c>
       <c r="F48" t="n">
-        <v>4.53495</v>
+        <v>2.51506</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.61657</v>
+        <v>6.66511</v>
       </c>
       <c r="C49" t="n">
-        <v>5.83389</v>
+        <v>4.94149</v>
       </c>
       <c r="D49" t="n">
-        <v>20.3054</v>
+        <v>19.028</v>
       </c>
       <c r="E49" t="n">
-        <v>4.73812</v>
+        <v>2.26192</v>
       </c>
       <c r="F49" t="n">
-        <v>4.85083</v>
+        <v>2.54674</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.65996</v>
+        <v>8.45603</v>
       </c>
       <c r="C50" t="n">
-        <v>7.71263</v>
+        <v>6.41676</v>
       </c>
       <c r="D50" t="n">
-        <v>15.0471</v>
+        <v>12.9351</v>
       </c>
       <c r="E50" t="n">
-        <v>2.99059</v>
+        <v>2.37107</v>
       </c>
       <c r="F50" t="n">
-        <v>3.30993</v>
+        <v>2.56935</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>12.0832</v>
+        <v>11.3932</v>
       </c>
       <c r="C51" t="n">
-        <v>2.51138</v>
+        <v>2.05094</v>
       </c>
       <c r="D51" t="n">
-        <v>16.1744</v>
+        <v>13.4078</v>
       </c>
       <c r="E51" t="n">
-        <v>3.0261</v>
+        <v>2.25601</v>
       </c>
       <c r="F51" t="n">
-        <v>3.34852</v>
+        <v>2.59494</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>16.3777</v>
+        <v>15.5311</v>
       </c>
       <c r="C52" t="n">
-        <v>2.54199</v>
+        <v>2.03648</v>
       </c>
       <c r="D52" t="n">
-        <v>17.4208</v>
+        <v>13.9696</v>
       </c>
       <c r="E52" t="n">
-        <v>3.05834</v>
+        <v>2.28754</v>
       </c>
       <c r="F52" t="n">
-        <v>3.38872</v>
+        <v>2.64854</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.05406</v>
+        <v>3.06332</v>
       </c>
       <c r="C53" t="n">
-        <v>2.5841</v>
+        <v>2.11205</v>
       </c>
       <c r="D53" t="n">
-        <v>18.6187</v>
+        <v>14.444</v>
       </c>
       <c r="E53" t="n">
-        <v>2.89525</v>
+        <v>2.31858</v>
       </c>
       <c r="F53" t="n">
-        <v>3.20215</v>
+        <v>2.69203</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.61672</v>
+        <v>3.13758</v>
       </c>
       <c r="C54" t="n">
-        <v>2.56386</v>
+        <v>2.11976</v>
       </c>
       <c r="D54" t="n">
-        <v>19.7684</v>
+        <v>15.0025</v>
       </c>
       <c r="E54" t="n">
-        <v>2.94021</v>
+        <v>2.34884</v>
       </c>
       <c r="F54" t="n">
-        <v>3.24746</v>
+        <v>2.72804</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.66646</v>
+        <v>3.20549</v>
       </c>
       <c r="C55" t="n">
-        <v>2.69766</v>
+        <v>2.19028</v>
       </c>
       <c r="D55" t="n">
-        <v>21.2855</v>
+        <v>15.5497</v>
       </c>
       <c r="E55" t="n">
-        <v>2.94806</v>
+        <v>2.46843</v>
       </c>
       <c r="F55" t="n">
-        <v>3.36665</v>
+        <v>2.80567</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.29697</v>
+        <v>3.2859</v>
       </c>
       <c r="C56" t="n">
-        <v>2.75128</v>
+        <v>2.26165</v>
       </c>
       <c r="D56" t="n">
-        <v>22.4598</v>
+        <v>16.0619</v>
       </c>
       <c r="E56" t="n">
-        <v>3.05173</v>
+        <v>2.5134</v>
       </c>
       <c r="F56" t="n">
-        <v>3.34419</v>
+        <v>2.85847</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.41307</v>
+        <v>3.42477</v>
       </c>
       <c r="C57" t="n">
-        <v>2.85806</v>
+        <v>2.35485</v>
       </c>
       <c r="D57" t="n">
-        <v>23.9479</v>
+        <v>16.5629</v>
       </c>
       <c r="E57" t="n">
-        <v>3.10602</v>
+        <v>2.57622</v>
       </c>
       <c r="F57" t="n">
-        <v>3.51676</v>
+        <v>2.92977</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.59767</v>
+        <v>3.59793</v>
       </c>
       <c r="C58" t="n">
-        <v>3.00476</v>
+        <v>2.47261</v>
       </c>
       <c r="D58" t="n">
-        <v>25.0023</v>
+        <v>17.1515</v>
       </c>
       <c r="E58" t="n">
-        <v>3.14587</v>
+        <v>2.72599</v>
       </c>
       <c r="F58" t="n">
-        <v>3.64191</v>
+        <v>2.97517</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.77591</v>
+        <v>3.8097</v>
       </c>
       <c r="C59" t="n">
-        <v>3.19089</v>
+        <v>2.60547</v>
       </c>
       <c r="D59" t="n">
-        <v>26.0942</v>
+        <v>17.5965</v>
       </c>
       <c r="E59" t="n">
-        <v>3.43381</v>
+        <v>2.82406</v>
       </c>
       <c r="F59" t="n">
-        <v>3.71573</v>
+        <v>3.16165</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.13905</v>
+        <v>4.11165</v>
       </c>
       <c r="C60" t="n">
-        <v>3.49161</v>
+        <v>2.95111</v>
       </c>
       <c r="D60" t="n">
-        <v>26.6106</v>
+        <v>18.0689</v>
       </c>
       <c r="E60" t="n">
-        <v>3.47701</v>
+        <v>2.87829</v>
       </c>
       <c r="F60" t="n">
-        <v>3.86831</v>
+        <v>3.2229</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.61048</v>
+        <v>4.65186</v>
       </c>
       <c r="C61" t="n">
-        <v>3.98343</v>
+        <v>3.37444</v>
       </c>
       <c r="D61" t="n">
-        <v>27.427</v>
+        <v>18.569</v>
       </c>
       <c r="E61" t="n">
-        <v>3.69871</v>
+        <v>3.05638</v>
       </c>
       <c r="F61" t="n">
-        <v>4.53346</v>
+        <v>3.43521</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.32396</v>
+        <v>5.30781</v>
       </c>
       <c r="C62" t="n">
-        <v>4.61159</v>
+        <v>3.84035</v>
       </c>
       <c r="D62" t="n">
-        <v>28.617</v>
+        <v>19.01</v>
       </c>
       <c r="E62" t="n">
-        <v>4.05941</v>
+        <v>3.37175</v>
       </c>
       <c r="F62" t="n">
-        <v>4.89047</v>
+        <v>3.71719</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.35936</v>
+        <v>6.32262</v>
       </c>
       <c r="C63" t="n">
-        <v>5.56861</v>
+        <v>4.75996</v>
       </c>
       <c r="D63" t="n">
-        <v>28.5425</v>
+        <v>19.5574</v>
       </c>
       <c r="E63" t="n">
-        <v>4.60812</v>
+        <v>2.69695</v>
       </c>
       <c r="F63" t="n">
-        <v>5.36435</v>
+        <v>3.0062</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>8.082660000000001</v>
+        <v>8.01449</v>
       </c>
       <c r="C64" t="n">
-        <v>7.03826</v>
+        <v>6.0656</v>
       </c>
       <c r="D64" t="n">
-        <v>19.0204</v>
+        <v>13.815</v>
       </c>
       <c r="E64" t="n">
-        <v>3.56385</v>
+        <v>2.76794</v>
       </c>
       <c r="F64" t="n">
-        <v>3.75083</v>
+        <v>3.0452</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.6074</v>
+        <v>10.67</v>
       </c>
       <c r="C65" t="n">
-        <v>2.97024</v>
+        <v>2.54463</v>
       </c>
       <c r="D65" t="n">
-        <v>18.4692</v>
+        <v>14.4702</v>
       </c>
       <c r="E65" t="n">
-        <v>3.28842</v>
+        <v>2.95382</v>
       </c>
       <c r="F65" t="n">
-        <v>3.80988</v>
+        <v>3.08623</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.5171</v>
+        <v>14.8031</v>
       </c>
       <c r="C66" t="n">
-        <v>2.99946</v>
+        <v>2.60043</v>
       </c>
       <c r="D66" t="n">
-        <v>20.07</v>
+        <v>15.2182</v>
       </c>
       <c r="E66" t="n">
-        <v>3.611</v>
+        <v>2.78373</v>
       </c>
       <c r="F66" t="n">
-        <v>3.85329</v>
+        <v>3.1314</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.55715</v>
+        <v>3.59596</v>
       </c>
       <c r="C67" t="n">
-        <v>3.04297</v>
+        <v>2.65327</v>
       </c>
       <c r="D67" t="n">
-        <v>21.686</v>
+        <v>15.9415</v>
       </c>
       <c r="E67" t="n">
-        <v>3.63224</v>
+        <v>2.75656</v>
       </c>
       <c r="F67" t="n">
-        <v>3.91503</v>
+        <v>3.18662</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.93584</v>
+        <v>3.58052</v>
       </c>
       <c r="C68" t="n">
-        <v>3.2075</v>
+        <v>2.66622</v>
       </c>
       <c r="D68" t="n">
-        <v>23.3096</v>
+        <v>16.914</v>
       </c>
       <c r="E68" t="n">
-        <v>3.40154</v>
+        <v>3.01547</v>
       </c>
       <c r="F68" t="n">
-        <v>3.99156</v>
+        <v>3.25177</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.76803</v>
+        <v>3.66025</v>
       </c>
       <c r="C69" t="n">
-        <v>3.25096</v>
+        <v>2.8112</v>
       </c>
       <c r="D69" t="n">
-        <v>24.2352</v>
+        <v>17.812</v>
       </c>
       <c r="E69" t="n">
-        <v>3.45368</v>
+        <v>2.87709</v>
       </c>
       <c r="F69" t="n">
-        <v>4.04988</v>
+        <v>3.30809</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.78202</v>
+        <v>3.73549</v>
       </c>
       <c r="C70" t="n">
-        <v>3.35122</v>
+        <v>2.70138</v>
       </c>
       <c r="D70" t="n">
-        <v>25.0079</v>
+        <v>18.8194</v>
       </c>
       <c r="E70" t="n">
-        <v>3.62787</v>
+        <v>2.96416</v>
       </c>
       <c r="F70" t="n">
-        <v>4.14135</v>
+        <v>3.44255</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.98681</v>
+        <v>3.88983</v>
       </c>
       <c r="C71" t="n">
-        <v>3.42625</v>
+        <v>2.95999</v>
       </c>
       <c r="D71" t="n">
-        <v>25.8959</v>
+        <v>19.8903</v>
       </c>
       <c r="E71" t="n">
-        <v>3.72657</v>
+        <v>2.9298</v>
       </c>
       <c r="F71" t="n">
-        <v>4.21954</v>
+        <v>3.59617</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.13928</v>
+        <v>4.00674</v>
       </c>
       <c r="C72" t="n">
-        <v>3.56149</v>
+        <v>2.91198</v>
       </c>
       <c r="D72" t="n">
-        <v>26.7248</v>
+        <v>20.9476</v>
       </c>
       <c r="E72" t="n">
-        <v>3.80878</v>
+        <v>3.01244</v>
       </c>
       <c r="F72" t="n">
-        <v>4.33221</v>
+        <v>3.71399</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.25874</v>
+        <v>4.26397</v>
       </c>
       <c r="C73" t="n">
-        <v>3.61008</v>
+        <v>3.26508</v>
       </c>
       <c r="D73" t="n">
-        <v>27.3018</v>
+        <v>22.1219</v>
       </c>
       <c r="E73" t="n">
-        <v>3.90906</v>
+        <v>3.11361</v>
       </c>
       <c r="F73" t="n">
-        <v>4.45666</v>
+        <v>3.85571</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.5914</v>
+        <v>4.58757</v>
       </c>
       <c r="C74" t="n">
-        <v>3.82443</v>
+        <v>3.35874</v>
       </c>
       <c r="D74" t="n">
-        <v>27.9772</v>
+        <v>23.4781</v>
       </c>
       <c r="E74" t="n">
-        <v>4.55405</v>
+        <v>3.27554</v>
       </c>
       <c r="F74" t="n">
-        <v>4.82084</v>
+        <v>3.89975</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.01429</v>
+        <v>5.04423</v>
       </c>
       <c r="C75" t="n">
-        <v>4.24008</v>
+        <v>3.75069</v>
       </c>
       <c r="D75" t="n">
-        <v>28.5911</v>
+        <v>24.8552</v>
       </c>
       <c r="E75" t="n">
-        <v>4.38801</v>
+        <v>3.48218</v>
       </c>
       <c r="F75" t="n">
-        <v>4.89157</v>
+        <v>4.09626</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.6482</v>
+        <v>5.67107</v>
       </c>
       <c r="C76" t="n">
-        <v>4.84044</v>
+        <v>4.23649</v>
       </c>
       <c r="D76" t="n">
-        <v>31.2973</v>
+        <v>26.3044</v>
       </c>
       <c r="E76" t="n">
-        <v>4.49081</v>
+        <v>3.78282</v>
       </c>
       <c r="F76" t="n">
-        <v>5.4323</v>
+        <v>4.51357</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.57255</v>
+        <v>6.83167</v>
       </c>
       <c r="C77" t="n">
-        <v>5.87043</v>
+        <v>5.03498</v>
       </c>
       <c r="D77" t="n">
-        <v>33.3427</v>
+        <v>28.0571</v>
       </c>
       <c r="E77" t="n">
-        <v>5.68829</v>
+        <v>2.99383</v>
       </c>
       <c r="F77" t="n">
-        <v>5.66416</v>
+        <v>3.47386</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.229290000000001</v>
+        <v>8.223549999999999</v>
       </c>
       <c r="C78" t="n">
-        <v>7.4436</v>
+        <v>6.29911</v>
       </c>
       <c r="D78" t="n">
-        <v>24.0913</v>
+        <v>24.4979</v>
       </c>
       <c r="E78" t="n">
-        <v>3.74118</v>
+        <v>3.02644</v>
       </c>
       <c r="F78" t="n">
-        <v>4.4709</v>
+        <v>3.51573</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.6846</v>
+        <v>10.7545</v>
       </c>
       <c r="C79" t="n">
-        <v>3.29967</v>
+        <v>2.91869</v>
       </c>
       <c r="D79" t="n">
-        <v>26.0491</v>
+        <v>25.6124</v>
       </c>
       <c r="E79" t="n">
-        <v>3.78448</v>
+        <v>3.06858</v>
       </c>
       <c r="F79" t="n">
-        <v>4.56346</v>
+        <v>3.611</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>14.6457</v>
+        <v>14.3537</v>
       </c>
       <c r="C80" t="n">
-        <v>3.38281</v>
+        <v>2.96211</v>
       </c>
       <c r="D80" t="n">
-        <v>27.4107</v>
+        <v>27.1263</v>
       </c>
       <c r="E80" t="n">
-        <v>3.85897</v>
+        <v>3.09124</v>
       </c>
       <c r="F80" t="n">
-        <v>4.77828</v>
+        <v>3.72238</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.5628</v>
+        <v>4.16141</v>
       </c>
       <c r="C81" t="n">
-        <v>3.41777</v>
+        <v>3.02464</v>
       </c>
       <c r="D81" t="n">
-        <v>29.0166</v>
+        <v>28.5724</v>
       </c>
       <c r="E81" t="n">
-        <v>3.94553</v>
+        <v>3.14592</v>
       </c>
       <c r="F81" t="n">
-        <v>4.88143</v>
+        <v>3.74767</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.77104</v>
+        <v>4.35564</v>
       </c>
       <c r="C82" t="n">
-        <v>3.56945</v>
+        <v>3.07796</v>
       </c>
       <c r="D82" t="n">
-        <v>30.0728</v>
+        <v>29.9781</v>
       </c>
       <c r="E82" t="n">
-        <v>3.99822</v>
+        <v>3.17627</v>
       </c>
       <c r="F82" t="n">
-        <v>5.20021</v>
+        <v>4.10522</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.84208</v>
+        <v>4.49229</v>
       </c>
       <c r="C83" t="n">
-        <v>3.59572</v>
+        <v>3.18733</v>
       </c>
       <c r="D83" t="n">
-        <v>31.4239</v>
+        <v>31.4662</v>
       </c>
       <c r="E83" t="n">
-        <v>4.15565</v>
+        <v>3.26144</v>
       </c>
       <c r="F83" t="n">
-        <v>5.4498</v>
+        <v>4.07346</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>5.0556</v>
+        <v>4.59268</v>
       </c>
       <c r="C84" t="n">
-        <v>3.91669</v>
+        <v>3.31894</v>
       </c>
       <c r="D84" t="n">
-        <v>32.8731</v>
+        <v>33.0661</v>
       </c>
       <c r="E84" t="n">
-        <v>4.29468</v>
+        <v>3.34271</v>
       </c>
       <c r="F84" t="n">
-        <v>5.58596</v>
+        <v>4.26322</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>5.34679</v>
+        <v>4.85374</v>
       </c>
       <c r="C85" t="n">
-        <v>3.93213</v>
+        <v>3.49597</v>
       </c>
       <c r="D85" t="n">
-        <v>34.3681</v>
+        <v>34.6212</v>
       </c>
       <c r="E85" t="n">
-        <v>4.39257</v>
+        <v>3.48722</v>
       </c>
       <c r="F85" t="n">
-        <v>5.32871</v>
+        <v>4.77036</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.85164</v>
+        <v>5.18886</v>
       </c>
       <c r="C86" t="n">
-        <v>4.42613</v>
+        <v>3.7064</v>
       </c>
       <c r="D86" t="n">
-        <v>36.066</v>
+        <v>36.3108</v>
       </c>
       <c r="E86" t="n">
-        <v>4.61587</v>
+        <v>3.6445</v>
       </c>
       <c r="F86" t="n">
-        <v>5.69257</v>
+        <v>5.12986</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>6.33241</v>
+        <v>5.61466</v>
       </c>
       <c r="C87" t="n">
-        <v>4.76249</v>
+        <v>3.99706</v>
       </c>
       <c r="D87" t="n">
-        <v>37.6966</v>
+        <v>38.0005</v>
       </c>
       <c r="E87" t="n">
-        <v>4.82694</v>
+        <v>3.90372</v>
       </c>
       <c r="F87" t="n">
-        <v>6.01387</v>
+        <v>5.31476</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.90399</v>
+        <v>6.21841</v>
       </c>
       <c r="C88" t="n">
-        <v>4.97231</v>
+        <v>4.36323</v>
       </c>
       <c r="D88" t="n">
-        <v>39.4389</v>
+        <v>39.5689</v>
       </c>
       <c r="E88" t="n">
-        <v>5.04997</v>
+        <v>4.09455</v>
       </c>
       <c r="F88" t="n">
-        <v>6.80684</v>
+        <v>5.73894</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>7.6896</v>
+        <v>7.0473</v>
       </c>
       <c r="C89" t="n">
-        <v>5.68956</v>
+        <v>4.86499</v>
       </c>
       <c r="D89" t="n">
-        <v>41.2337</v>
+        <v>41.5551</v>
       </c>
       <c r="E89" t="n">
-        <v>5.42265</v>
+        <v>4.40672</v>
       </c>
       <c r="F89" t="n">
-        <v>7.42183</v>
+        <v>6.27847</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>8.468120000000001</v>
+        <v>7.75007</v>
       </c>
       <c r="C90" t="n">
-        <v>6.22577</v>
+        <v>5.36865</v>
       </c>
       <c r="D90" t="n">
-        <v>43.0858</v>
+        <v>43.5488</v>
       </c>
       <c r="E90" t="n">
-        <v>5.97087</v>
+        <v>4.84569</v>
       </c>
       <c r="F90" t="n">
-        <v>8.1517</v>
+        <v>6.9239</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.89795</v>
+        <v>8.97579</v>
       </c>
       <c r="C91" t="n">
-        <v>7.00964</v>
+        <v>6.24772</v>
       </c>
       <c r="D91" t="n">
-        <v>44.913</v>
+        <v>45.574</v>
       </c>
       <c r="E91" t="n">
-        <v>6.69206</v>
+        <v>3.56464</v>
       </c>
       <c r="F91" t="n">
-        <v>9.12294</v>
+        <v>4.75464</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.3241</v>
+        <v>10.3614</v>
       </c>
       <c r="C92" t="n">
-        <v>8.45473</v>
+        <v>7.4041</v>
       </c>
       <c r="D92" t="n">
-        <v>36.6804</v>
+        <v>36.884</v>
       </c>
       <c r="E92" t="n">
-        <v>4.5491</v>
+        <v>3.68912</v>
       </c>
       <c r="F92" t="n">
-        <v>6.10879</v>
+        <v>5.01823</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>12.4257</v>
+        <v>12.429</v>
       </c>
       <c r="C93" t="n">
-        <v>10.617</v>
+        <v>9.02327</v>
       </c>
       <c r="D93" t="n">
-        <v>37.858</v>
+        <v>38.1271</v>
       </c>
       <c r="E93" t="n">
-        <v>4.70617</v>
+        <v>3.8461</v>
       </c>
       <c r="F93" t="n">
-        <v>6.50339</v>
+        <v>5.31143</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>15.738</v>
+        <v>15.8056</v>
       </c>
       <c r="C94" t="n">
-        <v>4.31329</v>
+        <v>3.99391</v>
       </c>
       <c r="D94" t="n">
-        <v>39.1357</v>
+        <v>39.3756</v>
       </c>
       <c r="E94" t="n">
-        <v>4.86878</v>
+        <v>4.00847</v>
       </c>
       <c r="F94" t="n">
-        <v>6.54986</v>
+        <v>5.62033</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>6.12007</v>
+        <v>6.2261</v>
       </c>
       <c r="C95" t="n">
-        <v>4.4581</v>
+        <v>4.18622</v>
       </c>
       <c r="D95" t="n">
-        <v>40.3395</v>
+        <v>40.6892</v>
       </c>
       <c r="E95" t="n">
-        <v>5.07509</v>
+        <v>4.16082</v>
       </c>
       <c r="F95" t="n">
-        <v>7.08815</v>
+        <v>5.95716</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.42238</v>
+        <v>6.45995</v>
       </c>
       <c r="C96" t="n">
-        <v>4.63963</v>
+        <v>4.30854</v>
       </c>
       <c r="D96" t="n">
-        <v>41.7093</v>
+        <v>42.0595</v>
       </c>
       <c r="E96" t="n">
-        <v>5.23938</v>
+        <v>4.31752</v>
       </c>
       <c r="F96" t="n">
-        <v>7.35127</v>
+        <v>6.25751</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.70697</v>
+        <v>6.72943</v>
       </c>
       <c r="C97" t="n">
-        <v>4.80388</v>
+        <v>4.4789</v>
       </c>
       <c r="D97" t="n">
-        <v>43.0649</v>
+        <v>43.4772</v>
       </c>
       <c r="E97" t="n">
-        <v>5.44112</v>
+        <v>4.49506</v>
       </c>
       <c r="F97" t="n">
-        <v>7.62765</v>
+        <v>6.54323</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>6.97749</v>
+        <v>7.08622</v>
       </c>
       <c r="C98" t="n">
-        <v>4.98094</v>
+        <v>4.62031</v>
       </c>
       <c r="D98" t="n">
-        <v>44.4658</v>
+        <v>44.8995</v>
       </c>
       <c r="E98" t="n">
-        <v>5.64514</v>
+        <v>4.67328</v>
       </c>
       <c r="F98" t="n">
-        <v>7.97852</v>
+        <v>6.81825</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.27993</v>
+        <v>7.39388</v>
       </c>
       <c r="C99" t="n">
-        <v>5.18664</v>
+        <v>4.84039</v>
       </c>
       <c r="D99" t="n">
-        <v>45.9369</v>
+        <v>46.4432</v>
       </c>
       <c r="E99" t="n">
-        <v>5.81138</v>
+        <v>4.84488</v>
       </c>
       <c r="F99" t="n">
-        <v>8.222060000000001</v>
+        <v>7.17085</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.61842</v>
+        <v>7.68876</v>
       </c>
       <c r="C100" t="n">
-        <v>5.4103</v>
+        <v>5.01477</v>
       </c>
       <c r="D100" t="n">
-        <v>47.4629</v>
+        <v>48.1095</v>
       </c>
       <c r="E100" t="n">
-        <v>6.01934</v>
+        <v>5.00586</v>
       </c>
       <c r="F100" t="n">
-        <v>8.6303</v>
+        <v>7.48932</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.97701</v>
+        <v>8.04692</v>
       </c>
       <c r="C101" t="n">
-        <v>5.66373</v>
+        <v>5.24975</v>
       </c>
       <c r="D101" t="n">
-        <v>49.0633</v>
+        <v>49.6055</v>
       </c>
       <c r="E101" t="n">
-        <v>6.29842</v>
+        <v>5.18981</v>
       </c>
       <c r="F101" t="n">
-        <v>9.04454</v>
+        <v>7.77722</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.417730000000001</v>
+        <v>8.50156</v>
       </c>
       <c r="C102" t="n">
-        <v>6.01845</v>
+        <v>5.55707</v>
       </c>
       <c r="D102" t="n">
-        <v>50.7794</v>
+        <v>51.5709</v>
       </c>
       <c r="E102" t="n">
-        <v>6.53736</v>
+        <v>5.409</v>
       </c>
       <c r="F102" t="n">
-        <v>9.54461</v>
+        <v>8.20778</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>9.02131</v>
+        <v>9.086930000000001</v>
       </c>
       <c r="C103" t="n">
-        <v>6.48291</v>
+        <v>5.9499</v>
       </c>
       <c r="D103" t="n">
-        <v>52.5632</v>
+        <v>53.3659</v>
       </c>
       <c r="E103" t="n">
-        <v>6.8838</v>
+        <v>5.68893</v>
       </c>
       <c r="F103" t="n">
-        <v>10.1795</v>
+        <v>8.81963</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.76768</v>
+        <v>9.85422</v>
       </c>
       <c r="C104" t="n">
-        <v>7.12634</v>
+        <v>6.54123</v>
       </c>
       <c r="D104" t="n">
-        <v>54.3955</v>
+        <v>55.3688</v>
       </c>
       <c r="E104" t="n">
-        <v>7.35315</v>
+        <v>6.06524</v>
       </c>
       <c r="F104" t="n">
-        <v>11.2829</v>
+        <v>9.4907</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.7863</v>
+        <v>10.8648</v>
       </c>
       <c r="C105" t="n">
-        <v>8.0931</v>
+        <v>7.34308</v>
       </c>
       <c r="D105" t="n">
-        <v>56.5077</v>
+        <v>57.3448</v>
       </c>
       <c r="E105" t="n">
-        <v>7.90217</v>
+        <v>4.47434</v>
       </c>
       <c r="F105" t="n">
-        <v>12.362</v>
+        <v>6.22547</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>12.2944</v>
+        <v>12.298</v>
       </c>
       <c r="C106" t="n">
-        <v>9.48099</v>
+        <v>8.52336</v>
       </c>
       <c r="D106" t="n">
-        <v>58.4622</v>
+        <v>59.2488</v>
       </c>
       <c r="E106" t="n">
-        <v>8.88203</v>
+        <v>4.55918</v>
       </c>
       <c r="F106" t="n">
-        <v>13.572</v>
+        <v>6.55979</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>14.2791</v>
+        <v>14.421</v>
       </c>
       <c r="C107" t="n">
-        <v>11.48</v>
+        <v>10.3101</v>
       </c>
       <c r="D107" t="n">
-        <v>44.5381</v>
+        <v>44.686</v>
       </c>
       <c r="E107" t="n">
-        <v>5.63038</v>
+        <v>4.67682</v>
       </c>
       <c r="F107" t="n">
-        <v>7.86123</v>
+        <v>6.66164</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.2446</v>
+        <v>17.41</v>
       </c>
       <c r="C108" t="n">
-        <v>4.99962</v>
+        <v>4.64307</v>
       </c>
       <c r="D108" t="n">
-        <v>45.6588</v>
+        <v>45.8366</v>
       </c>
       <c r="E108" t="n">
-        <v>5.76438</v>
+        <v>4.75783</v>
       </c>
       <c r="F108" t="n">
-        <v>8.15723</v>
+        <v>7.04362</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>22.0291</v>
+        <v>22.1333</v>
       </c>
       <c r="C109" t="n">
-        <v>5.17743</v>
+        <v>4.84153</v>
       </c>
       <c r="D109" t="n">
-        <v>46.8231</v>
+        <v>47.0897</v>
       </c>
       <c r="E109" t="n">
-        <v>6.05643</v>
+        <v>4.83464</v>
       </c>
       <c r="F109" t="n">
-        <v>8.67939</v>
+        <v>7.35688</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.52704</v>
+        <v>7.73157</v>
       </c>
       <c r="C110" t="n">
-        <v>5.29986</v>
+        <v>5.0489</v>
       </c>
       <c r="D110" t="n">
-        <v>48.0286</v>
+        <v>48.3802</v>
       </c>
       <c r="E110" t="n">
-        <v>6.00805</v>
+        <v>4.97853</v>
       </c>
       <c r="F110" t="n">
-        <v>8.985530000000001</v>
+        <v>7.83218</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.94023</v>
+        <v>8.001709999999999</v>
       </c>
       <c r="C111" t="n">
-        <v>5.4771</v>
+        <v>5.1386</v>
       </c>
       <c r="D111" t="n">
-        <v>49.2632</v>
+        <v>49.7483</v>
       </c>
       <c r="E111" t="n">
-        <v>6.2263</v>
+        <v>5.13028</v>
       </c>
       <c r="F111" t="n">
-        <v>9.53627</v>
+        <v>8.261559999999999</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>8.291259999999999</v>
+        <v>8.317270000000001</v>
       </c>
       <c r="C112" t="n">
-        <v>5.72</v>
+        <v>5.42073</v>
       </c>
       <c r="D112" t="n">
-        <v>50.5811</v>
+        <v>51.0951</v>
       </c>
       <c r="E112" t="n">
-        <v>6.38672</v>
+        <v>5.22013</v>
       </c>
       <c r="F112" t="n">
-        <v>9.98847</v>
+        <v>8.707470000000001</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.66024</v>
+        <v>8.69384</v>
       </c>
       <c r="C113" t="n">
-        <v>5.94888</v>
+        <v>5.60427</v>
       </c>
       <c r="D113" t="n">
-        <v>51.9841</v>
+        <v>52.6589</v>
       </c>
       <c r="E113" t="n">
-        <v>6.56797</v>
+        <v>5.44929</v>
       </c>
       <c r="F113" t="n">
-        <v>10.5582</v>
+        <v>9.231590000000001</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>9.07413</v>
+        <v>9.15438</v>
       </c>
       <c r="C114" t="n">
-        <v>6.29201</v>
+        <v>5.88508</v>
       </c>
       <c r="D114" t="n">
-        <v>53.3902</v>
+        <v>54.1896</v>
       </c>
       <c r="E114" t="n">
-        <v>6.88826</v>
+        <v>5.74003</v>
       </c>
       <c r="F114" t="n">
-        <v>11.1883</v>
+        <v>9.79406</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.721730000000001</v>
+        <v>9.81132</v>
       </c>
       <c r="C115" t="n">
-        <v>6.68522</v>
+        <v>6.22513</v>
       </c>
       <c r="D115" t="n">
-        <v>55.0016</v>
+        <v>55.8163</v>
       </c>
       <c r="E115" t="n">
-        <v>7.24537</v>
+        <v>6.0854</v>
       </c>
       <c r="F115" t="n">
-        <v>11.8482</v>
+        <v>10.3323</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>10.3137</v>
+        <v>10.466</v>
       </c>
       <c r="C116" t="n">
-        <v>7.21452</v>
+        <v>6.76445</v>
       </c>
       <c r="D116" t="n">
-        <v>56.5852</v>
+        <v>57.6315</v>
       </c>
       <c r="E116" t="n">
-        <v>7.71995</v>
+        <v>6.54292</v>
       </c>
       <c r="F116" t="n">
-        <v>12.4436</v>
+        <v>10.9441</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>11.0189</v>
+        <v>11.0876</v>
       </c>
       <c r="C117" t="n">
-        <v>7.75415</v>
+        <v>7.25413</v>
       </c>
       <c r="D117" t="n">
-        <v>58.3279</v>
+        <v>59.4351</v>
       </c>
       <c r="E117" t="n">
-        <v>8.194470000000001</v>
+        <v>7.00207</v>
       </c>
       <c r="F117" t="n">
-        <v>13.0245</v>
+        <v>11.5149</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.7614</v>
+        <v>11.883</v>
       </c>
       <c r="C118" t="n">
-        <v>8.38724</v>
+        <v>7.84078</v>
       </c>
       <c r="D118" t="n">
-        <v>60.1453</v>
+        <v>61.4066</v>
       </c>
       <c r="E118" t="n">
-        <v>8.69819</v>
+        <v>7.45291</v>
       </c>
       <c r="F118" t="n">
-        <v>13.7498</v>
+        <v>12.1213</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.7552</v>
+        <v>12.8547</v>
       </c>
       <c r="C119" t="n">
-        <v>9.29144</v>
+        <v>8.584009999999999</v>
       </c>
       <c r="D119" t="n">
-        <v>62.0604</v>
+        <v>63.3966</v>
       </c>
       <c r="E119" t="n">
-        <v>9.374700000000001</v>
+        <v>6.20018</v>
       </c>
       <c r="F119" t="n">
-        <v>14.6168</v>
+        <v>9.2332</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.9761</v>
+        <v>14.0845</v>
       </c>
       <c r="C120" t="n">
-        <v>10.4731</v>
+        <v>9.632239999999999</v>
       </c>
       <c r="D120" t="n">
-        <v>64.1063</v>
+        <v>65.5003</v>
       </c>
       <c r="E120" t="n">
-        <v>10.2039</v>
+        <v>6.27689</v>
       </c>
       <c r="F120" t="n">
-        <v>15.7777</v>
+        <v>9.39977</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.7262</v>
+        <v>15.8299</v>
       </c>
       <c r="C121" t="n">
-        <v>12.2584</v>
+        <v>11.2297</v>
       </c>
       <c r="D121" t="n">
-        <v>47.8918</v>
+        <v>48.1462</v>
       </c>
       <c r="E121" t="n">
-        <v>7.34565</v>
+        <v>6.35289</v>
       </c>
       <c r="F121" t="n">
-        <v>10.7155</v>
+        <v>9.68066</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>18.2183</v>
+        <v>18.3603</v>
       </c>
       <c r="C122" t="n">
-        <v>6.96261</v>
+        <v>6.64893</v>
       </c>
       <c r="D122" t="n">
-        <v>48.7644</v>
+        <v>49.3514</v>
       </c>
       <c r="E122" t="n">
-        <v>7.4562</v>
+        <v>6.83667</v>
       </c>
       <c r="F122" t="n">
-        <v>10.636</v>
+        <v>10.242</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.3445</v>
+        <v>22.4875</v>
       </c>
       <c r="C123" t="n">
-        <v>6.9547</v>
+        <v>6.54243</v>
       </c>
       <c r="D123" t="n">
-        <v>50.1489</v>
+        <v>50.4992</v>
       </c>
       <c r="E123" t="n">
-        <v>7.73333</v>
+        <v>6.80931</v>
       </c>
       <c r="F123" t="n">
-        <v>11.3409</v>
+        <v>10.2973</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>9.935919999999999</v>
+        <v>10.0076</v>
       </c>
       <c r="C124" t="n">
-        <v>7.30718</v>
+        <v>6.94267</v>
       </c>
       <c r="D124" t="n">
-        <v>51.3414</v>
+        <v>51.8198</v>
       </c>
       <c r="E124" t="n">
-        <v>8.001620000000001</v>
+        <v>7.05976</v>
       </c>
       <c r="F124" t="n">
-        <v>12.7878</v>
+        <v>10.7942</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.2103</v>
+        <v>10.3728</v>
       </c>
       <c r="C125" t="n">
-        <v>7.45562</v>
+        <v>6.9709</v>
       </c>
       <c r="D125" t="n">
-        <v>52.5417</v>
+        <v>52.8738</v>
       </c>
       <c r="E125" t="n">
-        <v>8.38862</v>
+        <v>7.43318</v>
       </c>
       <c r="F125" t="n">
-        <v>12.3839</v>
+        <v>11.1813</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.7448</v>
+        <v>10.6894</v>
       </c>
       <c r="C126" t="n">
-        <v>7.75434</v>
+        <v>7.36988</v>
       </c>
       <c r="D126" t="n">
-        <v>53.5582</v>
+        <v>54.2816</v>
       </c>
       <c r="E126" t="n">
-        <v>8.45166</v>
+        <v>7.49344</v>
       </c>
       <c r="F126" t="n">
-        <v>12.5676</v>
+        <v>11.4173</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.9656</v>
+        <v>11.0477</v>
       </c>
       <c r="C127" t="n">
-        <v>7.96358</v>
+        <v>7.61505</v>
       </c>
       <c r="D127" t="n">
-        <v>55.1978</v>
+        <v>56.0536</v>
       </c>
       <c r="E127" t="n">
-        <v>8.735620000000001</v>
+        <v>7.75182</v>
       </c>
       <c r="F127" t="n">
-        <v>13.0551</v>
+        <v>11.8388</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>11.0904</v>
+        <v>11.3225</v>
       </c>
       <c r="C128" t="n">
-        <v>7.73984</v>
+        <v>7.54406</v>
       </c>
       <c r="D128" t="n">
-        <v>56.6175</v>
+        <v>57.6042</v>
       </c>
       <c r="E128" t="n">
-        <v>9.08994</v>
+        <v>7.93065</v>
       </c>
       <c r="F128" t="n">
-        <v>13.6589</v>
+        <v>12.0723</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.6849</v>
+        <v>11.4872</v>
       </c>
       <c r="C129" t="n">
-        <v>8.29519</v>
+        <v>7.71664</v>
       </c>
       <c r="D129" t="n">
-        <v>58.1471</v>
+        <v>59.2712</v>
       </c>
       <c r="E129" t="n">
-        <v>9.310219999999999</v>
+        <v>8.195970000000001</v>
       </c>
       <c r="F129" t="n">
-        <v>14.0297</v>
+        <v>12.5899</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>12.0384</v>
+        <v>12.0074</v>
       </c>
       <c r="C130" t="n">
-        <v>8.92323</v>
+        <v>7.94153</v>
       </c>
       <c r="D130" t="n">
-        <v>59.7406</v>
+        <v>61.0365</v>
       </c>
       <c r="E130" t="n">
-        <v>9.429209999999999</v>
+        <v>8.32446</v>
       </c>
       <c r="F130" t="n">
-        <v>14.436</v>
+        <v>12.8854</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>12.3629</v>
+        <v>12.4457</v>
       </c>
       <c r="C131" t="n">
-        <v>9.135450000000001</v>
+        <v>8.38109</v>
       </c>
       <c r="D131" t="n">
-        <v>61.5081</v>
+        <v>62.6639</v>
       </c>
       <c r="E131" t="n">
-        <v>9.905670000000001</v>
+        <v>8.68934</v>
       </c>
       <c r="F131" t="n">
-        <v>15.215</v>
+        <v>13.5082</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>13.0166</v>
+        <v>13.1182</v>
       </c>
       <c r="C132" t="n">
-        <v>9.378220000000001</v>
+        <v>8.751110000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>63.3799</v>
+        <v>64.8026</v>
       </c>
       <c r="E132" t="n">
-        <v>10.4899</v>
+        <v>8.955080000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>15.8669</v>
+        <v>13.8734</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.8126</v>
+        <v>13.8112</v>
       </c>
       <c r="C133" t="n">
-        <v>10.0324</v>
+        <v>9.42543</v>
       </c>
       <c r="D133" t="n">
-        <v>65.0147</v>
+        <v>66.84520000000001</v>
       </c>
       <c r="E133" t="n">
-        <v>10.9085</v>
+        <v>9.286250000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>16.4789</v>
+        <v>14.4706</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.9112</v>
+        <v>14.9742</v>
       </c>
       <c r="C134" t="n">
-        <v>11.4287</v>
+        <v>10.4762</v>
       </c>
       <c r="D134" t="n">
-        <v>67.074</v>
+        <v>68.9854</v>
       </c>
       <c r="E134" t="n">
-        <v>11.5827</v>
+        <v>13.0303</v>
       </c>
       <c r="F134" t="n">
-        <v>17.8547</v>
+        <v>15.9691</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.6948</v>
+        <v>16.7189</v>
       </c>
       <c r="C135" t="n">
-        <v>13.0171</v>
+        <v>11.7559</v>
       </c>
       <c r="D135" t="n">
-        <v>49.8188</v>
+        <v>50.1036</v>
       </c>
       <c r="E135" t="n">
-        <v>15.4177</v>
+        <v>13.2923</v>
       </c>
       <c r="F135" t="n">
-        <v>17.9952</v>
+        <v>16.3162</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.8078</v>
+        <v>18.3674</v>
       </c>
       <c r="C136" t="n">
-        <v>13.8647</v>
+        <v>13.4254</v>
       </c>
       <c r="D136" t="n">
-        <v>50.9224</v>
+        <v>51.0488</v>
       </c>
       <c r="E136" t="n">
-        <v>15.4971</v>
+        <v>12.8663</v>
       </c>
       <c r="F136" t="n">
-        <v>19.1739</v>
+        <v>16.7126</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>22.3359</v>
+        <v>22.163</v>
       </c>
       <c r="C137" t="n">
-        <v>14.0344</v>
+        <v>13.5852</v>
       </c>
       <c r="D137" t="n">
-        <v>51.8013</v>
+        <v>52.4087</v>
       </c>
       <c r="E137" t="n">
-        <v>15.4838</v>
+        <v>13.3394</v>
       </c>
       <c r="F137" t="n">
-        <v>19.1218</v>
+        <v>16.6866</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.9917</v>
+        <v>16.8593</v>
       </c>
       <c r="C138" t="n">
-        <v>14.0714</v>
+        <v>13.6481</v>
       </c>
       <c r="D138" t="n">
-        <v>53.1075</v>
+        <v>53.5784</v>
       </c>
       <c r="E138" t="n">
-        <v>15.7429</v>
+        <v>13.4565</v>
       </c>
       <c r="F138" t="n">
-        <v>19.5205</v>
+        <v>16.9306</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.1515</v>
+        <v>17.1133</v>
       </c>
       <c r="C139" t="n">
-        <v>14.2752</v>
+        <v>13.7686</v>
       </c>
       <c r="D139" t="n">
-        <v>54.4383</v>
+        <v>55.0042</v>
       </c>
       <c r="E139" t="n">
-        <v>15.867</v>
+        <v>13.7266</v>
       </c>
       <c r="F139" t="n">
-        <v>19.9202</v>
+        <v>17.3566</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>17.325</v>
+        <v>17.3327</v>
       </c>
       <c r="C140" t="n">
-        <v>14.4177</v>
+        <v>13.7258</v>
       </c>
       <c r="D140" t="n">
-        <v>55.942</v>
+        <v>56.2409</v>
       </c>
       <c r="E140" t="n">
-        <v>15.9784</v>
+        <v>13.1118</v>
       </c>
       <c r="F140" t="n">
-        <v>19.5343</v>
+        <v>17.651</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>17.4272</v>
+        <v>17.1879</v>
       </c>
       <c r="C141" t="n">
-        <v>14.4619</v>
+        <v>13.9587</v>
       </c>
       <c r="D141" t="n">
-        <v>56.8912</v>
+        <v>57.7363</v>
       </c>
       <c r="E141" t="n">
-        <v>15.6747</v>
+        <v>13.7702</v>
       </c>
       <c r="F141" t="n">
-        <v>20.7594</v>
+        <v>17.8495</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.8697</v>
+        <v>17.7331</v>
       </c>
       <c r="C142" t="n">
-        <v>14.6021</v>
+        <v>14.0299</v>
       </c>
       <c r="D142" t="n">
-        <v>58.1593</v>
+        <v>59.3018</v>
       </c>
       <c r="E142" t="n">
-        <v>16.4612</v>
+        <v>14.1508</v>
       </c>
       <c r="F142" t="n">
-        <v>20.7568</v>
+        <v>18.3257</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.9712</v>
+        <v>17.789</v>
       </c>
       <c r="C143" t="n">
-        <v>14.8471</v>
+        <v>14.1795</v>
       </c>
       <c r="D143" t="n">
-        <v>59.7515</v>
+        <v>61.1435</v>
       </c>
       <c r="E143" t="n">
-        <v>16.7692</v>
+        <v>14.0118</v>
       </c>
       <c r="F143" t="n">
-        <v>20.7455</v>
+        <v>18.5305</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered unsuccessful looukp.xlsx
+++ b/clang-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.70451</v>
+        <v>2.75594</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0584</v>
+        <v>2.11733</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0263</v>
+        <v>11.8669</v>
       </c>
       <c r="E2" t="n">
-        <v>2.31906</v>
+        <v>2.31954</v>
       </c>
       <c r="F2" t="n">
-        <v>2.33274</v>
+        <v>2.65354</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.74691</v>
+        <v>2.82819</v>
       </c>
       <c r="C3" t="n">
-        <v>2.16401</v>
+        <v>2.25104</v>
       </c>
       <c r="D3" t="n">
-        <v>13.3459</v>
+        <v>12.531</v>
       </c>
       <c r="E3" t="n">
-        <v>2.41218</v>
+        <v>2.40931</v>
       </c>
       <c r="F3" t="n">
-        <v>2.42682</v>
+        <v>2.74075</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>2.90022</v>
+        <v>2.96461</v>
       </c>
       <c r="C4" t="n">
-        <v>2.317</v>
+        <v>2.35926</v>
       </c>
       <c r="D4" t="n">
-        <v>13.7887</v>
+        <v>13.0655</v>
       </c>
       <c r="E4" t="n">
-        <v>2.51324</v>
+        <v>2.44148</v>
       </c>
       <c r="F4" t="n">
-        <v>2.53649</v>
+        <v>2.76468</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.26191</v>
+        <v>3.2143</v>
       </c>
       <c r="C5" t="n">
-        <v>2.71359</v>
+        <v>2.64036</v>
       </c>
       <c r="D5" t="n">
-        <v>14.3586</v>
+        <v>13.5063</v>
       </c>
       <c r="E5" t="n">
-        <v>2.03256</v>
+        <v>1.99586</v>
       </c>
       <c r="F5" t="n">
-        <v>2.03857</v>
+        <v>2.3216</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.6892</v>
+        <v>4.504</v>
       </c>
       <c r="C6" t="n">
-        <v>3.47324</v>
+        <v>3.34741</v>
       </c>
       <c r="D6" t="n">
-        <v>15.1155</v>
+        <v>14.1197</v>
       </c>
       <c r="E6" t="n">
-        <v>2.04877</v>
+        <v>2.01263</v>
       </c>
       <c r="F6" t="n">
-        <v>2.04457</v>
+        <v>2.34884</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.29383</v>
+        <v>6.54903</v>
       </c>
       <c r="C7" t="n">
-        <v>5.18855</v>
+        <v>4.94784</v>
       </c>
       <c r="D7" t="n">
-        <v>10.1297</v>
+        <v>9.676769999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>2.06417</v>
+        <v>2.05015</v>
       </c>
       <c r="F7" t="n">
-        <v>2.06893</v>
+        <v>2.37913</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.656370000000001</v>
+        <v>9.03538</v>
       </c>
       <c r="C8" t="n">
-        <v>1.74485</v>
+        <v>1.73123</v>
       </c>
       <c r="D8" t="n">
-        <v>10.8011</v>
+        <v>10.4181</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08738</v>
+        <v>2.06411</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08764</v>
+        <v>2.39578</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.9772</v>
+        <v>12.7506</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7647</v>
+        <v>1.74864</v>
       </c>
       <c r="D9" t="n">
-        <v>11.5114</v>
+        <v>11.0681</v>
       </c>
       <c r="E9" t="n">
-        <v>2.10586</v>
+        <v>2.06453</v>
       </c>
       <c r="F9" t="n">
-        <v>2.10347</v>
+        <v>2.40093</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.64467</v>
+        <v>2.57577</v>
       </c>
       <c r="C10" t="n">
-        <v>1.80309</v>
+        <v>1.7621</v>
       </c>
       <c r="D10" t="n">
-        <v>12.1686</v>
+        <v>11.859</v>
       </c>
       <c r="E10" t="n">
-        <v>2.13453</v>
+        <v>2.07783</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1343</v>
+        <v>2.4204</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.70493</v>
+        <v>2.61898</v>
       </c>
       <c r="C11" t="n">
-        <v>1.83788</v>
+        <v>1.80279</v>
       </c>
       <c r="D11" t="n">
-        <v>12.6765</v>
+        <v>12.2852</v>
       </c>
       <c r="E11" t="n">
-        <v>2.16163</v>
+        <v>2.11274</v>
       </c>
       <c r="F11" t="n">
-        <v>2.18016</v>
+        <v>2.44488</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.72166</v>
+        <v>2.66315</v>
       </c>
       <c r="C12" t="n">
-        <v>1.86961</v>
+        <v>1.83095</v>
       </c>
       <c r="D12" t="n">
-        <v>13.2543</v>
+        <v>12.7532</v>
       </c>
       <c r="E12" t="n">
-        <v>2.18881</v>
+        <v>2.13247</v>
       </c>
       <c r="F12" t="n">
-        <v>2.19106</v>
+        <v>2.4721</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.72508</v>
+        <v>2.71661</v>
       </c>
       <c r="C13" t="n">
-        <v>1.90458</v>
+        <v>1.87891</v>
       </c>
       <c r="D13" t="n">
-        <v>13.8231</v>
+        <v>13.2527</v>
       </c>
       <c r="E13" t="n">
-        <v>2.21768</v>
+        <v>2.15346</v>
       </c>
       <c r="F13" t="n">
-        <v>2.21396</v>
+        <v>2.50045</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.78338</v>
+        <v>2.76748</v>
       </c>
       <c r="C14" t="n">
-        <v>2.00325</v>
+        <v>1.92893</v>
       </c>
       <c r="D14" t="n">
-        <v>14.4068</v>
+        <v>13.8129</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2535</v>
+        <v>2.18436</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2682</v>
+        <v>2.53584</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>2.89912</v>
+        <v>2.83229</v>
       </c>
       <c r="C15" t="n">
-        <v>2.08185</v>
+        <v>2.03318</v>
       </c>
       <c r="D15" t="n">
-        <v>14.8348</v>
+        <v>14.1644</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3063</v>
+        <v>2.24251</v>
       </c>
       <c r="F15" t="n">
-        <v>2.34677</v>
+        <v>2.58618</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.05365</v>
+        <v>3.01176</v>
       </c>
       <c r="C16" t="n">
-        <v>2.21809</v>
+        <v>2.16948</v>
       </c>
       <c r="D16" t="n">
-        <v>15.3409</v>
+        <v>14.6048</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3763</v>
+        <v>2.29669</v>
       </c>
       <c r="F16" t="n">
-        <v>2.40488</v>
+        <v>2.64288</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.15498</v>
+        <v>3.21801</v>
       </c>
       <c r="C17" t="n">
-        <v>2.40812</v>
+        <v>2.33373</v>
       </c>
       <c r="D17" t="n">
-        <v>15.8373</v>
+        <v>15.0686</v>
       </c>
       <c r="E17" t="n">
-        <v>2.44192</v>
+        <v>2.408</v>
       </c>
       <c r="F17" t="n">
-        <v>2.49169</v>
+        <v>2.74254</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.52452</v>
+        <v>3.64239</v>
       </c>
       <c r="C18" t="n">
-        <v>2.66938</v>
+        <v>2.62397</v>
       </c>
       <c r="D18" t="n">
-        <v>16.2441</v>
+        <v>15.4405</v>
       </c>
       <c r="E18" t="n">
-        <v>2.58098</v>
+        <v>2.54113</v>
       </c>
       <c r="F18" t="n">
-        <v>2.65872</v>
+        <v>2.8901</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.03357</v>
+        <v>4.32868</v>
       </c>
       <c r="C19" t="n">
-        <v>3.24519</v>
+        <v>3.09461</v>
       </c>
       <c r="D19" t="n">
-        <v>16.7446</v>
+        <v>15.9056</v>
       </c>
       <c r="E19" t="n">
-        <v>2.78922</v>
+        <v>2.6959</v>
       </c>
       <c r="F19" t="n">
-        <v>2.86568</v>
+        <v>3.05117</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.2695</v>
+        <v>5.49179</v>
       </c>
       <c r="C20" t="n">
-        <v>4.21283</v>
+        <v>3.87398</v>
       </c>
       <c r="D20" t="n">
-        <v>17.197</v>
+        <v>16.2481</v>
       </c>
       <c r="E20" t="n">
-        <v>2.07848</v>
+        <v>2.03383</v>
       </c>
       <c r="F20" t="n">
-        <v>2.13428</v>
+        <v>2.38913</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.76459</v>
+        <v>7.37292</v>
       </c>
       <c r="C21" t="n">
-        <v>5.47049</v>
+        <v>5.21075</v>
       </c>
       <c r="D21" t="n">
-        <v>11.8433</v>
+        <v>11.4752</v>
       </c>
       <c r="E21" t="n">
-        <v>2.09547</v>
+        <v>2.06093</v>
       </c>
       <c r="F21" t="n">
-        <v>2.14263</v>
+        <v>2.41139</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.44924</v>
+        <v>9.476979999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>1.81735</v>
+        <v>1.77608</v>
       </c>
       <c r="D22" t="n">
-        <v>12.4041</v>
+        <v>12.0061</v>
       </c>
       <c r="E22" t="n">
-        <v>2.12492</v>
+        <v>2.07635</v>
       </c>
       <c r="F22" t="n">
-        <v>2.19424</v>
+        <v>2.43837</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.7487</v>
+        <v>12.8326</v>
       </c>
       <c r="C23" t="n">
-        <v>1.83221</v>
+        <v>1.79671</v>
       </c>
       <c r="D23" t="n">
-        <v>12.9685</v>
+        <v>12.5203</v>
       </c>
       <c r="E23" t="n">
-        <v>2.14011</v>
+        <v>2.09381</v>
       </c>
       <c r="F23" t="n">
-        <v>2.20488</v>
+        <v>2.44366</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.73298</v>
+        <v>2.77625</v>
       </c>
       <c r="C24" t="n">
-        <v>1.88414</v>
+        <v>1.81339</v>
       </c>
       <c r="D24" t="n">
-        <v>13.5167</v>
+        <v>12.9543</v>
       </c>
       <c r="E24" t="n">
-        <v>2.16826</v>
+        <v>2.12441</v>
       </c>
       <c r="F24" t="n">
-        <v>2.23995</v>
+        <v>2.51066</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.78516</v>
+        <v>2.8039</v>
       </c>
       <c r="C25" t="n">
-        <v>1.90203</v>
+        <v>1.85572</v>
       </c>
       <c r="D25" t="n">
-        <v>14.0045</v>
+        <v>13.387</v>
       </c>
       <c r="E25" t="n">
-        <v>2.19621</v>
+        <v>2.17317</v>
       </c>
       <c r="F25" t="n">
-        <v>2.29652</v>
+        <v>2.57717</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>2.86163</v>
+        <v>2.87427</v>
       </c>
       <c r="C26" t="n">
-        <v>1.94556</v>
+        <v>1.97974</v>
       </c>
       <c r="D26" t="n">
-        <v>14.4595</v>
+        <v>13.8564</v>
       </c>
       <c r="E26" t="n">
-        <v>2.24401</v>
+        <v>2.19552</v>
       </c>
       <c r="F26" t="n">
-        <v>2.36177</v>
+        <v>2.63182</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>2.91385</v>
+        <v>2.96719</v>
       </c>
       <c r="C27" t="n">
-        <v>1.98802</v>
+        <v>2.00112</v>
       </c>
       <c r="D27" t="n">
-        <v>14.9805</v>
+        <v>14.2944</v>
       </c>
       <c r="E27" t="n">
-        <v>2.27068</v>
+        <v>2.24292</v>
       </c>
       <c r="F27" t="n">
-        <v>2.40178</v>
+        <v>2.69753</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.00315</v>
+        <v>3.02854</v>
       </c>
       <c r="C28" t="n">
-        <v>2.05748</v>
+        <v>2.06957</v>
       </c>
       <c r="D28" t="n">
-        <v>15.4662</v>
+        <v>14.7261</v>
       </c>
       <c r="E28" t="n">
-        <v>2.32893</v>
+        <v>2.28467</v>
       </c>
       <c r="F28" t="n">
-        <v>2.46117</v>
+        <v>2.7592</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.22385</v>
+        <v>3.17722</v>
       </c>
       <c r="C29" t="n">
-        <v>2.17508</v>
+        <v>2.16332</v>
       </c>
       <c r="D29" t="n">
-        <v>15.9333</v>
+        <v>15.0896</v>
       </c>
       <c r="E29" t="n">
-        <v>2.39463</v>
+        <v>2.3409</v>
       </c>
       <c r="F29" t="n">
-        <v>2.53726</v>
+        <v>2.82481</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.34772</v>
+        <v>3.31135</v>
       </c>
       <c r="C30" t="n">
-        <v>2.32095</v>
+        <v>2.27973</v>
       </c>
       <c r="D30" t="n">
-        <v>16.4364</v>
+        <v>15.4568</v>
       </c>
       <c r="E30" t="n">
-        <v>2.46384</v>
+        <v>2.41011</v>
       </c>
       <c r="F30" t="n">
-        <v>2.60841</v>
+        <v>2.89764</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.56802</v>
+        <v>3.57835</v>
       </c>
       <c r="C31" t="n">
-        <v>2.48738</v>
+        <v>2.46203</v>
       </c>
       <c r="D31" t="n">
-        <v>16.906</v>
+        <v>15.8669</v>
       </c>
       <c r="E31" t="n">
-        <v>2.5446</v>
+        <v>2.5009</v>
       </c>
       <c r="F31" t="n">
-        <v>2.72069</v>
+        <v>3.00809</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.04831</v>
+        <v>3.99603</v>
       </c>
       <c r="C32" t="n">
-        <v>2.75228</v>
+        <v>2.8451</v>
       </c>
       <c r="D32" t="n">
-        <v>17.2853</v>
+        <v>16.2497</v>
       </c>
       <c r="E32" t="n">
-        <v>2.67334</v>
+        <v>2.66972</v>
       </c>
       <c r="F32" t="n">
-        <v>2.86641</v>
+        <v>3.16215</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.81289</v>
+        <v>4.80412</v>
       </c>
       <c r="C33" t="n">
-        <v>3.28117</v>
+        <v>3.3519</v>
       </c>
       <c r="D33" t="n">
-        <v>17.739</v>
+        <v>16.6579</v>
       </c>
       <c r="E33" t="n">
-        <v>2.90247</v>
+        <v>2.91745</v>
       </c>
       <c r="F33" t="n">
-        <v>3.09478</v>
+        <v>3.38837</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.78199</v>
+        <v>5.74668</v>
       </c>
       <c r="C34" t="n">
-        <v>4.1035</v>
+        <v>4.16507</v>
       </c>
       <c r="D34" t="n">
-        <v>18.1793</v>
+        <v>17.1539</v>
       </c>
       <c r="E34" t="n">
-        <v>2.10912</v>
+        <v>2.0877</v>
       </c>
       <c r="F34" t="n">
-        <v>2.25109</v>
+        <v>2.58842</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.28887</v>
+        <v>6.8179</v>
       </c>
       <c r="C35" t="n">
-        <v>5.1935</v>
+        <v>5.34528</v>
       </c>
       <c r="D35" t="n">
-        <v>12.3532</v>
+        <v>12.049</v>
       </c>
       <c r="E35" t="n">
-        <v>2.1383</v>
+        <v>2.10995</v>
       </c>
       <c r="F35" t="n">
-        <v>2.26851</v>
+        <v>2.61589</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.776680000000001</v>
+        <v>8.83839</v>
       </c>
       <c r="C36" t="n">
-        <v>6.81791</v>
+        <v>7.02265</v>
       </c>
       <c r="D36" t="n">
-        <v>12.8768</v>
+        <v>12.4955</v>
       </c>
       <c r="E36" t="n">
-        <v>2.16279</v>
+        <v>2.14271</v>
       </c>
       <c r="F36" t="n">
-        <v>2.29722</v>
+        <v>2.65951</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.0352</v>
+        <v>12.0458</v>
       </c>
       <c r="C37" t="n">
-        <v>1.92646</v>
+        <v>1.96416</v>
       </c>
       <c r="D37" t="n">
-        <v>13.3178</v>
+        <v>12.926</v>
       </c>
       <c r="E37" t="n">
-        <v>2.19324</v>
+        <v>2.16228</v>
       </c>
       <c r="F37" t="n">
-        <v>2.37563</v>
+        <v>2.68917</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.82283</v>
+        <v>2.8883</v>
       </c>
       <c r="C38" t="n">
-        <v>1.92804</v>
+        <v>1.99724</v>
       </c>
       <c r="D38" t="n">
-        <v>13.8305</v>
+        <v>13.3909</v>
       </c>
       <c r="E38" t="n">
-        <v>2.21884</v>
+        <v>2.17342</v>
       </c>
       <c r="F38" t="n">
-        <v>2.38329</v>
+        <v>2.72347</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.87877</v>
+        <v>2.9328</v>
       </c>
       <c r="C39" t="n">
-        <v>2.02828</v>
+        <v>1.99652</v>
       </c>
       <c r="D39" t="n">
-        <v>14.3638</v>
+        <v>13.852</v>
       </c>
       <c r="E39" t="n">
-        <v>2.25648</v>
+        <v>2.20204</v>
       </c>
       <c r="F39" t="n">
-        <v>2.4381</v>
+        <v>2.75332</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>2.93914</v>
+        <v>3.00304</v>
       </c>
       <c r="C40" t="n">
-        <v>1.98512</v>
+        <v>2.06466</v>
       </c>
       <c r="D40" t="n">
-        <v>14.824</v>
+        <v>14.3037</v>
       </c>
       <c r="E40" t="n">
-        <v>2.28635</v>
+        <v>2.2435</v>
       </c>
       <c r="F40" t="n">
-        <v>2.51916</v>
+        <v>2.79775</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.02803</v>
+        <v>3.08865</v>
       </c>
       <c r="C41" t="n">
-        <v>2.12221</v>
+        <v>2.10795</v>
       </c>
       <c r="D41" t="n">
-        <v>15.2982</v>
+        <v>14.7568</v>
       </c>
       <c r="E41" t="n">
-        <v>2.3225</v>
+        <v>2.2708</v>
       </c>
       <c r="F41" t="n">
-        <v>2.57096</v>
+        <v>2.82516</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.0964</v>
+        <v>3.14625</v>
       </c>
       <c r="C42" t="n">
-        <v>2.17137</v>
+        <v>2.12745</v>
       </c>
       <c r="D42" t="n">
-        <v>15.7593</v>
+        <v>15.1833</v>
       </c>
       <c r="E42" t="n">
-        <v>2.37689</v>
+        <v>2.30187</v>
       </c>
       <c r="F42" t="n">
-        <v>2.60313</v>
+        <v>2.86043</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.23313</v>
+        <v>3.29477</v>
       </c>
       <c r="C43" t="n">
-        <v>2.208</v>
+        <v>2.25059</v>
       </c>
       <c r="D43" t="n">
-        <v>16.2501</v>
+        <v>15.5945</v>
       </c>
       <c r="E43" t="n">
-        <v>2.43141</v>
+        <v>2.36246</v>
       </c>
       <c r="F43" t="n">
-        <v>2.67469</v>
+        <v>2.91832</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.43912</v>
+        <v>3.49428</v>
       </c>
       <c r="C44" t="n">
-        <v>2.38865</v>
+        <v>2.37845</v>
       </c>
       <c r="D44" t="n">
-        <v>16.7032</v>
+        <v>16.0091</v>
       </c>
       <c r="E44" t="n">
-        <v>2.51631</v>
+        <v>2.43604</v>
       </c>
       <c r="F44" t="n">
-        <v>2.79754</v>
+        <v>2.98678</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.69668</v>
+        <v>3.79077</v>
       </c>
       <c r="C45" t="n">
-        <v>2.57169</v>
+        <v>2.59538</v>
       </c>
       <c r="D45" t="n">
-        <v>17.1464</v>
+        <v>16.3966</v>
       </c>
       <c r="E45" t="n">
-        <v>2.61816</v>
+        <v>2.53387</v>
       </c>
       <c r="F45" t="n">
-        <v>2.91419</v>
+        <v>3.08529</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.06904</v>
+        <v>4.10388</v>
       </c>
       <c r="C46" t="n">
-        <v>2.90911</v>
+        <v>2.85713</v>
       </c>
       <c r="D46" t="n">
-        <v>17.5941</v>
+        <v>16.812</v>
       </c>
       <c r="E46" t="n">
-        <v>2.76529</v>
+        <v>2.67247</v>
       </c>
       <c r="F46" t="n">
-        <v>3.04769</v>
+        <v>3.21322</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.60714</v>
+        <v>4.65667</v>
       </c>
       <c r="C47" t="n">
-        <v>3.3664</v>
+        <v>3.3509</v>
       </c>
       <c r="D47" t="n">
-        <v>18.0256</v>
+        <v>17.1886</v>
       </c>
       <c r="E47" t="n">
-        <v>3.00228</v>
+        <v>2.90551</v>
       </c>
       <c r="F47" t="n">
-        <v>3.29477</v>
+        <v>3.39976</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.50902</v>
+        <v>5.52176</v>
       </c>
       <c r="C48" t="n">
-        <v>4.00872</v>
+        <v>3.96347</v>
       </c>
       <c r="D48" t="n">
-        <v>18.6072</v>
+        <v>17.6081</v>
       </c>
       <c r="E48" t="n">
-        <v>2.25728</v>
+        <v>2.10363</v>
       </c>
       <c r="F48" t="n">
-        <v>2.51506</v>
+        <v>2.64649</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.66511</v>
+        <v>6.68473</v>
       </c>
       <c r="C49" t="n">
-        <v>4.94149</v>
+        <v>4.96439</v>
       </c>
       <c r="D49" t="n">
-        <v>19.028</v>
+        <v>18.0563</v>
       </c>
       <c r="E49" t="n">
-        <v>2.26192</v>
+        <v>2.13306</v>
       </c>
       <c r="F49" t="n">
-        <v>2.54674</v>
+        <v>2.68454</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.45603</v>
+        <v>8.55799</v>
       </c>
       <c r="C50" t="n">
-        <v>6.41676</v>
+        <v>6.44885</v>
       </c>
       <c r="D50" t="n">
-        <v>12.9351</v>
+        <v>12.6537</v>
       </c>
       <c r="E50" t="n">
-        <v>2.37107</v>
+        <v>2.26874</v>
       </c>
       <c r="F50" t="n">
-        <v>2.56935</v>
+        <v>2.70107</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>11.3932</v>
+        <v>11.4946</v>
       </c>
       <c r="C51" t="n">
-        <v>2.05094</v>
+        <v>2.03686</v>
       </c>
       <c r="D51" t="n">
-        <v>13.4078</v>
+        <v>13.1378</v>
       </c>
       <c r="E51" t="n">
-        <v>2.25601</v>
+        <v>2.27921</v>
       </c>
       <c r="F51" t="n">
-        <v>2.59494</v>
+        <v>2.74774</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.5311</v>
+        <v>15.6563</v>
       </c>
       <c r="C52" t="n">
-        <v>2.03648</v>
+        <v>2.08766</v>
       </c>
       <c r="D52" t="n">
-        <v>13.9696</v>
+        <v>13.6046</v>
       </c>
       <c r="E52" t="n">
-        <v>2.28754</v>
+        <v>2.31291</v>
       </c>
       <c r="F52" t="n">
-        <v>2.64854</v>
+        <v>2.78196</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.06332</v>
+        <v>2.98719</v>
       </c>
       <c r="C53" t="n">
-        <v>2.11205</v>
+        <v>2.07042</v>
       </c>
       <c r="D53" t="n">
-        <v>14.444</v>
+        <v>14.06</v>
       </c>
       <c r="E53" t="n">
-        <v>2.31858</v>
+        <v>2.33543</v>
       </c>
       <c r="F53" t="n">
-        <v>2.69203</v>
+        <v>2.82028</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.13758</v>
+        <v>3.08557</v>
       </c>
       <c r="C54" t="n">
-        <v>2.11976</v>
+        <v>2.08539</v>
       </c>
       <c r="D54" t="n">
-        <v>15.0025</v>
+        <v>14.4924</v>
       </c>
       <c r="E54" t="n">
-        <v>2.34884</v>
+        <v>2.30259</v>
       </c>
       <c r="F54" t="n">
-        <v>2.72804</v>
+        <v>2.83183</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.20549</v>
+        <v>3.15311</v>
       </c>
       <c r="C55" t="n">
-        <v>2.19028</v>
+        <v>2.15431</v>
       </c>
       <c r="D55" t="n">
-        <v>15.5497</v>
+        <v>14.94</v>
       </c>
       <c r="E55" t="n">
-        <v>2.46843</v>
+        <v>2.37652</v>
       </c>
       <c r="F55" t="n">
-        <v>2.80567</v>
+        <v>2.90112</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.2859</v>
+        <v>3.25882</v>
       </c>
       <c r="C56" t="n">
-        <v>2.26165</v>
+        <v>2.26911</v>
       </c>
       <c r="D56" t="n">
-        <v>16.0619</v>
+        <v>15.3704</v>
       </c>
       <c r="E56" t="n">
-        <v>2.5134</v>
+        <v>2.39621</v>
       </c>
       <c r="F56" t="n">
-        <v>2.85847</v>
+        <v>2.95721</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.42477</v>
+        <v>3.36893</v>
       </c>
       <c r="C57" t="n">
-        <v>2.35485</v>
+        <v>2.36989</v>
       </c>
       <c r="D57" t="n">
-        <v>16.5629</v>
+        <v>15.7978</v>
       </c>
       <c r="E57" t="n">
-        <v>2.57622</v>
+        <v>2.45139</v>
       </c>
       <c r="F57" t="n">
-        <v>2.92977</v>
+        <v>3.0235</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.59793</v>
+        <v>3.52963</v>
       </c>
       <c r="C58" t="n">
-        <v>2.47261</v>
+        <v>2.4543</v>
       </c>
       <c r="D58" t="n">
-        <v>17.1515</v>
+        <v>16.2108</v>
       </c>
       <c r="E58" t="n">
-        <v>2.72599</v>
+        <v>2.5471</v>
       </c>
       <c r="F58" t="n">
-        <v>2.97517</v>
+        <v>3.10604</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.8097</v>
+        <v>3.80611</v>
       </c>
       <c r="C59" t="n">
-        <v>2.60547</v>
+        <v>2.64499</v>
       </c>
       <c r="D59" t="n">
-        <v>17.5965</v>
+        <v>16.613</v>
       </c>
       <c r="E59" t="n">
-        <v>2.82406</v>
+        <v>2.66227</v>
       </c>
       <c r="F59" t="n">
-        <v>3.16165</v>
+        <v>3.17558</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.11165</v>
+        <v>4.14053</v>
       </c>
       <c r="C60" t="n">
-        <v>2.95111</v>
+        <v>2.92414</v>
       </c>
       <c r="D60" t="n">
-        <v>18.0689</v>
+        <v>17.0347</v>
       </c>
       <c r="E60" t="n">
-        <v>2.87829</v>
+        <v>2.83708</v>
       </c>
       <c r="F60" t="n">
-        <v>3.2229</v>
+        <v>3.34107</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.65186</v>
+        <v>4.63761</v>
       </c>
       <c r="C61" t="n">
-        <v>3.37444</v>
+        <v>3.31252</v>
       </c>
       <c r="D61" t="n">
-        <v>18.569</v>
+        <v>17.4799</v>
       </c>
       <c r="E61" t="n">
-        <v>3.05638</v>
+        <v>3.07582</v>
       </c>
       <c r="F61" t="n">
-        <v>3.43521</v>
+        <v>3.52897</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.30781</v>
+        <v>5.35456</v>
       </c>
       <c r="C62" t="n">
-        <v>3.84035</v>
+        <v>3.90655</v>
       </c>
       <c r="D62" t="n">
-        <v>19.01</v>
+        <v>17.9397</v>
       </c>
       <c r="E62" t="n">
-        <v>3.37175</v>
+        <v>3.3778</v>
       </c>
       <c r="F62" t="n">
-        <v>3.71719</v>
+        <v>3.85071</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.32262</v>
+        <v>6.42247</v>
       </c>
       <c r="C63" t="n">
-        <v>4.75996</v>
+        <v>4.81269</v>
       </c>
       <c r="D63" t="n">
-        <v>19.5574</v>
+        <v>18.4142</v>
       </c>
       <c r="E63" t="n">
-        <v>2.69695</v>
+        <v>2.66647</v>
       </c>
       <c r="F63" t="n">
-        <v>3.0062</v>
+        <v>3.09621</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>8.01449</v>
+        <v>8.067920000000001</v>
       </c>
       <c r="C64" t="n">
-        <v>6.0656</v>
+        <v>6.17628</v>
       </c>
       <c r="D64" t="n">
-        <v>13.815</v>
+        <v>13.3177</v>
       </c>
       <c r="E64" t="n">
-        <v>2.76794</v>
+        <v>2.6653</v>
       </c>
       <c r="F64" t="n">
-        <v>3.0452</v>
+        <v>3.13984</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.67</v>
+        <v>10.8689</v>
       </c>
       <c r="C65" t="n">
-        <v>2.54463</v>
+        <v>2.53848</v>
       </c>
       <c r="D65" t="n">
-        <v>14.4702</v>
+        <v>13.9446</v>
       </c>
       <c r="E65" t="n">
-        <v>2.95382</v>
+        <v>2.6656</v>
       </c>
       <c r="F65" t="n">
-        <v>3.08623</v>
+        <v>3.18866</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.8031</v>
+        <v>14.8736</v>
       </c>
       <c r="C66" t="n">
-        <v>2.60043</v>
+        <v>2.55302</v>
       </c>
       <c r="D66" t="n">
-        <v>15.2182</v>
+        <v>14.6495</v>
       </c>
       <c r="E66" t="n">
-        <v>2.78373</v>
+        <v>2.70151</v>
       </c>
       <c r="F66" t="n">
-        <v>3.1314</v>
+        <v>3.24293</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.59596</v>
+        <v>3.5657</v>
       </c>
       <c r="C67" t="n">
-        <v>2.65327</v>
+        <v>2.59009</v>
       </c>
       <c r="D67" t="n">
-        <v>15.9415</v>
+        <v>15.5061</v>
       </c>
       <c r="E67" t="n">
-        <v>2.75656</v>
+        <v>2.77173</v>
       </c>
       <c r="F67" t="n">
-        <v>3.18662</v>
+        <v>3.29292</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.58052</v>
+        <v>3.62829</v>
       </c>
       <c r="C68" t="n">
-        <v>2.66622</v>
+        <v>2.63704</v>
       </c>
       <c r="D68" t="n">
-        <v>16.914</v>
+        <v>16.2796</v>
       </c>
       <c r="E68" t="n">
-        <v>3.01547</v>
+        <v>2.75545</v>
       </c>
       <c r="F68" t="n">
-        <v>3.25177</v>
+        <v>3.35781</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.66025</v>
+        <v>3.7043</v>
       </c>
       <c r="C69" t="n">
-        <v>2.8112</v>
+        <v>2.67757</v>
       </c>
       <c r="D69" t="n">
-        <v>17.812</v>
+        <v>17.1064</v>
       </c>
       <c r="E69" t="n">
-        <v>2.87709</v>
+        <v>2.80415</v>
       </c>
       <c r="F69" t="n">
-        <v>3.30809</v>
+        <v>3.42057</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.73549</v>
+        <v>3.79056</v>
       </c>
       <c r="C70" t="n">
-        <v>2.70138</v>
+        <v>2.75917</v>
       </c>
       <c r="D70" t="n">
-        <v>18.8194</v>
+        <v>17.9824</v>
       </c>
       <c r="E70" t="n">
-        <v>2.96416</v>
+        <v>2.89368</v>
       </c>
       <c r="F70" t="n">
-        <v>3.44255</v>
+        <v>3.49915</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.88983</v>
+        <v>3.90494</v>
       </c>
       <c r="C71" t="n">
-        <v>2.95999</v>
+        <v>2.82754</v>
       </c>
       <c r="D71" t="n">
-        <v>19.8903</v>
+        <v>18.9471</v>
       </c>
       <c r="E71" t="n">
-        <v>2.9298</v>
+        <v>2.93924</v>
       </c>
       <c r="F71" t="n">
-        <v>3.59617</v>
+        <v>3.58171</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.00674</v>
+        <v>4.06449</v>
       </c>
       <c r="C72" t="n">
-        <v>2.91198</v>
+        <v>2.92408</v>
       </c>
       <c r="D72" t="n">
-        <v>20.9476</v>
+        <v>20.04</v>
       </c>
       <c r="E72" t="n">
-        <v>3.01244</v>
+        <v>3.00756</v>
       </c>
       <c r="F72" t="n">
-        <v>3.71399</v>
+        <v>3.67352</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.26397</v>
+        <v>4.21812</v>
       </c>
       <c r="C73" t="n">
-        <v>3.26508</v>
+        <v>3.04385</v>
       </c>
       <c r="D73" t="n">
-        <v>22.1219</v>
+        <v>21.1944</v>
       </c>
       <c r="E73" t="n">
-        <v>3.11361</v>
+        <v>3.05497</v>
       </c>
       <c r="F73" t="n">
-        <v>3.85571</v>
+        <v>3.80279</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.58757</v>
+        <v>4.50195</v>
       </c>
       <c r="C74" t="n">
-        <v>3.35874</v>
+        <v>3.27183</v>
       </c>
       <c r="D74" t="n">
-        <v>23.4781</v>
+        <v>22.6178</v>
       </c>
       <c r="E74" t="n">
-        <v>3.27554</v>
+        <v>3.2361</v>
       </c>
       <c r="F74" t="n">
-        <v>3.89975</v>
+        <v>3.94861</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.04423</v>
+        <v>4.95905</v>
       </c>
       <c r="C75" t="n">
-        <v>3.75069</v>
+        <v>3.63555</v>
       </c>
       <c r="D75" t="n">
-        <v>24.8552</v>
+        <v>24.1375</v>
       </c>
       <c r="E75" t="n">
-        <v>3.48218</v>
+        <v>3.39547</v>
       </c>
       <c r="F75" t="n">
-        <v>4.09626</v>
+        <v>4.16557</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.67107</v>
+        <v>5.62364</v>
       </c>
       <c r="C76" t="n">
-        <v>4.23649</v>
+        <v>4.19325</v>
       </c>
       <c r="D76" t="n">
-        <v>26.3044</v>
+        <v>25.7549</v>
       </c>
       <c r="E76" t="n">
-        <v>3.78282</v>
+        <v>3.69008</v>
       </c>
       <c r="F76" t="n">
-        <v>4.51357</v>
+        <v>4.45216</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.83167</v>
+        <v>6.5566</v>
       </c>
       <c r="C77" t="n">
-        <v>5.03498</v>
+        <v>4.98417</v>
       </c>
       <c r="D77" t="n">
-        <v>28.0571</v>
+        <v>27.4064</v>
       </c>
       <c r="E77" t="n">
-        <v>2.99383</v>
+        <v>2.97245</v>
       </c>
       <c r="F77" t="n">
-        <v>3.47386</v>
+        <v>3.4812</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.223549999999999</v>
+        <v>8.04998</v>
       </c>
       <c r="C78" t="n">
-        <v>6.29911</v>
+        <v>6.14969</v>
       </c>
       <c r="D78" t="n">
-        <v>24.4979</v>
+        <v>23.8805</v>
       </c>
       <c r="E78" t="n">
-        <v>3.02644</v>
+        <v>2.99864</v>
       </c>
       <c r="F78" t="n">
-        <v>3.51573</v>
+        <v>3.55145</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.7545</v>
+        <v>10.3736</v>
       </c>
       <c r="C79" t="n">
-        <v>2.91869</v>
+        <v>2.89664</v>
       </c>
       <c r="D79" t="n">
-        <v>25.6124</v>
+        <v>25.1408</v>
       </c>
       <c r="E79" t="n">
-        <v>3.06858</v>
+        <v>3.03385</v>
       </c>
       <c r="F79" t="n">
-        <v>3.611</v>
+        <v>3.6101</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>14.3537</v>
+        <v>14.0122</v>
       </c>
       <c r="C80" t="n">
-        <v>2.96211</v>
+        <v>2.92342</v>
       </c>
       <c r="D80" t="n">
-        <v>27.1263</v>
+        <v>26.5335</v>
       </c>
       <c r="E80" t="n">
-        <v>3.09124</v>
+        <v>3.07616</v>
       </c>
       <c r="F80" t="n">
-        <v>3.72238</v>
+        <v>3.66819</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.16141</v>
+        <v>4.08107</v>
       </c>
       <c r="C81" t="n">
-        <v>3.02464</v>
+        <v>2.95705</v>
       </c>
       <c r="D81" t="n">
-        <v>28.5724</v>
+        <v>27.8985</v>
       </c>
       <c r="E81" t="n">
-        <v>3.14592</v>
+        <v>3.10202</v>
       </c>
       <c r="F81" t="n">
-        <v>3.74767</v>
+        <v>3.72859</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.35564</v>
+        <v>4.1479</v>
       </c>
       <c r="C82" t="n">
-        <v>3.07796</v>
+        <v>3.0012</v>
       </c>
       <c r="D82" t="n">
-        <v>29.9781</v>
+        <v>29.4254</v>
       </c>
       <c r="E82" t="n">
-        <v>3.17627</v>
+        <v>3.1482</v>
       </c>
       <c r="F82" t="n">
-        <v>4.10522</v>
+        <v>3.80365</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.49229</v>
+        <v>4.22442</v>
       </c>
       <c r="C83" t="n">
-        <v>3.18733</v>
+        <v>3.05755</v>
       </c>
       <c r="D83" t="n">
-        <v>31.4662</v>
+        <v>30.9687</v>
       </c>
       <c r="E83" t="n">
-        <v>3.26144</v>
+        <v>3.17361</v>
       </c>
       <c r="F83" t="n">
-        <v>4.07346</v>
+        <v>3.87267</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.59268</v>
+        <v>4.36072</v>
       </c>
       <c r="C84" t="n">
-        <v>3.31894</v>
+        <v>3.13119</v>
       </c>
       <c r="D84" t="n">
-        <v>33.0661</v>
+        <v>32.5621</v>
       </c>
       <c r="E84" t="n">
-        <v>3.34271</v>
+        <v>3.23037</v>
       </c>
       <c r="F84" t="n">
-        <v>4.26322</v>
+        <v>3.98062</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>4.85374</v>
+        <v>4.45364</v>
       </c>
       <c r="C85" t="n">
-        <v>3.49597</v>
+        <v>3.21474</v>
       </c>
       <c r="D85" t="n">
-        <v>34.6212</v>
+        <v>34.1113</v>
       </c>
       <c r="E85" t="n">
-        <v>3.48722</v>
+        <v>3.28344</v>
       </c>
       <c r="F85" t="n">
-        <v>4.77036</v>
+        <v>4.10738</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.18886</v>
+        <v>4.63517</v>
       </c>
       <c r="C86" t="n">
-        <v>3.7064</v>
+        <v>3.34967</v>
       </c>
       <c r="D86" t="n">
-        <v>36.3108</v>
+        <v>35.7339</v>
       </c>
       <c r="E86" t="n">
-        <v>3.6445</v>
+        <v>3.34937</v>
       </c>
       <c r="F86" t="n">
-        <v>5.12986</v>
+        <v>4.27243</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.61466</v>
+        <v>4.91093</v>
       </c>
       <c r="C87" t="n">
-        <v>3.99706</v>
+        <v>3.53819</v>
       </c>
       <c r="D87" t="n">
-        <v>38.0005</v>
+        <v>37.4709</v>
       </c>
       <c r="E87" t="n">
-        <v>3.90372</v>
+        <v>3.54295</v>
       </c>
       <c r="F87" t="n">
-        <v>5.31476</v>
+        <v>4.51809</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.21841</v>
+        <v>5.28419</v>
       </c>
       <c r="C88" t="n">
-        <v>4.36323</v>
+        <v>3.80086</v>
       </c>
       <c r="D88" t="n">
-        <v>39.5689</v>
+        <v>39.1923</v>
       </c>
       <c r="E88" t="n">
-        <v>4.09455</v>
+        <v>3.68248</v>
       </c>
       <c r="F88" t="n">
-        <v>5.73894</v>
+        <v>4.96589</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>7.0473</v>
+        <v>5.80577</v>
       </c>
       <c r="C89" t="n">
-        <v>4.86499</v>
+        <v>4.20745</v>
       </c>
       <c r="D89" t="n">
-        <v>41.5551</v>
+        <v>41.0318</v>
       </c>
       <c r="E89" t="n">
-        <v>4.40672</v>
+        <v>3.92827</v>
       </c>
       <c r="F89" t="n">
-        <v>6.27847</v>
+        <v>5.35609</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.75007</v>
+        <v>6.57411</v>
       </c>
       <c r="C90" t="n">
-        <v>5.36865</v>
+        <v>4.7934</v>
       </c>
       <c r="D90" t="n">
-        <v>43.5488</v>
+        <v>42.9202</v>
       </c>
       <c r="E90" t="n">
-        <v>4.84569</v>
+        <v>4.30522</v>
       </c>
       <c r="F90" t="n">
-        <v>6.9239</v>
+        <v>6.04061</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.97579</v>
+        <v>7.69792</v>
       </c>
       <c r="C91" t="n">
-        <v>6.24772</v>
+        <v>5.65927</v>
       </c>
       <c r="D91" t="n">
-        <v>45.574</v>
+        <v>44.9472</v>
       </c>
       <c r="E91" t="n">
-        <v>3.56464</v>
+        <v>3.22913</v>
       </c>
       <c r="F91" t="n">
-        <v>4.75464</v>
+        <v>4.05617</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.3614</v>
+        <v>9.3773</v>
       </c>
       <c r="C92" t="n">
-        <v>7.4041</v>
+        <v>7.02385</v>
       </c>
       <c r="D92" t="n">
-        <v>36.884</v>
+        <v>36.7359</v>
       </c>
       <c r="E92" t="n">
-        <v>3.68912</v>
+        <v>3.2869</v>
       </c>
       <c r="F92" t="n">
-        <v>5.01823</v>
+        <v>4.28186</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>12.429</v>
+        <v>11.7784</v>
       </c>
       <c r="C93" t="n">
-        <v>9.02327</v>
+        <v>9.078010000000001</v>
       </c>
       <c r="D93" t="n">
-        <v>38.1271</v>
+        <v>37.9761</v>
       </c>
       <c r="E93" t="n">
-        <v>3.8461</v>
+        <v>3.36355</v>
       </c>
       <c r="F93" t="n">
-        <v>5.31143</v>
+        <v>4.55501</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>15.8056</v>
+        <v>15.3105</v>
       </c>
       <c r="C94" t="n">
-        <v>3.99391</v>
+        <v>3.42008</v>
       </c>
       <c r="D94" t="n">
-        <v>39.3756</v>
+        <v>39.179</v>
       </c>
       <c r="E94" t="n">
-        <v>4.00847</v>
+        <v>3.47279</v>
       </c>
       <c r="F94" t="n">
-        <v>5.62033</v>
+        <v>4.89817</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>6.2261</v>
+        <v>5.22716</v>
       </c>
       <c r="C95" t="n">
-        <v>4.18622</v>
+        <v>3.59165</v>
       </c>
       <c r="D95" t="n">
-        <v>40.6892</v>
+        <v>40.4707</v>
       </c>
       <c r="E95" t="n">
-        <v>4.16082</v>
+        <v>3.60572</v>
       </c>
       <c r="F95" t="n">
-        <v>5.95716</v>
+        <v>5.25622</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.45995</v>
+        <v>5.65251</v>
       </c>
       <c r="C96" t="n">
-        <v>4.30854</v>
+        <v>3.7776</v>
       </c>
       <c r="D96" t="n">
-        <v>42.0595</v>
+        <v>41.8014</v>
       </c>
       <c r="E96" t="n">
-        <v>4.31752</v>
+        <v>3.76075</v>
       </c>
       <c r="F96" t="n">
-        <v>6.25751</v>
+        <v>5.74844</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.72943</v>
+        <v>6.04633</v>
       </c>
       <c r="C97" t="n">
-        <v>4.4789</v>
+        <v>4.02558</v>
       </c>
       <c r="D97" t="n">
-        <v>43.4772</v>
+        <v>43.186</v>
       </c>
       <c r="E97" t="n">
-        <v>4.49506</v>
+        <v>3.95301</v>
       </c>
       <c r="F97" t="n">
-        <v>6.54323</v>
+        <v>6.28194</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>7.08622</v>
+        <v>6.52581</v>
       </c>
       <c r="C98" t="n">
-        <v>4.62031</v>
+        <v>4.2941</v>
       </c>
       <c r="D98" t="n">
-        <v>44.8995</v>
+        <v>44.6175</v>
       </c>
       <c r="E98" t="n">
-        <v>4.67328</v>
+        <v>4.19796</v>
       </c>
       <c r="F98" t="n">
-        <v>6.81825</v>
+        <v>6.88901</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.39388</v>
+        <v>7.07351</v>
       </c>
       <c r="C99" t="n">
-        <v>4.84039</v>
+        <v>4.62682</v>
       </c>
       <c r="D99" t="n">
-        <v>46.4432</v>
+        <v>46.1123</v>
       </c>
       <c r="E99" t="n">
-        <v>4.84488</v>
+        <v>4.52643</v>
       </c>
       <c r="F99" t="n">
-        <v>7.17085</v>
+        <v>7.54195</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.68876</v>
+        <v>7.6896</v>
       </c>
       <c r="C100" t="n">
-        <v>5.01477</v>
+        <v>5.04893</v>
       </c>
       <c r="D100" t="n">
-        <v>48.1095</v>
+        <v>47.7474</v>
       </c>
       <c r="E100" t="n">
-        <v>5.00586</v>
+        <v>4.90779</v>
       </c>
       <c r="F100" t="n">
-        <v>7.48932</v>
+        <v>8.27877</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>8.04692</v>
+        <v>8.371980000000001</v>
       </c>
       <c r="C101" t="n">
-        <v>5.24975</v>
+        <v>5.44612</v>
       </c>
       <c r="D101" t="n">
-        <v>49.6055</v>
+        <v>49.3346</v>
       </c>
       <c r="E101" t="n">
-        <v>5.18981</v>
+        <v>5.2764</v>
       </c>
       <c r="F101" t="n">
-        <v>7.77722</v>
+        <v>8.859640000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.50156</v>
+        <v>9.05152</v>
       </c>
       <c r="C102" t="n">
-        <v>5.55707</v>
+        <v>5.90602</v>
       </c>
       <c r="D102" t="n">
-        <v>51.5709</v>
+        <v>51.0432</v>
       </c>
       <c r="E102" t="n">
-        <v>5.409</v>
+        <v>5.69284</v>
       </c>
       <c r="F102" t="n">
-        <v>8.20778</v>
+        <v>9.593220000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>9.086930000000001</v>
+        <v>9.803839999999999</v>
       </c>
       <c r="C103" t="n">
-        <v>5.9499</v>
+        <v>6.45977</v>
       </c>
       <c r="D103" t="n">
-        <v>53.3659</v>
+        <v>52.9868</v>
       </c>
       <c r="E103" t="n">
-        <v>5.68893</v>
+        <v>6.13049</v>
       </c>
       <c r="F103" t="n">
-        <v>8.81963</v>
+        <v>10.2648</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.85422</v>
+        <v>10.6904</v>
       </c>
       <c r="C104" t="n">
-        <v>6.54123</v>
+        <v>7.10106</v>
       </c>
       <c r="D104" t="n">
-        <v>55.3688</v>
+        <v>54.8288</v>
       </c>
       <c r="E104" t="n">
-        <v>6.06524</v>
+        <v>6.65045</v>
       </c>
       <c r="F104" t="n">
-        <v>9.4907</v>
+        <v>10.9887</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.8648</v>
+        <v>11.7802</v>
       </c>
       <c r="C105" t="n">
-        <v>7.34308</v>
+        <v>7.93067</v>
       </c>
       <c r="D105" t="n">
-        <v>57.3448</v>
+        <v>56.6843</v>
       </c>
       <c r="E105" t="n">
-        <v>4.47434</v>
+        <v>4.75927</v>
       </c>
       <c r="F105" t="n">
-        <v>6.22547</v>
+        <v>7.50152</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>12.298</v>
+        <v>13.0525</v>
       </c>
       <c r="C106" t="n">
-        <v>8.52336</v>
+        <v>9.091799999999999</v>
       </c>
       <c r="D106" t="n">
-        <v>59.2488</v>
+        <v>58.7043</v>
       </c>
       <c r="E106" t="n">
-        <v>4.55918</v>
+        <v>4.89999</v>
       </c>
       <c r="F106" t="n">
-        <v>6.55979</v>
+        <v>7.83224</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>14.421</v>
+        <v>14.9435</v>
       </c>
       <c r="C107" t="n">
-        <v>10.3101</v>
+        <v>10.7808</v>
       </c>
       <c r="D107" t="n">
-        <v>44.686</v>
+        <v>44.6662</v>
       </c>
       <c r="E107" t="n">
-        <v>4.67682</v>
+        <v>5.14509</v>
       </c>
       <c r="F107" t="n">
-        <v>6.66164</v>
+        <v>8.197800000000001</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.41</v>
+        <v>17.6753</v>
       </c>
       <c r="C108" t="n">
-        <v>4.64307</v>
+        <v>5.39159</v>
       </c>
       <c r="D108" t="n">
-        <v>45.8366</v>
+        <v>45.8027</v>
       </c>
       <c r="E108" t="n">
-        <v>4.75783</v>
+        <v>5.3467</v>
       </c>
       <c r="F108" t="n">
-        <v>7.04362</v>
+        <v>8.485110000000001</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>22.1333</v>
+        <v>22.2208</v>
       </c>
       <c r="C109" t="n">
-        <v>4.84153</v>
+        <v>5.58152</v>
       </c>
       <c r="D109" t="n">
-        <v>47.0897</v>
+        <v>46.9845</v>
       </c>
       <c r="E109" t="n">
-        <v>4.83464</v>
+        <v>5.60054</v>
       </c>
       <c r="F109" t="n">
-        <v>7.35688</v>
+        <v>8.85167</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.73157</v>
+        <v>8.912409999999999</v>
       </c>
       <c r="C110" t="n">
-        <v>5.0489</v>
+        <v>5.75923</v>
       </c>
       <c r="D110" t="n">
-        <v>48.3802</v>
+        <v>48.2542</v>
       </c>
       <c r="E110" t="n">
-        <v>4.97853</v>
+        <v>5.78264</v>
       </c>
       <c r="F110" t="n">
-        <v>7.83218</v>
+        <v>9.20073</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>8.001709999999999</v>
+        <v>9.204969999999999</v>
       </c>
       <c r="C111" t="n">
-        <v>5.1386</v>
+        <v>5.92196</v>
       </c>
       <c r="D111" t="n">
-        <v>49.7483</v>
+        <v>49.563</v>
       </c>
       <c r="E111" t="n">
-        <v>5.13028</v>
+        <v>5.96715</v>
       </c>
       <c r="F111" t="n">
-        <v>8.261559999999999</v>
+        <v>9.48555</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>8.317270000000001</v>
+        <v>9.468220000000001</v>
       </c>
       <c r="C112" t="n">
-        <v>5.42073</v>
+        <v>6.09659</v>
       </c>
       <c r="D112" t="n">
-        <v>51.0951</v>
+        <v>50.9581</v>
       </c>
       <c r="E112" t="n">
-        <v>5.22013</v>
+        <v>6.14355</v>
       </c>
       <c r="F112" t="n">
-        <v>8.707470000000001</v>
+        <v>9.789160000000001</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.69384</v>
+        <v>9.770110000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>5.60427</v>
+        <v>6.30703</v>
       </c>
       <c r="D113" t="n">
-        <v>52.6589</v>
+        <v>52.3425</v>
       </c>
       <c r="E113" t="n">
-        <v>5.44929</v>
+        <v>6.35387</v>
       </c>
       <c r="F113" t="n">
-        <v>9.231590000000001</v>
+        <v>10.1406</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>9.15438</v>
+        <v>10.0753</v>
       </c>
       <c r="C114" t="n">
-        <v>5.88508</v>
+        <v>6.52659</v>
       </c>
       <c r="D114" t="n">
-        <v>54.1896</v>
+        <v>53.8897</v>
       </c>
       <c r="E114" t="n">
-        <v>5.74003</v>
+        <v>6.54734</v>
       </c>
       <c r="F114" t="n">
-        <v>9.79406</v>
+        <v>10.4911</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.81132</v>
+        <v>10.4356</v>
       </c>
       <c r="C115" t="n">
-        <v>6.22513</v>
+        <v>6.76988</v>
       </c>
       <c r="D115" t="n">
-        <v>55.8163</v>
+        <v>55.4533</v>
       </c>
       <c r="E115" t="n">
-        <v>6.0854</v>
+        <v>6.76716</v>
       </c>
       <c r="F115" t="n">
-        <v>10.3323</v>
+        <v>10.8114</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>10.466</v>
+        <v>10.9091</v>
       </c>
       <c r="C116" t="n">
-        <v>6.76445</v>
+        <v>7.09076</v>
       </c>
       <c r="D116" t="n">
-        <v>57.6315</v>
+        <v>57.1388</v>
       </c>
       <c r="E116" t="n">
-        <v>6.54292</v>
+        <v>7.01287</v>
       </c>
       <c r="F116" t="n">
-        <v>10.9441</v>
+        <v>11.2684</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>11.0876</v>
+        <v>11.4207</v>
       </c>
       <c r="C117" t="n">
-        <v>7.25413</v>
+        <v>7.48098</v>
       </c>
       <c r="D117" t="n">
-        <v>59.4351</v>
+        <v>58.9669</v>
       </c>
       <c r="E117" t="n">
-        <v>7.00207</v>
+        <v>7.30559</v>
       </c>
       <c r="F117" t="n">
-        <v>11.5149</v>
+        <v>11.7519</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.883</v>
+        <v>12.0988</v>
       </c>
       <c r="C118" t="n">
-        <v>7.84078</v>
+        <v>8.00071</v>
       </c>
       <c r="D118" t="n">
-        <v>61.4066</v>
+        <v>60.7459</v>
       </c>
       <c r="E118" t="n">
-        <v>7.45291</v>
+        <v>7.75459</v>
       </c>
       <c r="F118" t="n">
-        <v>12.1213</v>
+        <v>12.3343</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.8547</v>
+        <v>13.0069</v>
       </c>
       <c r="C119" t="n">
-        <v>8.584009999999999</v>
+        <v>8.70439</v>
       </c>
       <c r="D119" t="n">
-        <v>63.3966</v>
+        <v>62.6983</v>
       </c>
       <c r="E119" t="n">
-        <v>6.20018</v>
+        <v>6.53916</v>
       </c>
       <c r="F119" t="n">
-        <v>9.2332</v>
+        <v>9.179220000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>14.0845</v>
+        <v>14.1989</v>
       </c>
       <c r="C120" t="n">
-        <v>9.632239999999999</v>
+        <v>9.74222</v>
       </c>
       <c r="D120" t="n">
-        <v>65.5003</v>
+        <v>64.8189</v>
       </c>
       <c r="E120" t="n">
-        <v>6.27689</v>
+        <v>6.47527</v>
       </c>
       <c r="F120" t="n">
-        <v>9.39977</v>
+        <v>9.676740000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.8299</v>
+        <v>15.8748</v>
       </c>
       <c r="C121" t="n">
-        <v>11.2297</v>
+        <v>11.3078</v>
       </c>
       <c r="D121" t="n">
-        <v>48.1462</v>
+        <v>48.0584</v>
       </c>
       <c r="E121" t="n">
-        <v>6.35289</v>
+        <v>6.86162</v>
       </c>
       <c r="F121" t="n">
-        <v>9.68066</v>
+        <v>9.782</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>18.3603</v>
+        <v>18.3635</v>
       </c>
       <c r="C122" t="n">
-        <v>6.64893</v>
+        <v>6.63866</v>
       </c>
       <c r="D122" t="n">
-        <v>49.3514</v>
+        <v>49.1996</v>
       </c>
       <c r="E122" t="n">
-        <v>6.83667</v>
+        <v>6.78657</v>
       </c>
       <c r="F122" t="n">
-        <v>10.242</v>
+        <v>10.0969</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.4875</v>
+        <v>22.38</v>
       </c>
       <c r="C123" t="n">
-        <v>6.54243</v>
+        <v>6.53572</v>
       </c>
       <c r="D123" t="n">
-        <v>50.4992</v>
+        <v>50.2988</v>
       </c>
       <c r="E123" t="n">
-        <v>6.80931</v>
+        <v>6.68199</v>
       </c>
       <c r="F123" t="n">
-        <v>10.2973</v>
+        <v>10.9139</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>10.0076</v>
+        <v>9.87472</v>
       </c>
       <c r="C124" t="n">
-        <v>6.94267</v>
+        <v>6.73443</v>
       </c>
       <c r="D124" t="n">
-        <v>51.8198</v>
+        <v>51.5506</v>
       </c>
       <c r="E124" t="n">
-        <v>7.05976</v>
+        <v>6.93491</v>
       </c>
       <c r="F124" t="n">
-        <v>10.7942</v>
+        <v>10.7148</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.3728</v>
+        <v>10.2863</v>
       </c>
       <c r="C125" t="n">
-        <v>6.9709</v>
+        <v>6.84194</v>
       </c>
       <c r="D125" t="n">
-        <v>52.8738</v>
+        <v>52.9008</v>
       </c>
       <c r="E125" t="n">
-        <v>7.43318</v>
+        <v>7.1955</v>
       </c>
       <c r="F125" t="n">
-        <v>11.1813</v>
+        <v>11.0993</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.6894</v>
+        <v>10.6598</v>
       </c>
       <c r="C126" t="n">
-        <v>7.36988</v>
+        <v>7.36016</v>
       </c>
       <c r="D126" t="n">
-        <v>54.2816</v>
+        <v>54.227</v>
       </c>
       <c r="E126" t="n">
-        <v>7.49344</v>
+        <v>7.30828</v>
       </c>
       <c r="F126" t="n">
-        <v>11.4173</v>
+        <v>11.459</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>11.0477</v>
+        <v>10.7573</v>
       </c>
       <c r="C127" t="n">
-        <v>7.61505</v>
+        <v>7.22374</v>
       </c>
       <c r="D127" t="n">
-        <v>56.0536</v>
+        <v>55.6262</v>
       </c>
       <c r="E127" t="n">
-        <v>7.75182</v>
+        <v>7.48065</v>
       </c>
       <c r="F127" t="n">
-        <v>11.8388</v>
+        <v>11.6117</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>11.3225</v>
+        <v>11.1276</v>
       </c>
       <c r="C128" t="n">
-        <v>7.54406</v>
+        <v>7.29245</v>
       </c>
       <c r="D128" t="n">
-        <v>57.6042</v>
+        <v>57.1395</v>
       </c>
       <c r="E128" t="n">
-        <v>7.93065</v>
+        <v>7.53938</v>
       </c>
       <c r="F128" t="n">
-        <v>12.0723</v>
+        <v>11.8689</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.4872</v>
+        <v>11.5036</v>
       </c>
       <c r="C129" t="n">
-        <v>7.71664</v>
+        <v>7.63674</v>
       </c>
       <c r="D129" t="n">
-        <v>59.2712</v>
+        <v>58.7208</v>
       </c>
       <c r="E129" t="n">
-        <v>8.195970000000001</v>
+        <v>7.94956</v>
       </c>
       <c r="F129" t="n">
-        <v>12.5899</v>
+        <v>12.5304</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>12.0074</v>
+        <v>11.9964</v>
       </c>
       <c r="C130" t="n">
-        <v>7.94153</v>
+        <v>8.125400000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>61.0365</v>
+        <v>60.4753</v>
       </c>
       <c r="E130" t="n">
-        <v>8.32446</v>
+        <v>8.134729999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>12.8854</v>
+        <v>12.8037</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>12.4457</v>
+        <v>12.834</v>
       </c>
       <c r="C131" t="n">
-        <v>8.38109</v>
+        <v>8.31776</v>
       </c>
       <c r="D131" t="n">
-        <v>62.6639</v>
+        <v>62.2103</v>
       </c>
       <c r="E131" t="n">
-        <v>8.68934</v>
+        <v>8.594799999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>13.5082</v>
+        <v>13.5762</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>13.1182</v>
+        <v>13.1061</v>
       </c>
       <c r="C132" t="n">
-        <v>8.751110000000001</v>
+        <v>8.78201</v>
       </c>
       <c r="D132" t="n">
-        <v>64.8026</v>
+        <v>64.0911</v>
       </c>
       <c r="E132" t="n">
-        <v>8.955080000000001</v>
+        <v>8.820919999999999</v>
       </c>
       <c r="F132" t="n">
-        <v>13.8734</v>
+        <v>13.9719</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.8112</v>
+        <v>13.8914</v>
       </c>
       <c r="C133" t="n">
-        <v>9.42543</v>
+        <v>9.342499999999999</v>
       </c>
       <c r="D133" t="n">
-        <v>66.84520000000001</v>
+        <v>66.0638</v>
       </c>
       <c r="E133" t="n">
-        <v>9.286250000000001</v>
+        <v>9.280419999999999</v>
       </c>
       <c r="F133" t="n">
-        <v>14.4706</v>
+        <v>14.8377</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.9742</v>
+        <v>14.9455</v>
       </c>
       <c r="C134" t="n">
-        <v>10.4762</v>
+        <v>10.3223</v>
       </c>
       <c r="D134" t="n">
-        <v>68.9854</v>
+        <v>68.142</v>
       </c>
       <c r="E134" t="n">
-        <v>13.0303</v>
+        <v>12.8975</v>
       </c>
       <c r="F134" t="n">
-        <v>15.9691</v>
+        <v>16.3514</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.7189</v>
+        <v>16.7171</v>
       </c>
       <c r="C135" t="n">
-        <v>11.7559</v>
+        <v>11.7631</v>
       </c>
       <c r="D135" t="n">
-        <v>50.1036</v>
+        <v>49.9372</v>
       </c>
       <c r="E135" t="n">
-        <v>13.2923</v>
+        <v>13.3079</v>
       </c>
       <c r="F135" t="n">
-        <v>16.3162</v>
+        <v>16.366</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.3674</v>
+        <v>19.0053</v>
       </c>
       <c r="C136" t="n">
-        <v>13.4254</v>
+        <v>13.5098</v>
       </c>
       <c r="D136" t="n">
-        <v>51.0488</v>
+        <v>51.0536</v>
       </c>
       <c r="E136" t="n">
-        <v>12.8663</v>
+        <v>13.5161</v>
       </c>
       <c r="F136" t="n">
-        <v>16.7126</v>
+        <v>16.8177</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>22.163</v>
+        <v>22.68</v>
       </c>
       <c r="C137" t="n">
-        <v>13.5852</v>
+        <v>13.6046</v>
       </c>
       <c r="D137" t="n">
-        <v>52.4087</v>
+        <v>52.2208</v>
       </c>
       <c r="E137" t="n">
-        <v>13.3394</v>
+        <v>13.4982</v>
       </c>
       <c r="F137" t="n">
-        <v>16.6866</v>
+        <v>16.931</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.8593</v>
+        <v>17.0064</v>
       </c>
       <c r="C138" t="n">
-        <v>13.6481</v>
+        <v>13.6005</v>
       </c>
       <c r="D138" t="n">
-        <v>53.5784</v>
+        <v>53.4591</v>
       </c>
       <c r="E138" t="n">
-        <v>13.4565</v>
+        <v>13.5399</v>
       </c>
       <c r="F138" t="n">
-        <v>16.9306</v>
+        <v>16.3516</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>17.1133</v>
+        <v>17.0137</v>
       </c>
       <c r="C139" t="n">
-        <v>13.7686</v>
+        <v>13.7379</v>
       </c>
       <c r="D139" t="n">
-        <v>55.0042</v>
+        <v>54.758</v>
       </c>
       <c r="E139" t="n">
-        <v>13.7266</v>
+        <v>13.775</v>
       </c>
       <c r="F139" t="n">
-        <v>17.3566</v>
+        <v>17.5252</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>17.3327</v>
+        <v>17.4763</v>
       </c>
       <c r="C140" t="n">
-        <v>13.7258</v>
+        <v>13.751</v>
       </c>
       <c r="D140" t="n">
-        <v>56.2409</v>
+        <v>56.1151</v>
       </c>
       <c r="E140" t="n">
-        <v>13.1118</v>
+        <v>13.9526</v>
       </c>
       <c r="F140" t="n">
-        <v>17.651</v>
+        <v>17.7697</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>17.1879</v>
+        <v>17.5063</v>
       </c>
       <c r="C141" t="n">
-        <v>13.9587</v>
+        <v>13.807</v>
       </c>
       <c r="D141" t="n">
-        <v>57.7363</v>
+        <v>57.5229</v>
       </c>
       <c r="E141" t="n">
-        <v>13.7702</v>
+        <v>13.9993</v>
       </c>
       <c r="F141" t="n">
-        <v>17.8495</v>
+        <v>17.7906</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>17.7331</v>
+        <v>17.5414</v>
       </c>
       <c r="C142" t="n">
-        <v>14.0299</v>
+        <v>13.9746</v>
       </c>
       <c r="D142" t="n">
-        <v>59.3018</v>
+        <v>59.044</v>
       </c>
       <c r="E142" t="n">
-        <v>14.1508</v>
+        <v>14.129</v>
       </c>
       <c r="F142" t="n">
-        <v>18.3257</v>
+        <v>17.8205</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.789</v>
+        <v>17.9634</v>
       </c>
       <c r="C143" t="n">
-        <v>14.1795</v>
+        <v>14.1164</v>
       </c>
       <c r="D143" t="n">
-        <v>61.1435</v>
+        <v>60.4923</v>
       </c>
       <c r="E143" t="n">
-        <v>14.0118</v>
+        <v>13.4017</v>
       </c>
       <c r="F143" t="n">
-        <v>18.5305</v>
+        <v>18.6587</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered unsuccessful looukp.xlsx
+++ b/clang-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.62977</v>
+        <v>10.4541</v>
       </c>
       <c r="C2" t="n">
-        <v>3.56064</v>
+        <v>10.5222</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5766</v>
+        <v>29.352</v>
       </c>
       <c r="E2" t="n">
-        <v>2.97275</v>
+        <v>12.5963</v>
       </c>
       <c r="F2" t="n">
-        <v>3.19317</v>
+        <v>13.0754</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.75183</v>
+        <v>10.849</v>
       </c>
       <c r="C3" t="n">
-        <v>3.92058</v>
+        <v>10.9587</v>
       </c>
       <c r="D3" t="n">
-        <v>13.2372</v>
+        <v>29.9124</v>
       </c>
       <c r="E3" t="n">
-        <v>3.04392</v>
+        <v>12.6907</v>
       </c>
       <c r="F3" t="n">
-        <v>3.30641</v>
+        <v>13.1716</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.9827</v>
+        <v>11.3574</v>
       </c>
       <c r="C4" t="n">
-        <v>4.07486</v>
+        <v>11.3947</v>
       </c>
       <c r="D4" t="n">
-        <v>13.6536</v>
+        <v>30.5984</v>
       </c>
       <c r="E4" t="n">
-        <v>3.14589</v>
+        <v>12.9177</v>
       </c>
       <c r="F4" t="n">
-        <v>3.38582</v>
+        <v>13.3897</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>4.52277</v>
+        <v>12.1885</v>
       </c>
       <c r="C5" t="n">
-        <v>4.735</v>
+        <v>12.133</v>
       </c>
       <c r="D5" t="n">
-        <v>14.273</v>
+        <v>30.857</v>
       </c>
       <c r="E5" t="n">
-        <v>3.25252</v>
+        <v>13.2649</v>
       </c>
       <c r="F5" t="n">
-        <v>3.56499</v>
+        <v>13.751</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>5.68875</v>
+        <v>13.1668</v>
       </c>
       <c r="C6" t="n">
-        <v>5.69114</v>
+        <v>13.5426</v>
       </c>
       <c r="D6" t="n">
-        <v>14.6729</v>
+        <v>32.4885</v>
       </c>
       <c r="E6" t="n">
-        <v>3.54451</v>
+        <v>13.8456</v>
       </c>
       <c r="F6" t="n">
-        <v>3.96954</v>
+        <v>14.3491</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>7.93807</v>
+        <v>14.9202</v>
       </c>
       <c r="C7" t="n">
-        <v>8.27023</v>
+        <v>15.2771</v>
       </c>
       <c r="D7" t="n">
-        <v>10.153</v>
+        <v>27.0348</v>
       </c>
       <c r="E7" t="n">
-        <v>4.23301</v>
+        <v>15.0512</v>
       </c>
       <c r="F7" t="n">
-        <v>4.67502</v>
+        <v>15.5654</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>11.7084</v>
+        <v>17.8012</v>
       </c>
       <c r="C8" t="n">
-        <v>11.3719</v>
+        <v>18.0218</v>
       </c>
       <c r="D8" t="n">
-        <v>10.7569</v>
+        <v>27.6938</v>
       </c>
       <c r="E8" t="n">
-        <v>6.15747</v>
+        <v>17.1181</v>
       </c>
       <c r="F8" t="n">
-        <v>6.37709</v>
+        <v>17.6986</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.934</v>
+        <v>21.9179</v>
       </c>
       <c r="C9" t="n">
-        <v>15.7647</v>
+        <v>22.6482</v>
       </c>
       <c r="D9" t="n">
-        <v>11.4101</v>
+        <v>28.2739</v>
       </c>
       <c r="E9" t="n">
-        <v>2.77004</v>
+        <v>12.2495</v>
       </c>
       <c r="F9" t="n">
-        <v>2.90861</v>
+        <v>12.6455</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.27573</v>
+        <v>9.74765</v>
       </c>
       <c r="C10" t="n">
-        <v>3.37309</v>
+        <v>9.875679999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>11.8204</v>
+        <v>29.0902</v>
       </c>
       <c r="E10" t="n">
-        <v>2.796</v>
+        <v>12.284</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9367</v>
+        <v>12.6523</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.3404</v>
+        <v>9.82597</v>
       </c>
       <c r="C11" t="n">
-        <v>3.48493</v>
+        <v>9.973929999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>12.4018</v>
+        <v>30.0746</v>
       </c>
       <c r="E11" t="n">
-        <v>2.82308</v>
+        <v>12.3303</v>
       </c>
       <c r="F11" t="n">
-        <v>2.96847</v>
+        <v>12.6802</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.38978</v>
+        <v>9.8881</v>
       </c>
       <c r="C12" t="n">
-        <v>3.53389</v>
+        <v>10.073</v>
       </c>
       <c r="D12" t="n">
-        <v>12.9027</v>
+        <v>29.7602</v>
       </c>
       <c r="E12" t="n">
-        <v>2.87765</v>
+        <v>12.3584</v>
       </c>
       <c r="F12" t="n">
-        <v>3.04049</v>
+        <v>12.7679</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.4621</v>
+        <v>9.95166</v>
       </c>
       <c r="C13" t="n">
-        <v>3.57228</v>
+        <v>10.2203</v>
       </c>
       <c r="D13" t="n">
-        <v>13.4063</v>
+        <v>30.8485</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9152</v>
+        <v>12.4038</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0954</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.56616</v>
+        <v>10.1117</v>
       </c>
       <c r="C14" t="n">
-        <v>3.66842</v>
+        <v>10.3818</v>
       </c>
       <c r="D14" t="n">
-        <v>13.8581</v>
+        <v>31.1393</v>
       </c>
       <c r="E14" t="n">
-        <v>2.95835</v>
+        <v>12.4686</v>
       </c>
       <c r="F14" t="n">
-        <v>3.14632</v>
+        <v>12.877</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.67249</v>
+        <v>10.2586</v>
       </c>
       <c r="C15" t="n">
-        <v>3.7831</v>
+        <v>10.619</v>
       </c>
       <c r="D15" t="n">
-        <v>14.2732</v>
+        <v>32.2762</v>
       </c>
       <c r="E15" t="n">
-        <v>3.03891</v>
+        <v>12.5701</v>
       </c>
       <c r="F15" t="n">
-        <v>3.22713</v>
+        <v>13.0398</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.83508</v>
+        <v>10.4931</v>
       </c>
       <c r="C16" t="n">
-        <v>3.97347</v>
+        <v>10.9329</v>
       </c>
       <c r="D16" t="n">
-        <v>14.6237</v>
+        <v>32.9122</v>
       </c>
       <c r="E16" t="n">
-        <v>3.11998</v>
+        <v>12.6882</v>
       </c>
       <c r="F16" t="n">
-        <v>3.31929</v>
+        <v>13.1731</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>4.02842</v>
+        <v>10.7983</v>
       </c>
       <c r="C17" t="n">
-        <v>4.2435</v>
+        <v>11.3415</v>
       </c>
       <c r="D17" t="n">
-        <v>15.0762</v>
+        <v>33.4098</v>
       </c>
       <c r="E17" t="n">
-        <v>3.24324</v>
+        <v>12.8518</v>
       </c>
       <c r="F17" t="n">
-        <v>3.46325</v>
+        <v>13.3179</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.35094</v>
+        <v>11.2877</v>
       </c>
       <c r="C18" t="n">
-        <v>4.75641</v>
+        <v>11.8824</v>
       </c>
       <c r="D18" t="n">
-        <v>15.4482</v>
+        <v>33.7213</v>
       </c>
       <c r="E18" t="n">
-        <v>3.35596</v>
+        <v>13.0426</v>
       </c>
       <c r="F18" t="n">
-        <v>3.57993</v>
+        <v>13.4841</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>5.12417</v>
+        <v>11.9358</v>
       </c>
       <c r="C19" t="n">
-        <v>5.25253</v>
+        <v>12.6849</v>
       </c>
       <c r="D19" t="n">
-        <v>15.8403</v>
+        <v>35.0423</v>
       </c>
       <c r="E19" t="n">
-        <v>3.52879</v>
+        <v>13.3107</v>
       </c>
       <c r="F19" t="n">
-        <v>3.80131</v>
+        <v>13.811</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>6.21287</v>
+        <v>12.9574</v>
       </c>
       <c r="C20" t="n">
-        <v>6.28939</v>
+        <v>13.8484</v>
       </c>
       <c r="D20" t="n">
-        <v>16.2519</v>
+        <v>35.8575</v>
       </c>
       <c r="E20" t="n">
-        <v>3.92726</v>
+        <v>13.9305</v>
       </c>
       <c r="F20" t="n">
-        <v>4.22593</v>
+        <v>14.4903</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>8.141170000000001</v>
+        <v>14.6908</v>
       </c>
       <c r="C21" t="n">
-        <v>8.181850000000001</v>
+        <v>15.5886</v>
       </c>
       <c r="D21" t="n">
-        <v>11.634</v>
+        <v>29.0826</v>
       </c>
       <c r="E21" t="n">
-        <v>4.83593</v>
+        <v>14.8863</v>
       </c>
       <c r="F21" t="n">
-        <v>5.09045</v>
+        <v>15.5682</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>10.5265</v>
+        <v>17.3001</v>
       </c>
       <c r="C22" t="n">
-        <v>10.5983</v>
+        <v>18.2678</v>
       </c>
       <c r="D22" t="n">
-        <v>12.18</v>
+        <v>29.7227</v>
       </c>
       <c r="E22" t="n">
-        <v>7.02133</v>
+        <v>16.8804</v>
       </c>
       <c r="F22" t="n">
-        <v>6.95473</v>
+        <v>17.7076</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>14.6937</v>
+        <v>21.694</v>
       </c>
       <c r="C23" t="n">
-        <v>14.2027</v>
+        <v>22.4658</v>
       </c>
       <c r="D23" t="n">
-        <v>12.6454</v>
+        <v>30.4573</v>
       </c>
       <c r="E23" t="n">
-        <v>2.83619</v>
+        <v>12.3541</v>
       </c>
       <c r="F23" t="n">
-        <v>3.03373</v>
+        <v>12.7967</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>3.40749</v>
+        <v>9.85507</v>
       </c>
       <c r="C24" t="n">
-        <v>3.63527</v>
+        <v>10.4014</v>
       </c>
       <c r="D24" t="n">
-        <v>13.1911</v>
+        <v>31.1107</v>
       </c>
       <c r="E24" t="n">
-        <v>2.86659</v>
+        <v>12.4055</v>
       </c>
       <c r="F24" t="n">
-        <v>3.0804</v>
+        <v>12.8216</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.44783</v>
+        <v>9.89476</v>
       </c>
       <c r="C25" t="n">
-        <v>3.69837</v>
+        <v>10.7241</v>
       </c>
       <c r="D25" t="n">
-        <v>13.6219</v>
+        <v>31.6571</v>
       </c>
       <c r="E25" t="n">
-        <v>2.88935</v>
+        <v>12.4456</v>
       </c>
       <c r="F25" t="n">
-        <v>3.1045</v>
+        <v>12.9363</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.5383</v>
+        <v>10.0524</v>
       </c>
       <c r="C26" t="n">
-        <v>3.7807</v>
+        <v>10.747</v>
       </c>
       <c r="D26" t="n">
-        <v>14.0445</v>
+        <v>32.0029</v>
       </c>
       <c r="E26" t="n">
-        <v>2.92465</v>
+        <v>12.4636</v>
       </c>
       <c r="F26" t="n">
-        <v>3.16828</v>
+        <v>13.0097</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.59229</v>
+        <v>10.0997</v>
       </c>
       <c r="C27" t="n">
-        <v>3.88506</v>
+        <v>10.8638</v>
       </c>
       <c r="D27" t="n">
-        <v>14.4965</v>
+        <v>33.0438</v>
       </c>
       <c r="E27" t="n">
-        <v>2.96914</v>
+        <v>12.5361</v>
       </c>
       <c r="F27" t="n">
-        <v>3.23001</v>
+        <v>13.112</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.73479</v>
+        <v>10.2957</v>
       </c>
       <c r="C28" t="n">
-        <v>4.02517</v>
+        <v>11.0878</v>
       </c>
       <c r="D28" t="n">
-        <v>14.9539</v>
+        <v>33.769</v>
       </c>
       <c r="E28" t="n">
-        <v>3.01557</v>
+        <v>12.6431</v>
       </c>
       <c r="F28" t="n">
-        <v>3.30547</v>
+        <v>13.2077</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.81271</v>
+        <v>10.4699</v>
       </c>
       <c r="C29" t="n">
-        <v>4.14516</v>
+        <v>11.317</v>
       </c>
       <c r="D29" t="n">
-        <v>15.341</v>
+        <v>34.0333</v>
       </c>
       <c r="E29" t="n">
-        <v>3.11839</v>
+        <v>12.7428</v>
       </c>
       <c r="F29" t="n">
-        <v>3.39382</v>
+        <v>13.3996</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>4.04979</v>
+        <v>10.6694</v>
       </c>
       <c r="C30" t="n">
-        <v>4.3189</v>
+        <v>11.6072</v>
       </c>
       <c r="D30" t="n">
-        <v>15.7651</v>
+        <v>34.9675</v>
       </c>
       <c r="E30" t="n">
-        <v>3.17989</v>
+        <v>12.8872</v>
       </c>
       <c r="F30" t="n">
-        <v>3.47713</v>
+        <v>13.5221</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.36568</v>
+        <v>10.9613</v>
       </c>
       <c r="C31" t="n">
-        <v>4.60123</v>
+        <v>11.9156</v>
       </c>
       <c r="D31" t="n">
-        <v>16.1598</v>
+        <v>36.3068</v>
       </c>
       <c r="E31" t="n">
-        <v>3.29024</v>
+        <v>13.0228</v>
       </c>
       <c r="F31" t="n">
-        <v>3.61595</v>
+        <v>13.7456</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.86249</v>
+        <v>11.3758</v>
       </c>
       <c r="C32" t="n">
-        <v>5.06398</v>
+        <v>12.388</v>
       </c>
       <c r="D32" t="n">
-        <v>16.4735</v>
+        <v>36.4821</v>
       </c>
       <c r="E32" t="n">
-        <v>3.41889</v>
+        <v>13.1921</v>
       </c>
       <c r="F32" t="n">
-        <v>3.76492</v>
+        <v>13.9503</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>5.47202</v>
+        <v>11.9318</v>
       </c>
       <c r="C33" t="n">
-        <v>5.67189</v>
+        <v>12.9156</v>
       </c>
       <c r="D33" t="n">
-        <v>16.8666</v>
+        <v>37.1592</v>
       </c>
       <c r="E33" t="n">
-        <v>3.63575</v>
+        <v>13.4701</v>
       </c>
       <c r="F33" t="n">
-        <v>3.97432</v>
+        <v>14.2338</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>6.49394</v>
+        <v>13.0511</v>
       </c>
       <c r="C34" t="n">
-        <v>6.64457</v>
+        <v>13.9694</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2887</v>
+        <v>37.8684</v>
       </c>
       <c r="E34" t="n">
-        <v>4.11413</v>
+        <v>13.9746</v>
       </c>
       <c r="F34" t="n">
-        <v>4.36739</v>
+        <v>14.7719</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>8.134219999999999</v>
+        <v>14.4722</v>
       </c>
       <c r="C35" t="n">
-        <v>8.034369999999999</v>
+        <v>15.5719</v>
       </c>
       <c r="D35" t="n">
-        <v>12.044</v>
+        <v>29.9645</v>
       </c>
       <c r="E35" t="n">
-        <v>4.96655</v>
+        <v>14.8476</v>
       </c>
       <c r="F35" t="n">
-        <v>5.13183</v>
+        <v>15.7225</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>10.2033</v>
+        <v>17.0274</v>
       </c>
       <c r="C36" t="n">
-        <v>10.2743</v>
+        <v>18.2124</v>
       </c>
       <c r="D36" t="n">
-        <v>12.5476</v>
+        <v>31.3869</v>
       </c>
       <c r="E36" t="n">
-        <v>6.44424</v>
+        <v>16.3206</v>
       </c>
       <c r="F36" t="n">
-        <v>6.44499</v>
+        <v>17.1911</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.6696</v>
+        <v>20.4563</v>
       </c>
       <c r="C37" t="n">
-        <v>13.7027</v>
+        <v>21.5912</v>
       </c>
       <c r="D37" t="n">
-        <v>13.0016</v>
+        <v>31.3633</v>
       </c>
       <c r="E37" t="n">
-        <v>2.87348</v>
+        <v>12.5714</v>
       </c>
       <c r="F37" t="n">
-        <v>3.12536</v>
+        <v>13.128</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>3.49137</v>
+        <v>10.0102</v>
       </c>
       <c r="C38" t="n">
-        <v>3.87064</v>
+        <v>10.7854</v>
       </c>
       <c r="D38" t="n">
-        <v>13.4858</v>
+        <v>32.2189</v>
       </c>
       <c r="E38" t="n">
-        <v>2.93889</v>
+        <v>12.6357</v>
       </c>
       <c r="F38" t="n">
-        <v>3.17949</v>
+        <v>13.2286</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.57896</v>
+        <v>10.0858</v>
       </c>
       <c r="C39" t="n">
-        <v>3.94094</v>
+        <v>10.8788</v>
       </c>
       <c r="D39" t="n">
-        <v>13.9738</v>
+        <v>33.703</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9697</v>
+        <v>12.5981</v>
       </c>
       <c r="F39" t="n">
-        <v>3.2222</v>
+        <v>13.3288</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.60114</v>
+        <v>10.154</v>
       </c>
       <c r="C40" t="n">
-        <v>4.04966</v>
+        <v>11.0136</v>
       </c>
       <c r="D40" t="n">
-        <v>14.3912</v>
+        <v>34.2249</v>
       </c>
       <c r="E40" t="n">
-        <v>3.00135</v>
+        <v>12.655</v>
       </c>
       <c r="F40" t="n">
-        <v>3.28101</v>
+        <v>13.3568</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.6885</v>
+        <v>10.2067</v>
       </c>
       <c r="C41" t="n">
-        <v>4.12872</v>
+        <v>11.1399</v>
       </c>
       <c r="D41" t="n">
-        <v>14.836</v>
+        <v>34.4313</v>
       </c>
       <c r="E41" t="n">
-        <v>3.04952</v>
+        <v>12.7848</v>
       </c>
       <c r="F41" t="n">
-        <v>3.34644</v>
+        <v>13.4188</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.82564</v>
+        <v>10.3975</v>
       </c>
       <c r="C42" t="n">
-        <v>4.25521</v>
+        <v>11.3179</v>
       </c>
       <c r="D42" t="n">
-        <v>15.257</v>
+        <v>35.6695</v>
       </c>
       <c r="E42" t="n">
-        <v>3.08675</v>
+        <v>12.8215</v>
       </c>
       <c r="F42" t="n">
-        <v>3.41689</v>
+        <v>13.5249</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.95681</v>
+        <v>10.5721</v>
       </c>
       <c r="C43" t="n">
-        <v>4.37797</v>
+        <v>11.5208</v>
       </c>
       <c r="D43" t="n">
-        <v>15.7081</v>
+        <v>36.5214</v>
       </c>
       <c r="E43" t="n">
-        <v>3.15095</v>
+        <v>12.8665</v>
       </c>
       <c r="F43" t="n">
-        <v>3.52099</v>
+        <v>13.5811</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>4.19554</v>
+        <v>10.7375</v>
       </c>
       <c r="C44" t="n">
-        <v>4.58277</v>
+        <v>11.7856</v>
       </c>
       <c r="D44" t="n">
-        <v>16.0513</v>
+        <v>36.9939</v>
       </c>
       <c r="E44" t="n">
-        <v>3.24461</v>
+        <v>13.0284</v>
       </c>
       <c r="F44" t="n">
-        <v>3.64009</v>
+        <v>13.7753</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.47916</v>
+        <v>11.0585</v>
       </c>
       <c r="C45" t="n">
-        <v>4.82009</v>
+        <v>12.1332</v>
       </c>
       <c r="D45" t="n">
-        <v>16.4673</v>
+        <v>37.6817</v>
       </c>
       <c r="E45" t="n">
-        <v>3.36926</v>
+        <v>13.196</v>
       </c>
       <c r="F45" t="n">
-        <v>3.75725</v>
+        <v>13.9882</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.87985</v>
+        <v>11.4958</v>
       </c>
       <c r="C46" t="n">
-        <v>5.17527</v>
+        <v>12.6683</v>
       </c>
       <c r="D46" t="n">
-        <v>16.8065</v>
+        <v>39.8625</v>
       </c>
       <c r="E46" t="n">
-        <v>3.55692</v>
+        <v>13.3644</v>
       </c>
       <c r="F46" t="n">
-        <v>3.94618</v>
+        <v>14.1672</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>5.45284</v>
+        <v>12.0777</v>
       </c>
       <c r="C47" t="n">
-        <v>5.71734</v>
+        <v>13.1718</v>
       </c>
       <c r="D47" t="n">
-        <v>17.1968</v>
+        <v>42.339</v>
       </c>
       <c r="E47" t="n">
-        <v>3.81807</v>
+        <v>13.6266</v>
       </c>
       <c r="F47" t="n">
-        <v>4.16342</v>
+        <v>14.4771</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>6.27785</v>
+        <v>13.0083</v>
       </c>
       <c r="C48" t="n">
-        <v>6.53921</v>
+        <v>14.2092</v>
       </c>
       <c r="D48" t="n">
-        <v>17.6341</v>
+        <v>40.9924</v>
       </c>
       <c r="E48" t="n">
-        <v>4.28533</v>
+        <v>14.1054</v>
       </c>
       <c r="F48" t="n">
-        <v>4.57613</v>
+        <v>15.0049</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>7.55323</v>
+        <v>14.333</v>
       </c>
       <c r="C49" t="n">
-        <v>7.74511</v>
+        <v>15.6043</v>
       </c>
       <c r="D49" t="n">
-        <v>18.0765</v>
+        <v>44.6943</v>
       </c>
       <c r="E49" t="n">
-        <v>4.96127</v>
+        <v>14.814</v>
       </c>
       <c r="F49" t="n">
-        <v>5.19841</v>
+        <v>15.7779</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>9.60445</v>
+        <v>16.3971</v>
       </c>
       <c r="C50" t="n">
-        <v>9.645149999999999</v>
+        <v>17.7301</v>
       </c>
       <c r="D50" t="n">
-        <v>12.6693</v>
+        <v>36.7188</v>
       </c>
       <c r="E50" t="n">
-        <v>6.05718</v>
+        <v>15.9782</v>
       </c>
       <c r="F50" t="n">
-        <v>6.13443</v>
+        <v>16.9742</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>12.6274</v>
+        <v>19.6993</v>
       </c>
       <c r="C51" t="n">
-        <v>12.6609</v>
+        <v>21.0729</v>
       </c>
       <c r="D51" t="n">
-        <v>13.1295</v>
+        <v>38.0033</v>
       </c>
       <c r="E51" t="n">
-        <v>3.22939</v>
+        <v>13.067</v>
       </c>
       <c r="F51" t="n">
-        <v>3.63069</v>
+        <v>13.6679</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>17.2046</v>
+        <v>24.9981</v>
       </c>
       <c r="C52" t="n">
-        <v>17.3007</v>
+        <v>26.5397</v>
       </c>
       <c r="D52" t="n">
-        <v>13.6212</v>
+        <v>39.4875</v>
       </c>
       <c r="E52" t="n">
-        <v>3.26195</v>
+        <v>13.5762</v>
       </c>
       <c r="F52" t="n">
-        <v>3.59241</v>
+        <v>13.9832</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.72118</v>
+        <v>10.5704</v>
       </c>
       <c r="C53" t="n">
-        <v>4.25294</v>
+        <v>11.713</v>
       </c>
       <c r="D53" t="n">
-        <v>14.081</v>
+        <v>40.5824</v>
       </c>
       <c r="E53" t="n">
-        <v>3.14547</v>
+        <v>13.2104</v>
       </c>
       <c r="F53" t="n">
-        <v>3.64835</v>
+        <v>14.214</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.76223</v>
+        <v>10.5084</v>
       </c>
       <c r="C54" t="n">
-        <v>4.35353</v>
+        <v>11.5394</v>
       </c>
       <c r="D54" t="n">
-        <v>14.5689</v>
+        <v>39.8402</v>
       </c>
       <c r="E54" t="n">
-        <v>3.29271</v>
+        <v>13.1167</v>
       </c>
       <c r="F54" t="n">
-        <v>3.73373</v>
+        <v>14.2114</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.87928</v>
+        <v>10.9322</v>
       </c>
       <c r="C55" t="n">
-        <v>4.44882</v>
+        <v>12.2655</v>
       </c>
       <c r="D55" t="n">
-        <v>15.0418</v>
+        <v>46.614</v>
       </c>
       <c r="E55" t="n">
-        <v>3.33217</v>
+        <v>13.2223</v>
       </c>
       <c r="F55" t="n">
-        <v>3.78042</v>
+        <v>14.3909</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.98941</v>
+        <v>10.8409</v>
       </c>
       <c r="C56" t="n">
-        <v>4.55193</v>
+        <v>11.8975</v>
       </c>
       <c r="D56" t="n">
-        <v>15.5132</v>
+        <v>47.5914</v>
       </c>
       <c r="E56" t="n">
-        <v>3.43248</v>
+        <v>13.2664</v>
       </c>
       <c r="F56" t="n">
-        <v>3.86615</v>
+        <v>14.0626</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>4.12156</v>
+        <v>10.9364</v>
       </c>
       <c r="C57" t="n">
-        <v>4.68048</v>
+        <v>12.6446</v>
       </c>
       <c r="D57" t="n">
-        <v>15.9899</v>
+        <v>54.0589</v>
       </c>
       <c r="E57" t="n">
-        <v>3.41394</v>
+        <v>14.0848</v>
       </c>
       <c r="F57" t="n">
-        <v>3.90464</v>
+        <v>14.495</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>4.33388</v>
+        <v>11.2758</v>
       </c>
       <c r="C58" t="n">
-        <v>4.84865</v>
+        <v>12.3588</v>
       </c>
       <c r="D58" t="n">
-        <v>16.4422</v>
+        <v>51.6314</v>
       </c>
       <c r="E58" t="n">
-        <v>3.4268</v>
+        <v>13.6285</v>
       </c>
       <c r="F58" t="n">
-        <v>3.96915</v>
+        <v>14.478</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>4.57155</v>
+        <v>11.142</v>
       </c>
       <c r="C59" t="n">
-        <v>5.07436</v>
+        <v>13.4767</v>
       </c>
       <c r="D59" t="n">
-        <v>16.8993</v>
+        <v>63.3473</v>
       </c>
       <c r="E59" t="n">
-        <v>3.56965</v>
+        <v>13.6467</v>
       </c>
       <c r="F59" t="n">
-        <v>4.16444</v>
+        <v>14.5738</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>5.06626</v>
+        <v>11.7384</v>
       </c>
       <c r="C60" t="n">
-        <v>5.40058</v>
+        <v>13.113</v>
       </c>
       <c r="D60" t="n">
-        <v>17.333</v>
+        <v>65.8789</v>
       </c>
       <c r="E60" t="n">
-        <v>3.78415</v>
+        <v>13.8791</v>
       </c>
       <c r="F60" t="n">
-        <v>4.29177</v>
+        <v>14.8454</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.55617</v>
+        <v>12.2522</v>
       </c>
       <c r="C61" t="n">
-        <v>6.04158</v>
+        <v>14.5561</v>
       </c>
       <c r="D61" t="n">
-        <v>17.8268</v>
+        <v>72.34529999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>4.15512</v>
+        <v>13.8835</v>
       </c>
       <c r="F61" t="n">
-        <v>4.52857</v>
+        <v>15.4894</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>6.23081</v>
+        <v>13.2244</v>
       </c>
       <c r="C62" t="n">
-        <v>6.68078</v>
+        <v>14.7406</v>
       </c>
       <c r="D62" t="n">
-        <v>18.2822</v>
+        <v>77.854</v>
       </c>
       <c r="E62" t="n">
-        <v>4.56212</v>
+        <v>14.5383</v>
       </c>
       <c r="F62" t="n">
-        <v>4.88957</v>
+        <v>15.7783</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>7.55306</v>
+        <v>14.302</v>
       </c>
       <c r="C63" t="n">
-        <v>7.89579</v>
+        <v>16.545</v>
       </c>
       <c r="D63" t="n">
-        <v>18.9849</v>
+        <v>88.0543</v>
       </c>
       <c r="E63" t="n">
-        <v>5.16185</v>
+        <v>15.0463</v>
       </c>
       <c r="F63" t="n">
-        <v>5.4804</v>
+        <v>16.6716</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>9.36735</v>
+        <v>16.2237</v>
       </c>
       <c r="C64" t="n">
-        <v>9.625080000000001</v>
+        <v>18.6308</v>
       </c>
       <c r="D64" t="n">
-        <v>14.4846</v>
+        <v>74.85939999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>6.02799</v>
+        <v>16.3269</v>
       </c>
       <c r="F64" t="n">
-        <v>6.36322</v>
+        <v>17.7118</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>12.242</v>
+        <v>18.977</v>
       </c>
       <c r="C65" t="n">
-        <v>12.4444</v>
+        <v>21.5262</v>
       </c>
       <c r="D65" t="n">
-        <v>15.2509</v>
+        <v>81.1904</v>
       </c>
       <c r="E65" t="n">
-        <v>7.76864</v>
+        <v>18.4112</v>
       </c>
       <c r="F65" t="n">
-        <v>7.97692</v>
+        <v>19.2196</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.8836</v>
+        <v>23.997</v>
       </c>
       <c r="C66" t="n">
-        <v>16.8858</v>
+        <v>25.3933</v>
       </c>
       <c r="D66" t="n">
-        <v>16.1358</v>
+        <v>86.4332</v>
       </c>
       <c r="E66" t="n">
-        <v>3.66272</v>
+        <v>15.1568</v>
       </c>
       <c r="F66" t="n">
-        <v>4.23174</v>
+        <v>15.9097</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>4.19521</v>
+        <v>12.2464</v>
       </c>
       <c r="C67" t="n">
-        <v>5.04051</v>
+        <v>13.978</v>
       </c>
       <c r="D67" t="n">
-        <v>17.1319</v>
+        <v>94.1058</v>
       </c>
       <c r="E67" t="n">
-        <v>3.69283</v>
+        <v>14.9435</v>
       </c>
       <c r="F67" t="n">
-        <v>4.29712</v>
+        <v>16.026</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>4.29291</v>
+        <v>12.392</v>
       </c>
       <c r="C68" t="n">
-        <v>5.19584</v>
+        <v>14.1128</v>
       </c>
       <c r="D68" t="n">
-        <v>17.9321</v>
+        <v>99.6952</v>
       </c>
       <c r="E68" t="n">
-        <v>3.73728</v>
+        <v>15.0847</v>
       </c>
       <c r="F68" t="n">
-        <v>4.36781</v>
+        <v>15.9263</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>4.37539</v>
+        <v>12.2831</v>
       </c>
       <c r="C69" t="n">
-        <v>5.27048</v>
+        <v>14.3715</v>
       </c>
       <c r="D69" t="n">
-        <v>18.8569</v>
+        <v>105.334</v>
       </c>
       <c r="E69" t="n">
-        <v>3.78789</v>
+        <v>15.0472</v>
       </c>
       <c r="F69" t="n">
-        <v>4.43534</v>
+        <v>15.5472</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>4.46848</v>
+        <v>12.467</v>
       </c>
       <c r="C70" t="n">
-        <v>5.42179</v>
+        <v>14.595</v>
       </c>
       <c r="D70" t="n">
-        <v>20.0657</v>
+        <v>111.277</v>
       </c>
       <c r="E70" t="n">
-        <v>3.78169</v>
+        <v>15.132</v>
       </c>
       <c r="F70" t="n">
-        <v>4.52139</v>
+        <v>16.2384</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>4.57266</v>
+        <v>12.6188</v>
       </c>
       <c r="C71" t="n">
-        <v>5.6124</v>
+        <v>14.8176</v>
       </c>
       <c r="D71" t="n">
-        <v>21.0428</v>
+        <v>118.77</v>
       </c>
       <c r="E71" t="n">
-        <v>3.87791</v>
+        <v>15.2478</v>
       </c>
       <c r="F71" t="n">
-        <v>4.54688</v>
+        <v>16.2032</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.75692</v>
+        <v>12.8093</v>
       </c>
       <c r="C72" t="n">
-        <v>5.86594</v>
+        <v>15.2019</v>
       </c>
       <c r="D72" t="n">
-        <v>22.4031</v>
+        <v>126.951</v>
       </c>
       <c r="E72" t="n">
-        <v>3.96791</v>
+        <v>15.4203</v>
       </c>
       <c r="F72" t="n">
-        <v>4.65871</v>
+        <v>16.6298</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>5.01414</v>
+        <v>13.0727</v>
       </c>
       <c r="C73" t="n">
-        <v>6.20941</v>
+        <v>15.1589</v>
       </c>
       <c r="D73" t="n">
-        <v>23.6359</v>
+        <v>137.583</v>
       </c>
       <c r="E73" t="n">
-        <v>4.05936</v>
+        <v>15.5579</v>
       </c>
       <c r="F73" t="n">
-        <v>4.85591</v>
+        <v>16.1261</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>5.38436</v>
+        <v>13.5411</v>
       </c>
       <c r="C74" t="n">
-        <v>6.58343</v>
+        <v>15.4628</v>
       </c>
       <c r="D74" t="n">
-        <v>24.9498</v>
+        <v>148.63</v>
       </c>
       <c r="E74" t="n">
-        <v>4.23903</v>
+        <v>15.7737</v>
       </c>
       <c r="F74" t="n">
-        <v>5.01466</v>
+        <v>16.942</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.87889</v>
+        <v>14.0643</v>
       </c>
       <c r="C75" t="n">
-        <v>7.23003</v>
+        <v>16.3138</v>
       </c>
       <c r="D75" t="n">
-        <v>26.1883</v>
+        <v>162.518</v>
       </c>
       <c r="E75" t="n">
-        <v>4.46959</v>
+        <v>16.203</v>
       </c>
       <c r="F75" t="n">
-        <v>5.21455</v>
+        <v>17.3638</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>6.5995</v>
+        <v>14.8935</v>
       </c>
       <c r="C76" t="n">
-        <v>8.21312</v>
+        <v>18.6797</v>
       </c>
       <c r="D76" t="n">
-        <v>27.6544</v>
+        <v>150.504</v>
       </c>
       <c r="E76" t="n">
-        <v>4.8016</v>
+        <v>16.3391</v>
       </c>
       <c r="F76" t="n">
-        <v>5.66423</v>
+        <v>17.9681</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>7.77343</v>
+        <v>15.8512</v>
       </c>
       <c r="C77" t="n">
-        <v>9.733169999999999</v>
+        <v>20.4127</v>
       </c>
       <c r="D77" t="n">
-        <v>28.9414</v>
+        <v>158.474</v>
       </c>
       <c r="E77" t="n">
-        <v>5.34096</v>
+        <v>16.9481</v>
       </c>
       <c r="F77" t="n">
-        <v>6.23491</v>
+        <v>18.6948</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>9.32494</v>
+        <v>17.6678</v>
       </c>
       <c r="C78" t="n">
-        <v>11.6752</v>
+        <v>23.5582</v>
       </c>
       <c r="D78" t="n">
-        <v>24.4801</v>
+        <v>127.809</v>
       </c>
       <c r="E78" t="n">
-        <v>6.21311</v>
+        <v>17.8945</v>
       </c>
       <c r="F78" t="n">
-        <v>7.18299</v>
+        <v>19.8914</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>12.0922</v>
+        <v>20.0059</v>
       </c>
       <c r="C79" t="n">
-        <v>15.075</v>
+        <v>28.2921</v>
       </c>
       <c r="D79" t="n">
-        <v>25.6188</v>
+        <v>134.225</v>
       </c>
       <c r="E79" t="n">
-        <v>7.73309</v>
+        <v>19.7559</v>
       </c>
       <c r="F79" t="n">
-        <v>8.76534</v>
+        <v>21.9339</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.2706</v>
+        <v>23.9581</v>
       </c>
       <c r="C80" t="n">
-        <v>19.9269</v>
+        <v>34.344</v>
       </c>
       <c r="D80" t="n">
-        <v>26.9074</v>
+        <v>149.173</v>
       </c>
       <c r="E80" t="n">
-        <v>4.01353</v>
+        <v>16.6282</v>
       </c>
       <c r="F80" t="n">
-        <v>4.72856</v>
+        <v>16.8256</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.9312</v>
+        <v>12.8581</v>
       </c>
       <c r="C81" t="n">
-        <v>6.78614</v>
+        <v>16.2232</v>
       </c>
       <c r="D81" t="n">
-        <v>28.2648</v>
+        <v>143.15</v>
       </c>
       <c r="E81" t="n">
-        <v>4.19792</v>
+        <v>16.694</v>
       </c>
       <c r="F81" t="n">
-        <v>4.98401</v>
+        <v>17.5467</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>5.05853</v>
+        <v>13.6569</v>
       </c>
       <c r="C82" t="n">
-        <v>7.21024</v>
+        <v>17.1738</v>
       </c>
       <c r="D82" t="n">
-        <v>29.6341</v>
+        <v>159.001</v>
       </c>
       <c r="E82" t="n">
-        <v>4.25455</v>
+        <v>16.788</v>
       </c>
       <c r="F82" t="n">
-        <v>5.1465</v>
+        <v>17.5722</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>5.26874</v>
+        <v>13.0401</v>
       </c>
       <c r="C83" t="n">
-        <v>7.72844</v>
+        <v>17.7858</v>
       </c>
       <c r="D83" t="n">
-        <v>31.0485</v>
+        <v>152.82</v>
       </c>
       <c r="E83" t="n">
-        <v>4.33785</v>
+        <v>16.8358</v>
       </c>
       <c r="F83" t="n">
-        <v>5.35678</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>5.5362</v>
+        <v>14.1676</v>
       </c>
       <c r="C84" t="n">
-        <v>8.27449</v>
+        <v>18.6814</v>
       </c>
       <c r="D84" t="n">
-        <v>32.5091</v>
+        <v>161.899</v>
       </c>
       <c r="E84" t="n">
-        <v>4.43623</v>
+        <v>16.9025</v>
       </c>
       <c r="F84" t="n">
-        <v>5.57128</v>
+        <v>17.9827</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>5.87419</v>
+        <v>13.2928</v>
       </c>
       <c r="C85" t="n">
-        <v>8.95147</v>
+        <v>20.0065</v>
       </c>
       <c r="D85" t="n">
-        <v>34.0632</v>
+        <v>163.314</v>
       </c>
       <c r="E85" t="n">
-        <v>4.60649</v>
+        <v>16.9923</v>
       </c>
       <c r="F85" t="n">
-        <v>5.91585</v>
+        <v>18.3903</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>6.203</v>
+        <v>13.6475</v>
       </c>
       <c r="C86" t="n">
-        <v>9.58498</v>
+        <v>20.9329</v>
       </c>
       <c r="D86" t="n">
-        <v>35.6158</v>
+        <v>168.26</v>
       </c>
       <c r="E86" t="n">
-        <v>4.80443</v>
+        <v>17.1585</v>
       </c>
       <c r="F86" t="n">
-        <v>6.33213</v>
+        <v>18.9894</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>6.62956</v>
+        <v>14.9392</v>
       </c>
       <c r="C87" t="n">
-        <v>10.4336</v>
+        <v>22.8903</v>
       </c>
       <c r="D87" t="n">
-        <v>37.374</v>
+        <v>197.702</v>
       </c>
       <c r="E87" t="n">
-        <v>4.97177</v>
+        <v>17.399</v>
       </c>
       <c r="F87" t="n">
-        <v>6.74292</v>
+        <v>19.3884</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>7.11154</v>
+        <v>15.2879</v>
       </c>
       <c r="C88" t="n">
-        <v>11.3938</v>
+        <v>25.1767</v>
       </c>
       <c r="D88" t="n">
-        <v>39.0978</v>
+        <v>180.087</v>
       </c>
       <c r="E88" t="n">
-        <v>5.19047</v>
+        <v>17.7192</v>
       </c>
       <c r="F88" t="n">
-        <v>7.242</v>
+        <v>20.0868</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>7.89965</v>
+        <v>16.028</v>
       </c>
       <c r="C89" t="n">
-        <v>12.4547</v>
+        <v>26.5406</v>
       </c>
       <c r="D89" t="n">
-        <v>40.8592</v>
+        <v>194.148</v>
       </c>
       <c r="E89" t="n">
-        <v>5.5976</v>
+        <v>17.8662</v>
       </c>
       <c r="F89" t="n">
-        <v>7.85837</v>
+        <v>21.3411</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>8.5753</v>
+        <v>17.1675</v>
       </c>
       <c r="C90" t="n">
-        <v>13.6141</v>
+        <v>29.2621</v>
       </c>
       <c r="D90" t="n">
-        <v>42.8219</v>
+        <v>191.319</v>
       </c>
       <c r="E90" t="n">
-        <v>6.13568</v>
+        <v>18.4776</v>
       </c>
       <c r="F90" t="n">
-        <v>8.59117</v>
+        <v>22.4486</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>10.1523</v>
+        <v>18.566</v>
       </c>
       <c r="C91" t="n">
-        <v>15.3639</v>
+        <v>31.2116</v>
       </c>
       <c r="D91" t="n">
-        <v>44.7927</v>
+        <v>201.15</v>
       </c>
       <c r="E91" t="n">
-        <v>6.77529</v>
+        <v>19.2803</v>
       </c>
       <c r="F91" t="n">
-        <v>9.641389999999999</v>
+        <v>24.3606</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>11.8791</v>
+        <v>20.268</v>
       </c>
       <c r="C92" t="n">
-        <v>17.7364</v>
+        <v>35.2803</v>
       </c>
       <c r="D92" t="n">
-        <v>36.6577</v>
+        <v>157.923</v>
       </c>
       <c r="E92" t="n">
-        <v>7.78397</v>
+        <v>20.3799</v>
       </c>
       <c r="F92" t="n">
-        <v>11.0085</v>
+        <v>26.0682</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>14.5513</v>
+        <v>23.8106</v>
       </c>
       <c r="C93" t="n">
-        <v>21.1207</v>
+        <v>39.8468</v>
       </c>
       <c r="D93" t="n">
-        <v>37.891</v>
+        <v>161.97</v>
       </c>
       <c r="E93" t="n">
-        <v>9.41502</v>
+        <v>21.5553</v>
       </c>
       <c r="F93" t="n">
-        <v>12.6525</v>
+        <v>29.2311</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>18.2205</v>
+        <v>28.6583</v>
       </c>
       <c r="C94" t="n">
-        <v>25.7609</v>
+        <v>47.4375</v>
       </c>
       <c r="D94" t="n">
-        <v>39.0993</v>
+        <v>166.058</v>
       </c>
       <c r="E94" t="n">
-        <v>5.25537</v>
+        <v>17.3179</v>
       </c>
       <c r="F94" t="n">
-        <v>7.09076</v>
+        <v>20.4845</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>6.968</v>
+        <v>15.5146</v>
       </c>
       <c r="C95" t="n">
-        <v>10.898</v>
+        <v>23.6306</v>
       </c>
       <c r="D95" t="n">
-        <v>40.4284</v>
+        <v>170.525</v>
       </c>
       <c r="E95" t="n">
-        <v>5.41642</v>
+        <v>17.8521</v>
       </c>
       <c r="F95" t="n">
-        <v>7.36236</v>
+        <v>21.0343</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>7.30584</v>
+        <v>16.0746</v>
       </c>
       <c r="C96" t="n">
-        <v>11.4352</v>
+        <v>24.8459</v>
       </c>
       <c r="D96" t="n">
-        <v>41.7539</v>
+        <v>172.285</v>
       </c>
       <c r="E96" t="n">
-        <v>5.60568</v>
+        <v>17.7368</v>
       </c>
       <c r="F96" t="n">
-        <v>7.71286</v>
+        <v>21.1927</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>7.59591</v>
+        <v>15.9783</v>
       </c>
       <c r="C97" t="n">
-        <v>11.978</v>
+        <v>27.2699</v>
       </c>
       <c r="D97" t="n">
-        <v>43.1502</v>
+        <v>179.184</v>
       </c>
       <c r="E97" t="n">
-        <v>5.82578</v>
+        <v>18.2801</v>
       </c>
       <c r="F97" t="n">
-        <v>8.06786</v>
+        <v>21.8752</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>7.95264</v>
+        <v>17.2638</v>
       </c>
       <c r="C98" t="n">
-        <v>12.6348</v>
+        <v>26.6638</v>
       </c>
       <c r="D98" t="n">
-        <v>44.5353</v>
+        <v>183.763</v>
       </c>
       <c r="E98" t="n">
-        <v>6.00412</v>
+        <v>18.5814</v>
       </c>
       <c r="F98" t="n">
-        <v>8.42792</v>
+        <v>23.5205</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>8.338900000000001</v>
+        <v>17.9749</v>
       </c>
       <c r="C99" t="n">
-        <v>13.4257</v>
+        <v>27.9386</v>
       </c>
       <c r="D99" t="n">
-        <v>46.0501</v>
+        <v>188.991</v>
       </c>
       <c r="E99" t="n">
-        <v>6.22898</v>
+        <v>19.0996</v>
       </c>
       <c r="F99" t="n">
-        <v>8.83141</v>
+        <v>23.7602</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>8.70459</v>
+        <v>18.349</v>
       </c>
       <c r="C100" t="n">
-        <v>14.2826</v>
+        <v>28.416</v>
       </c>
       <c r="D100" t="n">
-        <v>47.6578</v>
+        <v>194.831</v>
       </c>
       <c r="E100" t="n">
-        <v>6.38594</v>
+        <v>19.1795</v>
       </c>
       <c r="F100" t="n">
-        <v>9.178699999999999</v>
+        <v>25.3765</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>9.14359</v>
+        <v>18.9913</v>
       </c>
       <c r="C101" t="n">
-        <v>15.3433</v>
+        <v>30.1648</v>
       </c>
       <c r="D101" t="n">
-        <v>49.2856</v>
+        <v>199.702</v>
       </c>
       <c r="E101" t="n">
-        <v>6.65436</v>
+        <v>19.6221</v>
       </c>
       <c r="F101" t="n">
-        <v>9.52947</v>
+        <v>25.3765</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>9.64321</v>
+        <v>20.3886</v>
       </c>
       <c r="C102" t="n">
-        <v>16.4625</v>
+        <v>32.6093</v>
       </c>
       <c r="D102" t="n">
-        <v>51.0419</v>
+        <v>211.426</v>
       </c>
       <c r="E102" t="n">
-        <v>6.95324</v>
+        <v>20.1037</v>
       </c>
       <c r="F102" t="n">
-        <v>10.0765</v>
+        <v>26.3052</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>10.3756</v>
+        <v>21.7172</v>
       </c>
       <c r="C103" t="n">
-        <v>17.7696</v>
+        <v>33.295</v>
       </c>
       <c r="D103" t="n">
-        <v>52.906</v>
+        <v>212.11</v>
       </c>
       <c r="E103" t="n">
-        <v>7.33294</v>
+        <v>21.0943</v>
       </c>
       <c r="F103" t="n">
-        <v>10.697</v>
+        <v>27.0425</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>11.2759</v>
+        <v>22.964</v>
       </c>
       <c r="C104" t="n">
-        <v>19.3084</v>
+        <v>34.917</v>
       </c>
       <c r="D104" t="n">
-        <v>54.7203</v>
+        <v>245.237</v>
       </c>
       <c r="E104" t="n">
-        <v>7.6099</v>
+        <v>21.8324</v>
       </c>
       <c r="F104" t="n">
-        <v>11.5282</v>
+        <v>28.0169</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>12.5096</v>
+        <v>24.6071</v>
       </c>
       <c r="C105" t="n">
-        <v>21.1278</v>
+        <v>37.0279</v>
       </c>
       <c r="D105" t="n">
-        <v>56.6124</v>
+        <v>250.316</v>
       </c>
       <c r="E105" t="n">
-        <v>8.381629999999999</v>
+        <v>22.8355</v>
       </c>
       <c r="F105" t="n">
-        <v>12.5806</v>
+        <v>29.3906</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>14.2323</v>
+        <v>26.6996</v>
       </c>
       <c r="C106" t="n">
-        <v>23.3886</v>
+        <v>40.0413</v>
       </c>
       <c r="D106" t="n">
-        <v>58.6572</v>
+        <v>256.684</v>
       </c>
       <c r="E106" t="n">
-        <v>9.293419999999999</v>
+        <v>24.0499</v>
       </c>
       <c r="F106" t="n">
-        <v>14.101</v>
+        <v>31.0648</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>16.678</v>
+        <v>29.3645</v>
       </c>
       <c r="C107" t="n">
-        <v>26.3176</v>
+        <v>47.0051</v>
       </c>
       <c r="D107" t="n">
-        <v>44.6185</v>
+        <v>175.809</v>
       </c>
       <c r="E107" t="n">
-        <v>10.7608</v>
+        <v>24.8574</v>
       </c>
       <c r="F107" t="n">
-        <v>16.2438</v>
+        <v>33.9269</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>20.0694</v>
+        <v>34.8562</v>
       </c>
       <c r="C108" t="n">
-        <v>30.7816</v>
+        <v>55.3428</v>
       </c>
       <c r="D108" t="n">
-        <v>45.7746</v>
+        <v>180.42</v>
       </c>
       <c r="E108" t="n">
-        <v>5.9795</v>
+        <v>19.9086</v>
       </c>
       <c r="F108" t="n">
-        <v>8.76972</v>
+        <v>24.3653</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>24.9795</v>
+        <v>42.4727</v>
       </c>
       <c r="C109" t="n">
-        <v>37.6642</v>
+        <v>65.9847</v>
       </c>
       <c r="D109" t="n">
-        <v>46.9261</v>
+        <v>184.801</v>
       </c>
       <c r="E109" t="n">
-        <v>6.22805</v>
+        <v>20.6323</v>
       </c>
       <c r="F109" t="n">
-        <v>9.157489999999999</v>
+        <v>24.7676</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>8.525169999999999</v>
+        <v>19.7132</v>
       </c>
       <c r="C110" t="n">
-        <v>15.3253</v>
+        <v>29.5848</v>
       </c>
       <c r="D110" t="n">
-        <v>48.1842</v>
+        <v>188.213</v>
       </c>
       <c r="E110" t="n">
-        <v>6.38062</v>
+        <v>20.8863</v>
       </c>
       <c r="F110" t="n">
-        <v>9.349460000000001</v>
+        <v>25.2204</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>8.889139999999999</v>
+        <v>20.7443</v>
       </c>
       <c r="C111" t="n">
-        <v>15.9595</v>
+        <v>30.4337</v>
       </c>
       <c r="D111" t="n">
-        <v>49.4376</v>
+        <v>193.33</v>
       </c>
       <c r="E111" t="n">
-        <v>6.52919</v>
+        <v>20.6752</v>
       </c>
       <c r="F111" t="n">
-        <v>9.990069999999999</v>
+        <v>25.6623</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>9.190110000000001</v>
+        <v>20.6479</v>
       </c>
       <c r="C112" t="n">
-        <v>16.5549</v>
+        <v>31.2176</v>
       </c>
       <c r="D112" t="n">
-        <v>50.8502</v>
+        <v>198.487</v>
       </c>
       <c r="E112" t="n">
-        <v>6.71736</v>
+        <v>21.3369</v>
       </c>
       <c r="F112" t="n">
-        <v>10.5039</v>
+        <v>26.0272</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>9.61955</v>
+        <v>21.7891</v>
       </c>
       <c r="C113" t="n">
-        <v>17.1823</v>
+        <v>32.2438</v>
       </c>
       <c r="D113" t="n">
-        <v>52.2136</v>
+        <v>203.136</v>
       </c>
       <c r="E113" t="n">
-        <v>6.92466</v>
+        <v>21.6201</v>
       </c>
       <c r="F113" t="n">
-        <v>11.1286</v>
+        <v>26.5121</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>10.2455</v>
+        <v>22.3409</v>
       </c>
       <c r="C114" t="n">
-        <v>17.8761</v>
+        <v>33.0654</v>
       </c>
       <c r="D114" t="n">
-        <v>53.7522</v>
+        <v>208.246</v>
       </c>
       <c r="E114" t="n">
-        <v>7.28251</v>
+        <v>21.9143</v>
       </c>
       <c r="F114" t="n">
-        <v>11.7441</v>
+        <v>26.3317</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>10.7422</v>
+        <v>22.9596</v>
       </c>
       <c r="C115" t="n">
-        <v>18.6247</v>
+        <v>34.3151</v>
       </c>
       <c r="D115" t="n">
-        <v>54.9627</v>
+        <v>214.156</v>
       </c>
       <c r="E115" t="n">
-        <v>7.61094</v>
+        <v>22.2277</v>
       </c>
       <c r="F115" t="n">
-        <v>12.3869</v>
+        <v>26.8969</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>11.3857</v>
+        <v>23.5821</v>
       </c>
       <c r="C116" t="n">
-        <v>19.4345</v>
+        <v>35.6179</v>
       </c>
       <c r="D116" t="n">
-        <v>56.6116</v>
+        <v>219.48</v>
       </c>
       <c r="E116" t="n">
-        <v>7.98617</v>
+        <v>22.6872</v>
       </c>
       <c r="F116" t="n">
-        <v>13.0114</v>
+        <v>27.5699</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>12.2803</v>
+        <v>24.6148</v>
       </c>
       <c r="C117" t="n">
-        <v>20.4329</v>
+        <v>37.2121</v>
       </c>
       <c r="D117" t="n">
-        <v>58.8678</v>
+        <v>226.803</v>
       </c>
       <c r="E117" t="n">
-        <v>8.292310000000001</v>
+        <v>23.1488</v>
       </c>
       <c r="F117" t="n">
-        <v>13.7094</v>
+        <v>30.2782</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>13.214</v>
+        <v>25.7921</v>
       </c>
       <c r="C118" t="n">
-        <v>21.6585</v>
+        <v>37.9742</v>
       </c>
       <c r="D118" t="n">
-        <v>60.703</v>
+        <v>248.497</v>
       </c>
       <c r="E118" t="n">
-        <v>8.912459999999999</v>
+        <v>23.7444</v>
       </c>
       <c r="F118" t="n">
-        <v>14.4479</v>
+        <v>30.1969</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>14.4344</v>
+        <v>27.3556</v>
       </c>
       <c r="C119" t="n">
-        <v>23.2613</v>
+        <v>40.4376</v>
       </c>
       <c r="D119" t="n">
-        <v>62.398</v>
+        <v>239.892</v>
       </c>
       <c r="E119" t="n">
-        <v>9.86666</v>
+        <v>24.5507</v>
       </c>
       <c r="F119" t="n">
-        <v>15.4102</v>
+        <v>31.3764</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>15.9424</v>
+        <v>29.603</v>
       </c>
       <c r="C120" t="n">
-        <v>25.3441</v>
+        <v>45.3785</v>
       </c>
       <c r="D120" t="n">
-        <v>64.7843</v>
+        <v>268.566</v>
       </c>
       <c r="E120" t="n">
-        <v>10.606</v>
+        <v>25.7122</v>
       </c>
       <c r="F120" t="n">
-        <v>16.5989</v>
+        <v>32.4018</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>18.0246</v>
+        <v>32.7901</v>
       </c>
       <c r="C121" t="n">
-        <v>28.2775</v>
+        <v>49.6014</v>
       </c>
       <c r="D121" t="n">
-        <v>48.062</v>
+        <v>183.526</v>
       </c>
       <c r="E121" t="n">
-        <v>12.0609</v>
+        <v>27.4446</v>
       </c>
       <c r="F121" t="n">
-        <v>18.3561</v>
+        <v>36.2265</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>20.9583</v>
+        <v>37.4899</v>
       </c>
       <c r="C122" t="n">
-        <v>32.6108</v>
+        <v>58.4093</v>
       </c>
       <c r="D122" t="n">
-        <v>48.8095</v>
+        <v>189.053</v>
       </c>
       <c r="E122" t="n">
-        <v>14.2458</v>
+        <v>29.5861</v>
       </c>
       <c r="F122" t="n">
-        <v>21.1652</v>
+        <v>40.7575</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>25.2705</v>
+        <v>44.8217</v>
       </c>
       <c r="C123" t="n">
-        <v>39.3367</v>
+        <v>70.7375</v>
       </c>
       <c r="D123" t="n">
-        <v>50.3854</v>
+        <v>193.599</v>
       </c>
       <c r="E123" t="n">
-        <v>8.25484</v>
+        <v>21.159</v>
       </c>
       <c r="F123" t="n">
-        <v>12.0769</v>
+        <v>30.3647</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>11.0282</v>
+        <v>22.3859</v>
       </c>
       <c r="C124" t="n">
-        <v>17.733</v>
+        <v>33.7597</v>
       </c>
       <c r="D124" t="n">
-        <v>51.5876</v>
+        <v>196.798</v>
       </c>
       <c r="E124" t="n">
-        <v>8.468669999999999</v>
+        <v>22.7179</v>
       </c>
       <c r="F124" t="n">
-        <v>12.3702</v>
+        <v>27.3689</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>11.5618</v>
+        <v>23.2244</v>
       </c>
       <c r="C125" t="n">
-        <v>17.8919</v>
+        <v>34.3622</v>
       </c>
       <c r="D125" t="n">
-        <v>52.4815</v>
+        <v>201.465</v>
       </c>
       <c r="E125" t="n">
-        <v>9.60965</v>
+        <v>24.0125</v>
       </c>
       <c r="F125" t="n">
-        <v>13.5964</v>
+        <v>28.9202</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>11.5676</v>
+        <v>23.2732</v>
       </c>
       <c r="C126" t="n">
-        <v>18.7541</v>
+        <v>36.9832</v>
       </c>
       <c r="D126" t="n">
-        <v>54.2567</v>
+        <v>206.11</v>
       </c>
       <c r="E126" t="n">
-        <v>9.014699999999999</v>
+        <v>22.8437</v>
       </c>
       <c r="F126" t="n">
-        <v>13.1756</v>
+        <v>29.5044</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>11.9574</v>
+        <v>23.6603</v>
       </c>
       <c r="C127" t="n">
-        <v>18.7168</v>
+        <v>38.3339</v>
       </c>
       <c r="D127" t="n">
-        <v>55.6007</v>
+        <v>211.964</v>
       </c>
       <c r="E127" t="n">
-        <v>9.40738</v>
+        <v>23.8651</v>
       </c>
       <c r="F127" t="n">
-        <v>14.225</v>
+        <v>28.8645</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>12.1968</v>
+        <v>23.9231</v>
       </c>
       <c r="C128" t="n">
-        <v>20.0921</v>
+        <v>38.4797</v>
       </c>
       <c r="D128" t="n">
-        <v>57.126</v>
+        <v>216.369</v>
       </c>
       <c r="E128" t="n">
-        <v>9.21575</v>
+        <v>23.3857</v>
       </c>
       <c r="F128" t="n">
-        <v>14.044</v>
+        <v>30.9617</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>12.6937</v>
+        <v>24.3667</v>
       </c>
       <c r="C129" t="n">
-        <v>20.4983</v>
+        <v>40.8902</v>
       </c>
       <c r="D129" t="n">
-        <v>58.7446</v>
+        <v>233.286</v>
       </c>
       <c r="E129" t="n">
-        <v>9.83962</v>
+        <v>22.5273</v>
       </c>
       <c r="F129" t="n">
-        <v>14.5314</v>
+        <v>31.0075</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>13.1116</v>
+        <v>26.452</v>
       </c>
       <c r="C130" t="n">
-        <v>20.8467</v>
+        <v>41.6499</v>
       </c>
       <c r="D130" t="n">
-        <v>60.4147</v>
+        <v>238.049</v>
       </c>
       <c r="E130" t="n">
-        <v>9.65272</v>
+        <v>23.8375</v>
       </c>
       <c r="F130" t="n">
-        <v>14.7229</v>
+        <v>31.8938</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>13.908</v>
+        <v>26.8456</v>
       </c>
       <c r="C131" t="n">
-        <v>22.3973</v>
+        <v>47.8053</v>
       </c>
       <c r="D131" t="n">
-        <v>62.2152</v>
+        <v>250.543</v>
       </c>
       <c r="E131" t="n">
-        <v>10.3763</v>
+        <v>23.4655</v>
       </c>
       <c r="F131" t="n">
-        <v>15.469</v>
+        <v>33.562</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.3501</v>
+        <v>29.5105</v>
       </c>
       <c r="C132" t="n">
-        <v>23.5582</v>
+        <v>48.6433</v>
       </c>
       <c r="D132" t="n">
-        <v>64.13249999999999</v>
+        <v>256.285</v>
       </c>
       <c r="E132" t="n">
-        <v>10.5674</v>
+        <v>25.5864</v>
       </c>
       <c r="F132" t="n">
-        <v>16.0776</v>
+        <v>34.8647</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>15.5112</v>
+        <v>30.0519</v>
       </c>
       <c r="C133" t="n">
-        <v>25.1326</v>
+        <v>50.5884</v>
       </c>
       <c r="D133" t="n">
-        <v>66.158</v>
+        <v>262.644</v>
       </c>
       <c r="E133" t="n">
-        <v>11.3315</v>
+        <v>26.2887</v>
       </c>
       <c r="F133" t="n">
-        <v>17.3247</v>
+        <v>37.4474</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>17.029</v>
+        <v>37.8094</v>
       </c>
       <c r="C134" t="n">
-        <v>26.9703</v>
+        <v>54.0373</v>
       </c>
       <c r="D134" t="n">
-        <v>68.3015</v>
+        <v>263.215</v>
       </c>
       <c r="E134" t="n">
-        <v>12.1883</v>
+        <v>27.4113</v>
       </c>
       <c r="F134" t="n">
-        <v>18.2933</v>
+        <v>38.9312</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>18.6951</v>
+        <v>34.7333</v>
       </c>
       <c r="C135" t="n">
-        <v>29.7929</v>
+        <v>59.3878</v>
       </c>
       <c r="D135" t="n">
-        <v>49.7713</v>
+        <v>188.727</v>
       </c>
       <c r="E135" t="n">
-        <v>12.8514</v>
+        <v>28.1131</v>
       </c>
       <c r="F135" t="n">
-        <v>19.9201</v>
+        <v>40.4233</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>21.4935</v>
+        <v>39.1433</v>
       </c>
       <c r="C136" t="n">
-        <v>33.9181</v>
+        <v>64.5278</v>
       </c>
       <c r="D136" t="n">
-        <v>50.9183</v>
+        <v>193.186</v>
       </c>
       <c r="E136" t="n">
-        <v>15.0627</v>
+        <v>31.7123</v>
       </c>
       <c r="F136" t="n">
-        <v>22.4463</v>
+        <v>40.5744</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>25.0064</v>
+        <v>46.7386</v>
       </c>
       <c r="C137" t="n">
-        <v>40.2322</v>
+        <v>80.3263</v>
       </c>
       <c r="D137" t="n">
-        <v>52.3359</v>
+        <v>200.67</v>
       </c>
       <c r="E137" t="n">
-        <v>15.9233</v>
+        <v>41.2508</v>
       </c>
       <c r="F137" t="n">
-        <v>19.5411</v>
+        <v>51.1596</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.701</v>
+        <v>47.1996</v>
       </c>
       <c r="C138" t="n">
-        <v>24.4034</v>
+        <v>60.0908</v>
       </c>
       <c r="D138" t="n">
-        <v>53.274</v>
+        <v>203.974</v>
       </c>
       <c r="E138" t="n">
-        <v>16.5307</v>
+        <v>41.7163</v>
       </c>
       <c r="F138" t="n">
-        <v>20.8653</v>
+        <v>51.3046</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>18.4836</v>
+        <v>44.7297</v>
       </c>
       <c r="C139" t="n">
-        <v>25.68</v>
+        <v>60.6764</v>
       </c>
       <c r="D139" t="n">
-        <v>54.8453</v>
+        <v>208.304</v>
       </c>
       <c r="E139" t="n">
-        <v>16.8882</v>
+        <v>43.0861</v>
       </c>
       <c r="F139" t="n">
-        <v>20.9772</v>
+        <v>52.6418</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>19.1791</v>
+        <v>44.3962</v>
       </c>
       <c r="C140" t="n">
-        <v>26.0652</v>
+        <v>61.894</v>
       </c>
       <c r="D140" t="n">
-        <v>56.1461</v>
+        <v>212.958</v>
       </c>
       <c r="E140" t="n">
-        <v>17.0439</v>
+        <v>42.0883</v>
       </c>
       <c r="F140" t="n">
-        <v>21.4367</v>
+        <v>55.3245</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>18.9638</v>
+        <v>45.9353</v>
       </c>
       <c r="C141" t="n">
-        <v>26.6267</v>
+        <v>62.7536</v>
       </c>
       <c r="D141" t="n">
-        <v>57.5582</v>
+        <v>218.099</v>
       </c>
       <c r="E141" t="n">
-        <v>16.6915</v>
+        <v>41.4683</v>
       </c>
       <c r="F141" t="n">
-        <v>21.2055</v>
+        <v>55.6804</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>19.5616</v>
+        <v>46.8927</v>
       </c>
       <c r="C142" t="n">
-        <v>27.2934</v>
+        <v>61.5344</v>
       </c>
       <c r="D142" t="n">
-        <v>59.0552</v>
+        <v>222.869</v>
       </c>
       <c r="E142" t="n">
-        <v>17.3691</v>
+        <v>44.2852</v>
       </c>
       <c r="F142" t="n">
-        <v>22.3025</v>
+        <v>55.1329</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>19.6806</v>
+        <v>47.3903</v>
       </c>
       <c r="C143" t="n">
-        <v>27.8645</v>
+        <v>65.7559</v>
       </c>
       <c r="D143" t="n">
-        <v>60.365</v>
+        <v>227.042</v>
       </c>
       <c r="E143" t="n">
-        <v>17.6671</v>
+        <v>42.2987</v>
       </c>
       <c r="F143" t="n">
-        <v>21.954</v>
+        <v>54.7062</v>
       </c>
     </row>
   </sheetData>

--- a/clang-x64/Scattered unsuccessful looukp.xlsx
+++ b/clang-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>10.4541</v>
+        <v>3.27878</v>
       </c>
       <c r="C2" t="n">
-        <v>10.5222</v>
+        <v>3.38829</v>
       </c>
       <c r="D2" t="n">
-        <v>29.352</v>
+        <v>14.23</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5963</v>
+        <v>2.9511</v>
       </c>
       <c r="F2" t="n">
-        <v>13.0754</v>
+        <v>3.1017</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>10.849</v>
+        <v>3.36551</v>
       </c>
       <c r="C3" t="n">
-        <v>10.9587</v>
+        <v>3.81206</v>
       </c>
       <c r="D3" t="n">
-        <v>29.9124</v>
+        <v>14.6762</v>
       </c>
       <c r="E3" t="n">
-        <v>12.6907</v>
+        <v>2.99756</v>
       </c>
       <c r="F3" t="n">
-        <v>13.1716</v>
+        <v>3.13877</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>11.3574</v>
+        <v>3.63929</v>
       </c>
       <c r="C4" t="n">
-        <v>11.3947</v>
+        <v>4.11438</v>
       </c>
       <c r="D4" t="n">
-        <v>30.5984</v>
+        <v>15.1424</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9177</v>
+        <v>3.12964</v>
       </c>
       <c r="F4" t="n">
-        <v>13.3897</v>
+        <v>3.28967</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>12.1885</v>
+        <v>4.161</v>
       </c>
       <c r="C5" t="n">
-        <v>12.133</v>
+        <v>4.46944</v>
       </c>
       <c r="D5" t="n">
-        <v>30.857</v>
+        <v>15.9269</v>
       </c>
       <c r="E5" t="n">
-        <v>13.2649</v>
+        <v>3.20648</v>
       </c>
       <c r="F5" t="n">
-        <v>13.751</v>
+        <v>3.39904</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>13.1668</v>
+        <v>5.51533</v>
       </c>
       <c r="C6" t="n">
-        <v>13.5426</v>
+        <v>5.8208</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4885</v>
+        <v>16.4583</v>
       </c>
       <c r="E6" t="n">
-        <v>13.8456</v>
+        <v>3.41404</v>
       </c>
       <c r="F6" t="n">
-        <v>14.3491</v>
+        <v>3.74393</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>14.9202</v>
+        <v>8.19459</v>
       </c>
       <c r="C7" t="n">
-        <v>15.2771</v>
+        <v>7.97031</v>
       </c>
       <c r="D7" t="n">
-        <v>27.0348</v>
+        <v>10.7264</v>
       </c>
       <c r="E7" t="n">
-        <v>15.0512</v>
+        <v>4.03325</v>
       </c>
       <c r="F7" t="n">
-        <v>15.5654</v>
+        <v>4.35799</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>17.8012</v>
+        <v>10.8998</v>
       </c>
       <c r="C8" t="n">
-        <v>18.0218</v>
+        <v>11.6135</v>
       </c>
       <c r="D8" t="n">
-        <v>27.6938</v>
+        <v>11.5702</v>
       </c>
       <c r="E8" t="n">
-        <v>17.1181</v>
+        <v>5.80515</v>
       </c>
       <c r="F8" t="n">
-        <v>17.6986</v>
+        <v>5.90366</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.9179</v>
+        <v>14.7452</v>
       </c>
       <c r="C9" t="n">
-        <v>22.6482</v>
+        <v>14.7499</v>
       </c>
       <c r="D9" t="n">
-        <v>28.2739</v>
+        <v>12.1266</v>
       </c>
       <c r="E9" t="n">
-        <v>12.2495</v>
+        <v>2.77223</v>
       </c>
       <c r="F9" t="n">
-        <v>12.6455</v>
+        <v>2.73071</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>9.74765</v>
+        <v>3.19752</v>
       </c>
       <c r="C10" t="n">
-        <v>9.875679999999999</v>
+        <v>3.28281</v>
       </c>
       <c r="D10" t="n">
-        <v>29.0902</v>
+        <v>12.5459</v>
       </c>
       <c r="E10" t="n">
-        <v>12.284</v>
+        <v>2.89115</v>
       </c>
       <c r="F10" t="n">
-        <v>12.6523</v>
+        <v>2.76601</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>9.82597</v>
+        <v>3.30344</v>
       </c>
       <c r="C11" t="n">
-        <v>9.973929999999999</v>
+        <v>3.31776</v>
       </c>
       <c r="D11" t="n">
-        <v>30.0746</v>
+        <v>13.1376</v>
       </c>
       <c r="E11" t="n">
-        <v>12.3303</v>
+        <v>2.81511</v>
       </c>
       <c r="F11" t="n">
-        <v>12.6802</v>
+        <v>2.79135</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>9.8881</v>
+        <v>3.32297</v>
       </c>
       <c r="C12" t="n">
-        <v>10.073</v>
+        <v>3.39997</v>
       </c>
       <c r="D12" t="n">
-        <v>29.7602</v>
+        <v>13.6738</v>
       </c>
       <c r="E12" t="n">
-        <v>12.3584</v>
+        <v>2.91393</v>
       </c>
       <c r="F12" t="n">
-        <v>12.7679</v>
+        <v>2.835</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>9.95166</v>
+        <v>3.37511</v>
       </c>
       <c r="C13" t="n">
-        <v>10.2203</v>
+        <v>3.47121</v>
       </c>
       <c r="D13" t="n">
-        <v>30.8485</v>
+        <v>14.2146</v>
       </c>
       <c r="E13" t="n">
-        <v>12.4038</v>
+        <v>2.9545</v>
       </c>
       <c r="F13" t="n">
-        <v>12.82</v>
+        <v>2.87884</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>10.1117</v>
+        <v>3.48368</v>
       </c>
       <c r="C14" t="n">
-        <v>10.3818</v>
+        <v>3.56669</v>
       </c>
       <c r="D14" t="n">
-        <v>31.1393</v>
+        <v>14.7992</v>
       </c>
       <c r="E14" t="n">
-        <v>12.4686</v>
+        <v>3.00979</v>
       </c>
       <c r="F14" t="n">
-        <v>12.877</v>
+        <v>2.98405</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>10.2586</v>
+        <v>3.56426</v>
       </c>
       <c r="C15" t="n">
-        <v>10.619</v>
+        <v>3.68567</v>
       </c>
       <c r="D15" t="n">
-        <v>32.2762</v>
+        <v>15.1707</v>
       </c>
       <c r="E15" t="n">
-        <v>12.5701</v>
+        <v>3.02597</v>
       </c>
       <c r="F15" t="n">
-        <v>13.0398</v>
+        <v>3.01142</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>10.4931</v>
+        <v>3.66903</v>
       </c>
       <c r="C16" t="n">
-        <v>10.9329</v>
+        <v>3.83931</v>
       </c>
       <c r="D16" t="n">
-        <v>32.9122</v>
+        <v>15.6075</v>
       </c>
       <c r="E16" t="n">
-        <v>12.6882</v>
+        <v>3.2462</v>
       </c>
       <c r="F16" t="n">
-        <v>13.1731</v>
+        <v>3.12226</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>10.7983</v>
+        <v>3.92049</v>
       </c>
       <c r="C17" t="n">
-        <v>11.3415</v>
+        <v>4.10295</v>
       </c>
       <c r="D17" t="n">
-        <v>33.4098</v>
+        <v>16.0138</v>
       </c>
       <c r="E17" t="n">
-        <v>12.8518</v>
+        <v>3.2546</v>
       </c>
       <c r="F17" t="n">
-        <v>13.3179</v>
+        <v>3.27187</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>11.2877</v>
+        <v>4.29005</v>
       </c>
       <c r="C18" t="n">
-        <v>11.8824</v>
+        <v>4.58082</v>
       </c>
       <c r="D18" t="n">
-        <v>33.7213</v>
+        <v>16.4574</v>
       </c>
       <c r="E18" t="n">
-        <v>13.0426</v>
+        <v>3.44326</v>
       </c>
       <c r="F18" t="n">
-        <v>13.4841</v>
+        <v>3.36131</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>11.9358</v>
+        <v>5.21998</v>
       </c>
       <c r="C19" t="n">
-        <v>12.6849</v>
+        <v>5.38848</v>
       </c>
       <c r="D19" t="n">
-        <v>35.0423</v>
+        <v>16.9968</v>
       </c>
       <c r="E19" t="n">
-        <v>13.3107</v>
+        <v>3.51477</v>
       </c>
       <c r="F19" t="n">
-        <v>13.811</v>
+        <v>3.605</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>12.9574</v>
+        <v>6.25746</v>
       </c>
       <c r="C20" t="n">
-        <v>13.8484</v>
+        <v>6.52877</v>
       </c>
       <c r="D20" t="n">
-        <v>35.8575</v>
+        <v>17.3346</v>
       </c>
       <c r="E20" t="n">
-        <v>13.9305</v>
+        <v>3.91605</v>
       </c>
       <c r="F20" t="n">
-        <v>14.4903</v>
+        <v>3.93888</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>14.6908</v>
+        <v>8.122920000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>15.5886</v>
+        <v>8.25647</v>
       </c>
       <c r="D21" t="n">
-        <v>29.0826</v>
+        <v>12.2735</v>
       </c>
       <c r="E21" t="n">
-        <v>14.8863</v>
+        <v>4.68284</v>
       </c>
       <c r="F21" t="n">
-        <v>15.5682</v>
+        <v>4.88918</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>17.3001</v>
+        <v>10.5896</v>
       </c>
       <c r="C22" t="n">
-        <v>18.2678</v>
+        <v>10.8291</v>
       </c>
       <c r="D22" t="n">
-        <v>29.7227</v>
+        <v>12.7789</v>
       </c>
       <c r="E22" t="n">
-        <v>16.8804</v>
+        <v>6.69682</v>
       </c>
       <c r="F22" t="n">
-        <v>17.7076</v>
+        <v>6.6501</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>21.694</v>
+        <v>13.9458</v>
       </c>
       <c r="C23" t="n">
-        <v>22.4658</v>
+        <v>14.6085</v>
       </c>
       <c r="D23" t="n">
-        <v>30.4573</v>
+        <v>13.3276</v>
       </c>
       <c r="E23" t="n">
-        <v>12.3541</v>
+        <v>3.40803</v>
       </c>
       <c r="F23" t="n">
-        <v>12.7967</v>
+        <v>3.32313</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>9.85507</v>
+        <v>3.4999</v>
       </c>
       <c r="C24" t="n">
-        <v>10.4014</v>
+        <v>3.93061</v>
       </c>
       <c r="D24" t="n">
-        <v>31.1107</v>
+        <v>13.8781</v>
       </c>
       <c r="E24" t="n">
-        <v>12.4055</v>
+        <v>2.84514</v>
       </c>
       <c r="F24" t="n">
-        <v>12.8216</v>
+        <v>3.29059</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>9.89476</v>
+        <v>3.60123</v>
       </c>
       <c r="C25" t="n">
-        <v>10.7241</v>
+        <v>4.01567</v>
       </c>
       <c r="D25" t="n">
-        <v>31.6571</v>
+        <v>14.3594</v>
       </c>
       <c r="E25" t="n">
-        <v>12.4456</v>
+        <v>2.87505</v>
       </c>
       <c r="F25" t="n">
-        <v>12.9363</v>
+        <v>3.46375</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>10.0524</v>
+        <v>3.61323</v>
       </c>
       <c r="C26" t="n">
-        <v>10.747</v>
+        <v>4.1243</v>
       </c>
       <c r="D26" t="n">
-        <v>32.0029</v>
+        <v>14.6139</v>
       </c>
       <c r="E26" t="n">
-        <v>12.4636</v>
+        <v>2.9354</v>
       </c>
       <c r="F26" t="n">
-        <v>13.0097</v>
+        <v>3.0803</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>10.0997</v>
+        <v>3.73667</v>
       </c>
       <c r="C27" t="n">
-        <v>10.8638</v>
+        <v>4.18823</v>
       </c>
       <c r="D27" t="n">
-        <v>33.0438</v>
+        <v>15.2719</v>
       </c>
       <c r="E27" t="n">
-        <v>12.5361</v>
+        <v>2.99819</v>
       </c>
       <c r="F27" t="n">
-        <v>13.112</v>
+        <v>3.15505</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>10.2957</v>
+        <v>3.83072</v>
       </c>
       <c r="C28" t="n">
-        <v>11.0878</v>
+        <v>4.29173</v>
       </c>
       <c r="D28" t="n">
-        <v>33.769</v>
+        <v>15.6399</v>
       </c>
       <c r="E28" t="n">
-        <v>12.6431</v>
+        <v>3.02317</v>
       </c>
       <c r="F28" t="n">
-        <v>13.2077</v>
+        <v>3.67901</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>10.4699</v>
+        <v>3.9567</v>
       </c>
       <c r="C29" t="n">
-        <v>11.317</v>
+        <v>4.43341</v>
       </c>
       <c r="D29" t="n">
-        <v>34.0333</v>
+        <v>16.0874</v>
       </c>
       <c r="E29" t="n">
-        <v>12.7428</v>
+        <v>3.14085</v>
       </c>
       <c r="F29" t="n">
-        <v>13.3996</v>
+        <v>3.33061</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>10.6694</v>
+        <v>4.06556</v>
       </c>
       <c r="C30" t="n">
-        <v>11.6072</v>
+        <v>4.61115</v>
       </c>
       <c r="D30" t="n">
-        <v>34.9675</v>
+        <v>16.5974</v>
       </c>
       <c r="E30" t="n">
-        <v>12.8872</v>
+        <v>3.18926</v>
       </c>
       <c r="F30" t="n">
-        <v>13.5221</v>
+        <v>3.80415</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>10.9613</v>
+        <v>4.35607</v>
       </c>
       <c r="C31" t="n">
-        <v>11.9156</v>
+        <v>4.77468</v>
       </c>
       <c r="D31" t="n">
-        <v>36.3068</v>
+        <v>17.1333</v>
       </c>
       <c r="E31" t="n">
-        <v>13.0228</v>
+        <v>3.59558</v>
       </c>
       <c r="F31" t="n">
-        <v>13.7456</v>
+        <v>3.90946</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>11.3758</v>
+        <v>4.8956</v>
       </c>
       <c r="C32" t="n">
-        <v>12.388</v>
+        <v>5.22577</v>
       </c>
       <c r="D32" t="n">
-        <v>36.4821</v>
+        <v>17.4342</v>
       </c>
       <c r="E32" t="n">
-        <v>13.1921</v>
+        <v>3.45723</v>
       </c>
       <c r="F32" t="n">
-        <v>13.9503</v>
+        <v>3.6667</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>11.9318</v>
+        <v>5.51063</v>
       </c>
       <c r="C33" t="n">
-        <v>12.9156</v>
+        <v>6.00105</v>
       </c>
       <c r="D33" t="n">
-        <v>37.1592</v>
+        <v>17.9523</v>
       </c>
       <c r="E33" t="n">
-        <v>13.4701</v>
+        <v>3.92254</v>
       </c>
       <c r="F33" t="n">
-        <v>14.2338</v>
+        <v>4.22678</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>13.0511</v>
+        <v>6.58726</v>
       </c>
       <c r="C34" t="n">
-        <v>13.9694</v>
+        <v>6.78028</v>
       </c>
       <c r="D34" t="n">
-        <v>37.8684</v>
+        <v>18.4163</v>
       </c>
       <c r="E34" t="n">
-        <v>13.9746</v>
+        <v>4.03367</v>
       </c>
       <c r="F34" t="n">
-        <v>14.7719</v>
+        <v>4.22838</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>14.4722</v>
+        <v>8.10491</v>
       </c>
       <c r="C35" t="n">
-        <v>15.5719</v>
+        <v>8.326750000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>29.9645</v>
+        <v>12.3672</v>
       </c>
       <c r="E35" t="n">
-        <v>14.8476</v>
+        <v>4.83782</v>
       </c>
       <c r="F35" t="n">
-        <v>15.7225</v>
+        <v>5.22675</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>17.0274</v>
+        <v>10.2854</v>
       </c>
       <c r="C36" t="n">
-        <v>18.2124</v>
+        <v>10.7891</v>
       </c>
       <c r="D36" t="n">
-        <v>31.3869</v>
+        <v>13.1037</v>
       </c>
       <c r="E36" t="n">
-        <v>16.3206</v>
+        <v>6.18961</v>
       </c>
       <c r="F36" t="n">
-        <v>17.1911</v>
+        <v>6.19115</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>20.4563</v>
+        <v>13.9179</v>
       </c>
       <c r="C37" t="n">
-        <v>21.5912</v>
+        <v>14.088</v>
       </c>
       <c r="D37" t="n">
-        <v>31.3633</v>
+        <v>13.6554</v>
       </c>
       <c r="E37" t="n">
-        <v>12.5714</v>
+        <v>3.53659</v>
       </c>
       <c r="F37" t="n">
-        <v>13.128</v>
+        <v>3.68436</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>10.0102</v>
+        <v>4.03427</v>
       </c>
       <c r="C38" t="n">
-        <v>10.7854</v>
+        <v>4.11526</v>
       </c>
       <c r="D38" t="n">
-        <v>32.2189</v>
+        <v>14.0894</v>
       </c>
       <c r="E38" t="n">
-        <v>12.6357</v>
+        <v>3.21442</v>
       </c>
       <c r="F38" t="n">
-        <v>13.2286</v>
+        <v>3.7215</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>10.0858</v>
+        <v>4.11407</v>
       </c>
       <c r="C39" t="n">
-        <v>10.8788</v>
+        <v>4.17745</v>
       </c>
       <c r="D39" t="n">
-        <v>33.703</v>
+        <v>14.7433</v>
       </c>
       <c r="E39" t="n">
-        <v>12.5981</v>
+        <v>3.26319</v>
       </c>
       <c r="F39" t="n">
-        <v>13.3288</v>
+        <v>3.78142</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>10.154</v>
+        <v>4.1978</v>
       </c>
       <c r="C40" t="n">
-        <v>11.0136</v>
+        <v>4.27567</v>
       </c>
       <c r="D40" t="n">
-        <v>34.2249</v>
+        <v>15.291</v>
       </c>
       <c r="E40" t="n">
-        <v>12.655</v>
+        <v>3.30754</v>
       </c>
       <c r="F40" t="n">
-        <v>13.3568</v>
+        <v>3.82169</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>10.2067</v>
+        <v>4.26939</v>
       </c>
       <c r="C41" t="n">
-        <v>11.1399</v>
+        <v>4.34322</v>
       </c>
       <c r="D41" t="n">
-        <v>34.4313</v>
+        <v>15.7783</v>
       </c>
       <c r="E41" t="n">
-        <v>12.7848</v>
+        <v>3.35052</v>
       </c>
       <c r="F41" t="n">
-        <v>13.4188</v>
+        <v>3.87892</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>10.3975</v>
+        <v>4.35174</v>
       </c>
       <c r="C42" t="n">
-        <v>11.3179</v>
+        <v>4.4372</v>
       </c>
       <c r="D42" t="n">
-        <v>35.6695</v>
+        <v>16.6502</v>
       </c>
       <c r="E42" t="n">
-        <v>12.8215</v>
+        <v>3.39855</v>
       </c>
       <c r="F42" t="n">
-        <v>13.5249</v>
+        <v>3.9274</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>10.5721</v>
+        <v>4.52051</v>
       </c>
       <c r="C43" t="n">
-        <v>11.5208</v>
+        <v>4.5864</v>
       </c>
       <c r="D43" t="n">
-        <v>36.5214</v>
+        <v>17.794</v>
       </c>
       <c r="E43" t="n">
-        <v>12.8665</v>
+        <v>3.46829</v>
       </c>
       <c r="F43" t="n">
-        <v>13.5811</v>
+        <v>3.99705</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>10.7375</v>
+        <v>4.73669</v>
       </c>
       <c r="C44" t="n">
-        <v>11.7856</v>
+        <v>4.80135</v>
       </c>
       <c r="D44" t="n">
-        <v>36.9939</v>
+        <v>18.0919</v>
       </c>
       <c r="E44" t="n">
-        <v>13.0284</v>
+        <v>3.6135</v>
       </c>
       <c r="F44" t="n">
-        <v>13.7753</v>
+        <v>3.83115</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>11.0585</v>
+        <v>5.06045</v>
       </c>
       <c r="C45" t="n">
-        <v>12.1332</v>
+        <v>5.4002</v>
       </c>
       <c r="D45" t="n">
-        <v>37.6817</v>
+        <v>18.556</v>
       </c>
       <c r="E45" t="n">
-        <v>13.196</v>
+        <v>3.69233</v>
       </c>
       <c r="F45" t="n">
-        <v>13.9882</v>
+        <v>3.88419</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>11.4958</v>
+        <v>5.08809</v>
       </c>
       <c r="C46" t="n">
-        <v>12.6683</v>
+        <v>5.39479</v>
       </c>
       <c r="D46" t="n">
-        <v>39.8625</v>
+        <v>19.3783</v>
       </c>
       <c r="E46" t="n">
-        <v>13.3644</v>
+        <v>3.8503</v>
       </c>
       <c r="F46" t="n">
-        <v>14.1672</v>
+        <v>4.30911</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>12.0777</v>
+        <v>5.99554</v>
       </c>
       <c r="C47" t="n">
-        <v>13.1718</v>
+        <v>5.90769</v>
       </c>
       <c r="D47" t="n">
-        <v>42.339</v>
+        <v>20.5282</v>
       </c>
       <c r="E47" t="n">
-        <v>13.6266</v>
+        <v>4.06776</v>
       </c>
       <c r="F47" t="n">
-        <v>14.4771</v>
+        <v>4.32148</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>13.0083</v>
+        <v>6.77643</v>
       </c>
       <c r="C48" t="n">
-        <v>14.2092</v>
+        <v>7.02352</v>
       </c>
       <c r="D48" t="n">
-        <v>40.9924</v>
+        <v>21.5657</v>
       </c>
       <c r="E48" t="n">
-        <v>14.1054</v>
+        <v>4.23266</v>
       </c>
       <c r="F48" t="n">
-        <v>15.0049</v>
+        <v>4.62333</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>14.333</v>
+        <v>8.15771</v>
       </c>
       <c r="C49" t="n">
-        <v>15.6043</v>
+        <v>7.97887</v>
       </c>
       <c r="D49" t="n">
-        <v>44.6943</v>
+        <v>23.0815</v>
       </c>
       <c r="E49" t="n">
-        <v>14.814</v>
+        <v>4.99028</v>
       </c>
       <c r="F49" t="n">
-        <v>15.7779</v>
+        <v>5.26072</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>16.3971</v>
+        <v>9.586449999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>17.7301</v>
+        <v>9.866709999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>36.7188</v>
+        <v>17.1243</v>
       </c>
       <c r="E50" t="n">
-        <v>15.9782</v>
+        <v>5.79654</v>
       </c>
       <c r="F50" t="n">
-        <v>16.9742</v>
+        <v>6.15915</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>19.6993</v>
+        <v>12.7059</v>
       </c>
       <c r="C51" t="n">
-        <v>21.0729</v>
+        <v>12.9481</v>
       </c>
       <c r="D51" t="n">
-        <v>38.0033</v>
+        <v>18.8234</v>
       </c>
       <c r="E51" t="n">
-        <v>13.067</v>
+        <v>3.07638</v>
       </c>
       <c r="F51" t="n">
-        <v>13.6679</v>
+        <v>3.34621</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>24.9981</v>
+        <v>17.3502</v>
       </c>
       <c r="C52" t="n">
-        <v>26.5397</v>
+        <v>18.7323</v>
       </c>
       <c r="D52" t="n">
-        <v>39.4875</v>
+        <v>20.1474</v>
       </c>
       <c r="E52" t="n">
-        <v>13.5762</v>
+        <v>3.15699</v>
       </c>
       <c r="F52" t="n">
-        <v>13.9832</v>
+        <v>3.31305</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>10.5704</v>
+        <v>4.14242</v>
       </c>
       <c r="C53" t="n">
-        <v>11.713</v>
+        <v>4.41231</v>
       </c>
       <c r="D53" t="n">
-        <v>40.5824</v>
+        <v>20.3935</v>
       </c>
       <c r="E53" t="n">
-        <v>13.2104</v>
+        <v>3.1735</v>
       </c>
       <c r="F53" t="n">
-        <v>14.214</v>
+        <v>3.43922</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>10.5084</v>
+        <v>3.70465</v>
       </c>
       <c r="C54" t="n">
-        <v>11.5394</v>
+        <v>4.45467</v>
       </c>
       <c r="D54" t="n">
-        <v>39.8402</v>
+        <v>21.55</v>
       </c>
       <c r="E54" t="n">
-        <v>13.1167</v>
+        <v>3.22516</v>
       </c>
       <c r="F54" t="n">
-        <v>14.2114</v>
+        <v>3.52761</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>10.9322</v>
+        <v>3.78853</v>
       </c>
       <c r="C55" t="n">
-        <v>12.2655</v>
+        <v>4.59318</v>
       </c>
       <c r="D55" t="n">
-        <v>46.614</v>
+        <v>22.981</v>
       </c>
       <c r="E55" t="n">
-        <v>13.2223</v>
+        <v>3.25621</v>
       </c>
       <c r="F55" t="n">
-        <v>14.3909</v>
+        <v>3.51315</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>10.8409</v>
+        <v>4.1363</v>
       </c>
       <c r="C56" t="n">
-        <v>11.8975</v>
+        <v>4.70569</v>
       </c>
       <c r="D56" t="n">
-        <v>47.5914</v>
+        <v>24.2759</v>
       </c>
       <c r="E56" t="n">
-        <v>13.2664</v>
+        <v>3.301</v>
       </c>
       <c r="F56" t="n">
-        <v>14.0626</v>
+        <v>3.63732</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>10.9364</v>
+        <v>3.99948</v>
       </c>
       <c r="C57" t="n">
-        <v>12.6446</v>
+        <v>4.8357</v>
       </c>
       <c r="D57" t="n">
-        <v>54.0589</v>
+        <v>25.6158</v>
       </c>
       <c r="E57" t="n">
-        <v>14.0848</v>
+        <v>3.35385</v>
       </c>
       <c r="F57" t="n">
-        <v>14.495</v>
+        <v>3.72246</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>11.2758</v>
+        <v>4.25645</v>
       </c>
       <c r="C58" t="n">
-        <v>12.3588</v>
+        <v>5.05804</v>
       </c>
       <c r="D58" t="n">
-        <v>51.6314</v>
+        <v>26.5936</v>
       </c>
       <c r="E58" t="n">
-        <v>13.6285</v>
+        <v>3.44526</v>
       </c>
       <c r="F58" t="n">
-        <v>14.478</v>
+        <v>3.77055</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>11.142</v>
+        <v>4.50959</v>
       </c>
       <c r="C59" t="n">
-        <v>13.4767</v>
+        <v>5.35034</v>
       </c>
       <c r="D59" t="n">
-        <v>63.3473</v>
+        <v>27.6546</v>
       </c>
       <c r="E59" t="n">
-        <v>13.6467</v>
+        <v>3.47334</v>
       </c>
       <c r="F59" t="n">
-        <v>14.5738</v>
+        <v>3.93474</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>11.7384</v>
+        <v>4.90496</v>
       </c>
       <c r="C60" t="n">
-        <v>13.113</v>
+        <v>5.3836</v>
       </c>
       <c r="D60" t="n">
-        <v>65.8789</v>
+        <v>27.5919</v>
       </c>
       <c r="E60" t="n">
-        <v>13.8791</v>
+        <v>3.67185</v>
       </c>
       <c r="F60" t="n">
-        <v>14.8454</v>
+        <v>4.01676</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>12.2522</v>
+        <v>5.47251</v>
       </c>
       <c r="C61" t="n">
-        <v>14.5561</v>
+        <v>6.19859</v>
       </c>
       <c r="D61" t="n">
-        <v>72.34529999999999</v>
+        <v>28.6964</v>
       </c>
       <c r="E61" t="n">
-        <v>13.8835</v>
+        <v>3.93883</v>
       </c>
       <c r="F61" t="n">
-        <v>15.4894</v>
+        <v>4.27885</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>13.2244</v>
+        <v>6.25337</v>
       </c>
       <c r="C62" t="n">
-        <v>14.7406</v>
+        <v>6.61578</v>
       </c>
       <c r="D62" t="n">
-        <v>77.854</v>
+        <v>29.9581</v>
       </c>
       <c r="E62" t="n">
-        <v>14.5383</v>
+        <v>4.49865</v>
       </c>
       <c r="F62" t="n">
-        <v>15.7783</v>
+        <v>5.18531</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>14.302</v>
+        <v>7.44251</v>
       </c>
       <c r="C63" t="n">
-        <v>16.545</v>
+        <v>7.76303</v>
       </c>
       <c r="D63" t="n">
-        <v>88.0543</v>
+        <v>30.1196</v>
       </c>
       <c r="E63" t="n">
-        <v>15.0463</v>
+        <v>5.04484</v>
       </c>
       <c r="F63" t="n">
-        <v>16.6716</v>
+        <v>5.72177</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>16.2237</v>
+        <v>9.21199</v>
       </c>
       <c r="C64" t="n">
-        <v>18.6308</v>
+        <v>9.52857</v>
       </c>
       <c r="D64" t="n">
-        <v>74.85939999999999</v>
+        <v>17.5769</v>
       </c>
       <c r="E64" t="n">
-        <v>16.3269</v>
+        <v>5.848</v>
       </c>
       <c r="F64" t="n">
-        <v>17.7118</v>
+        <v>5.97004</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>18.977</v>
+        <v>12.0466</v>
       </c>
       <c r="C65" t="n">
-        <v>21.5262</v>
+        <v>13.2681</v>
       </c>
       <c r="D65" t="n">
-        <v>81.1904</v>
+        <v>18.9204</v>
       </c>
       <c r="E65" t="n">
-        <v>18.4112</v>
+        <v>7.40579</v>
       </c>
       <c r="F65" t="n">
-        <v>19.2196</v>
+        <v>7.58156</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>23.997</v>
+        <v>16.3655</v>
       </c>
       <c r="C66" t="n">
-        <v>25.3933</v>
+        <v>17.4209</v>
       </c>
       <c r="D66" t="n">
-        <v>86.4332</v>
+        <v>19.8852</v>
       </c>
       <c r="E66" t="n">
-        <v>15.1568</v>
+        <v>3.66421</v>
       </c>
       <c r="F66" t="n">
-        <v>15.9097</v>
+        <v>3.99967</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>12.2464</v>
+        <v>4.29423</v>
       </c>
       <c r="C67" t="n">
-        <v>13.978</v>
+        <v>4.9112</v>
       </c>
       <c r="D67" t="n">
-        <v>94.1058</v>
+        <v>21.3555</v>
       </c>
       <c r="E67" t="n">
-        <v>14.9435</v>
+        <v>3.89191</v>
       </c>
       <c r="F67" t="n">
-        <v>16.026</v>
+        <v>4.06477</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>12.392</v>
+        <v>4.18441</v>
       </c>
       <c r="C68" t="n">
-        <v>14.1128</v>
+        <v>5.02084</v>
       </c>
       <c r="D68" t="n">
-        <v>99.6952</v>
+        <v>22.6931</v>
       </c>
       <c r="E68" t="n">
-        <v>15.0847</v>
+        <v>3.94503</v>
       </c>
       <c r="F68" t="n">
-        <v>15.9263</v>
+        <v>4.1223</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>12.2831</v>
+        <v>4.27601</v>
       </c>
       <c r="C69" t="n">
-        <v>14.3715</v>
+        <v>5.13166</v>
       </c>
       <c r="D69" t="n">
-        <v>105.334</v>
+        <v>24.3644</v>
       </c>
       <c r="E69" t="n">
-        <v>15.0472</v>
+        <v>3.99624</v>
       </c>
       <c r="F69" t="n">
-        <v>15.5472</v>
+        <v>4.19305</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>12.467</v>
+        <v>4.3668</v>
       </c>
       <c r="C70" t="n">
-        <v>14.595</v>
+        <v>5.26721</v>
       </c>
       <c r="D70" t="n">
-        <v>111.277</v>
+        <v>25.4826</v>
       </c>
       <c r="E70" t="n">
-        <v>15.132</v>
+        <v>3.93851</v>
       </c>
       <c r="F70" t="n">
-        <v>16.2384</v>
+        <v>4.27919</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>12.6188</v>
+        <v>4.53675</v>
       </c>
       <c r="C71" t="n">
-        <v>14.8176</v>
+        <v>5.46351</v>
       </c>
       <c r="D71" t="n">
-        <v>118.77</v>
+        <v>26.2699</v>
       </c>
       <c r="E71" t="n">
-        <v>15.2478</v>
+        <v>3.87761</v>
       </c>
       <c r="F71" t="n">
-        <v>16.2032</v>
+        <v>4.4041</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>12.8093</v>
+        <v>4.86534</v>
       </c>
       <c r="C72" t="n">
-        <v>15.2019</v>
+        <v>5.68553</v>
       </c>
       <c r="D72" t="n">
-        <v>126.951</v>
+        <v>27.3091</v>
       </c>
       <c r="E72" t="n">
-        <v>15.4203</v>
+        <v>3.95803</v>
       </c>
       <c r="F72" t="n">
-        <v>16.6298</v>
+        <v>4.52069</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>13.0727</v>
+        <v>4.93672</v>
       </c>
       <c r="C73" t="n">
-        <v>15.1589</v>
+        <v>5.96038</v>
       </c>
       <c r="D73" t="n">
-        <v>137.583</v>
+        <v>28.1677</v>
       </c>
       <c r="E73" t="n">
-        <v>15.5579</v>
+        <v>4.06354</v>
       </c>
       <c r="F73" t="n">
-        <v>16.1261</v>
+        <v>4.66764</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>13.5411</v>
+        <v>5.32579</v>
       </c>
       <c r="C74" t="n">
-        <v>15.4628</v>
+        <v>6.36083</v>
       </c>
       <c r="D74" t="n">
-        <v>148.63</v>
+        <v>29.1277</v>
       </c>
       <c r="E74" t="n">
-        <v>15.7737</v>
+        <v>4.20108</v>
       </c>
       <c r="F74" t="n">
-        <v>16.942</v>
+        <v>5.14189</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>14.0643</v>
+        <v>5.90616</v>
       </c>
       <c r="C75" t="n">
-        <v>16.3138</v>
+        <v>7.12047</v>
       </c>
       <c r="D75" t="n">
-        <v>162.518</v>
+        <v>32.0571</v>
       </c>
       <c r="E75" t="n">
-        <v>16.203</v>
+        <v>4.52893</v>
       </c>
       <c r="F75" t="n">
-        <v>17.3638</v>
+        <v>5.06927</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>14.8935</v>
+        <v>6.61625</v>
       </c>
       <c r="C76" t="n">
-        <v>18.6797</v>
+        <v>7.78102</v>
       </c>
       <c r="D76" t="n">
-        <v>150.504</v>
+        <v>31.6537</v>
       </c>
       <c r="E76" t="n">
-        <v>16.3391</v>
+        <v>4.7556</v>
       </c>
       <c r="F76" t="n">
-        <v>17.9681</v>
+        <v>5.32494</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>15.8512</v>
+        <v>7.67243</v>
       </c>
       <c r="C77" t="n">
-        <v>20.4127</v>
+        <v>9.11304</v>
       </c>
       <c r="D77" t="n">
-        <v>158.474</v>
+        <v>32.5498</v>
       </c>
       <c r="E77" t="n">
-        <v>16.9481</v>
+        <v>5.43504</v>
       </c>
       <c r="F77" t="n">
-        <v>18.6948</v>
+        <v>5.82997</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>17.6678</v>
+        <v>9.45058</v>
       </c>
       <c r="C78" t="n">
-        <v>23.5582</v>
+        <v>11.1507</v>
       </c>
       <c r="D78" t="n">
-        <v>127.809</v>
+        <v>26.2567</v>
       </c>
       <c r="E78" t="n">
-        <v>17.8945</v>
+        <v>6.09665</v>
       </c>
       <c r="F78" t="n">
-        <v>19.8914</v>
+        <v>6.6275</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>20.0059</v>
+        <v>12.0912</v>
       </c>
       <c r="C79" t="n">
-        <v>28.2921</v>
+        <v>14.447</v>
       </c>
       <c r="D79" t="n">
-        <v>134.225</v>
+        <v>27.6144</v>
       </c>
       <c r="E79" t="n">
-        <v>19.7559</v>
+        <v>7.72989</v>
       </c>
       <c r="F79" t="n">
-        <v>21.9339</v>
+        <v>8.31284</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>23.9581</v>
+        <v>16.353</v>
       </c>
       <c r="C80" t="n">
-        <v>34.344</v>
+        <v>19.641</v>
       </c>
       <c r="D80" t="n">
-        <v>149.173</v>
+        <v>28.7099</v>
       </c>
       <c r="E80" t="n">
-        <v>16.6282</v>
+        <v>4.10915</v>
       </c>
       <c r="F80" t="n">
-        <v>16.8256</v>
+        <v>4.56468</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>12.8581</v>
+        <v>4.68331</v>
       </c>
       <c r="C81" t="n">
-        <v>16.2232</v>
+        <v>6.28011</v>
       </c>
       <c r="D81" t="n">
-        <v>143.15</v>
+        <v>30.0835</v>
       </c>
       <c r="E81" t="n">
-        <v>16.694</v>
+        <v>4.15948</v>
       </c>
       <c r="F81" t="n">
-        <v>17.5467</v>
+        <v>4.68709</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>13.6569</v>
+        <v>4.89913</v>
       </c>
       <c r="C82" t="n">
-        <v>17.1738</v>
+        <v>6.65182</v>
       </c>
       <c r="D82" t="n">
-        <v>159.001</v>
+        <v>31.3694</v>
       </c>
       <c r="E82" t="n">
-        <v>16.788</v>
+        <v>4.23149</v>
       </c>
       <c r="F82" t="n">
-        <v>17.5722</v>
+        <v>4.84684</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>13.0401</v>
+        <v>5.00539</v>
       </c>
       <c r="C83" t="n">
-        <v>17.7858</v>
+        <v>7.1983</v>
       </c>
       <c r="D83" t="n">
-        <v>152.82</v>
+        <v>32.7767</v>
       </c>
       <c r="E83" t="n">
-        <v>16.8358</v>
+        <v>4.31101</v>
       </c>
       <c r="F83" t="n">
-        <v>17.91</v>
+        <v>5.01305</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>14.1676</v>
+        <v>5.31324</v>
       </c>
       <c r="C84" t="n">
-        <v>18.6814</v>
+        <v>7.78038</v>
       </c>
       <c r="D84" t="n">
-        <v>161.899</v>
+        <v>34.1926</v>
       </c>
       <c r="E84" t="n">
-        <v>16.9025</v>
+        <v>4.43212</v>
       </c>
       <c r="F84" t="n">
-        <v>17.9827</v>
+        <v>5.26908</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>13.2928</v>
+        <v>5.63197</v>
       </c>
       <c r="C85" t="n">
-        <v>20.0065</v>
+        <v>8.56659</v>
       </c>
       <c r="D85" t="n">
-        <v>163.314</v>
+        <v>35.6406</v>
       </c>
       <c r="E85" t="n">
-        <v>16.9923</v>
+        <v>4.55758</v>
       </c>
       <c r="F85" t="n">
-        <v>18.3903</v>
+        <v>5.45205</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>13.6475</v>
+        <v>6.14093</v>
       </c>
       <c r="C86" t="n">
-        <v>20.9329</v>
+        <v>9.45261</v>
       </c>
       <c r="D86" t="n">
-        <v>168.26</v>
+        <v>37.1648</v>
       </c>
       <c r="E86" t="n">
-        <v>17.1585</v>
+        <v>4.78558</v>
       </c>
       <c r="F86" t="n">
-        <v>18.9894</v>
+        <v>5.79262</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>14.9392</v>
+        <v>6.59823</v>
       </c>
       <c r="C87" t="n">
-        <v>22.8903</v>
+        <v>10.359</v>
       </c>
       <c r="D87" t="n">
-        <v>197.702</v>
+        <v>38.7878</v>
       </c>
       <c r="E87" t="n">
-        <v>17.399</v>
+        <v>5.08971</v>
       </c>
       <c r="F87" t="n">
-        <v>19.3884</v>
+        <v>6.2533</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>15.2879</v>
+        <v>7.22835</v>
       </c>
       <c r="C88" t="n">
-        <v>25.1767</v>
+        <v>11.0131</v>
       </c>
       <c r="D88" t="n">
-        <v>180.087</v>
+        <v>40.5002</v>
       </c>
       <c r="E88" t="n">
-        <v>17.7192</v>
+        <v>5.41781</v>
       </c>
       <c r="F88" t="n">
-        <v>20.0868</v>
+        <v>7.11485</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>16.028</v>
+        <v>8.149789999999999</v>
       </c>
       <c r="C89" t="n">
-        <v>26.5406</v>
+        <v>12.5737</v>
       </c>
       <c r="D89" t="n">
-        <v>194.148</v>
+        <v>42.4329</v>
       </c>
       <c r="E89" t="n">
-        <v>17.8662</v>
+        <v>5.83938</v>
       </c>
       <c r="F89" t="n">
-        <v>21.3411</v>
+        <v>7.76702</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>17.1675</v>
+        <v>9.17109</v>
       </c>
       <c r="C90" t="n">
-        <v>29.2621</v>
+        <v>13.8765</v>
       </c>
       <c r="D90" t="n">
-        <v>191.319</v>
+        <v>44.3359</v>
       </c>
       <c r="E90" t="n">
-        <v>18.4776</v>
+        <v>6.34497</v>
       </c>
       <c r="F90" t="n">
-        <v>22.4486</v>
+        <v>8.336970000000001</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>18.566</v>
+        <v>10.7207</v>
       </c>
       <c r="C91" t="n">
-        <v>31.2116</v>
+        <v>15.8343</v>
       </c>
       <c r="D91" t="n">
-        <v>201.15</v>
+        <v>46.3326</v>
       </c>
       <c r="E91" t="n">
-        <v>19.2803</v>
+        <v>7.04508</v>
       </c>
       <c r="F91" t="n">
-        <v>24.3606</v>
+        <v>9.27281</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>20.268</v>
+        <v>12.7287</v>
       </c>
       <c r="C92" t="n">
-        <v>35.2803</v>
+        <v>18.428</v>
       </c>
       <c r="D92" t="n">
-        <v>157.923</v>
+        <v>38.1843</v>
       </c>
       <c r="E92" t="n">
-        <v>20.3799</v>
+        <v>8.031330000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>26.0682</v>
+        <v>10.4565</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>23.8106</v>
+        <v>15.1279</v>
       </c>
       <c r="C93" t="n">
-        <v>39.8468</v>
+        <v>21.8267</v>
       </c>
       <c r="D93" t="n">
-        <v>161.97</v>
+        <v>39.4205</v>
       </c>
       <c r="E93" t="n">
-        <v>21.5553</v>
+        <v>9.67184</v>
       </c>
       <c r="F93" t="n">
-        <v>29.2311</v>
+        <v>12.6544</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>28.6583</v>
+        <v>18.6799</v>
       </c>
       <c r="C94" t="n">
-        <v>47.4375</v>
+        <v>26.2881</v>
       </c>
       <c r="D94" t="n">
-        <v>166.058</v>
+        <v>40.6362</v>
       </c>
       <c r="E94" t="n">
-        <v>17.3179</v>
+        <v>5.35505</v>
       </c>
       <c r="F94" t="n">
-        <v>20.4845</v>
+        <v>6.96016</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>15.5146</v>
+        <v>7.03252</v>
       </c>
       <c r="C95" t="n">
-        <v>23.6306</v>
+        <v>10.8991</v>
       </c>
       <c r="D95" t="n">
-        <v>170.525</v>
+        <v>41.9983</v>
       </c>
       <c r="E95" t="n">
-        <v>17.8521</v>
+        <v>5.54035</v>
       </c>
       <c r="F95" t="n">
-        <v>21.0343</v>
+        <v>7.32226</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>16.0746</v>
+        <v>7.35133</v>
       </c>
       <c r="C96" t="n">
-        <v>24.8459</v>
+        <v>11.5685</v>
       </c>
       <c r="D96" t="n">
-        <v>172.285</v>
+        <v>43.3395</v>
       </c>
       <c r="E96" t="n">
-        <v>17.7368</v>
+        <v>5.74105</v>
       </c>
       <c r="F96" t="n">
-        <v>21.1927</v>
+        <v>7.68061</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>15.9783</v>
+        <v>7.72707</v>
       </c>
       <c r="C97" t="n">
-        <v>27.2699</v>
+        <v>12.1788</v>
       </c>
       <c r="D97" t="n">
-        <v>179.184</v>
+        <v>44.7199</v>
       </c>
       <c r="E97" t="n">
-        <v>18.2801</v>
+        <v>5.94383</v>
       </c>
       <c r="F97" t="n">
-        <v>21.8752</v>
+        <v>8.043810000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>17.2638</v>
+        <v>8.10445</v>
       </c>
       <c r="C98" t="n">
-        <v>26.6638</v>
+        <v>12.9393</v>
       </c>
       <c r="D98" t="n">
-        <v>183.763</v>
+        <v>46.1014</v>
       </c>
       <c r="E98" t="n">
-        <v>18.5814</v>
+        <v>6.14353</v>
       </c>
       <c r="F98" t="n">
-        <v>23.5205</v>
+        <v>8.35468</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>17.9749</v>
+        <v>8.46411</v>
       </c>
       <c r="C99" t="n">
-        <v>27.9386</v>
+        <v>13.7443</v>
       </c>
       <c r="D99" t="n">
-        <v>188.991</v>
+        <v>47.6426</v>
       </c>
       <c r="E99" t="n">
-        <v>19.0996</v>
+        <v>6.37688</v>
       </c>
       <c r="F99" t="n">
-        <v>23.7602</v>
+        <v>8.73296</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>18.349</v>
+        <v>8.90957</v>
       </c>
       <c r="C100" t="n">
-        <v>28.416</v>
+        <v>14.693</v>
       </c>
       <c r="D100" t="n">
-        <v>194.831</v>
+        <v>49.2579</v>
       </c>
       <c r="E100" t="n">
-        <v>19.1795</v>
+        <v>6.60885</v>
       </c>
       <c r="F100" t="n">
-        <v>25.3765</v>
+        <v>9.143700000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>18.9913</v>
+        <v>9.36022</v>
       </c>
       <c r="C101" t="n">
-        <v>30.1648</v>
+        <v>15.655</v>
       </c>
       <c r="D101" t="n">
-        <v>199.702</v>
+        <v>50.9123</v>
       </c>
       <c r="E101" t="n">
-        <v>19.6221</v>
+        <v>6.88891</v>
       </c>
       <c r="F101" t="n">
-        <v>25.3765</v>
+        <v>9.51173</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>20.3886</v>
+        <v>9.983689999999999</v>
       </c>
       <c r="C102" t="n">
-        <v>32.6093</v>
+        <v>16.8564</v>
       </c>
       <c r="D102" t="n">
-        <v>211.426</v>
+        <v>52.7156</v>
       </c>
       <c r="E102" t="n">
-        <v>20.1037</v>
+        <v>7.14101</v>
       </c>
       <c r="F102" t="n">
-        <v>26.3052</v>
+        <v>10.1258</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>21.7172</v>
+        <v>10.7655</v>
       </c>
       <c r="C103" t="n">
-        <v>33.295</v>
+        <v>18.1775</v>
       </c>
       <c r="D103" t="n">
-        <v>212.11</v>
+        <v>54.5672</v>
       </c>
       <c r="E103" t="n">
-        <v>21.0943</v>
+        <v>7.49693</v>
       </c>
       <c r="F103" t="n">
-        <v>27.0425</v>
+        <v>10.7822</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>22.964</v>
+        <v>11.7718</v>
       </c>
       <c r="C104" t="n">
-        <v>34.917</v>
+        <v>19.6836</v>
       </c>
       <c r="D104" t="n">
-        <v>245.237</v>
+        <v>56.4974</v>
       </c>
       <c r="E104" t="n">
-        <v>21.8324</v>
+        <v>7.99479</v>
       </c>
       <c r="F104" t="n">
-        <v>28.0169</v>
+        <v>11.5757</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>24.6071</v>
+        <v>12.9845</v>
       </c>
       <c r="C105" t="n">
-        <v>37.0279</v>
+        <v>21.403</v>
       </c>
       <c r="D105" t="n">
-        <v>250.316</v>
+        <v>58.5437</v>
       </c>
       <c r="E105" t="n">
-        <v>22.8355</v>
+        <v>8.585319999999999</v>
       </c>
       <c r="F105" t="n">
-        <v>29.3906</v>
+        <v>12.6638</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>26.6996</v>
+        <v>14.7737</v>
       </c>
       <c r="C106" t="n">
-        <v>40.0413</v>
+        <v>23.639</v>
       </c>
       <c r="D106" t="n">
-        <v>256.684</v>
+        <v>60.6713</v>
       </c>
       <c r="E106" t="n">
-        <v>24.0499</v>
+        <v>9.51835</v>
       </c>
       <c r="F106" t="n">
-        <v>31.0648</v>
+        <v>14.2281</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>29.3645</v>
+        <v>17.0273</v>
       </c>
       <c r="C107" t="n">
-        <v>47.0051</v>
+        <v>26.605</v>
       </c>
       <c r="D107" t="n">
-        <v>175.809</v>
+        <v>46.8298</v>
       </c>
       <c r="E107" t="n">
-        <v>24.8574</v>
+        <v>11.1463</v>
       </c>
       <c r="F107" t="n">
-        <v>33.9269</v>
+        <v>16.4152</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>34.8562</v>
+        <v>20.297</v>
       </c>
       <c r="C108" t="n">
-        <v>55.3428</v>
+        <v>31.078</v>
       </c>
       <c r="D108" t="n">
-        <v>180.42</v>
+        <v>48.0223</v>
       </c>
       <c r="E108" t="n">
-        <v>19.9086</v>
+        <v>6.1159</v>
       </c>
       <c r="F108" t="n">
-        <v>24.3653</v>
+        <v>8.65136</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>42.4727</v>
+        <v>25.4321</v>
       </c>
       <c r="C109" t="n">
-        <v>65.9847</v>
+        <v>37.9819</v>
       </c>
       <c r="D109" t="n">
-        <v>184.801</v>
+        <v>49.2399</v>
       </c>
       <c r="E109" t="n">
-        <v>20.6323</v>
+        <v>6.39532</v>
       </c>
       <c r="F109" t="n">
-        <v>24.7676</v>
+        <v>8.94434</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>19.7132</v>
+        <v>8.64024</v>
       </c>
       <c r="C110" t="n">
-        <v>29.5848</v>
+        <v>15.4703</v>
       </c>
       <c r="D110" t="n">
-        <v>188.213</v>
+        <v>50.5012</v>
       </c>
       <c r="E110" t="n">
-        <v>20.8863</v>
+        <v>6.52563</v>
       </c>
       <c r="F110" t="n">
-        <v>25.2204</v>
+        <v>9.53473</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>20.7443</v>
+        <v>9.02468</v>
       </c>
       <c r="C111" t="n">
-        <v>30.4337</v>
+        <v>16.1565</v>
       </c>
       <c r="D111" t="n">
-        <v>193.33</v>
+        <v>51.7906</v>
       </c>
       <c r="E111" t="n">
-        <v>20.6752</v>
+        <v>6.75391</v>
       </c>
       <c r="F111" t="n">
-        <v>25.6623</v>
+        <v>10.071</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>20.6479</v>
+        <v>9.414149999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>31.2176</v>
+        <v>16.7022</v>
       </c>
       <c r="D112" t="n">
-        <v>198.487</v>
+        <v>53.0911</v>
       </c>
       <c r="E112" t="n">
-        <v>21.3369</v>
+        <v>6.93761</v>
       </c>
       <c r="F112" t="n">
-        <v>26.0272</v>
+        <v>10.6386</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>21.7891</v>
+        <v>9.958909999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>32.2438</v>
+        <v>17.4151</v>
       </c>
       <c r="D113" t="n">
-        <v>203.136</v>
+        <v>54.5422</v>
       </c>
       <c r="E113" t="n">
-        <v>21.6201</v>
+        <v>7.14051</v>
       </c>
       <c r="F113" t="n">
-        <v>26.5121</v>
+        <v>11.166</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>22.3409</v>
+        <v>10.5004</v>
       </c>
       <c r="C114" t="n">
-        <v>33.0654</v>
+        <v>18.0583</v>
       </c>
       <c r="D114" t="n">
-        <v>208.246</v>
+        <v>56.1363</v>
       </c>
       <c r="E114" t="n">
-        <v>21.9143</v>
+        <v>7.50533</v>
       </c>
       <c r="F114" t="n">
-        <v>26.3317</v>
+        <v>11.8101</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>22.9596</v>
+        <v>11.2378</v>
       </c>
       <c r="C115" t="n">
-        <v>34.3151</v>
+        <v>18.8557</v>
       </c>
       <c r="D115" t="n">
-        <v>214.156</v>
+        <v>57.809</v>
       </c>
       <c r="E115" t="n">
-        <v>22.2277</v>
+        <v>7.80133</v>
       </c>
       <c r="F115" t="n">
-        <v>26.8969</v>
+        <v>12.4277</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>23.5821</v>
+        <v>12.0019</v>
       </c>
       <c r="C116" t="n">
-        <v>35.6179</v>
+        <v>19.7252</v>
       </c>
       <c r="D116" t="n">
-        <v>219.48</v>
+        <v>59.5387</v>
       </c>
       <c r="E116" t="n">
-        <v>22.6872</v>
+        <v>8.33672</v>
       </c>
       <c r="F116" t="n">
-        <v>27.5699</v>
+        <v>13.0938</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>24.6148</v>
+        <v>12.7948</v>
       </c>
       <c r="C117" t="n">
-        <v>37.2121</v>
+        <v>20.7324</v>
       </c>
       <c r="D117" t="n">
-        <v>226.803</v>
+        <v>61.3148</v>
       </c>
       <c r="E117" t="n">
-        <v>23.1488</v>
+        <v>8.734690000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>30.2782</v>
+        <v>13.7515</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>25.7921</v>
+        <v>13.7455</v>
       </c>
       <c r="C118" t="n">
-        <v>37.9742</v>
+        <v>22.0179</v>
       </c>
       <c r="D118" t="n">
-        <v>248.497</v>
+        <v>63.2036</v>
       </c>
       <c r="E118" t="n">
-        <v>23.7444</v>
+        <v>9.32043</v>
       </c>
       <c r="F118" t="n">
-        <v>30.1969</v>
+        <v>14.475</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>27.3556</v>
+        <v>14.903</v>
       </c>
       <c r="C119" t="n">
-        <v>40.4376</v>
+        <v>23.6079</v>
       </c>
       <c r="D119" t="n">
-        <v>239.892</v>
+        <v>65.25230000000001</v>
       </c>
       <c r="E119" t="n">
-        <v>24.5507</v>
+        <v>10.0383</v>
       </c>
       <c r="F119" t="n">
-        <v>31.3764</v>
+        <v>15.4063</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>29.603</v>
+        <v>16.4016</v>
       </c>
       <c r="C120" t="n">
-        <v>45.3785</v>
+        <v>25.6235</v>
       </c>
       <c r="D120" t="n">
-        <v>268.566</v>
+        <v>67.3283</v>
       </c>
       <c r="E120" t="n">
-        <v>25.7122</v>
+        <v>11.0125</v>
       </c>
       <c r="F120" t="n">
-        <v>32.4018</v>
+        <v>16.682</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>32.7901</v>
+        <v>18.4316</v>
       </c>
       <c r="C121" t="n">
-        <v>49.6014</v>
+        <v>28.4746</v>
       </c>
       <c r="D121" t="n">
-        <v>183.526</v>
+        <v>50.507</v>
       </c>
       <c r="E121" t="n">
-        <v>27.4446</v>
+        <v>12.3928</v>
       </c>
       <c r="F121" t="n">
-        <v>36.2265</v>
+        <v>18.5227</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>37.4899</v>
+        <v>21.3177</v>
       </c>
       <c r="C122" t="n">
-        <v>58.4093</v>
+        <v>32.7188</v>
       </c>
       <c r="D122" t="n">
-        <v>189.053</v>
+        <v>51.6699</v>
       </c>
       <c r="E122" t="n">
-        <v>29.5861</v>
+        <v>14.8172</v>
       </c>
       <c r="F122" t="n">
-        <v>40.7575</v>
+        <v>21.4146</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>44.8217</v>
+        <v>25.8021</v>
       </c>
       <c r="C123" t="n">
-        <v>70.7375</v>
+        <v>39.4715</v>
       </c>
       <c r="D123" t="n">
-        <v>193.599</v>
+        <v>52.8492</v>
       </c>
       <c r="E123" t="n">
-        <v>21.159</v>
+        <v>8.179779999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>30.3647</v>
+        <v>12.0886</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>22.3859</v>
+        <v>10.7174</v>
       </c>
       <c r="C124" t="n">
-        <v>33.7597</v>
+        <v>17.9032</v>
       </c>
       <c r="D124" t="n">
-        <v>196.798</v>
+        <v>54.0379</v>
       </c>
       <c r="E124" t="n">
-        <v>22.7179</v>
+        <v>8.986370000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>27.3689</v>
+        <v>12.0303</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>23.2244</v>
+        <v>11.5101</v>
       </c>
       <c r="C125" t="n">
-        <v>34.3622</v>
+        <v>18.7528</v>
       </c>
       <c r="D125" t="n">
-        <v>201.465</v>
+        <v>55.3263</v>
       </c>
       <c r="E125" t="n">
-        <v>24.0125</v>
+        <v>9.166919999999999</v>
       </c>
       <c r="F125" t="n">
-        <v>28.9202</v>
+        <v>12.9317</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>23.2732</v>
+        <v>11.9323</v>
       </c>
       <c r="C126" t="n">
-        <v>36.9832</v>
+        <v>19.1572</v>
       </c>
       <c r="D126" t="n">
-        <v>206.11</v>
+        <v>56.6954</v>
       </c>
       <c r="E126" t="n">
-        <v>22.8437</v>
+        <v>9.507899999999999</v>
       </c>
       <c r="F126" t="n">
-        <v>29.5044</v>
+        <v>13.6438</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>23.6603</v>
+        <v>12.4449</v>
       </c>
       <c r="C127" t="n">
-        <v>38.3339</v>
+        <v>19.562</v>
       </c>
       <c r="D127" t="n">
-        <v>211.964</v>
+        <v>58.1667</v>
       </c>
       <c r="E127" t="n">
-        <v>23.8651</v>
+        <v>9.517530000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>28.8645</v>
+        <v>13.8634</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>23.9231</v>
+        <v>12.634</v>
       </c>
       <c r="C128" t="n">
-        <v>38.4797</v>
+        <v>20.3419</v>
       </c>
       <c r="D128" t="n">
-        <v>216.369</v>
+        <v>59.6623</v>
       </c>
       <c r="E128" t="n">
-        <v>23.3857</v>
+        <v>9.76873</v>
       </c>
       <c r="F128" t="n">
-        <v>30.9617</v>
+        <v>14.2597</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>24.3667</v>
+        <v>12.7438</v>
       </c>
       <c r="C129" t="n">
-        <v>40.8902</v>
+        <v>21.0348</v>
       </c>
       <c r="D129" t="n">
-        <v>233.286</v>
+        <v>61.2596</v>
       </c>
       <c r="E129" t="n">
-        <v>22.5273</v>
+        <v>10.1753</v>
       </c>
       <c r="F129" t="n">
-        <v>31.0075</v>
+        <v>14.255</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>26.452</v>
+        <v>13.5688</v>
       </c>
       <c r="C130" t="n">
-        <v>41.6499</v>
+        <v>21.8018</v>
       </c>
       <c r="D130" t="n">
-        <v>238.049</v>
+        <v>62.9088</v>
       </c>
       <c r="E130" t="n">
-        <v>23.8375</v>
+        <v>10.2648</v>
       </c>
       <c r="F130" t="n">
-        <v>31.8938</v>
+        <v>15.136</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>26.8456</v>
+        <v>14.4173</v>
       </c>
       <c r="C131" t="n">
-        <v>47.8053</v>
+        <v>22.9019</v>
       </c>
       <c r="D131" t="n">
-        <v>250.543</v>
+        <v>64.7942</v>
       </c>
       <c r="E131" t="n">
-        <v>23.4655</v>
+        <v>10.7308</v>
       </c>
       <c r="F131" t="n">
-        <v>33.562</v>
+        <v>15.8478</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>29.5105</v>
+        <v>14.9367</v>
       </c>
       <c r="C132" t="n">
-        <v>48.6433</v>
+        <v>24.2087</v>
       </c>
       <c r="D132" t="n">
-        <v>256.285</v>
+        <v>66.669</v>
       </c>
       <c r="E132" t="n">
-        <v>25.5864</v>
+        <v>10.8984</v>
       </c>
       <c r="F132" t="n">
-        <v>34.8647</v>
+        <v>16.4977</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>30.0519</v>
+        <v>16.0041</v>
       </c>
       <c r="C133" t="n">
-        <v>50.5884</v>
+        <v>25.4417</v>
       </c>
       <c r="D133" t="n">
-        <v>262.644</v>
+        <v>68.70010000000001</v>
       </c>
       <c r="E133" t="n">
-        <v>26.2887</v>
+        <v>11.576</v>
       </c>
       <c r="F133" t="n">
-        <v>37.4474</v>
+        <v>17.3515</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>37.8094</v>
+        <v>17.4345</v>
       </c>
       <c r="C134" t="n">
-        <v>54.0373</v>
+        <v>27.6515</v>
       </c>
       <c r="D134" t="n">
-        <v>263.215</v>
+        <v>70.8413</v>
       </c>
       <c r="E134" t="n">
-        <v>27.4113</v>
+        <v>12.3593</v>
       </c>
       <c r="F134" t="n">
-        <v>38.9312</v>
+        <v>18.6154</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>34.7333</v>
+        <v>19.314</v>
       </c>
       <c r="C135" t="n">
-        <v>59.3878</v>
+        <v>30.359</v>
       </c>
       <c r="D135" t="n">
-        <v>188.727</v>
+        <v>52.4186</v>
       </c>
       <c r="E135" t="n">
-        <v>28.1131</v>
+        <v>13.6493</v>
       </c>
       <c r="F135" t="n">
-        <v>40.4233</v>
+        <v>20.2358</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>39.1433</v>
+        <v>22.3311</v>
       </c>
       <c r="C136" t="n">
-        <v>64.5278</v>
+        <v>34.2936</v>
       </c>
       <c r="D136" t="n">
-        <v>193.186</v>
+        <v>53.64</v>
       </c>
       <c r="E136" t="n">
-        <v>31.7123</v>
+        <v>15.8793</v>
       </c>
       <c r="F136" t="n">
-        <v>40.5744</v>
+        <v>23.0894</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>46.7386</v>
+        <v>26.5551</v>
       </c>
       <c r="C137" t="n">
-        <v>80.3263</v>
+        <v>40.778</v>
       </c>
       <c r="D137" t="n">
-        <v>200.67</v>
+        <v>54.8242</v>
       </c>
       <c r="E137" t="n">
-        <v>41.2508</v>
+        <v>17.3494</v>
       </c>
       <c r="F137" t="n">
-        <v>51.1596</v>
+        <v>20.898</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>47.1996</v>
+        <v>19.2933</v>
       </c>
       <c r="C138" t="n">
-        <v>60.0908</v>
+        <v>25.7862</v>
       </c>
       <c r="D138" t="n">
-        <v>203.974</v>
+        <v>56.1133</v>
       </c>
       <c r="E138" t="n">
-        <v>41.7163</v>
+        <v>17.5911</v>
       </c>
       <c r="F138" t="n">
-        <v>51.3046</v>
+        <v>21.4354</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>44.7297</v>
+        <v>19.5131</v>
       </c>
       <c r="C139" t="n">
-        <v>60.6764</v>
+        <v>26.3603</v>
       </c>
       <c r="D139" t="n">
-        <v>208.304</v>
+        <v>57.3918</v>
       </c>
       <c r="E139" t="n">
-        <v>43.0861</v>
+        <v>17.6797</v>
       </c>
       <c r="F139" t="n">
-        <v>52.6418</v>
+        <v>22.0789</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>44.3962</v>
+        <v>19.6478</v>
       </c>
       <c r="C140" t="n">
-        <v>61.894</v>
+        <v>26.8356</v>
       </c>
       <c r="D140" t="n">
-        <v>212.958</v>
+        <v>58.7212</v>
       </c>
       <c r="E140" t="n">
-        <v>42.0883</v>
+        <v>17.9677</v>
       </c>
       <c r="F140" t="n">
-        <v>55.3245</v>
+        <v>22.1053</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>45.9353</v>
+        <v>19.8623</v>
       </c>
       <c r="C141" t="n">
-        <v>62.7536</v>
+        <v>27.3954</v>
       </c>
       <c r="D141" t="n">
-        <v>218.099</v>
+        <v>60.1637</v>
       </c>
       <c r="E141" t="n">
-        <v>41.4683</v>
+        <v>17.952</v>
       </c>
       <c r="F141" t="n">
-        <v>55.6804</v>
+        <v>21.4626</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>46.8927</v>
+        <v>20.1883</v>
       </c>
       <c r="C142" t="n">
-        <v>61.5344</v>
+        <v>27.9672</v>
       </c>
       <c r="D142" t="n">
-        <v>222.869</v>
+        <v>61.6384</v>
       </c>
       <c r="E142" t="n">
-        <v>44.2852</v>
+        <v>18.1414</v>
       </c>
       <c r="F142" t="n">
-        <v>55.1329</v>
+        <v>22.6536</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>47.3903</v>
+        <v>20.3488</v>
       </c>
       <c r="C143" t="n">
-        <v>65.7559</v>
+        <v>28.5319</v>
       </c>
       <c r="D143" t="n">
-        <v>227.042</v>
+        <v>63.2221</v>
       </c>
       <c r="E143" t="n">
-        <v>42.2987</v>
+        <v>18.382</v>
       </c>
       <c r="F143" t="n">
-        <v>54.7062</v>
+        <v>23.2799</v>
       </c>
     </row>
   </sheetData>
